--- a/network.xlsx
+++ b/network.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/SystemDocumentation/github/uactechdoc/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB8B916-AEBB-D640-BF2E-D82BF5D262FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD39B844-699B-9F40-8853-B611888D7FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3620" yWindow="3800" windowWidth="26620" windowHeight="15840" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
+    <workbookView xWindow="6620" yWindow="3800" windowWidth="23620" windowHeight="15840" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
   <sheets>
     <sheet name="network" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="279">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -906,6 +906,33 @@
   </si>
   <si>
     <t>KB0034</t>
+  </si>
+  <si>
+    <t>2604-2401</t>
+  </si>
+  <si>
+    <t>80-99-E7-4D-A8-5E</t>
+  </si>
+  <si>
+    <t>2604-2402</t>
+  </si>
+  <si>
+    <t>2604-2403</t>
+  </si>
+  <si>
+    <t>58-18-62-6B-1D-2B</t>
+  </si>
+  <si>
+    <t>192.168.201.20</t>
+  </si>
+  <si>
+    <t>192.168.201.21</t>
+  </si>
+  <si>
+    <t>192.168.201.22</t>
+  </si>
+  <si>
+    <t>58-18-62-6B-1D-2C</t>
   </si>
 </sst>
 </file>
@@ -1078,30 +1105,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1109,44 +1133,16 @@
     <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="13">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="10"/>
-        <name val="Calibri Light"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri Light"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1232,6 +1228,24 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1304,6 +1318,18 @@
         <scheme val="major"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1394,24 +1420,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K79" totalsRowShown="0" headerRowDxfId="12" dataDxfId="1">
-  <autoFilter ref="A1:K79" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K82" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K82" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K74">
     <sortCondition ref="A2:A74"/>
     <sortCondition ref="B2:B74"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{EF2C341F-E5C1-604C-942C-FB7E9F76F1CD}" name="AssetTag" dataDxfId="11"/>
-    <tableColumn id="13" xr3:uid="{41250547-1480-7146-952C-14798A4748DA}" name="NIC" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{5FD75CC6-F089-3C49-9E51-1565A7A8B99A}" name="MAC" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{2045B636-E35D-274F-BBD3-3FF47E121094}" name="Static-Reserved" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{10F05B30-ACC5-4444-9BCB-C4F83EBE82E8}" name="IP" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{D8CE5014-251A-FD49-B36C-92F7DAE750CB}" name="URL" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{51987960-7E23-714D-8524-EE3E88D77DA5}" name="Services" dataDxfId="0" dataCellStyle="Hyperlink"/>
-    <tableColumn id="15" xr3:uid="{16C691FB-14A7-3342-ACEE-B45625DAF5F5}" name="Monitor" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{D6182358-29F5-9D47-8228-7124B0F8D7E0}" name="RelatedIssueId" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{6C62EAB0-EF42-3142-95A8-47F7C21989EE}" name="Usage" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{890B1E64-D13A-3548-8BF0-C28FFF87E38B}" name="Notes" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{EF2C341F-E5C1-604C-942C-FB7E9F76F1CD}" name="AssetTag" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{41250547-1480-7146-952C-14798A4748DA}" name="NIC" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{5FD75CC6-F089-3C49-9E51-1565A7A8B99A}" name="MAC" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{2045B636-E35D-274F-BBD3-3FF47E121094}" name="Static-Reserved" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{10F05B30-ACC5-4444-9BCB-C4F83EBE82E8}" name="IP" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{D8CE5014-251A-FD49-B36C-92F7DAE750CB}" name="URL" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{51987960-7E23-714D-8524-EE3E88D77DA5}" name="Services" dataDxfId="4" dataCellStyle="Hyperlink"/>
+    <tableColumn id="15" xr3:uid="{16C691FB-14A7-3342-ACEE-B45625DAF5F5}" name="Monitor" dataDxfId="3"/>
+    <tableColumn id="16" xr3:uid="{D6182358-29F5-9D47-8228-7124B0F8D7E0}" name="RelatedIssueId" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{6C62EAB0-EF42-3142-95A8-47F7C21989EE}" name="Usage" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{890B1E64-D13A-3548-8BF0-C28FFF87E38B}" name="Notes" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1800,29 +1826,29 @@
       <c r="B3" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12" t="s">
+      <c r="D3" s="6"/>
+      <c r="E3" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
       <c r="H3" s="8" t="s">
         <v>178</v>
       </c>
       <c r="I3" s="9"/>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="K3" s="12"/>
+      <c r="K3" s="6"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B4" s="11"/>
+      <c r="B4" s="5"/>
       <c r="C4" s="6" t="s">
         <v>166</v>
       </c>
@@ -1842,73 +1868,73 @@
       <c r="K4" s="6"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="5" t="s">
         <v>202</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12" t="s">
+      <c r="D5" s="6"/>
+      <c r="E5" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
       <c r="H5" s="8" t="s">
         <v>178</v>
       </c>
       <c r="I5" s="9"/>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="K5" s="12"/>
+      <c r="K5" s="6"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
       <c r="H6" s="8" t="s">
         <v>179</v>
       </c>
       <c r="I6" s="9"/>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="K6" s="12"/>
+      <c r="K6" s="6"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11" t="s">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12" t="s">
+      <c r="D7" s="6"/>
+      <c r="E7" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
       <c r="H7" s="8" t="s">
         <v>178</v>
       </c>
       <c r="I7" s="9"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
@@ -1955,46 +1981,46 @@
       <c r="B10" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12" t="s">
+      <c r="D10" s="6"/>
+      <c r="E10" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
       <c r="H10" s="8" t="s">
         <v>178</v>
       </c>
       <c r="I10" s="9"/>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="K10" s="12"/>
+      <c r="K10" s="6"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
       <c r="H11" s="8" t="s">
         <v>179</v>
       </c>
       <c r="I11" s="9"/>
-      <c r="J11" s="12" t="s">
+      <c r="J11" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="K11" s="12"/>
+      <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
@@ -2003,101 +2029,101 @@
       <c r="B12" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12" t="s">
+      <c r="D12" s="6"/>
+      <c r="E12" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
       <c r="H12" s="8" t="s">
         <v>178</v>
       </c>
       <c r="I12" s="9"/>
-      <c r="J12" s="12" t="s">
+      <c r="J12" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="K12" s="12"/>
+      <c r="K12" s="6"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
       <c r="H13" s="8" t="s">
         <v>179</v>
       </c>
       <c r="I13" s="9"/>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K13" s="12"/>
+      <c r="K13" s="6"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="5" t="s">
         <v>229</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12" t="s">
+      <c r="D14" s="6"/>
+      <c r="E14" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
       <c r="H14" s="8" t="s">
         <v>178</v>
       </c>
       <c r="I14" s="9"/>
-      <c r="J14" s="12" t="s">
+      <c r="J14" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="K14" s="12"/>
+      <c r="K14" s="6"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
       <c r="H15" s="8" t="s">
         <v>179</v>
       </c>
       <c r="I15" s="9"/>
-      <c r="J15" s="12" t="s">
+      <c r="J15" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="K15" s="12"/>
+      <c r="K15" s="6"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
         <v>148</v>
       </c>
       <c r="B16" s="6"/>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="11" t="s">
         <v>146</v>
       </c>
       <c r="D16" s="6" t="s">
@@ -2115,15 +2141,15 @@
       <c r="J16" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="K16" s="14" t="s">
+      <c r="K16" s="12" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="15"/>
+      <c r="B17" s="13"/>
       <c r="C17" s="6" t="s">
         <v>21</v>
       </c>
@@ -2143,27 +2169,27 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="11" t="s">
+      <c r="B18" s="14"/>
+      <c r="C18" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12" t="s">
+      <c r="D18" s="6"/>
+      <c r="E18" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12" t="s">
+      <c r="F18" s="6"/>
+      <c r="G18" s="6" t="s">
         <v>245</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>178</v>
       </c>
       <c r="I18" s="9"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
@@ -2172,7 +2198,7 @@
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="15" t="s">
         <v>192</v>
       </c>
       <c r="F19" s="6"/>
@@ -2258,7 +2284,7 @@
         <v>7</v>
       </c>
       <c r="B23" s="5"/>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D23" s="6"/>
@@ -2285,11 +2311,11 @@
       <c r="B24" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="15" t="s">
         <v>159</v>
       </c>
       <c r="D24" s="6"/>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="15" t="s">
         <v>183</v>
       </c>
       <c r="F24" s="6"/>
@@ -2312,7 +2338,7 @@
       <c r="B25" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="17" t="s">
         <v>174</v>
       </c>
       <c r="D25" s="6"/>
@@ -2339,11 +2365,11 @@
       <c r="B26" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="15" t="s">
         <v>184</v>
       </c>
       <c r="D26" s="6"/>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="15" t="s">
         <v>185</v>
       </c>
       <c r="F26" s="6"/>
@@ -2453,7 +2479,7 @@
       <c r="J30" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="K30" s="14"/>
+      <c r="K30" s="12"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
@@ -2656,7 +2682,7 @@
       <c r="J40" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="K40" s="14"/>
+      <c r="K40" s="12"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
@@ -2686,7 +2712,7 @@
       <c r="J41" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="K41" s="14"/>
+      <c r="K41" s="12"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
@@ -2716,7 +2742,7 @@
       <c r="J42" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="K42" s="14"/>
+      <c r="K42" s="12"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
@@ -2729,7 +2755,7 @@
       <c r="D43" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="E43" s="17" t="s">
+      <c r="E43" s="15" t="s">
         <v>135</v>
       </c>
       <c r="F43" s="7" t="str">
@@ -2776,7 +2802,7 @@
       <c r="J44" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="K44" s="14"/>
+      <c r="K44" s="12"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
@@ -2898,27 +2924,27 @@
       <c r="K49" s="6"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B50" s="11"/>
-      <c r="C50" s="11" t="s">
+      <c r="B50" s="5"/>
+      <c r="C50" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12" t="s">
+      <c r="D50" s="6"/>
+      <c r="E50" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="F50" s="12"/>
-      <c r="G50" s="12"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
       <c r="H50" s="8" t="s">
         <v>178</v>
       </c>
       <c r="I50" s="9"/>
-      <c r="J50" s="12" t="s">
+      <c r="J50" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="K50" s="12"/>
+      <c r="K50" s="6"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
@@ -2943,7 +2969,7 @@
       <c r="J51" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="K51" s="14" t="s">
+      <c r="K51" s="12" t="s">
         <v>79</v>
       </c>
     </row>
@@ -2952,7 +2978,7 @@
         <v>60</v>
       </c>
       <c r="B52" s="6"/>
-      <c r="C52" s="27" t="s">
+      <c r="C52" s="23" t="s">
         <v>59</v>
       </c>
       <c r="D52" s="6" t="s">
@@ -2979,7 +3005,7 @@
         <v>54</v>
       </c>
       <c r="B53" s="6"/>
-      <c r="C53" s="27" t="s">
+      <c r="C53" s="23" t="s">
         <v>53</v>
       </c>
       <c r="D53" s="6" t="s">
@@ -3006,7 +3032,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="6"/>
-      <c r="C54" s="27" t="s">
+      <c r="C54" s="23" t="s">
         <v>51</v>
       </c>
       <c r="D54" s="6" t="s">
@@ -3033,7 +3059,7 @@
         <v>50</v>
       </c>
       <c r="B55" s="6"/>
-      <c r="C55" s="27" t="s">
+      <c r="C55" s="23" t="s">
         <v>48</v>
       </c>
       <c r="D55" s="6" t="s">
@@ -3056,10 +3082,10 @@
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A56" s="20" t="s">
+      <c r="A56" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="20"/>
+      <c r="B56" s="10"/>
       <c r="C56" s="6" t="s">
         <v>56</v>
       </c>
@@ -3120,7 +3146,7 @@
         <v>122</v>
       </c>
       <c r="B58" s="6"/>
-      <c r="C58" s="21" t="s">
+      <c r="C58" s="18" t="s">
         <v>120</v>
       </c>
       <c r="D58" s="6" t="s">
@@ -3176,7 +3202,7 @@
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A60" s="22" t="s">
+      <c r="A60" s="19" t="s">
         <v>114</v>
       </c>
       <c r="B60" s="6"/>
@@ -3236,7 +3262,7 @@
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A62" s="23" t="s">
+      <c r="A62" s="20" t="s">
         <v>240</v>
       </c>
       <c r="B62" s="5"/>
@@ -3272,7 +3298,7 @@
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
-      <c r="H63" s="24" t="s">
+      <c r="H63" s="21" t="s">
         <v>178</v>
       </c>
       <c r="I63" s="9"/>
@@ -3300,14 +3326,14 @@
         <v>http://192.168.206.7</v>
       </c>
       <c r="G64" s="7"/>
-      <c r="H64" s="24" t="s">
+      <c r="H64" s="21" t="s">
         <v>178</v>
       </c>
       <c r="I64" s="9"/>
       <c r="J64" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K64" s="14" t="s">
+      <c r="K64" s="12" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3330,14 +3356,14 @@
         <v>http://192.168.0.192</v>
       </c>
       <c r="G65" s="7"/>
-      <c r="H65" s="24" t="s">
+      <c r="H65" s="21" t="s">
         <v>179</v>
       </c>
       <c r="I65" s="9"/>
       <c r="J65" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="K65" s="14" t="s">
+      <c r="K65" s="12" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3357,7 +3383,7 @@
       </c>
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
-      <c r="H66" s="24" t="s">
+      <c r="H66" s="21" t="s">
         <v>179</v>
       </c>
       <c r="I66" s="9"/>
@@ -3384,14 +3410,14 @@
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
-      <c r="H67" s="24" t="s">
+      <c r="H67" s="21" t="s">
         <v>178</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="K67" s="14" t="s">
+      <c r="K67" s="12" t="s">
         <v>79</v>
       </c>
     </row>
@@ -3414,14 +3440,14 @@
         <v>ftp://192.168.0.189</v>
       </c>
       <c r="G68" s="7"/>
-      <c r="H68" s="24" t="s">
+      <c r="H68" s="21" t="s">
         <v>178</v>
       </c>
       <c r="I68" s="9"/>
       <c r="J68" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="K68" s="14" t="s">
+      <c r="K68" s="12" t="s">
         <v>79</v>
       </c>
     </row>
@@ -3444,14 +3470,14 @@
         <v>ftp://192.168.0.190</v>
       </c>
       <c r="G69" s="7"/>
-      <c r="H69" s="24" t="s">
+      <c r="H69" s="21" t="s">
         <v>178</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="K69" s="14" t="s">
+      <c r="K69" s="12" t="s">
         <v>79</v>
       </c>
     </row>
@@ -3476,7 +3502,7 @@
       <c r="G70" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="H70" s="24" t="s">
+      <c r="H70" s="21" t="s">
         <v>178</v>
       </c>
       <c r="I70" s="9"/>
@@ -3508,7 +3534,7 @@
       <c r="G71" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="H71" s="24" t="s">
+      <c r="H71" s="21" t="s">
         <v>178</v>
       </c>
       <c r="I71" s="9"/>
@@ -3540,7 +3566,7 @@
       <c r="G72" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="H72" s="24" t="s">
+      <c r="H72" s="21" t="s">
         <v>178</v>
       </c>
       <c r="I72" s="9"/>
@@ -3572,7 +3598,7 @@
       <c r="G73" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="H73" s="24" t="s">
+      <c r="H73" s="21" t="s">
         <v>178</v>
       </c>
       <c r="I73" s="9"/>
@@ -3595,7 +3621,7 @@
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
       <c r="G74" s="6"/>
-      <c r="H74" s="24" t="s">
+      <c r="H74" s="21" t="s">
         <v>179</v>
       </c>
       <c r="I74" s="9"/>
@@ -3607,175 +3633,244 @@
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A75" s="11" t="s">
+      <c r="A75" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="B75" s="11"/>
+      <c r="B75" s="5"/>
       <c r="C75" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="D75" s="12"/>
-      <c r="E75" s="12" t="s">
+      <c r="D75" s="6"/>
+      <c r="E75" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="F75" s="12"/>
-      <c r="G75" s="25" t="s">
+      <c r="F75" s="6"/>
+      <c r="G75" s="22" t="s">
         <v>245</v>
       </c>
-      <c r="H75" s="24" t="s">
+      <c r="H75" s="21" t="s">
         <v>178</v>
       </c>
       <c r="I75" s="9"/>
-      <c r="J75" s="12" t="s">
+      <c r="J75" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="K75" s="12"/>
+      <c r="K75" s="6"/>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="B76" s="11"/>
-      <c r="C76" s="11"/>
-      <c r="D76" s="12"/>
-      <c r="E76" s="12"/>
-      <c r="F76" s="12"/>
-      <c r="G76" s="25"/>
-      <c r="H76" s="24" t="s">
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="22"/>
+      <c r="H76" s="21" t="s">
         <v>179</v>
       </c>
       <c r="I76" s="9"/>
-      <c r="J76" s="12"/>
-      <c r="K76" s="12"/>
+      <c r="J76" s="6"/>
+      <c r="K76" s="6"/>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A77" s="11" t="s">
+      <c r="A77" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="B77" s="11"/>
-      <c r="C77" s="11"/>
-      <c r="D77" s="12"/>
-      <c r="E77" s="12" t="s">
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="F77" s="12"/>
-      <c r="G77" s="25"/>
-      <c r="H77" s="24"/>
+      <c r="F77" s="6"/>
+      <c r="G77" s="22"/>
+      <c r="H77" s="21"/>
       <c r="I77" s="9"/>
-      <c r="J77" s="12"/>
-      <c r="K77" s="12"/>
+      <c r="J77" s="6"/>
+      <c r="K77" s="6"/>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B78" s="11"/>
-      <c r="C78" s="11"/>
-      <c r="D78" s="12"/>
-      <c r="E78" s="12" t="s">
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="F78" s="12"/>
-      <c r="G78" s="25" t="s">
+      <c r="F78" s="6"/>
+      <c r="G78" s="22" t="s">
         <v>261</v>
       </c>
-      <c r="H78" s="24" t="s">
+      <c r="H78" s="21" t="s">
         <v>178</v>
       </c>
       <c r="I78" s="9"/>
-      <c r="J78" s="12" t="s">
+      <c r="J78" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="K78" s="12"/>
+      <c r="K78" s="6"/>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A79" s="11" t="s">
+      <c r="A79" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="B79" s="11"/>
-      <c r="C79" s="11"/>
-      <c r="D79" s="12"/>
-      <c r="E79" s="26" t="s">
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="F79" s="12"/>
-      <c r="G79" s="25" t="s">
+      <c r="F79" s="6"/>
+      <c r="G79" s="22" t="s">
         <v>260</v>
       </c>
-      <c r="H79" s="24" t="s">
+      <c r="H79" s="21" t="s">
         <v>178</v>
       </c>
       <c r="I79" s="9"/>
-      <c r="J79" s="12" t="s">
+      <c r="J79" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="K79" s="12"/>
+      <c r="K79" s="6"/>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H80"/>
-      <c r="I80"/>
-    </row>
-    <row r="81" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H81"/>
-      <c r="I81"/>
-    </row>
-    <row r="82" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H82"/>
-      <c r="I82"/>
-    </row>
-    <row r="83" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="A80" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="B80" s="24"/>
+      <c r="C80" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E80" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="F80" s="25"/>
+      <c r="G80" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="H80" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="I80" s="26"/>
+      <c r="J80" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K80" s="25"/>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A81" s="24" t="s">
+        <v>272</v>
+      </c>
+      <c r="B81" s="24"/>
+      <c r="C81" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E81" s="25" t="s">
+        <v>276</v>
+      </c>
+      <c r="F81" s="25"/>
+      <c r="G81" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="H81" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="I81" s="26"/>
+      <c r="J81" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K81" s="25"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A82" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="B82" s="24"/>
+      <c r="C82" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E82" s="25" t="s">
+        <v>277</v>
+      </c>
+      <c r="F82" s="25"/>
+      <c r="G82" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="H82" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="I82" s="26"/>
+      <c r="J82" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K82" s="25"/>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H83"/>
       <c r="I83"/>
     </row>
-    <row r="84" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H84"/>
       <c r="I84"/>
     </row>
-    <row r="85" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H85"/>
       <c r="I85"/>
     </row>
-    <row r="86" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H86"/>
       <c r="I86"/>
     </row>
-    <row r="87" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H87"/>
       <c r="I87"/>
     </row>
-    <row r="88" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H88"/>
       <c r="I88"/>
     </row>
-    <row r="89" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H89"/>
       <c r="I89"/>
     </row>
-    <row r="90" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H90"/>
       <c r="I90"/>
     </row>
-    <row r="91" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H91"/>
       <c r="I91"/>
     </row>
-    <row r="92" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H92"/>
       <c r="I92"/>
     </row>
-    <row r="93" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H93"/>
       <c r="I93"/>
     </row>
-    <row r="94" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H94"/>
       <c r="I94"/>
     </row>
-    <row r="95" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H95"/>
       <c r="I95"/>
     </row>
-    <row r="96" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H96"/>
       <c r="I96"/>
     </row>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD39B844-699B-9F40-8853-B611888D7FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4914360D-6D87-EA46-BF16-BB4B328DCC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6620" yWindow="3800" windowWidth="23620" windowHeight="15840" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -1105,7 +1105,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1134,9 +1134,6 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3535,7 +3532,7 @@
         <v>242</v>
       </c>
       <c r="H71" s="21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I71" s="9"/>
       <c r="J71" s="6" t="s">
@@ -3567,7 +3564,7 @@
         <v>242</v>
       </c>
       <c r="H72" s="21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I72" s="9"/>
       <c r="J72" s="6" t="s">
@@ -3599,7 +3596,7 @@
         <v>242</v>
       </c>
       <c r="H73" s="21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I73" s="9"/>
       <c r="J73" s="6" t="s">
@@ -3738,85 +3735,85 @@
       <c r="K79" s="6"/>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A80" s="24" t="s">
+      <c r="A80" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="B80" s="24"/>
-      <c r="C80" s="24" t="s">
+      <c r="B80" s="5"/>
+      <c r="C80" s="5" t="s">
         <v>271</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E80" s="25" t="s">
+      <c r="E80" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="F80" s="25"/>
+      <c r="F80" s="6"/>
       <c r="G80" s="7" t="s">
         <v>242</v>
       </c>
       <c r="H80" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="I80" s="26"/>
+      <c r="I80" s="9"/>
       <c r="J80" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="K80" s="25"/>
+      <c r="K80" s="6"/>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A81" s="24" t="s">
+      <c r="A81" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B81" s="24"/>
-      <c r="C81" s="24" t="s">
+      <c r="B81" s="5"/>
+      <c r="C81" s="5" t="s">
         <v>274</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E81" s="25" t="s">
+      <c r="E81" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="F81" s="25"/>
+      <c r="F81" s="6"/>
       <c r="G81" s="7" t="s">
         <v>242</v>
       </c>
       <c r="H81" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="I81" s="26"/>
+      <c r="I81" s="9"/>
       <c r="J81" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="K81" s="25"/>
+      <c r="K81" s="6"/>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A82" s="24" t="s">
+      <c r="A82" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="B82" s="24"/>
-      <c r="C82" s="24" t="s">
+      <c r="B82" s="5"/>
+      <c r="C82" s="5" t="s">
         <v>278</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E82" s="25" t="s">
+      <c r="E82" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="F82" s="25"/>
+      <c r="F82" s="6"/>
       <c r="G82" s="7" t="s">
         <v>242</v>
       </c>
       <c r="H82" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="I82" s="26"/>
+      <c r="I82" s="9"/>
       <c r="J82" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="K82" s="25"/>
+      <c r="K82" s="6"/>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H83"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4914360D-6D87-EA46-BF16-BB4B328DCC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15AFC45B-6FC4-4443-A5A3-C99596B4A45B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6620" yWindow="3800" windowWidth="23620" windowHeight="15840" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
+    <workbookView xWindow="4320" yWindow="1460" windowWidth="25920" windowHeight="18180" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
   <sheets>
     <sheet name="network" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="282">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -933,6 +933,15 @@
   </si>
   <si>
     <t>58-18-62-6B-1D-2C</t>
+  </si>
+  <si>
+    <t>192.168.201.2</t>
+  </si>
+  <si>
+    <t>2603-1205</t>
+  </si>
+  <si>
+    <t>AV Net Controller</t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1114,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1134,6 +1143,9 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1417,8 +1429,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K82" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K82" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K83" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K83" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K74">
     <sortCondition ref="A2:A74"/>
     <sortCondition ref="B2:B74"/>
@@ -3816,8 +3828,27 @@
       <c r="K82" s="6"/>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H83"/>
-      <c r="I83"/>
+      <c r="A83" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="B83" s="24"/>
+      <c r="C83" s="24"/>
+      <c r="D83" s="25"/>
+      <c r="E83" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="F83" s="25"/>
+      <c r="G83" s="22" t="s">
+        <v>245</v>
+      </c>
+      <c r="H83" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="I83" s="26"/>
+      <c r="J83" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="K83" s="25"/>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H84"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15AFC45B-6FC4-4443-A5A3-C99596B4A45B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4372B93A-28F7-7B44-8D04-E1B4607C6665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4320" yWindow="1460" windowWidth="25920" windowHeight="18180" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="283">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -942,6 +942,9 @@
   </si>
   <si>
     <t>AV Net Controller</t>
+  </si>
+  <si>
+    <t>KB0040</t>
   </si>
 </sst>
 </file>
@@ -1114,7 +1117,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1143,9 +1146,6 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3514,7 +3514,9 @@
       <c r="H70" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="I70" s="9"/>
+      <c r="I70" s="9" t="s">
+        <v>282</v>
+      </c>
       <c r="J70" s="6" t="s">
         <v>64</v>
       </c>
@@ -3828,27 +3830,27 @@
       <c r="K82" s="6"/>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A83" s="24" t="s">
+      <c r="A83" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B83" s="24"/>
-      <c r="C83" s="24"/>
-      <c r="D83" s="25"/>
-      <c r="E83" s="25" t="s">
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="F83" s="25"/>
+      <c r="F83" s="6"/>
       <c r="G83" s="22" t="s">
         <v>245</v>
       </c>
       <c r="H83" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="I83" s="26"/>
-      <c r="J83" s="25" t="s">
+      <c r="I83" s="9"/>
+      <c r="J83" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="K83" s="25"/>
+      <c r="K83" s="6"/>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H84"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4372B93A-28F7-7B44-8D04-E1B4607C6665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427F7B40-9B28-EC46-BF7D-34E535C06E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="1460" windowWidth="25920" windowHeight="18180" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
+    <workbookView xWindow="8320" yWindow="1460" windowWidth="21920" windowHeight="18180" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
   <sheets>
     <sheet name="network" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="284">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -945,6 +945,9 @@
   </si>
   <si>
     <t>KB0040</t>
+  </si>
+  <si>
+    <t>KB0041</t>
   </si>
 </sst>
 </file>
@@ -3001,7 +3004,9 @@
       <c r="H52" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="I52" s="9"/>
+      <c r="I52" s="9" t="s">
+        <v>283</v>
+      </c>
       <c r="J52" s="6" t="s">
         <v>49</v>
       </c>
@@ -3028,7 +3033,9 @@
       <c r="H53" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="I53" s="9"/>
+      <c r="I53" s="9" t="s">
+        <v>283</v>
+      </c>
       <c r="J53" s="6" t="s">
         <v>49</v>
       </c>
@@ -3055,7 +3062,9 @@
       <c r="H54" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="I54" s="9"/>
+      <c r="I54" s="9" t="s">
+        <v>283</v>
+      </c>
       <c r="J54" s="6" t="s">
         <v>49</v>
       </c>
@@ -3082,7 +3091,9 @@
       <c r="H55" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="I55" s="9"/>
+      <c r="I55" s="9" t="s">
+        <v>283</v>
+      </c>
       <c r="J55" s="6" t="s">
         <v>49</v>
       </c>
@@ -3202,7 +3213,9 @@
       <c r="H59" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="I59" s="9"/>
+      <c r="I59" s="9" t="s">
+        <v>283</v>
+      </c>
       <c r="J59" s="6" t="s">
         <v>117</v>
       </c>
@@ -3422,7 +3435,9 @@
       <c r="H67" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="I67" s="9"/>
+      <c r="I67" s="9" t="s">
+        <v>283</v>
+      </c>
       <c r="J67" s="6" t="s">
         <v>102</v>
       </c>
@@ -3452,7 +3467,9 @@
       <c r="H68" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="I68" s="9"/>
+      <c r="I68" s="9" t="s">
+        <v>283</v>
+      </c>
       <c r="J68" s="6" t="s">
         <v>82</v>
       </c>
@@ -3482,7 +3499,9 @@
       <c r="H69" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="I69" s="9"/>
+      <c r="I69" s="9" t="s">
+        <v>283</v>
+      </c>
       <c r="J69" s="6" t="s">
         <v>82</v>
       </c>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427F7B40-9B28-EC46-BF7D-34E535C06E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA31CF37-BC5D-744B-9006-89A0AE02ED27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8320" yWindow="1460" windowWidth="21920" windowHeight="18180" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="279">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -477,21 +477,6 @@
   </si>
   <si>
     <t>ZVCU-A001</t>
-  </si>
-  <si>
-    <t>192.168.0.182</t>
-  </si>
-  <si>
-    <t>Static</t>
-  </si>
-  <si>
-    <t>00:A0:DE:25:6C:2C</t>
-  </si>
-  <si>
-    <t>Audio Console</t>
-  </si>
-  <si>
-    <t>ZAKU-0001</t>
   </si>
   <si>
     <t>192.168.0.26</t>
@@ -1432,11 +1417,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K83" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K83" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K74">
-    <sortCondition ref="A2:A74"/>
-    <sortCondition ref="B2:B74"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K82" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K82" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K73">
+    <sortCondition ref="A2:A73"/>
+    <sortCondition ref="B2:B73"/>
   </sortState>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{EF2C341F-E5C1-604C-942C-FB7E9F76F1CD}" name="AssetTag" dataDxfId="10"/>
@@ -1752,7 +1737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC7A309-0B6A-4549-9590-6CFCF97D2DB0}">
-  <dimension ref="A1:K1748"/>
+  <dimension ref="A1:K1747"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
@@ -1772,50 +1757,50 @@
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="I1" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="6" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F2" s="7" t="str">
         <f>CONCATENATE("http://", E2)</f>
@@ -1823,126 +1808,126 @@
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="6" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="K2" s="6"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="5" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="K3" s="6"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="6" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="6" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="K4" s="6"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="6" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K5" s="6"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>207</v>
-      </c>
       <c r="C6" s="5" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="K6" s="6"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="H7" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="6"/>
@@ -1950,18 +1935,18 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="6"/>
@@ -1969,18 +1954,18 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="6"/>
@@ -1988,170 +1973,170 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="6" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="K10" s="6"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="6" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="6" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K12" s="6"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="6" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="K13" s="6"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="6" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="K14" s="6"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>229</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>234</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="6" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="K15" s="6"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="11" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="K16" s="12" t="s">
         <v>79</v>
@@ -2170,7 +2155,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="6" t="s">
@@ -2182,22 +2167,22 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="5" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="6"/>
@@ -2211,12 +2196,12 @@
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="15" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="6" t="s">
@@ -2229,21 +2214,21 @@
         <v>7</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="6"/>
@@ -2254,21 +2239,21 @@
         <v>7</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
       <c r="H21" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I21" s="9"/>
       <c r="J21" s="5" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="K21" s="6"/>
     </row>
@@ -2277,7 +2262,7 @@
         <v>7</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="6"/>
@@ -2285,7 +2270,7 @@
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
       <c r="H22" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="6"/>
@@ -2308,7 +2293,7 @@
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I23" s="9"/>
       <c r="J23" s="6" t="s">
@@ -2321,25 +2306,25 @@
         <v>1</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="15" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I24" s="9"/>
       <c r="J24" s="6" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K24" s="6"/>
     </row>
@@ -2348,25 +2333,25 @@
         <v>1</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I25" s="9"/>
       <c r="J25" s="6" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="K25" s="6"/>
     </row>
@@ -2375,83 +2360,83 @@
         <v>1</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="15" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="6" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I26" s="9"/>
       <c r="J26" s="6" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="K26" s="6"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
       <c r="H27" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I27" s="9"/>
       <c r="J27" s="6" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K27" s="6"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I28" s="9"/>
       <c r="J28" s="6" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="K28" s="6"/>
     </row>
     <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -2460,23 +2445,23 @@
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
       <c r="H29" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="K29" s="6"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>106</v>
@@ -2485,11 +2470,11 @@
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
       <c r="H30" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="K30" s="12"/>
     </row>
@@ -2504,7 +2489,7 @@
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="6" t="s">
@@ -2523,7 +2508,7 @@
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="6" t="s">
@@ -2542,7 +2527,7 @@
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I33" s="9"/>
       <c r="J33" s="6" t="s">
@@ -2561,7 +2546,7 @@
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I34" s="9"/>
       <c r="J34" s="6" t="s">
@@ -2580,7 +2565,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I35" s="9"/>
       <c r="J35" s="6" t="s">
@@ -2601,7 +2586,7 @@
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="6" t="s">
@@ -2620,7 +2605,7 @@
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
       <c r="H37" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I37" s="9"/>
       <c r="J37" s="6" t="s">
@@ -2639,7 +2624,7 @@
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
       <c r="H38" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="6" t="s">
@@ -2658,7 +2643,7 @@
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
       <c r="H39" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I39" s="9"/>
       <c r="J39" s="6" t="s">
@@ -2672,27 +2657,27 @@
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>106</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F40" s="7" t="str">
         <f>CONCATENATE("http://", E40)</f>
         <v>http://192.168.0.22</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I40" s="9"/>
       <c r="J40" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K40" s="12"/>
     </row>
@@ -2702,27 +2687,27 @@
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>106</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F41" s="7" t="str">
         <f>CONCATENATE("http://", E41)</f>
         <v>http://192.168.0.23</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I41" s="9"/>
       <c r="J41" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K41" s="12"/>
     </row>
@@ -2732,27 +2717,27 @@
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>106</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="F42" s="7" t="str">
         <f>CONCATENATE("http://", E42)</f>
         <v>http://192.168.0.24</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I42" s="9"/>
       <c r="J42" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K42" s="12"/>
     </row>
@@ -2762,27 +2747,27 @@
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>106</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F43" s="7" t="str">
         <f>CONCATENATE("http://", E43)</f>
         <v>http://192.168.0.25</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K43" s="6"/>
     </row>
@@ -2792,27 +2777,27 @@
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>106</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F44" s="7" t="str">
         <f>CONCATENATE("http://", E44)</f>
         <v>http://192.168.0.26</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I44" s="9"/>
       <c r="J44" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K44" s="12"/>
     </row>
@@ -2821,7 +2806,7 @@
         <v>46</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>45</v>
@@ -2835,14 +2820,14 @@
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="6" t="s">
         <v>42</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
@@ -2850,7 +2835,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="6"/>
@@ -2858,11 +2843,11 @@
       <c r="F46" s="6"/>
       <c r="G46" s="7"/>
       <c r="H46" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I46" s="9"/>
       <c r="J46" s="6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="K46" s="6"/>
     </row>
@@ -2871,7 +2856,7 @@
         <v>43</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>41</v>
@@ -2885,14 +2870,14 @@
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
       <c r="H47" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I47" s="9"/>
       <c r="J47" s="6" t="s">
         <v>42</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
@@ -2900,7 +2885,7 @@
         <v>43</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="6"/>
@@ -2908,11 +2893,11 @@
       <c r="F48" s="6"/>
       <c r="G48" s="7"/>
       <c r="H48" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I48" s="9"/>
       <c r="J48" s="6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="K48" s="6"/>
     </row>
@@ -2945,67 +2930,69 @@
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
       <c r="H50" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="6" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="K50" s="6"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
-        <v>131</v>
+        <v>60</v>
       </c>
       <c r="B51" s="6"/>
-      <c r="C51" s="6" t="s">
-        <v>129</v>
+      <c r="C51" s="23" t="s">
+        <v>59</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>128</v>
+        <v>40</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>127</v>
+        <v>260</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
       <c r="H51" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="I51" s="9"/>
+        <v>173</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>278</v>
+      </c>
       <c r="J51" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="K51" s="12" t="s">
-        <v>79</v>
+        <v>49</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="23" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
       <c r="H52" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="J52" s="6" t="s">
         <v>49</v>
@@ -3016,25 +3003,25 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="23" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="6"/>
       <c r="H53" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="J53" s="6" t="s">
         <v>49</v>
@@ -3045,25 +3032,25 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="23" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
       <c r="H54" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="J54" s="6" t="s">
         <v>49</v>
@@ -3073,287 +3060,288 @@
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A55" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B55" s="6"/>
-      <c r="C55" s="23" t="s">
-        <v>48</v>
+      <c r="A55" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B55" s="10"/>
+      <c r="C55" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="F55" s="6" t="str">
+        <f>CONCATENATE("http://", E55, ":8080")</f>
+        <v>http://192.168.0.197:8080</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>239</v>
+      </c>
       <c r="H55" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="I55" s="9" t="s">
-        <v>283</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="I55" s="9"/>
       <c r="J55" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="K55" s="6" t="s">
-        <v>47</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="K55" s="6"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A56" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="B56" s="10"/>
+      <c r="A56" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" s="6"/>
       <c r="C56" s="6" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F56" s="6" t="str">
-        <f>CONCATENATE("http://", E56, ":8080")</f>
-        <v>http://192.168.0.197:8080</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>244</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="F56" s="7" t="str">
+        <f>CONCATENATE("http://", E56)</f>
+        <v>http://192.168.0.186</v>
+      </c>
+      <c r="G56" s="7"/>
       <c r="H56" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I56" s="9"/>
       <c r="J56" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K56" s="6"/>
+        <v>125</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B57" s="6"/>
-      <c r="C57" s="6" t="s">
-        <v>124</v>
+      <c r="C57" s="18" t="s">
+        <v>120</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F57" s="7" t="str">
         <f>CONCATENATE("http://", E57)</f>
-        <v>http://192.168.0.186</v>
+        <v>http://192.168.0.187</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B58" s="6"/>
-      <c r="C58" s="18" t="s">
-        <v>120</v>
+      <c r="C58" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F58" s="7" t="str">
         <f>CONCATENATE("http://", E58)</f>
-        <v>http://192.168.0.187</v>
+        <v>http://192.168.0.188</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="I58" s="9"/>
+        <v>173</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>278</v>
+      </c>
       <c r="J58" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A59" s="6" t="s">
-        <v>118</v>
+      <c r="A59" s="19" t="s">
+        <v>114</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F59" s="7" t="str">
         <f>CONCATENATE("http://", E59)</f>
-        <v>http://192.168.0.188</v>
+        <v>http://192.168.0.180</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="I59" s="9" t="s">
-        <v>283</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="I59" s="9"/>
       <c r="J59" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A60" s="19" t="s">
-        <v>114</v>
+      <c r="A60" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="6" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>106</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="F60" s="7" t="str">
         <f>CONCATENATE("http://", E60)</f>
-        <v>http://192.168.0.180</v>
+        <v>http://192.168.0.181</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I60" s="9"/>
       <c r="J60" s="6" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A61" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B61" s="6"/>
+      <c r="A61" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="B61" s="5"/>
       <c r="C61" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>106</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="D61" s="6"/>
       <c r="E61" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="F61" s="7" t="str">
-        <f>CONCATENATE("http://", E61)</f>
-        <v>http://192.168.0.181</v>
-      </c>
-      <c r="G61" s="7"/>
+        <v>156</v>
+      </c>
+      <c r="F61" s="6"/>
+      <c r="G61" s="6"/>
       <c r="H61" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="K61" s="6" t="s">
-        <v>104</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="K61" s="6"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A62" s="20" t="s">
-        <v>240</v>
+      <c r="A62" s="5" t="s">
+        <v>157</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="6" t="s">
-        <v>14</v>
+        <v>158</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6" t="s">
-        <v>161</v>
+        <v>196</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="6"/>
-      <c r="H62" s="8" t="s">
-        <v>179</v>
+      <c r="H62" s="21" t="s">
+        <v>173</v>
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="6" t="s">
-        <v>15</v>
+        <v>195</v>
       </c>
       <c r="K62" s="6"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A63" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B63" s="5"/>
+      <c r="A63" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B63" s="6"/>
       <c r="C63" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D63" s="6"/>
+        <v>97</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="E63" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
+        <v>185</v>
+      </c>
+      <c r="F63" s="7" t="str">
+        <f>CONCATENATE("http://", E63)</f>
+        <v>http://192.168.206.7</v>
+      </c>
+      <c r="G63" s="7"/>
       <c r="H63" s="21" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="K63" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="K63" s="12" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" s="6" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="6" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>190</v>
+        <v>88</v>
       </c>
       <c r="F64" s="7" t="str">
         <f>CONCATENATE("http://", E64)</f>
-        <v>http://192.168.206.7</v>
+        <v>http://192.168.0.192</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="21" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I64" s="9"/>
       <c r="J64" s="6" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="K64" s="12" t="s">
         <v>87</v>
@@ -3361,85 +3349,87 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="F65" s="7" t="str">
-        <f>CONCATENATE("http://", E65)</f>
-        <v>http://192.168.0.192</v>
-      </c>
-      <c r="G65" s="7"/>
+        <v>93</v>
+      </c>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
       <c r="H65" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I65" s="9"/>
       <c r="J65" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="K65" s="12" t="s">
-        <v>87</v>
+        <v>95</v>
+      </c>
+      <c r="K65" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="6" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="6" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
       <c r="H66" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="I66" s="9"/>
+        <v>173</v>
+      </c>
+      <c r="I66" s="9" t="s">
+        <v>278</v>
+      </c>
       <c r="J66" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="K66" s="6" t="s">
-        <v>92</v>
+        <v>102</v>
+      </c>
+      <c r="K66" s="12" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6"/>
+        <v>84</v>
+      </c>
+      <c r="F67" s="7" t="str">
+        <f>CONCATENATE("ftp://", E67)</f>
+        <v>ftp://192.168.0.189</v>
+      </c>
+      <c r="G67" s="7"/>
       <c r="H67" s="21" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="K67" s="12" t="s">
         <v>79</v>
@@ -3447,28 +3437,28 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F68" s="7" t="str">
         <f>CONCATENATE("ftp://", E68)</f>
-        <v>ftp://192.168.0.189</v>
+        <v>ftp://192.168.0.190</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="21" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="J68" s="6" t="s">
         <v>82</v>
@@ -3479,314 +3469,309 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="6" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F69" s="7" t="str">
-        <f>CONCATENATE("ftp://", E69)</f>
-        <v>ftp://192.168.0.190</v>
-      </c>
-      <c r="G69" s="7"/>
+        <f>CONCATENATE("http://", E69)</f>
+        <v>http://192.168.0.183</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>237</v>
+      </c>
       <c r="H69" s="21" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="K69" s="12" t="s">
-        <v>79</v>
+        <v>64</v>
+      </c>
+      <c r="K69" s="6" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" s="6" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="6" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="F70" s="7" t="str">
         <f>CONCATENATE("http://", E70)</f>
-        <v>http://192.168.0.183</v>
+        <v>http://192.168.0.193</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="H70" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="I70" s="9" t="s">
-        <v>282</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="I70" s="9"/>
       <c r="J70" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F71" s="7" t="str">
         <f>CONCATENATE("http://", E71)</f>
-        <v>http://192.168.0.193</v>
+        <v>http://192.168.0.194</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="H71" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I71" s="9"/>
       <c r="J71" s="6" t="s">
         <v>69</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B72" s="6"/>
       <c r="C72" s="6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F72" s="7" t="str">
         <f>CONCATENATE("http://", E72)</f>
-        <v>http://192.168.0.194</v>
+        <v>http://192.168.0.195</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="H72" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I72" s="9"/>
       <c r="J72" s="6" t="s">
         <v>69</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A73" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B73" s="6"/>
+      <c r="A73" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B73" s="5"/>
       <c r="C73" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F73" s="7" t="str">
-        <f>CONCATENATE("http://", E73)</f>
-        <v>http://192.168.0.195</v>
-      </c>
-      <c r="G73" s="7" t="s">
-        <v>242</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
       <c r="H73" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I73" s="9"/>
       <c r="J73" s="6" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="K73" s="6" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
-        <v>19</v>
+        <v>243</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="6" t="s">
-        <v>17</v>
+        <v>242</v>
       </c>
       <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
+      <c r="E74" s="6" t="s">
+        <v>241</v>
+      </c>
       <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
+      <c r="G74" s="22" t="s">
+        <v>240</v>
+      </c>
       <c r="H74" s="21" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I74" s="9"/>
       <c r="J74" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K74" s="6" t="s">
-        <v>16</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="K74" s="6"/>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B75" s="5"/>
-      <c r="C75" s="6" t="s">
-        <v>247</v>
-      </c>
+      <c r="C75" s="5"/>
       <c r="D75" s="6"/>
-      <c r="E75" s="6" t="s">
-        <v>246</v>
-      </c>
+      <c r="E75" s="6"/>
       <c r="F75" s="6"/>
-      <c r="G75" s="22" t="s">
-        <v>245</v>
-      </c>
+      <c r="G75" s="22"/>
       <c r="H75" s="21" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I75" s="9"/>
-      <c r="J75" s="6" t="s">
-        <v>249</v>
-      </c>
+      <c r="J75" s="6"/>
       <c r="K75" s="6"/>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
       <c r="D76" s="6"/>
-      <c r="E76" s="6"/>
+      <c r="E76" s="6" t="s">
+        <v>248</v>
+      </c>
       <c r="F76" s="6"/>
       <c r="G76" s="22"/>
-      <c r="H76" s="21" t="s">
-        <v>179</v>
-      </c>
+      <c r="H76" s="21"/>
       <c r="I76" s="9"/>
       <c r="J76" s="6"/>
       <c r="K76" s="6"/>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
       <c r="D77" s="6"/>
       <c r="E77" s="6" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F77" s="6"/>
-      <c r="G77" s="22"/>
-      <c r="H77" s="21"/>
+      <c r="G77" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="H77" s="21" t="s">
+        <v>173</v>
+      </c>
       <c r="I77" s="9"/>
-      <c r="J77" s="6"/>
+      <c r="J77" s="6" t="s">
+        <v>250</v>
+      </c>
       <c r="K77" s="6"/>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
       <c r="D78" s="6"/>
-      <c r="E78" s="6" t="s">
-        <v>254</v>
+      <c r="E78" s="15" t="s">
+        <v>253</v>
       </c>
       <c r="F78" s="6"/>
       <c r="G78" s="22" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="H78" s="21" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I78" s="9"/>
       <c r="J78" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K78" s="6"/>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B79" s="5"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="15" t="s">
-        <v>258</v>
+      <c r="C79" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>270</v>
       </c>
       <c r="F79" s="6"/>
-      <c r="G79" s="22" t="s">
-        <v>260</v>
+      <c r="G79" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="H79" s="21" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I79" s="9"/>
       <c r="J79" s="6" t="s">
-        <v>259</v>
+        <v>69</v>
       </c>
       <c r="K79" s="6"/>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B80" s="5"/>
       <c r="C80" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F80" s="6"/>
       <c r="G80" s="7" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="H80" s="21" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I80" s="9"/>
       <c r="J80" s="6" t="s">
@@ -3796,24 +3781,24 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B81" s="5"/>
       <c r="C81" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F81" s="6"/>
       <c r="G81" s="7" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="H81" s="21" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="6" t="s">
@@ -3823,53 +3808,30 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B82" s="5"/>
-      <c r="C82" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>40</v>
-      </c>
+      <c r="C82" s="5"/>
+      <c r="D82" s="6"/>
       <c r="E82" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F82" s="6"/>
-      <c r="G82" s="7" t="s">
-        <v>242</v>
+      <c r="G82" s="22" t="s">
+        <v>240</v>
       </c>
       <c r="H82" s="21" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I82" s="9"/>
       <c r="J82" s="6" t="s">
-        <v>69</v>
+        <v>276</v>
       </c>
       <c r="K82" s="6"/>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A83" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="B83" s="5"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="6"/>
-      <c r="E83" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="F83" s="6"/>
-      <c r="G83" s="22" t="s">
-        <v>245</v>
-      </c>
-      <c r="H83" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="I83" s="9"/>
-      <c r="J83" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="K83" s="6"/>
+      <c r="H83"/>
+      <c r="I83"/>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H84"/>
@@ -10527,30 +10489,25 @@
       <c r="H1747"/>
       <c r="I1747"/>
     </row>
-    <row r="1748" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1748"/>
-      <c r="I1748"/>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E51" r:id="rId1" xr:uid="{A67D0EEE-D14B-FD4B-A457-4A5F3CF70C05}"/>
-    <hyperlink ref="F64" r:id="rId2" display="http://192.169.0.112" xr:uid="{D2404E72-FA69-6648-ACE3-1F155CD355DD}"/>
-    <hyperlink ref="F70" r:id="rId3" display="http://192.169.0.112" xr:uid="{3F5BA59D-C194-FC49-9DCB-1F6B1CEAE85A}"/>
-    <hyperlink ref="F61" r:id="rId4" display="http://192.169.0.112" xr:uid="{80722F7C-2A8A-4A43-A5D3-BCFFE30BBC25}"/>
-    <hyperlink ref="F60" r:id="rId5" display="http://192.169.0.112" xr:uid="{7AFCBEF6-4325-D24D-B711-037F038931A3}"/>
-    <hyperlink ref="F13:F15" r:id="rId6" display="http://192.169.0.112" xr:uid="{40E3D96B-FF32-1147-AA42-7A87222DBFE8}"/>
-    <hyperlink ref="F4:F8" r:id="rId7" display="http://192.169.0.112" xr:uid="{EFA55FC0-66D6-5341-B122-15ED7113DE4A}"/>
-    <hyperlink ref="F65" r:id="rId8" display="http://192.169.0.112" xr:uid="{206574CD-0A69-6A49-BF19-8696C0B23754}"/>
-    <hyperlink ref="F21:F23" r:id="rId9" display="http://192.169.0.112" xr:uid="{ABAD7AC1-281C-974C-8BD8-79EEDE34950A}"/>
-    <hyperlink ref="F68" r:id="rId10" display="http://192.169.0.112" xr:uid="{2FA0DCAE-2864-024C-9351-79F3CBFD408D}"/>
-    <hyperlink ref="F69" r:id="rId11" display="http://192.169.0.112" xr:uid="{0E717F48-1348-0440-9A96-15E3AB13C8AE}"/>
-    <hyperlink ref="F2" r:id="rId12" display="http://192.169.0.112" xr:uid="{B7709A6B-F68E-6F45-9F1A-5CCF46F3BFD7}"/>
+    <hyperlink ref="F63" r:id="rId1" display="http://192.169.0.112" xr:uid="{D2404E72-FA69-6648-ACE3-1F155CD355DD}"/>
+    <hyperlink ref="F69" r:id="rId2" display="http://192.169.0.112" xr:uid="{3F5BA59D-C194-FC49-9DCB-1F6B1CEAE85A}"/>
+    <hyperlink ref="F60" r:id="rId3" display="http://192.169.0.112" xr:uid="{80722F7C-2A8A-4A43-A5D3-BCFFE30BBC25}"/>
+    <hyperlink ref="F59" r:id="rId4" display="http://192.169.0.112" xr:uid="{7AFCBEF6-4325-D24D-B711-037F038931A3}"/>
+    <hyperlink ref="F13:F15" r:id="rId5" display="http://192.169.0.112" xr:uid="{40E3D96B-FF32-1147-AA42-7A87222DBFE8}"/>
+    <hyperlink ref="F4:F8" r:id="rId6" display="http://192.169.0.112" xr:uid="{EFA55FC0-66D6-5341-B122-15ED7113DE4A}"/>
+    <hyperlink ref="F64" r:id="rId7" display="http://192.169.0.112" xr:uid="{206574CD-0A69-6A49-BF19-8696C0B23754}"/>
+    <hyperlink ref="F21:F23" r:id="rId8" display="http://192.169.0.112" xr:uid="{ABAD7AC1-281C-974C-8BD8-79EEDE34950A}"/>
+    <hyperlink ref="F67" r:id="rId9" display="http://192.169.0.112" xr:uid="{2FA0DCAE-2864-024C-9351-79F3CBFD408D}"/>
+    <hyperlink ref="F68" r:id="rId10" display="http://192.169.0.112" xr:uid="{0E717F48-1348-0440-9A96-15E3AB13C8AE}"/>
+    <hyperlink ref="F2" r:id="rId11" display="http://192.169.0.112" xr:uid="{B7709A6B-F68E-6F45-9F1A-5CCF46F3BFD7}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <legacyDrawing r:id="rId13"/>
+  <legacyDrawing r:id="rId12"/>
   <tableParts count="1">
-    <tablePart r:id="rId14"/>
+    <tablePart r:id="rId13"/>
   </tableParts>
 </worksheet>
 </file>
--- a/network.xlsx
+++ b/network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA31CF37-BC5D-744B-9006-89A0AE02ED27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B885147-4BDA-A94C-B58B-86DCE4AA399D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8320" yWindow="1460" windowWidth="21920" windowHeight="18180" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="294">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -389,9 +389,6 @@
     <t>ZVKU-A003</t>
   </si>
   <si>
-    <t>00:1d:56:03:81:45</t>
-  </si>
-  <si>
     <t>Matrix Switch</t>
   </si>
   <si>
@@ -653,9 +650,6 @@
     <t>USB Nic</t>
   </si>
   <si>
-    <t>192.168.206.7</t>
-  </si>
-  <si>
     <t>192.168.0.210</t>
   </si>
   <si>
@@ -933,6 +927,57 @@
   </si>
   <si>
     <t>KB0041</t>
+  </si>
+  <si>
+    <t>2603-1203</t>
+  </si>
+  <si>
+    <t>98-BA-5F-91-07-6A</t>
+  </si>
+  <si>
+    <t>Omada</t>
+  </si>
+  <si>
+    <t>192.168.201.105</t>
+  </si>
+  <si>
+    <t>7C-2E-0D-A8-52-4F</t>
+  </si>
+  <si>
+    <t>7C-2E-0D-20-68-69</t>
+  </si>
+  <si>
+    <t>00-1D-56-04-CC-E3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:1d:56:03:81:45 </t>
+  </si>
+  <si>
+    <t>Unknown Mac</t>
+  </si>
+  <si>
+    <t>192.168.201.110</t>
+  </si>
+  <si>
+    <t>2411-1330</t>
+  </si>
+  <si>
+    <t>2507-1000</t>
+  </si>
+  <si>
+    <t>D0-C8-57-81-F2-19</t>
+  </si>
+  <si>
+    <t>NDI</t>
+  </si>
+  <si>
+    <t>D0-C8-57-82-74-B9</t>
+  </si>
+  <si>
+    <t>192.168.204.32</t>
+  </si>
+  <si>
+    <t>192.168.204.31</t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1150,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1134,6 +1179,10 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1417,8 +1466,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K82" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K82" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K86" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K86" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K73">
     <sortCondition ref="A2:A73"/>
     <sortCondition ref="B2:B73"/>
@@ -1757,50 +1806,50 @@
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>149</v>
-      </c>
       <c r="K1" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F2" s="7" t="str">
         <f>CONCATENATE("http://", E2)</f>
@@ -1808,126 +1857,126 @@
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K2" s="6"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K3" s="6"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K4" s="6"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>197</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>199</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="K5" s="6"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K6" s="6"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="H7" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="6"/>
@@ -1935,18 +1984,20 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B8" s="5"/>
-      <c r="C8" s="6"/>
+      <c r="C8" s="6" t="s">
+        <v>281</v>
+      </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="6"/>
@@ -1954,18 +2005,20 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B9" s="5"/>
-      <c r="C9" s="6"/>
+      <c r="C9" s="6" t="s">
+        <v>282</v>
+      </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="6"/>
@@ -1973,170 +2026,170 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K10" s="6"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K12" s="6"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K13" s="6"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K14" s="6"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="K15" s="6"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K16" s="12" t="s">
         <v>79</v>
@@ -2155,7 +2208,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="6" t="s">
@@ -2167,22 +2220,22 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="6"/>
@@ -2196,12 +2249,12 @@
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="6" t="s">
@@ -2214,21 +2267,21 @@
         <v>7</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="6"/>
@@ -2239,21 +2292,21 @@
         <v>7</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
       <c r="H21" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I21" s="9"/>
       <c r="J21" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K21" s="6"/>
     </row>
@@ -2262,7 +2315,7 @@
         <v>7</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="6"/>
@@ -2270,7 +2323,7 @@
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
       <c r="H22" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="6"/>
@@ -2293,7 +2346,7 @@
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I23" s="9"/>
       <c r="J23" s="6" t="s">
@@ -2306,25 +2359,25 @@
         <v>1</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I24" s="9"/>
       <c r="J24" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K24" s="6"/>
     </row>
@@ -2333,25 +2386,25 @@
         <v>1</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I25" s="9"/>
       <c r="J25" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K25" s="6"/>
     </row>
@@ -2360,83 +2413,83 @@
         <v>1</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I26" s="9"/>
       <c r="J26" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K26" s="6"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
       <c r="H27" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I27" s="9"/>
       <c r="J27" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K27" s="6"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I28" s="9"/>
       <c r="J28" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K28" s="6"/>
     </row>
     <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -2445,36 +2498,36 @@
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
       <c r="H29" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="K29" s="6"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
       <c r="H30" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K30" s="12"/>
     </row>
@@ -2489,7 +2542,7 @@
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="6" t="s">
@@ -2508,7 +2561,7 @@
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="6" t="s">
@@ -2527,7 +2580,7 @@
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I33" s="9"/>
       <c r="J33" s="6" t="s">
@@ -2546,7 +2599,7 @@
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I34" s="9"/>
       <c r="J34" s="6" t="s">
@@ -2565,7 +2618,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I35" s="9"/>
       <c r="J35" s="6" t="s">
@@ -2586,7 +2639,7 @@
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="6" t="s">
@@ -2605,7 +2658,7 @@
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
       <c r="H37" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I37" s="9"/>
       <c r="J37" s="6" t="s">
@@ -2624,7 +2677,7 @@
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
       <c r="H38" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="6" t="s">
@@ -2643,7 +2696,7 @@
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
       <c r="H39" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I39" s="9"/>
       <c r="J39" s="6" t="s">
@@ -2657,27 +2710,27 @@
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F40" s="7" t="str">
         <f>CONCATENATE("http://", E40)</f>
         <v>http://192.168.0.22</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I40" s="9"/>
       <c r="J40" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K40" s="12"/>
     </row>
@@ -2687,27 +2740,27 @@
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F41" s="7" t="str">
         <f>CONCATENATE("http://", E41)</f>
         <v>http://192.168.0.23</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I41" s="9"/>
       <c r="J41" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K41" s="12"/>
     </row>
@@ -2717,27 +2770,27 @@
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F42" s="7" t="str">
         <f>CONCATENATE("http://", E42)</f>
         <v>http://192.168.0.24</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I42" s="9"/>
       <c r="J42" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K42" s="12"/>
     </row>
@@ -2747,27 +2800,27 @@
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F43" s="7" t="str">
         <f>CONCATENATE("http://", E43)</f>
         <v>http://192.168.0.25</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K43" s="6"/>
     </row>
@@ -2777,27 +2830,27 @@
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F44" s="7" t="str">
         <f>CONCATENATE("http://", E44)</f>
         <v>http://192.168.0.26</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I44" s="9"/>
       <c r="J44" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K44" s="12"/>
     </row>
@@ -2806,7 +2859,7 @@
         <v>46</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>45</v>
@@ -2820,14 +2873,14 @@
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="6" t="s">
         <v>42</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
@@ -2835,7 +2888,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="6"/>
@@ -2843,11 +2896,11 @@
       <c r="F46" s="6"/>
       <c r="G46" s="7"/>
       <c r="H46" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I46" s="9"/>
       <c r="J46" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K46" s="6"/>
     </row>
@@ -2856,7 +2909,7 @@
         <v>43</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>41</v>
@@ -2870,14 +2923,14 @@
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
       <c r="H47" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I47" s="9"/>
       <c r="J47" s="6" t="s">
         <v>42</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
@@ -2885,7 +2938,7 @@
         <v>43</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="6"/>
@@ -2893,11 +2946,11 @@
       <c r="F48" s="6"/>
       <c r="G48" s="7"/>
       <c r="H48" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I48" s="9"/>
       <c r="J48" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K48" s="6"/>
     </row>
@@ -2930,16 +2983,16 @@
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
       <c r="H50" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="K50" s="6"/>
     </row>
@@ -2955,15 +3008,15 @@
         <v>40</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
       <c r="H51" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J51" s="6" t="s">
         <v>49</v>
@@ -2984,15 +3037,15 @@
         <v>40</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
       <c r="H52" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J52" s="6" t="s">
         <v>49</v>
@@ -3013,15 +3066,15 @@
         <v>40</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="6"/>
       <c r="H53" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J53" s="6" t="s">
         <v>49</v>
@@ -3042,15 +3095,15 @@
         <v>40</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
       <c r="H54" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J54" s="6" t="s">
         <v>49</v>
@@ -3078,10 +3131,10 @@
         <v>http://192.168.0.197:8080</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="6" t="s">
@@ -3091,17 +3144,17 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F56" s="7" t="str">
         <f>CONCATENATE("http://", E56)</f>
@@ -3109,11 +3162,11 @@
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I56" s="9"/>
       <c r="J56" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>75</v>
@@ -3121,17 +3174,17 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F57" s="7" t="str">
         <f>CONCATENATE("http://", E57)</f>
@@ -3139,11 +3192,11 @@
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>71</v>
@@ -3151,17 +3204,17 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B58" s="6"/>
       <c r="C58" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F58" s="7" t="str">
         <f>CONCATENATE("http://", E58)</f>
@@ -3169,13 +3222,13 @@
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>66</v>
@@ -3183,17 +3236,17 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F59" s="7" t="str">
         <f>CONCATENATE("http://", E59)</f>
@@ -3201,29 +3254,29 @@
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F60" s="7" t="str">
         <f>CONCATENATE("http://", E60)</f>
@@ -3231,19 +3284,19 @@
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I60" s="9"/>
       <c r="J60" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="6" t="s">
@@ -3251,12 +3304,12 @@
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
       <c r="H61" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="6" t="s">
@@ -3266,52 +3319,54 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="6"/>
       <c r="H62" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K62" s="6"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="6" t="s">
-        <v>97</v>
+        <v>283</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>185</v>
+        <v>286</v>
       </c>
       <c r="F63" s="7" t="str">
         <f>CONCATENATE("http://", E63)</f>
-        <v>http://192.168.206.7</v>
-      </c>
-      <c r="G63" s="7"/>
+        <v>http://192.168.201.110</v>
+      </c>
+      <c r="G63" s="27" t="s">
+        <v>238</v>
+      </c>
       <c r="H63" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K63" s="12" t="s">
         <v>87</v>
@@ -3337,7 +3392,7 @@
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I64" s="9"/>
       <c r="J64" s="6" t="s">
@@ -3364,7 +3419,7 @@
       <c r="F65" s="6"/>
       <c r="G65" s="6"/>
       <c r="H65" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I65" s="9"/>
       <c r="J65" s="6" t="s">
@@ -3376,28 +3431,28 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
       <c r="H66" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K66" s="12" t="s">
         <v>79</v>
@@ -3423,10 +3478,10 @@
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J67" s="6" t="s">
         <v>82</v>
@@ -3455,10 +3510,10 @@
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J68" s="6" t="s">
         <v>82</v>
@@ -3486,13 +3541,13 @@
         <v>http://192.168.0.183</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H69" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J69" s="6" t="s">
         <v>64</v>
@@ -3520,10 +3575,10 @@
         <v>http://192.168.0.193</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H70" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I70" s="9"/>
       <c r="J70" s="6" t="s">
@@ -3552,10 +3607,10 @@
         <v>http://192.168.0.194</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H71" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I71" s="9"/>
       <c r="J71" s="6" t="s">
@@ -3584,10 +3639,10 @@
         <v>http://192.168.0.195</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H72" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I72" s="9"/>
       <c r="J72" s="6" t="s">
@@ -3610,7 +3665,7 @@
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
       <c r="H73" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I73" s="9"/>
       <c r="J73" s="6" t="s">
@@ -3622,32 +3677,32 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F74" s="6"/>
       <c r="G74" s="22" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H74" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I74" s="9"/>
       <c r="J74" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="K74" s="6"/>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -3656,7 +3711,7 @@
       <c r="F75" s="6"/>
       <c r="G75" s="22"/>
       <c r="H75" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="6"/>
@@ -3664,13 +3719,13 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
       <c r="D76" s="6"/>
       <c r="E76" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F76" s="6"/>
       <c r="G76" s="22"/>
@@ -3681,70 +3736,70 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
       <c r="D77" s="6"/>
       <c r="E77" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F77" s="6"/>
       <c r="G77" s="22" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H77" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K77" s="6"/>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
       <c r="D78" s="6"/>
       <c r="E78" s="15" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F78" s="6"/>
       <c r="G78" s="22" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H78" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I78" s="9"/>
       <c r="J78" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="K78" s="6"/>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B79" s="5"/>
       <c r="C79" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F79" s="6"/>
       <c r="G79" s="7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H79" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I79" s="9"/>
       <c r="J79" s="6" t="s">
@@ -3754,24 +3809,24 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B80" s="5"/>
       <c r="C80" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F80" s="6"/>
       <c r="G80" s="7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H80" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I80" s="9"/>
       <c r="J80" s="6" t="s">
@@ -3781,24 +3836,24 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B81" s="5"/>
       <c r="C81" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F81" s="6"/>
       <c r="G81" s="7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H81" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="6" t="s">
@@ -3808,42 +3863,116 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
       <c r="D82" s="6"/>
       <c r="E82" s="6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F82" s="6"/>
       <c r="G82" s="22" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H82" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I82" s="9"/>
       <c r="J82" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K82" s="6"/>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H83"/>
-      <c r="I83"/>
+      <c r="A83" s="24" t="s">
+        <v>277</v>
+      </c>
+      <c r="B83" s="24"/>
+      <c r="C83" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="D83" s="25"/>
+      <c r="E83" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="F83" s="25"/>
+      <c r="G83" s="22"/>
+      <c r="H83" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I83" s="26"/>
+      <c r="J83" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="K83" s="25"/>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H84"/>
-      <c r="I84"/>
+      <c r="A84" s="24"/>
+      <c r="B84" s="24"/>
+      <c r="C84" s="24" t="s">
+        <v>284</v>
+      </c>
+      <c r="D84" s="25"/>
+      <c r="E84" s="25"/>
+      <c r="F84" s="25"/>
+      <c r="G84" s="22"/>
+      <c r="H84" s="21"/>
+      <c r="I84" s="26"/>
+      <c r="J84" s="25"/>
+      <c r="K84" s="25" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H85"/>
-      <c r="I85"/>
+      <c r="A85" s="24" t="s">
+        <v>287</v>
+      </c>
+      <c r="B85" s="24"/>
+      <c r="C85" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="D85" s="25"/>
+      <c r="E85" s="25" t="s">
+        <v>292</v>
+      </c>
+      <c r="F85" s="25"/>
+      <c r="G85" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="H85" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I85" s="26"/>
+      <c r="J85" s="25" t="s">
+        <v>290</v>
+      </c>
+      <c r="K85" s="25"/>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H86"/>
-      <c r="I86"/>
+      <c r="A86" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="B86" s="24"/>
+      <c r="C86" s="24" t="s">
+        <v>291</v>
+      </c>
+      <c r="D86" s="25"/>
+      <c r="E86" s="25" t="s">
+        <v>293</v>
+      </c>
+      <c r="F86" s="25"/>
+      <c r="G86" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="H86" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I86" s="26"/>
+      <c r="J86" s="25" t="s">
+        <v>290</v>
+      </c>
+      <c r="K86" s="25"/>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H87"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B885147-4BDA-A94C-B58B-86DCE4AA399D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26EE30E-47C6-0C48-BFD4-6BD8600B8406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8320" yWindow="1460" windowWidth="21920" windowHeight="18180" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="298">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -978,6 +978,18 @@
   </si>
   <si>
     <t>192.168.204.31</t>
+  </si>
+  <si>
+    <t>14-3F-A6-B8-EA-5D</t>
+  </si>
+  <si>
+    <t>192.168.207.100</t>
+  </si>
+  <si>
+    <t>2310-1700</t>
+  </si>
+  <si>
+    <t>Lobby TV</t>
   </si>
 </sst>
 </file>
@@ -1179,10 +1191,10 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1466,8 +1478,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K86" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K86" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K87" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K87" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K73">
     <sortCondition ref="A2:A73"/>
     <sortCondition ref="B2:B73"/>
@@ -3358,7 +3370,7 @@
         <f>CONCATENATE("http://", E63)</f>
         <v>http://192.168.201.110</v>
       </c>
-      <c r="G63" s="27" t="s">
+      <c r="G63" s="24" t="s">
         <v>238</v>
       </c>
       <c r="H63" s="21" t="s">
@@ -3885,98 +3897,117 @@
       <c r="K82" s="6"/>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A83" s="24" t="s">
+      <c r="A83" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="B83" s="24"/>
+      <c r="B83" s="5"/>
       <c r="C83" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="D83" s="25"/>
-      <c r="E83" s="25" t="s">
+      <c r="D83" s="6"/>
+      <c r="E83" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="F83" s="25"/>
+      <c r="F83" s="6"/>
       <c r="G83" s="22"/>
       <c r="H83" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="I83" s="26"/>
-      <c r="J83" s="25" t="s">
+      <c r="I83" s="9"/>
+      <c r="J83" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="K83" s="25"/>
+      <c r="K83" s="6"/>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A84" s="24"/>
-      <c r="B84" s="24"/>
-      <c r="C84" s="24" t="s">
+      <c r="A84" s="5"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="D84" s="25"/>
-      <c r="E84" s="25"/>
-      <c r="F84" s="25"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="6"/>
       <c r="G84" s="22"/>
       <c r="H84" s="21"/>
-      <c r="I84" s="26"/>
-      <c r="J84" s="25"/>
-      <c r="K84" s="25" t="s">
+      <c r="I84" s="9"/>
+      <c r="J84" s="6"/>
+      <c r="K84" s="6" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A85" s="24" t="s">
+      <c r="A85" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="B85" s="24"/>
-      <c r="C85" s="24" t="s">
+      <c r="B85" s="5"/>
+      <c r="C85" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="D85" s="25"/>
-      <c r="E85" s="25" t="s">
+      <c r="D85" s="6"/>
+      <c r="E85" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="F85" s="25"/>
+      <c r="F85" s="6"/>
       <c r="G85" s="22" t="s">
         <v>238</v>
       </c>
       <c r="H85" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I85" s="26"/>
-      <c r="J85" s="25" t="s">
+      <c r="I85" s="9"/>
+      <c r="J85" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="K85" s="25"/>
+      <c r="K85" s="6"/>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A86" s="24" t="s">
+      <c r="A86" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="B86" s="24"/>
-      <c r="C86" s="24" t="s">
+      <c r="B86" s="5"/>
+      <c r="C86" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="D86" s="25"/>
-      <c r="E86" s="25" t="s">
+      <c r="D86" s="6"/>
+      <c r="E86" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="F86" s="25"/>
+      <c r="F86" s="6"/>
       <c r="G86" s="22" t="s">
         <v>238</v>
       </c>
       <c r="H86" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I86" s="26"/>
-      <c r="J86" s="25" t="s">
+      <c r="I86" s="9"/>
+      <c r="J86" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="K86" s="25"/>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H87"/>
-      <c r="I87"/>
+      <c r="K86" s="6"/>
+    </row>
+    <row r="87" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A87" s="25" t="s">
+        <v>296</v>
+      </c>
+      <c r="B87" s="25"/>
+      <c r="C87" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="D87" s="26"/>
+      <c r="E87" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="F87" s="26"/>
+      <c r="G87" s="22"/>
+      <c r="H87" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I87" s="27"/>
+      <c r="J87" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="K87" s="26"/>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H88"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26EE30E-47C6-0C48-BFD4-6BD8600B8406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8866A086-482F-7046-9EAE-D859752DDC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8320" yWindow="1460" windowWidth="21920" windowHeight="18180" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="300">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -990,6 +990,12 @@
   </si>
   <si>
     <t>Lobby TV</t>
+  </si>
+  <si>
+    <t>2603-1206</t>
+  </si>
+  <si>
+    <t>192.168.201.103</t>
   </si>
 </sst>
 </file>
@@ -1110,7 +1116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1157,12 +1163,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1195,6 +1210,7 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1478,8 +1494,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K87" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K87" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K88" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K88" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K73">
     <sortCondition ref="A2:A73"/>
     <sortCondition ref="B2:B73"/>
@@ -3986,7 +4002,7 @@
       </c>
       <c r="K86" s="6"/>
     </row>
-    <row r="87" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A87" s="25" t="s">
         <v>296</v>
       </c>
@@ -4009,9 +4025,24 @@
       </c>
       <c r="K87" s="26"/>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H88"/>
-      <c r="I88"/>
+    <row r="88" spans="1:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="28" t="s">
+        <v>298</v>
+      </c>
+      <c r="B88" s="25"/>
+      <c r="C88" s="25"/>
+      <c r="D88" s="26"/>
+      <c r="E88" s="26" t="s">
+        <v>299</v>
+      </c>
+      <c r="F88" s="26"/>
+      <c r="G88" s="22"/>
+      <c r="H88" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I88" s="27"/>
+      <c r="J88" s="26"/>
+      <c r="K88" s="26"/>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H89"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8866A086-482F-7046-9EAE-D859752DDC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3047F815-4589-0C4C-B5FE-8230DD344A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8320" yWindow="1460" windowWidth="21920" windowHeight="18180" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
+    <workbookView xWindow="1880" yWindow="1460" windowWidth="28360" windowHeight="18180" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
   <sheets>
     <sheet name="network" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="385">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -996,6 +996,261 @@
   </si>
   <si>
     <t>192.168.201.103</t>
+  </si>
+  <si>
+    <t>00-21-84-03-C3-DC</t>
+  </si>
+  <si>
+    <t>192.168.200.68</t>
+  </si>
+  <si>
+    <t>AV Network</t>
+  </si>
+  <si>
+    <t>AV Amp 2603-1200</t>
+  </si>
+  <si>
+    <t>00-04-C4-0F-E3-C3</t>
+  </si>
+  <si>
+    <t>00-1D-C1-9C-47-33</t>
+  </si>
+  <si>
+    <t>192.168.200.102</t>
+  </si>
+  <si>
+    <t>00-04-C4-11-3C-B6</t>
+  </si>
+  <si>
+    <t>00-21-84-03-C3-D8</t>
+  </si>
+  <si>
+    <t>192.168.200.69</t>
+  </si>
+  <si>
+    <t>00-21-84-03-7F-5C</t>
+  </si>
+  <si>
+    <t>192.168.200.61</t>
+  </si>
+  <si>
+    <t>00-1D-C1-9B-6C-4D</t>
+  </si>
+  <si>
+    <t>192.168.200.107</t>
+  </si>
+  <si>
+    <t>00-1D-C1-9A-6E-02</t>
+  </si>
+  <si>
+    <t>192.168.200.113</t>
+  </si>
+  <si>
+    <t>00-21-84-03-7F-32</t>
+  </si>
+  <si>
+    <t>192.168.200.62</t>
+  </si>
+  <si>
+    <t>00-04-C4-13-E2-61</t>
+  </si>
+  <si>
+    <t>00-1D-C1-9A-70-3A</t>
+  </si>
+  <si>
+    <t>192.168.200.108</t>
+  </si>
+  <si>
+    <t>00-04-C4-14-A2-0F</t>
+  </si>
+  <si>
+    <t>00-21-84-03-7F-31</t>
+  </si>
+  <si>
+    <t>192.168.200.63</t>
+  </si>
+  <si>
+    <t>00-21-84-03-7F-5A</t>
+  </si>
+  <si>
+    <t>192.168.200.64</t>
+  </si>
+  <si>
+    <t>00-0C-15-06-B9-31</t>
+  </si>
+  <si>
+    <t>192.168.206.6</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>00-21-84-03-7F-5B</t>
+  </si>
+  <si>
+    <t>192.168.200.65</t>
+  </si>
+  <si>
+    <t>00-21-84-03-7F-34</t>
+  </si>
+  <si>
+    <t>192.168.200.66</t>
+  </si>
+  <si>
+    <t>00-21-84-03-85-94</t>
+  </si>
+  <si>
+    <t>192.168.200.67</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>00-60-74-EE-53-EF</t>
+  </si>
+  <si>
+    <t>00-1D-C1-51-73-2D</t>
+  </si>
+  <si>
+    <t>14-98-77-82-73-BD</t>
+  </si>
+  <si>
+    <t>A8-6E-84-07-E5-B1</t>
+  </si>
+  <si>
+    <t>34-1B-22-84-24-6B</t>
+  </si>
+  <si>
+    <t>192.168.201.100</t>
+  </si>
+  <si>
+    <t>AV Balcony 2603-1203</t>
+  </si>
+  <si>
+    <t>ZVIU-G001 resi</t>
+  </si>
+  <si>
+    <t>34-1B-22-84-24-57</t>
+  </si>
+  <si>
+    <t>192.168.201.101</t>
+  </si>
+  <si>
+    <t>A4-FC-14-28-2E-B6</t>
+  </si>
+  <si>
+    <t>00-1D-C1-52-94-50</t>
+  </si>
+  <si>
+    <t>TVs</t>
+  </si>
+  <si>
+    <t>2507-0700-BMD-VideoHub</t>
+  </si>
+  <si>
+    <t>2601-2800-BMD-Cons</t>
+  </si>
+  <si>
+    <t>20-A5-CB-CE-4E-B8</t>
+  </si>
+  <si>
+    <t>AV FoH 2603-1201</t>
+  </si>
+  <si>
+    <t>AV Booth TSC</t>
+  </si>
+  <si>
+    <t>00-60-74-ED-D0-97</t>
+  </si>
+  <si>
+    <t>00-04-C4-14-70-C8</t>
+  </si>
+  <si>
+    <t>00-1D-C1-54-00-59</t>
+  </si>
+  <si>
+    <t>klang-KRB14486</t>
+  </si>
+  <si>
+    <t>00-04-C4-31-29-BA</t>
+  </si>
+  <si>
+    <t>192.168.200.199</t>
+  </si>
+  <si>
+    <t>AV Stage 2603-1202</t>
+  </si>
+  <si>
+    <t>klang-KRB14514</t>
+  </si>
+  <si>
+    <t>00-04-C4-31-29-D6</t>
+  </si>
+  <si>
+    <t>192.168.200.123</t>
+  </si>
+  <si>
+    <t>klang-KRB14506</t>
+  </si>
+  <si>
+    <t>00-04-C4-31-29-CE</t>
+  </si>
+  <si>
+    <t>192.168.200.149</t>
+  </si>
+  <si>
+    <t>klang-KRB14070</t>
+  </si>
+  <si>
+    <t>00-04-C4-31-28-1A</t>
+  </si>
+  <si>
+    <t>192.168.200.150</t>
+  </si>
+  <si>
+    <t>klang-KRB14513</t>
+  </si>
+  <si>
+    <t>00-04-C4-31-29-D5</t>
+  </si>
+  <si>
+    <t>192.168.200.100</t>
+  </si>
+  <si>
+    <t>klang-KRB14510</t>
+  </si>
+  <si>
+    <t>00-04-C4-31-29-D2</t>
+  </si>
+  <si>
+    <t>192.168.200.147</t>
+  </si>
+  <si>
+    <t>klang-KRB14415</t>
+  </si>
+  <si>
+    <t>00-04-C4-31-29-73</t>
+  </si>
+  <si>
+    <t>192.168.200.138</t>
+  </si>
+  <si>
+    <t>klang-KRB14512</t>
+  </si>
+  <si>
+    <t>00-04-C4-31-29-D4</t>
+  </si>
+  <si>
+    <t>192.168.200.130</t>
+  </si>
+  <si>
+    <t>klang-KRB14072</t>
+  </si>
+  <si>
+    <t>00-04-C4-31-28-1C</t>
+  </si>
+  <si>
+    <t>192.168.200.148</t>
   </si>
 </sst>
 </file>
@@ -1090,7 +1345,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1115,8 +1370,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor theme="8" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1172,12 +1433,80 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="8" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="8" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="8" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="8" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="8" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="8" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="8" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="8" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="8" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="8" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="8" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="8" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="8" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1211,6 +1540,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1494,8 +1835,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K88" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K88" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K157" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K157" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K73">
     <sortCondition ref="A2:A73"/>
     <sortCondition ref="B2:B73"/>
@@ -1814,11 +2155,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC7A309-0B6A-4549-9590-6CFCF97D2DB0}">
-  <dimension ref="A1:K1747"/>
+  <dimension ref="A1:K1744"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -4045,290 +4386,1433 @@
       <c r="K88" s="26"/>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H89"/>
-      <c r="I89"/>
+      <c r="A89" s="25"/>
+      <c r="B89" s="31"/>
+      <c r="C89" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="D89" s="26"/>
+      <c r="E89" s="32" t="s">
+        <v>301</v>
+      </c>
+      <c r="F89" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="G89" s="22"/>
+      <c r="H89" s="21"/>
+      <c r="I89" s="27"/>
+      <c r="J89" s="26"/>
+      <c r="K89" s="26"/>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H90"/>
-      <c r="I90"/>
+      <c r="A90" s="5"/>
+      <c r="B90" s="33"/>
+      <c r="C90" s="34" t="s">
+        <v>304</v>
+      </c>
+      <c r="D90" s="6"/>
+      <c r="E90" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="F90" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="G90" s="7"/>
+      <c r="H90" s="8"/>
+      <c r="I90" s="9"/>
+      <c r="J90" s="6"/>
+      <c r="K90" s="6"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H91"/>
-      <c r="I91"/>
+      <c r="A91" s="5"/>
+      <c r="B91" s="29"/>
+      <c r="C91" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="D91" s="6"/>
+      <c r="E91" s="30" t="s">
+        <v>306</v>
+      </c>
+      <c r="F91" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="G91" s="7"/>
+      <c r="H91" s="8"/>
+      <c r="I91" s="9"/>
+      <c r="J91" s="6"/>
+      <c r="K91" s="6"/>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H92"/>
-      <c r="I92"/>
+      <c r="A92" s="5"/>
+      <c r="B92" s="33"/>
+      <c r="C92" s="34" t="s">
+        <v>307</v>
+      </c>
+      <c r="D92" s="6"/>
+      <c r="E92" s="34" t="s">
+        <v>198</v>
+      </c>
+      <c r="F92" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="G92" s="7"/>
+      <c r="H92" s="8"/>
+      <c r="I92" s="9"/>
+      <c r="J92" s="6"/>
+      <c r="K92" s="6"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H93"/>
-      <c r="I93"/>
+      <c r="A93" s="5"/>
+      <c r="B93" s="29"/>
+      <c r="C93" s="30" t="s">
+        <v>308</v>
+      </c>
+      <c r="D93" s="6"/>
+      <c r="E93" s="30" t="s">
+        <v>309</v>
+      </c>
+      <c r="F93" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="G93" s="7"/>
+      <c r="H93" s="8"/>
+      <c r="I93" s="9"/>
+      <c r="J93" s="6"/>
+      <c r="K93" s="6"/>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H94"/>
-      <c r="I94"/>
+      <c r="A94" s="5"/>
+      <c r="B94" s="33"/>
+      <c r="C94" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="D94" s="6"/>
+      <c r="E94" s="34" t="s">
+        <v>311</v>
+      </c>
+      <c r="F94" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="G94" s="7"/>
+      <c r="H94" s="8"/>
+      <c r="I94" s="9"/>
+      <c r="J94" s="6"/>
+      <c r="K94" s="6"/>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H95"/>
-      <c r="I95"/>
+      <c r="A95" s="5"/>
+      <c r="B95" s="29"/>
+      <c r="C95" s="30" t="s">
+        <v>312</v>
+      </c>
+      <c r="D95" s="6"/>
+      <c r="E95" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="F95" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="G95" s="7"/>
+      <c r="H95" s="8"/>
+      <c r="I95" s="9"/>
+      <c r="J95" s="6"/>
+      <c r="K95" s="6"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H96"/>
-      <c r="I96"/>
-    </row>
-    <row r="97" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H97"/>
-      <c r="I97"/>
-    </row>
-    <row r="98" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H98"/>
-      <c r="I98"/>
-    </row>
-    <row r="99" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H99"/>
-      <c r="I99"/>
-    </row>
-    <row r="100" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H100"/>
-      <c r="I100"/>
-    </row>
-    <row r="101" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H101"/>
-      <c r="I101"/>
-    </row>
-    <row r="102" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H102"/>
-      <c r="I102"/>
-    </row>
-    <row r="103" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H103"/>
-      <c r="I103"/>
-    </row>
-    <row r="104" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H104"/>
-      <c r="I104"/>
-    </row>
-    <row r="105" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H105"/>
-      <c r="I105"/>
-    </row>
-    <row r="106" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H106"/>
-      <c r="I106"/>
-    </row>
-    <row r="107" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H107"/>
-      <c r="I107"/>
-    </row>
-    <row r="108" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H108"/>
-      <c r="I108"/>
-    </row>
-    <row r="109" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H109"/>
-      <c r="I109"/>
-    </row>
-    <row r="110" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H110"/>
-      <c r="I110"/>
-    </row>
-    <row r="111" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H111"/>
-      <c r="I111"/>
-    </row>
-    <row r="112" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H112"/>
-      <c r="I112"/>
-    </row>
-    <row r="113" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H113"/>
-      <c r="I113"/>
-    </row>
-    <row r="114" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H114"/>
-      <c r="I114"/>
-    </row>
-    <row r="115" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H115"/>
-      <c r="I115"/>
-    </row>
-    <row r="116" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H116"/>
-      <c r="I116"/>
-    </row>
-    <row r="117" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H117"/>
-      <c r="I117"/>
-    </row>
-    <row r="118" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H118"/>
-      <c r="I118"/>
-    </row>
-    <row r="119" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H119"/>
-      <c r="I119"/>
-    </row>
-    <row r="120" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H120"/>
-      <c r="I120"/>
-    </row>
-    <row r="121" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H121"/>
-      <c r="I121"/>
-    </row>
-    <row r="122" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H122"/>
-      <c r="I122"/>
-    </row>
-    <row r="123" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H123"/>
-      <c r="I123"/>
-    </row>
-    <row r="124" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H124"/>
-      <c r="I124"/>
-    </row>
-    <row r="125" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H125"/>
-      <c r="I125"/>
-    </row>
-    <row r="126" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H126"/>
-      <c r="I126"/>
-    </row>
-    <row r="127" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H127"/>
-      <c r="I127"/>
-    </row>
-    <row r="128" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H128"/>
-      <c r="I128"/>
-    </row>
-    <row r="129" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H129"/>
-      <c r="I129"/>
-    </row>
-    <row r="130" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H130"/>
-      <c r="I130"/>
-    </row>
-    <row r="131" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H131"/>
-      <c r="I131"/>
-    </row>
-    <row r="132" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H132"/>
-      <c r="I132"/>
-    </row>
-    <row r="133" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H133"/>
-      <c r="I133"/>
-    </row>
-    <row r="134" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H134"/>
-      <c r="I134"/>
-    </row>
-    <row r="135" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H135"/>
-      <c r="I135"/>
-    </row>
-    <row r="136" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H136"/>
-      <c r="I136"/>
-    </row>
-    <row r="137" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H137"/>
-      <c r="I137"/>
-    </row>
-    <row r="138" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H138"/>
-      <c r="I138"/>
-    </row>
-    <row r="139" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H139"/>
-      <c r="I139"/>
-    </row>
-    <row r="140" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H140"/>
-      <c r="I140"/>
-    </row>
-    <row r="141" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H141"/>
-      <c r="I141"/>
-    </row>
-    <row r="142" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H142"/>
-      <c r="I142"/>
-    </row>
-    <row r="143" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H143"/>
-      <c r="I143"/>
-    </row>
-    <row r="144" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H144"/>
-      <c r="I144"/>
-    </row>
-    <row r="145" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H145"/>
-      <c r="I145"/>
-    </row>
-    <row r="146" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H146"/>
-      <c r="I146"/>
-    </row>
-    <row r="147" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H147"/>
-      <c r="I147"/>
-    </row>
-    <row r="148" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H148"/>
-      <c r="I148"/>
-    </row>
-    <row r="149" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H149"/>
-      <c r="I149"/>
-    </row>
-    <row r="150" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H150"/>
-      <c r="I150"/>
-    </row>
-    <row r="151" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H151"/>
-      <c r="I151"/>
-    </row>
-    <row r="152" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H152"/>
-      <c r="I152"/>
-    </row>
-    <row r="153" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H153"/>
-      <c r="I153"/>
-    </row>
-    <row r="154" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H154"/>
-      <c r="I154"/>
-    </row>
-    <row r="155" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H155"/>
-      <c r="I155"/>
-    </row>
-    <row r="156" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H156"/>
-      <c r="I156"/>
-    </row>
-    <row r="157" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H157"/>
-      <c r="I157"/>
-    </row>
-    <row r="158" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="A96" s="5"/>
+      <c r="B96" s="33"/>
+      <c r="C96" s="34" t="s">
+        <v>314</v>
+      </c>
+      <c r="D96" s="6"/>
+      <c r="E96" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="F96" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="G96" s="7"/>
+      <c r="H96" s="8"/>
+      <c r="I96" s="9"/>
+      <c r="J96" s="6"/>
+      <c r="K96" s="6"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A97" s="5"/>
+      <c r="B97" s="29"/>
+      <c r="C97" s="30" t="s">
+        <v>316</v>
+      </c>
+      <c r="D97" s="6"/>
+      <c r="E97" s="30" t="s">
+        <v>317</v>
+      </c>
+      <c r="F97" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="G97" s="7"/>
+      <c r="H97" s="8"/>
+      <c r="I97" s="9"/>
+      <c r="J97" s="6"/>
+      <c r="K97" s="6"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A98" s="5"/>
+      <c r="B98" s="33"/>
+      <c r="C98" s="34" t="s">
+        <v>318</v>
+      </c>
+      <c r="D98" s="6"/>
+      <c r="E98" s="34" t="s">
+        <v>209</v>
+      </c>
+      <c r="F98" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="G98" s="7"/>
+      <c r="H98" s="8"/>
+      <c r="I98" s="9"/>
+      <c r="J98" s="6"/>
+      <c r="K98" s="6"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A99" s="25"/>
+      <c r="B99" s="31"/>
+      <c r="C99" s="32" t="s">
+        <v>319</v>
+      </c>
+      <c r="D99" s="26"/>
+      <c r="E99" s="32" t="s">
+        <v>320</v>
+      </c>
+      <c r="F99" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="G99" s="22"/>
+      <c r="H99" s="21"/>
+      <c r="I99" s="27"/>
+      <c r="J99" s="26"/>
+      <c r="K99" s="26"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A100" s="5"/>
+      <c r="B100" s="33"/>
+      <c r="C100" s="34" t="s">
+        <v>321</v>
+      </c>
+      <c r="D100" s="6"/>
+      <c r="E100" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="F100" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="G100" s="7"/>
+      <c r="H100" s="8"/>
+      <c r="I100" s="9"/>
+      <c r="J100" s="6"/>
+      <c r="K100" s="6"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A101" s="5"/>
+      <c r="B101" s="29"/>
+      <c r="C101" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="D101" s="6"/>
+      <c r="E101" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="F101" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="G101" s="7"/>
+      <c r="H101" s="8"/>
+      <c r="I101" s="9"/>
+      <c r="J101" s="6"/>
+      <c r="K101" s="6"/>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A102" s="5"/>
+      <c r="B102" s="33"/>
+      <c r="C102" s="34" t="s">
+        <v>324</v>
+      </c>
+      <c r="D102" s="6"/>
+      <c r="E102" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="F102" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="G102" s="7"/>
+      <c r="H102" s="8"/>
+      <c r="I102" s="9"/>
+      <c r="J102" s="6"/>
+      <c r="K102" s="6"/>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A103" s="5"/>
+      <c r="B103" s="29"/>
+      <c r="C103" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="D103" s="6"/>
+      <c r="E103" s="30" t="s">
+        <v>327</v>
+      </c>
+      <c r="F103" s="30" t="s">
+        <v>328</v>
+      </c>
+      <c r="G103" s="7"/>
+      <c r="H103" s="8"/>
+      <c r="I103" s="9"/>
+      <c r="J103" s="6"/>
+      <c r="K103" s="6"/>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A104" s="5"/>
+      <c r="B104" s="33"/>
+      <c r="C104" s="34" t="s">
+        <v>329</v>
+      </c>
+      <c r="D104" s="6"/>
+      <c r="E104" s="34" t="s">
+        <v>330</v>
+      </c>
+      <c r="F104" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="G104" s="7"/>
+      <c r="H104" s="8"/>
+      <c r="I104" s="9"/>
+      <c r="J104" s="6"/>
+      <c r="K104" s="6"/>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A105" s="5"/>
+      <c r="B105" s="29"/>
+      <c r="C105" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="D105" s="6"/>
+      <c r="E105" s="30" t="s">
+        <v>332</v>
+      </c>
+      <c r="F105" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="G105" s="7"/>
+      <c r="H105" s="8"/>
+      <c r="I105" s="9"/>
+      <c r="J105" s="6"/>
+      <c r="K105" s="6"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A106" s="5"/>
+      <c r="B106" s="33"/>
+      <c r="C106" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="D106" s="6"/>
+      <c r="E106" s="34" t="s">
+        <v>334</v>
+      </c>
+      <c r="F106" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="G106" s="7"/>
+      <c r="H106" s="8"/>
+      <c r="I106" s="9"/>
+      <c r="J106" s="6"/>
+      <c r="K106" s="6"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A107" s="5"/>
+      <c r="B107" s="29"/>
+      <c r="C107" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="D107" s="6"/>
+      <c r="E107" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="F107" s="30" t="s">
+        <v>335</v>
+      </c>
+      <c r="G107" s="7"/>
+      <c r="H107" s="8"/>
+      <c r="I107" s="9"/>
+      <c r="J107" s="6"/>
+      <c r="K107" s="6"/>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A108" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="B108" s="5"/>
+      <c r="C108" s="34" t="s">
+        <v>336</v>
+      </c>
+      <c r="D108" s="6"/>
+      <c r="E108" s="34" t="s">
+        <v>207</v>
+      </c>
+      <c r="F108" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="G108" s="7"/>
+      <c r="H108" s="8"/>
+      <c r="I108" s="9"/>
+      <c r="J108" s="6"/>
+      <c r="K108" s="6"/>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A109" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="B109" s="5"/>
+      <c r="C109" s="30" t="s">
+        <v>267</v>
+      </c>
+      <c r="D109" s="6"/>
+      <c r="E109" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="F109" s="30" t="s">
+        <v>335</v>
+      </c>
+      <c r="G109" s="7"/>
+      <c r="H109" s="8"/>
+      <c r="I109" s="9"/>
+      <c r="J109" s="6"/>
+      <c r="K109" s="6"/>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A110" s="36"/>
+      <c r="B110" s="5"/>
+      <c r="C110" s="37" t="s">
+        <v>337</v>
+      </c>
+      <c r="D110" s="26"/>
+      <c r="E110" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="F110" s="37" t="s">
+        <v>302</v>
+      </c>
+      <c r="G110" s="22"/>
+      <c r="H110" s="21"/>
+      <c r="I110" s="27"/>
+      <c r="J110" s="32" t="s">
+        <v>303</v>
+      </c>
+      <c r="K110" s="38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A111" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="B111" s="5"/>
+      <c r="C111" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="D111" s="6"/>
+      <c r="E111" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="F111" s="30" t="s">
+        <v>335</v>
+      </c>
+      <c r="G111" s="7"/>
+      <c r="H111" s="8"/>
+      <c r="I111" s="9"/>
+      <c r="J111" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="K111" s="39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A112" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B112" s="5"/>
+      <c r="C112" s="34" t="s">
+        <v>338</v>
+      </c>
+      <c r="D112" s="6"/>
+      <c r="E112" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F112" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="G112" s="7"/>
+      <c r="H112" s="8"/>
+      <c r="I112" s="9"/>
+      <c r="J112" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="K112" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A113" s="5"/>
+      <c r="B113" s="29"/>
+      <c r="C113" s="30" t="s">
+        <v>339</v>
+      </c>
+      <c r="D113" s="6"/>
+      <c r="E113" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="F113" s="30" t="s">
+        <v>335</v>
+      </c>
+      <c r="G113" s="7"/>
+      <c r="H113" s="8"/>
+      <c r="I113" s="9"/>
+      <c r="J113" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="K113" s="39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A114" s="5"/>
+      <c r="B114" s="33"/>
+      <c r="C114" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="D114" s="6"/>
+      <c r="E114" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="F114" s="34" t="s">
+        <v>335</v>
+      </c>
+      <c r="G114" s="7"/>
+      <c r="H114" s="8"/>
+      <c r="I114" s="9"/>
+      <c r="J114" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="K114" s="35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A115" s="29" t="s">
+        <v>343</v>
+      </c>
+      <c r="B115" s="5"/>
+      <c r="C115" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="D115" s="6"/>
+      <c r="E115" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="F115" s="30" t="s">
+        <v>335</v>
+      </c>
+      <c r="G115" s="7"/>
+      <c r="H115" s="8"/>
+      <c r="I115" s="9"/>
+      <c r="J115" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="K115" s="39">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A116" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="B116" s="5"/>
+      <c r="C116" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="D116" s="6"/>
+      <c r="E116" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="F116" s="34" t="s">
+        <v>335</v>
+      </c>
+      <c r="G116" s="7"/>
+      <c r="H116" s="8"/>
+      <c r="I116" s="9"/>
+      <c r="J116" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="K116" s="35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A117" s="5"/>
+      <c r="B117" s="29"/>
+      <c r="C117" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="D117" s="6"/>
+      <c r="E117" s="30" t="s">
+        <v>345</v>
+      </c>
+      <c r="F117" s="30" t="s">
+        <v>335</v>
+      </c>
+      <c r="G117" s="7"/>
+      <c r="H117" s="8"/>
+      <c r="I117" s="9"/>
+      <c r="J117" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="K117" s="39">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A118" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="B118" s="5"/>
+      <c r="C118" s="34" t="s">
+        <v>346</v>
+      </c>
+      <c r="D118" s="6"/>
+      <c r="E118" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="F118" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="G118" s="7"/>
+      <c r="H118" s="8"/>
+      <c r="I118" s="9"/>
+      <c r="J118" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="K118" s="35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A119" s="5"/>
+      <c r="B119" s="29"/>
+      <c r="C119" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="D119" s="6"/>
+      <c r="E119" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="F119" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="G119" s="7"/>
+      <c r="H119" s="8"/>
+      <c r="I119" s="9"/>
+      <c r="J119" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="K119" s="39">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A120" s="5"/>
+      <c r="B120" s="33"/>
+      <c r="C120" s="34" t="s">
+        <v>294</v>
+      </c>
+      <c r="D120" s="6"/>
+      <c r="E120" s="34" t="s">
+        <v>295</v>
+      </c>
+      <c r="F120" s="34" t="s">
+        <v>348</v>
+      </c>
+      <c r="G120" s="7"/>
+      <c r="H120" s="8"/>
+      <c r="I120" s="9"/>
+      <c r="J120" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="K120" s="35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A121" s="29" t="s">
+        <v>288</v>
+      </c>
+      <c r="B121" s="5"/>
+      <c r="C121" s="30" t="s">
+        <v>291</v>
+      </c>
+      <c r="D121" s="6"/>
+      <c r="E121" s="30" t="s">
+        <v>293</v>
+      </c>
+      <c r="F121" s="30" t="s">
+        <v>290</v>
+      </c>
+      <c r="G121" s="7"/>
+      <c r="H121" s="8"/>
+      <c r="I121" s="9"/>
+      <c r="J121" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="K121" s="39">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A122" s="33" t="s">
+        <v>349</v>
+      </c>
+      <c r="B122" s="5"/>
+      <c r="C122" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="D122" s="6"/>
+      <c r="E122" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="F122" s="34" t="s">
+        <v>335</v>
+      </c>
+      <c r="G122" s="7"/>
+      <c r="H122" s="8"/>
+      <c r="I122" s="9"/>
+      <c r="J122" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="K122" s="35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A123" s="29" t="s">
+        <v>350</v>
+      </c>
+      <c r="B123" s="5"/>
+      <c r="C123" s="30" t="s">
+        <v>282</v>
+      </c>
+      <c r="D123" s="6"/>
+      <c r="E123" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="F123" s="30" t="s">
+        <v>335</v>
+      </c>
+      <c r="G123" s="7"/>
+      <c r="H123" s="8"/>
+      <c r="I123" s="9"/>
+      <c r="J123" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="K123" s="39">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A124" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="B124" s="5"/>
+      <c r="C124" s="37" t="s">
+        <v>351</v>
+      </c>
+      <c r="D124" s="26"/>
+      <c r="E124" s="37" t="s">
+        <v>177</v>
+      </c>
+      <c r="F124" s="37" t="s">
+        <v>302</v>
+      </c>
+      <c r="G124" s="22"/>
+      <c r="H124" s="21"/>
+      <c r="I124" s="27"/>
+      <c r="J124" s="32" t="s">
+        <v>303</v>
+      </c>
+      <c r="K124" s="38">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A125" s="29" t="s">
+        <v>353</v>
+      </c>
+      <c r="B125" s="5"/>
+      <c r="C125" s="30" t="s">
+        <v>354</v>
+      </c>
+      <c r="D125" s="6"/>
+      <c r="E125" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="F125" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="G125" s="7"/>
+      <c r="H125" s="8"/>
+      <c r="I125" s="9"/>
+      <c r="J125" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="K125" s="39">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A126" s="5"/>
+      <c r="B126" s="33"/>
+      <c r="C126" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="D126" s="6"/>
+      <c r="E126" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="F126" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="G126" s="7"/>
+      <c r="H126" s="8"/>
+      <c r="I126" s="9"/>
+      <c r="J126" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="K126" s="35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A127" s="5"/>
+      <c r="B127" s="29"/>
+      <c r="C127" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="D127" s="6"/>
+      <c r="E127" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="F127" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="G127" s="7"/>
+      <c r="H127" s="8"/>
+      <c r="I127" s="9"/>
+      <c r="J127" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="K127" s="39">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A128" s="33" t="s">
+        <v>357</v>
+      </c>
+      <c r="B128" s="5"/>
+      <c r="C128" s="34" t="s">
+        <v>358</v>
+      </c>
+      <c r="D128" s="6"/>
+      <c r="E128" s="34" t="s">
+        <v>359</v>
+      </c>
+      <c r="F128" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="G128" s="7"/>
+      <c r="H128" s="8"/>
+      <c r="I128" s="9"/>
+      <c r="J128" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="K128" s="35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A129" s="29" t="s">
+        <v>361</v>
+      </c>
+      <c r="B129" s="5"/>
+      <c r="C129" s="30" t="s">
+        <v>362</v>
+      </c>
+      <c r="D129" s="6"/>
+      <c r="E129" s="30" t="s">
+        <v>363</v>
+      </c>
+      <c r="F129" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="G129" s="7"/>
+      <c r="H129" s="8"/>
+      <c r="I129" s="9"/>
+      <c r="J129" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="K129" s="39">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A130" s="33" t="s">
+        <v>364</v>
+      </c>
+      <c r="B130" s="5"/>
+      <c r="C130" s="34" t="s">
+        <v>365</v>
+      </c>
+      <c r="D130" s="6"/>
+      <c r="E130" s="34" t="s">
+        <v>366</v>
+      </c>
+      <c r="F130" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="G130" s="7"/>
+      <c r="H130" s="8"/>
+      <c r="I130" s="9"/>
+      <c r="J130" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="K130" s="35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A131" s="29" t="s">
+        <v>367</v>
+      </c>
+      <c r="B131" s="5"/>
+      <c r="C131" s="30" t="s">
+        <v>368</v>
+      </c>
+      <c r="D131" s="6"/>
+      <c r="E131" s="30" t="s">
+        <v>369</v>
+      </c>
+      <c r="F131" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="G131" s="7"/>
+      <c r="H131" s="8"/>
+      <c r="I131" s="9"/>
+      <c r="J131" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="K131" s="39">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A132" s="33" t="s">
+        <v>370</v>
+      </c>
+      <c r="B132" s="5"/>
+      <c r="C132" s="34" t="s">
+        <v>371</v>
+      </c>
+      <c r="D132" s="6"/>
+      <c r="E132" s="34" t="s">
+        <v>372</v>
+      </c>
+      <c r="F132" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="G132" s="7"/>
+      <c r="H132" s="8"/>
+      <c r="I132" s="9"/>
+      <c r="J132" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="K132" s="35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A133" s="29" t="s">
+        <v>373</v>
+      </c>
+      <c r="B133" s="5"/>
+      <c r="C133" s="30" t="s">
+        <v>374</v>
+      </c>
+      <c r="D133" s="6"/>
+      <c r="E133" s="30" t="s">
+        <v>375</v>
+      </c>
+      <c r="F133" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="G133" s="7"/>
+      <c r="H133" s="8"/>
+      <c r="I133" s="9"/>
+      <c r="J133" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="K133" s="39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A134" s="33" t="s">
+        <v>376</v>
+      </c>
+      <c r="B134" s="5"/>
+      <c r="C134" s="34" t="s">
+        <v>377</v>
+      </c>
+      <c r="D134" s="6"/>
+      <c r="E134" s="34" t="s">
+        <v>378</v>
+      </c>
+      <c r="F134" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="G134" s="7"/>
+      <c r="H134" s="8"/>
+      <c r="I134" s="9"/>
+      <c r="J134" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="K134" s="35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A135" s="29" t="s">
+        <v>379</v>
+      </c>
+      <c r="B135" s="5"/>
+      <c r="C135" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="D135" s="6"/>
+      <c r="E135" s="30" t="s">
+        <v>381</v>
+      </c>
+      <c r="F135" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="G135" s="7"/>
+      <c r="H135" s="8"/>
+      <c r="I135" s="9"/>
+      <c r="J135" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="K135" s="39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A136" s="33" t="s">
+        <v>382</v>
+      </c>
+      <c r="B136" s="5"/>
+      <c r="C136" s="34" t="s">
+        <v>383</v>
+      </c>
+      <c r="D136" s="6"/>
+      <c r="E136" s="34" t="s">
+        <v>384</v>
+      </c>
+      <c r="F136" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="G136" s="7"/>
+      <c r="H136" s="8"/>
+      <c r="I136" s="9"/>
+      <c r="J136" s="30" t="s">
+        <v>342</v>
+      </c>
+      <c r="K136" s="35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A137" s="25"/>
+      <c r="B137" s="25"/>
+      <c r="C137" s="25"/>
+      <c r="D137" s="26"/>
+      <c r="E137" s="26"/>
+      <c r="F137" s="26"/>
+      <c r="G137" s="22"/>
+      <c r="H137" s="21"/>
+      <c r="I137" s="27"/>
+      <c r="J137" s="37" t="s">
+        <v>342</v>
+      </c>
+      <c r="K137" s="40">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A138" s="5"/>
+      <c r="B138" s="5"/>
+      <c r="C138" s="5"/>
+      <c r="D138" s="6"/>
+      <c r="E138" s="6"/>
+      <c r="F138" s="6"/>
+      <c r="G138" s="7"/>
+      <c r="H138" s="8"/>
+      <c r="I138" s="9"/>
+      <c r="J138" s="30" t="s">
+        <v>342</v>
+      </c>
+      <c r="K138" s="35">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A139" s="5"/>
+      <c r="B139" s="5"/>
+      <c r="C139" s="5"/>
+      <c r="D139" s="6"/>
+      <c r="E139" s="6"/>
+      <c r="F139" s="6"/>
+      <c r="G139" s="7"/>
+      <c r="H139" s="8"/>
+      <c r="I139" s="9"/>
+      <c r="J139" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="K139" s="39">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A140" s="5"/>
+      <c r="B140" s="5"/>
+      <c r="C140" s="5"/>
+      <c r="D140" s="6"/>
+      <c r="E140" s="6"/>
+      <c r="F140" s="6"/>
+      <c r="G140" s="7"/>
+      <c r="H140" s="8"/>
+      <c r="I140" s="9"/>
+      <c r="J140" s="30" t="s">
+        <v>342</v>
+      </c>
+      <c r="K140" s="35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A141" s="5"/>
+      <c r="B141" s="5"/>
+      <c r="C141" s="5"/>
+      <c r="D141" s="6"/>
+      <c r="E141" s="6"/>
+      <c r="F141" s="6"/>
+      <c r="G141" s="7"/>
+      <c r="H141" s="8"/>
+      <c r="I141" s="9"/>
+      <c r="J141" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="K141" s="39">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A142" s="5"/>
+      <c r="B142" s="5"/>
+      <c r="C142" s="5"/>
+      <c r="D142" s="6"/>
+      <c r="E142" s="6"/>
+      <c r="F142" s="6"/>
+      <c r="G142" s="7"/>
+      <c r="H142" s="8"/>
+      <c r="I142" s="9"/>
+      <c r="J142" s="30" t="s">
+        <v>342</v>
+      </c>
+      <c r="K142" s="35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A143" s="5"/>
+      <c r="B143" s="5"/>
+      <c r="C143" s="5"/>
+      <c r="D143" s="6"/>
+      <c r="E143" s="6"/>
+      <c r="F143" s="6"/>
+      <c r="G143" s="7"/>
+      <c r="H143" s="8"/>
+      <c r="I143" s="9"/>
+      <c r="J143" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="K143" s="39">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A144" s="5"/>
+      <c r="B144" s="5"/>
+      <c r="C144" s="5"/>
+      <c r="D144" s="6"/>
+      <c r="E144" s="6"/>
+      <c r="F144" s="6"/>
+      <c r="G144" s="7"/>
+      <c r="H144" s="8"/>
+      <c r="I144" s="9"/>
+      <c r="J144" s="30" t="s">
+        <v>342</v>
+      </c>
+      <c r="K144" s="35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A145" s="5"/>
+      <c r="B145" s="5"/>
+      <c r="C145" s="5"/>
+      <c r="D145" s="6"/>
+      <c r="E145" s="6"/>
+      <c r="F145" s="6"/>
+      <c r="G145" s="7"/>
+      <c r="H145" s="8"/>
+      <c r="I145" s="9"/>
+      <c r="J145" s="34" t="s">
+        <v>352</v>
+      </c>
+      <c r="K145" s="39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A146" s="25"/>
+      <c r="B146" s="25"/>
+      <c r="C146" s="25"/>
+      <c r="D146" s="26"/>
+      <c r="E146" s="26"/>
+      <c r="F146" s="26"/>
+      <c r="G146" s="22"/>
+      <c r="H146" s="21"/>
+      <c r="I146" s="27"/>
+      <c r="J146" s="32" t="s">
+        <v>352</v>
+      </c>
+      <c r="K146" s="38">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A147" s="5"/>
+      <c r="B147" s="5"/>
+      <c r="C147" s="5"/>
+      <c r="D147" s="6"/>
+      <c r="E147" s="6"/>
+      <c r="F147" s="6"/>
+      <c r="G147" s="7"/>
+      <c r="H147" s="8"/>
+      <c r="I147" s="9"/>
+      <c r="J147" s="34" t="s">
+        <v>352</v>
+      </c>
+      <c r="K147" s="39">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A148" s="5"/>
+      <c r="B148" s="5"/>
+      <c r="C148" s="5"/>
+      <c r="D148" s="6"/>
+      <c r="E148" s="6"/>
+      <c r="F148" s="6"/>
+      <c r="G148" s="7"/>
+      <c r="H148" s="8"/>
+      <c r="I148" s="9"/>
+      <c r="J148" s="30" t="s">
+        <v>352</v>
+      </c>
+      <c r="K148" s="35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A149" s="5"/>
+      <c r="B149" s="5"/>
+      <c r="C149" s="5"/>
+      <c r="D149" s="6"/>
+      <c r="E149" s="6"/>
+      <c r="F149" s="6"/>
+      <c r="G149" s="7"/>
+      <c r="H149" s="8"/>
+      <c r="I149" s="9"/>
+      <c r="J149" s="34" t="s">
+        <v>360</v>
+      </c>
+      <c r="K149" s="39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A150" s="5"/>
+      <c r="B150" s="5"/>
+      <c r="C150" s="5"/>
+      <c r="D150" s="6"/>
+      <c r="E150" s="6"/>
+      <c r="F150" s="6"/>
+      <c r="G150" s="7"/>
+      <c r="H150" s="8"/>
+      <c r="I150" s="9"/>
+      <c r="J150" s="30" t="s">
+        <v>360</v>
+      </c>
+      <c r="K150" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A151" s="5"/>
+      <c r="B151" s="5"/>
+      <c r="C151" s="5"/>
+      <c r="D151" s="6"/>
+      <c r="E151" s="6"/>
+      <c r="F151" s="6"/>
+      <c r="G151" s="7"/>
+      <c r="H151" s="8"/>
+      <c r="I151" s="9"/>
+      <c r="J151" s="34" t="s">
+        <v>360</v>
+      </c>
+      <c r="K151" s="39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A152" s="5"/>
+      <c r="B152" s="5"/>
+      <c r="C152" s="5"/>
+      <c r="D152" s="6"/>
+      <c r="E152" s="6"/>
+      <c r="F152" s="6"/>
+      <c r="G152" s="7"/>
+      <c r="H152" s="8"/>
+      <c r="I152" s="9"/>
+      <c r="J152" s="30" t="s">
+        <v>360</v>
+      </c>
+      <c r="K152" s="35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A153" s="5"/>
+      <c r="B153" s="5"/>
+      <c r="C153" s="5"/>
+      <c r="D153" s="6"/>
+      <c r="E153" s="6"/>
+      <c r="F153" s="6"/>
+      <c r="G153" s="7"/>
+      <c r="H153" s="8"/>
+      <c r="I153" s="9"/>
+      <c r="J153" s="34" t="s">
+        <v>360</v>
+      </c>
+      <c r="K153" s="39">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A154" s="25"/>
+      <c r="B154" s="25"/>
+      <c r="C154" s="25"/>
+      <c r="D154" s="26"/>
+      <c r="E154" s="26"/>
+      <c r="F154" s="26"/>
+      <c r="G154" s="22"/>
+      <c r="H154" s="21"/>
+      <c r="I154" s="27"/>
+      <c r="J154" s="32" t="s">
+        <v>360</v>
+      </c>
+      <c r="K154" s="38">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A155" s="5"/>
+      <c r="B155" s="5"/>
+      <c r="C155" s="5"/>
+      <c r="D155" s="6"/>
+      <c r="E155" s="6"/>
+      <c r="F155" s="6"/>
+      <c r="G155" s="7"/>
+      <c r="H155" s="8"/>
+      <c r="I155" s="9"/>
+      <c r="J155" s="34" t="s">
+        <v>360</v>
+      </c>
+      <c r="K155" s="39">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A156" s="5"/>
+      <c r="B156" s="5"/>
+      <c r="C156" s="5"/>
+      <c r="D156" s="6"/>
+      <c r="E156" s="6"/>
+      <c r="F156" s="6"/>
+      <c r="G156" s="7"/>
+      <c r="H156" s="8"/>
+      <c r="I156" s="9"/>
+      <c r="J156" s="30" t="s">
+        <v>360</v>
+      </c>
+      <c r="K156" s="35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A157" s="25"/>
+      <c r="B157" s="25"/>
+      <c r="C157" s="25"/>
+      <c r="D157" s="26"/>
+      <c r="E157" s="26"/>
+      <c r="F157" s="26"/>
+      <c r="G157" s="22"/>
+      <c r="H157" s="21"/>
+      <c r="I157" s="27"/>
+      <c r="J157" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="K157" s="40">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H158"/>
       <c r="I158"/>
     </row>
-    <row r="159" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H159"/>
       <c r="I159"/>
     </row>
-    <row r="160" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H160"/>
       <c r="I160"/>
     </row>
@@ -10667,18 +12151,6 @@
     <row r="1744" spans="8:9" x14ac:dyDescent="0.2">
       <c r="H1744"/>
       <c r="I1744"/>
-    </row>
-    <row r="1745" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1745"/>
-      <c r="I1745"/>
-    </row>
-    <row r="1746" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1746"/>
-      <c r="I1746"/>
-    </row>
-    <row r="1747" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1747"/>
-      <c r="I1747"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3047F815-4589-0C4C-B5FE-8230DD344A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E67D45F-9851-E64E-9A6D-C39B48465555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1880" yWindow="1460" windowWidth="28360" windowHeight="18180" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">network!$A$1:$K$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">network!$A$1:$K$40</definedName>
     <definedName name="taxrate">'[1]mixer costs'!$I$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="381">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -140,9 +140,6 @@
     <t>ZAIU-E001</t>
   </si>
   <si>
-    <t>1C-69-7A-65-CB-33</t>
-  </si>
-  <si>
     <t>Stream Encoder</t>
   </si>
   <si>
@@ -569,9 +566,6 @@
     <t>ZVIU-G001</t>
   </si>
   <si>
-    <t>1C-69-7A-66-87-69</t>
-  </si>
-  <si>
     <t>2405-1307</t>
   </si>
   <si>
@@ -890,18 +884,12 @@
     <t>2604-2401</t>
   </si>
   <si>
-    <t>80-99-E7-4D-A8-5E</t>
-  </si>
-  <si>
     <t>2604-2402</t>
   </si>
   <si>
     <t>2604-2403</t>
   </si>
   <si>
-    <t>58-18-62-6B-1D-2B</t>
-  </si>
-  <si>
     <t>192.168.201.20</t>
   </si>
   <si>
@@ -911,9 +899,6 @@
     <t>192.168.201.22</t>
   </si>
   <si>
-    <t>58-18-62-6B-1D-2C</t>
-  </si>
-  <si>
     <t>192.168.201.2</t>
   </si>
   <si>
@@ -932,24 +917,12 @@
     <t>2603-1203</t>
   </si>
   <si>
-    <t>98-BA-5F-91-07-6A</t>
-  </si>
-  <si>
     <t>Omada</t>
   </si>
   <si>
     <t>192.168.201.105</t>
   </si>
   <si>
-    <t>7C-2E-0D-A8-52-4F</t>
-  </si>
-  <si>
-    <t>7C-2E-0D-20-68-69</t>
-  </si>
-  <si>
-    <t>00-1D-56-04-CC-E3</t>
-  </si>
-  <si>
     <t xml:space="preserve">00:1d:56:03:81:45 </t>
   </si>
   <si>
@@ -965,24 +938,15 @@
     <t>2507-1000</t>
   </si>
   <si>
-    <t>D0-C8-57-81-F2-19</t>
-  </si>
-  <si>
     <t>NDI</t>
   </si>
   <si>
-    <t>D0-C8-57-82-74-B9</t>
-  </si>
-  <si>
     <t>192.168.204.32</t>
   </si>
   <si>
     <t>192.168.204.31</t>
   </si>
   <si>
-    <t>14-3F-A6-B8-EA-5D</t>
-  </si>
-  <si>
     <t>192.168.207.100</t>
   </si>
   <si>
@@ -998,9 +962,6 @@
     <t>192.168.201.103</t>
   </si>
   <si>
-    <t>00-21-84-03-C3-DC</t>
-  </si>
-  <si>
     <t>192.168.200.68</t>
   </si>
   <si>
@@ -1010,117 +971,51 @@
     <t>AV Amp 2603-1200</t>
   </si>
   <si>
-    <t>00-04-C4-0F-E3-C3</t>
-  </si>
-  <si>
-    <t>00-1D-C1-9C-47-33</t>
-  </si>
-  <si>
     <t>192.168.200.102</t>
   </si>
   <si>
-    <t>00-04-C4-11-3C-B6</t>
-  </si>
-  <si>
-    <t>00-21-84-03-C3-D8</t>
-  </si>
-  <si>
     <t>192.168.200.69</t>
   </si>
   <si>
-    <t>00-21-84-03-7F-5C</t>
-  </si>
-  <si>
     <t>192.168.200.61</t>
   </si>
   <si>
-    <t>00-1D-C1-9B-6C-4D</t>
-  </si>
-  <si>
     <t>192.168.200.107</t>
   </si>
   <si>
-    <t>00-1D-C1-9A-6E-02</t>
-  </si>
-  <si>
     <t>192.168.200.113</t>
   </si>
   <si>
-    <t>00-21-84-03-7F-32</t>
-  </si>
-  <si>
     <t>192.168.200.62</t>
   </si>
   <si>
-    <t>00-04-C4-13-E2-61</t>
-  </si>
-  <si>
-    <t>00-1D-C1-9A-70-3A</t>
-  </si>
-  <si>
     <t>192.168.200.108</t>
   </si>
   <si>
-    <t>00-04-C4-14-A2-0F</t>
-  </si>
-  <si>
-    <t>00-21-84-03-7F-31</t>
-  </si>
-  <si>
     <t>192.168.200.63</t>
   </si>
   <si>
-    <t>00-21-84-03-7F-5A</t>
-  </si>
-  <si>
     <t>192.168.200.64</t>
   </si>
   <si>
-    <t>00-0C-15-06-B9-31</t>
-  </si>
-  <si>
     <t>192.168.206.6</t>
   </si>
   <si>
     <t>Control</t>
   </si>
   <si>
-    <t>00-21-84-03-7F-5B</t>
-  </si>
-  <si>
     <t>192.168.200.65</t>
   </si>
   <si>
-    <t>00-21-84-03-7F-34</t>
-  </si>
-  <si>
     <t>192.168.200.66</t>
   </si>
   <si>
-    <t>00-21-84-03-85-94</t>
-  </si>
-  <si>
     <t>192.168.200.67</t>
   </si>
   <si>
     <t>Default</t>
   </si>
   <si>
-    <t>00-60-74-EE-53-EF</t>
-  </si>
-  <si>
-    <t>00-1D-C1-51-73-2D</t>
-  </si>
-  <si>
-    <t>14-98-77-82-73-BD</t>
-  </si>
-  <si>
-    <t>A8-6E-84-07-E5-B1</t>
-  </si>
-  <si>
-    <t>34-1B-22-84-24-6B</t>
-  </si>
-  <si>
     <t>192.168.201.100</t>
   </si>
   <si>
@@ -1130,18 +1025,9 @@
     <t>ZVIU-G001 resi</t>
   </si>
   <si>
-    <t>34-1B-22-84-24-57</t>
-  </si>
-  <si>
     <t>192.168.201.101</t>
   </si>
   <si>
-    <t>A4-FC-14-28-2E-B6</t>
-  </si>
-  <si>
-    <t>00-1D-C1-52-94-50</t>
-  </si>
-  <si>
     <t>TVs</t>
   </si>
   <si>
@@ -1151,106 +1037,208 @@
     <t>2601-2800-BMD-Cons</t>
   </si>
   <si>
-    <t>20-A5-CB-CE-4E-B8</t>
-  </si>
-  <si>
-    <t>AV FoH 2603-1201</t>
-  </si>
-  <si>
     <t>AV Booth TSC</t>
   </si>
   <si>
-    <t>00-60-74-ED-D0-97</t>
-  </si>
-  <si>
-    <t>00-04-C4-14-70-C8</t>
-  </si>
-  <si>
-    <t>00-1D-C1-54-00-59</t>
-  </si>
-  <si>
     <t>klang-KRB14486</t>
   </si>
   <si>
-    <t>00-04-C4-31-29-BA</t>
-  </si>
-  <si>
     <t>192.168.200.199</t>
   </si>
   <si>
-    <t>AV Stage 2603-1202</t>
-  </si>
-  <si>
     <t>klang-KRB14514</t>
   </si>
   <si>
-    <t>00-04-C4-31-29-D6</t>
-  </si>
-  <si>
     <t>192.168.200.123</t>
   </si>
   <si>
     <t>klang-KRB14506</t>
   </si>
   <si>
-    <t>00-04-C4-31-29-CE</t>
-  </si>
-  <si>
     <t>192.168.200.149</t>
   </si>
   <si>
     <t>klang-KRB14070</t>
   </si>
   <si>
-    <t>00-04-C4-31-28-1A</t>
-  </si>
-  <si>
     <t>192.168.200.150</t>
   </si>
   <si>
     <t>klang-KRB14513</t>
   </si>
   <si>
-    <t>00-04-C4-31-29-D5</t>
-  </si>
-  <si>
     <t>192.168.200.100</t>
   </si>
   <si>
     <t>klang-KRB14510</t>
   </si>
   <si>
-    <t>00-04-C4-31-29-D2</t>
-  </si>
-  <si>
     <t>192.168.200.147</t>
   </si>
   <si>
     <t>klang-KRB14415</t>
   </si>
   <si>
-    <t>00-04-C4-31-29-73</t>
-  </si>
-  <si>
     <t>192.168.200.138</t>
   </si>
   <si>
     <t>klang-KRB14512</t>
   </si>
   <si>
-    <t>00-04-C4-31-29-D4</t>
-  </si>
-  <si>
     <t>192.168.200.130</t>
   </si>
   <si>
     <t>klang-KRB14072</t>
   </si>
   <si>
-    <t>00-04-C4-31-28-1C</t>
-  </si>
-  <si>
     <t>192.168.200.148</t>
+  </si>
+  <si>
+    <t>00:04:C4:0F:E3:C3</t>
+  </si>
+  <si>
+    <t>00:04:C4:11:3C:B6</t>
+  </si>
+  <si>
+    <t>00:04:C4:13:E2:61</t>
+  </si>
+  <si>
+    <t>00:04:C4:14:70:C8</t>
+  </si>
+  <si>
+    <t>00:04:C4:14:A2:0F</t>
+  </si>
+  <si>
+    <t>00:04:C4:31:28:1A</t>
+  </si>
+  <si>
+    <t>00:04:C4:31:28:1C</t>
+  </si>
+  <si>
+    <t>00:04:C4:31:29:73</t>
+  </si>
+  <si>
+    <t>00:04:C4:31:29:BA</t>
+  </si>
+  <si>
+    <t>00:04:C4:31:29:CE</t>
+  </si>
+  <si>
+    <t>00:04:C4:31:29:D2</t>
+  </si>
+  <si>
+    <t>00:04:C4:31:29:D4</t>
+  </si>
+  <si>
+    <t>00:04:C4:31:29:D5</t>
+  </si>
+  <si>
+    <t>00:04:C4:31:29:D6</t>
+  </si>
+  <si>
+    <t>00:0C:15:06:B9:31</t>
+  </si>
+  <si>
+    <t>00:1D:56:04:CC:E3</t>
+  </si>
+  <si>
+    <t>00:1D:C1:51:73:2D</t>
+  </si>
+  <si>
+    <t>00:1D:C1:52:94:50</t>
+  </si>
+  <si>
+    <t>00:1D:C1:54:00:59</t>
+  </si>
+  <si>
+    <t>00:1D:C1:9A:6E:02</t>
+  </si>
+  <si>
+    <t>00:1D:C1:9A:70:3A</t>
+  </si>
+  <si>
+    <t>00:1D:C1:9B:6C:4D</t>
+  </si>
+  <si>
+    <t>00:1D:C1:9C:47:33</t>
+  </si>
+  <si>
+    <t>00:21:84:03:7F:31</t>
+  </si>
+  <si>
+    <t>00:21:84:03:7F:32</t>
+  </si>
+  <si>
+    <t>00:21:84:03:7F:34</t>
+  </si>
+  <si>
+    <t>00:21:84:03:7F:5A</t>
+  </si>
+  <si>
+    <t>00:21:84:03:7F:5B</t>
+  </si>
+  <si>
+    <t>00:21:84:03:7F:5C</t>
+  </si>
+  <si>
+    <t>00:21:84:03:85:94</t>
+  </si>
+  <si>
+    <t>00:21:84:03:C3:D8</t>
+  </si>
+  <si>
+    <t>00:21:84:03:C3:DC</t>
+  </si>
+  <si>
+    <t>00:60:74:EE:53:EF</t>
+  </si>
+  <si>
+    <t>14:3F:A6:B8:EA:5D</t>
+  </si>
+  <si>
+    <t>1C:69:7A:65:CB:33</t>
+  </si>
+  <si>
+    <t>1C:69:7A:66:87:69</t>
+  </si>
+  <si>
+    <t>20:A5:CB:CE:4E:B8</t>
+  </si>
+  <si>
+    <t>34:1B:22:84:24:57</t>
+  </si>
+  <si>
+    <t>34:1B:22:84:24:6B</t>
+  </si>
+  <si>
+    <t>58:18:62:6B:1D:2B</t>
+  </si>
+  <si>
+    <t>58:18:62:6B:1D:2C</t>
+  </si>
+  <si>
+    <t>7C:2E:0D:20:68:69</t>
+  </si>
+  <si>
+    <t>7C:2E:0D:A8:52:4F</t>
+  </si>
+  <si>
+    <t>80:99:E7:4D:A8:5E</t>
+  </si>
+  <si>
+    <t>98:BA:5F:91:07:6A</t>
+  </si>
+  <si>
+    <t>A4:FC:14:28:2E:B6</t>
+  </si>
+  <si>
+    <t>A8:6E:84:07:E5:B1</t>
+  </si>
+  <si>
+    <t>D0:C8:57:81:F2:19</t>
+  </si>
+  <si>
+    <t>D0:C8:57:82:74:B9</t>
   </si>
 </sst>
 </file>
@@ -1506,7 +1494,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1530,7 +1518,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
@@ -1539,10 +1526,8 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1552,6 +1537,18 @@
     <xf numFmtId="49" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1835,11 +1832,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K157" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K157" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K73">
-    <sortCondition ref="A2:A73"/>
-    <sortCondition ref="B2:B73"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K156" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K156" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K156">
+    <sortCondition ref="C2:C156"/>
+    <sortCondition ref="A2:A156"/>
   </sortState>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{EF2C341F-E5C1-604C-942C-FB7E9F76F1CD}" name="AssetTag" dataDxfId="10"/>
@@ -2155,7 +2152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC7A309-0B6A-4549-9590-6CFCF97D2DB0}">
-  <dimension ref="A1:K1744"/>
+  <dimension ref="A1:K1743"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
@@ -2175,3294 +2172,3278 @@
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="K1" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6" t="s">
-        <v>152</v>
+      <c r="A2" s="5"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24" t="s">
+        <v>332</v>
       </c>
       <c r="D2" s="6"/>
-      <c r="E2" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="F2" s="7" t="str">
-        <f>CONCATENATE("http://", E2)</f>
-        <v>http://192.168.0.208</v>
+      <c r="E2" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>289</v>
       </c>
       <c r="G2" s="7"/>
-      <c r="H2" s="8" t="s">
-        <v>172</v>
-      </c>
+      <c r="H2" s="8"/>
       <c r="I2" s="9"/>
-      <c r="J2" s="6" t="s">
-        <v>151</v>
-      </c>
+      <c r="J2" s="6"/>
       <c r="K2" s="6"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
-        <v>205</v>
+      <c r="A3" s="5" t="s">
+        <v>193</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I3" s="9"/>
-      <c r="J3" s="5" t="s">
-        <v>202</v>
+      <c r="J3" s="6" t="s">
+        <v>197</v>
       </c>
       <c r="K3" s="6"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="6" t="s">
-        <v>160</v>
+      <c r="A4" s="5"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24" t="s">
+        <v>333</v>
       </c>
       <c r="D4" s="6"/>
-      <c r="E4" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="8" t="s">
-        <v>173</v>
-      </c>
+      <c r="E4" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="8"/>
       <c r="I4" s="9"/>
-      <c r="J4" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="J4" s="6"/>
       <c r="K4" s="6"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>196</v>
+        <v>193</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>198</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D5" s="6"/>
-      <c r="E5" s="6" t="s">
-        <v>198</v>
-      </c>
+      <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="6" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="K5" s="6"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>200</v>
+      <c r="A6" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>194</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
+      <c r="E6" s="6" t="s">
+        <v>207</v>
+      </c>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="6" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="K6" s="6"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5" t="s">
-        <v>230</v>
+      <c r="A7" s="5"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24" t="s">
+        <v>334</v>
       </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="8" t="s">
-        <v>172</v>
-      </c>
+      <c r="E7" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8"/>
       <c r="I7" s="9"/>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="6" t="s">
-        <v>281</v>
+      <c r="A8" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="D8" s="6"/>
-      <c r="E8" s="6" t="s">
-        <v>162</v>
-      </c>
+      <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I8" s="9"/>
-      <c r="J8" s="6"/>
+      <c r="J8" s="6" t="s">
+        <v>217</v>
+      </c>
       <c r="K8" s="6"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="6" t="s">
-        <v>282</v>
+        <v>220</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>224</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6" t="s">
-        <v>163</v>
+        <v>223</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I9" s="9"/>
-      <c r="J9" s="6"/>
+      <c r="J9" s="6" t="s">
+        <v>221</v>
+      </c>
       <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>210</v>
+      <c r="A10" s="5"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24" t="s">
+        <v>335</v>
       </c>
       <c r="D10" s="6"/>
-      <c r="E10" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="8" t="s">
-        <v>172</v>
-      </c>
+      <c r="E10" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="8"/>
       <c r="I10" s="9"/>
-      <c r="J10" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="K10" s="6"/>
+      <c r="J10" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="K10" s="38">
+        <v>26</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>215</v>
+      <c r="A11" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="6" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K12" s="6"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>214</v>
+      <c r="A13" s="5"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24" t="s">
+        <v>336</v>
       </c>
       <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="8" t="s">
-        <v>173</v>
-      </c>
+      <c r="E13" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="G13" s="7"/>
+      <c r="H13" s="8"/>
       <c r="I13" s="9"/>
-      <c r="J13" s="6" t="s">
-        <v>218</v>
-      </c>
+      <c r="J13" s="6"/>
       <c r="K13" s="6"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>196</v>
+      <c r="A14" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>198</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="D14" s="6"/>
-      <c r="E14" s="6" t="s">
-        <v>225</v>
-      </c>
+      <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="6" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="K14" s="6"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>227</v>
+      <c r="A15" s="38" t="s">
+        <v>320</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="38" t="s">
+        <v>337</v>
       </c>
       <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="8" t="s">
-        <v>173</v>
-      </c>
+      <c r="E15" s="38" t="s">
+        <v>321</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="G15" s="7"/>
+      <c r="H15" s="8"/>
       <c r="I15" s="9"/>
-      <c r="J15" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="K15" s="6"/>
+      <c r="J15" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="K15" s="24">
+        <v>36</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="11" t="s">
+      <c r="A16" s="24" t="s">
+        <v>330</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="24" t="s">
+        <v>338</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="24" t="s">
+        <v>331</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="G16" s="7"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="38" t="s">
+        <v>307</v>
+      </c>
+      <c r="K16" s="38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="24" t="s">
+        <v>326</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="24" t="s">
+        <v>339</v>
+      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" s="24" t="s">
+        <v>327</v>
+      </c>
+      <c r="F17" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="G17" s="7"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="K17" s="38">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="24" t="s">
+        <v>314</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="24" t="s">
+        <v>340</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="24" t="s">
+        <v>315</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="G18" s="7"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="K18" s="38">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="24" t="s">
+        <v>319</v>
+      </c>
+      <c r="F19" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="G19" s="7"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="K19" s="38">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="38" t="s">
+        <v>324</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="38" t="s">
+        <v>342</v>
+      </c>
+      <c r="D20" s="6"/>
+      <c r="E20" s="38" t="s">
+        <v>325</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="G20" s="7"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="K20" s="24">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="38" t="s">
+        <v>328</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="38" t="s">
+        <v>343</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="38" t="s">
+        <v>329</v>
+      </c>
+      <c r="F21" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="G21" s="7"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="K21" s="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="24" t="s">
+        <v>322</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="24" t="s">
+        <v>344</v>
+      </c>
+      <c r="D22" s="6"/>
+      <c r="E22" s="24" t="s">
+        <v>323</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="G22" s="7"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="K22" s="38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="38" t="s">
+        <v>345</v>
+      </c>
+      <c r="D23" s="6"/>
+      <c r="E23" s="38" t="s">
+        <v>317</v>
+      </c>
+      <c r="F23" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="G23" s="7"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="K23" s="24">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" s="5"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38" t="s">
+        <v>346</v>
+      </c>
+      <c r="D24" s="6"/>
+      <c r="E24" s="38" t="s">
+        <v>300</v>
+      </c>
+      <c r="F24" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="G24" s="7"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="6"/>
+      <c r="C27" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="6"/>
+      <c r="C28" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B29" s="6"/>
+      <c r="C29" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I29" s="9"/>
+      <c r="J29" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="K16" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I19" s="9"/>
-      <c r="J19" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K19" s="6"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I20" s="9"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I21" s="9"/>
-      <c r="J21" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="K21" s="6"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I22" s="9"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G23" s="6"/>
-      <c r="H23" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I23" s="9"/>
-      <c r="J23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K23" s="6"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I24" s="9"/>
-      <c r="J24" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="K24" s="6"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I25" s="9"/>
-      <c r="J25" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="K25" s="6"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="D26" s="6"/>
-      <c r="E26" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I26" s="9"/>
-      <c r="J26" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="K26" s="6"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I27" s="9"/>
-      <c r="J27" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="K27" s="6"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I28" s="9"/>
-      <c r="J28" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="K28" s="6"/>
-    </row>
-    <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="K29" s="6"/>
+      <c r="K29" s="12" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>105</v>
-      </c>
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="D30" s="6"/>
       <c r="E30" s="6"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="8" t="s">
-        <v>173</v>
-      </c>
+      <c r="F30" s="6"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="8"/>
       <c r="I30" s="9"/>
-      <c r="J30" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="K30" s="12"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
+      <c r="C31" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="F31" s="7" t="str">
+        <f>CONCATENATE("http://", E31)</f>
+        <v>http://192.168.201.110</v>
+      </c>
+      <c r="G31" s="23" t="s">
+        <v>236</v>
+      </c>
       <c r="H31" s="8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K31" s="6"/>
+        <v>96</v>
+      </c>
+      <c r="K31" s="12" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
+        <v>45</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K32" s="6"/>
+        <v>41</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
+        <v>42</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>38</v>
+      </c>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I33" s="9"/>
       <c r="J33" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K33" s="6"/>
+        <v>41</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
+      <c r="A34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
+      <c r="E34" s="6" t="s">
+        <v>229</v>
+      </c>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I34" s="9"/>
       <c r="J34" s="6" t="s">
-        <v>27</v>
+        <v>230</v>
       </c>
       <c r="K34" s="6"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I35" s="9"/>
-      <c r="J35" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K35" s="6" t="s">
-        <v>26</v>
+      <c r="A35" s="24"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="24" t="s">
+        <v>348</v>
+      </c>
+      <c r="D35" s="25"/>
+      <c r="E35" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="F35" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="G35" s="21"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="K35" s="38">
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
+        <v>203</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>202</v>
+      </c>
       <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
+      <c r="E36" s="6" t="s">
+        <v>201</v>
+      </c>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I36" s="9"/>
-      <c r="J36" s="6" t="s">
-        <v>27</v>
+      <c r="J36" s="5" t="s">
+        <v>200</v>
       </c>
       <c r="K36" s="6"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
+      <c r="A37" s="5"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="38" t="s">
+        <v>349</v>
+      </c>
       <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="8" t="s">
-        <v>173</v>
-      </c>
+      <c r="E37" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="F37" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="G37" s="7"/>
+      <c r="H37" s="8"/>
       <c r="I37" s="9"/>
-      <c r="J37" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K37" s="6"/>
+      <c r="J37" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="K37" s="24">
+        <v>11</v>
+      </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
+      <c r="A38" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5" t="s">
+        <v>228</v>
+      </c>
       <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
+      <c r="E38" s="6" t="s">
+        <v>227</v>
+      </c>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
       <c r="H38" s="8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I38" s="9"/>
-      <c r="J38" s="6" t="s">
-        <v>27</v>
-      </c>
+      <c r="J38" s="6"/>
       <c r="K38" s="6"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
+      <c r="A39" s="5"/>
+      <c r="B39" s="38"/>
+      <c r="C39" s="38" t="s">
+        <v>350</v>
+      </c>
       <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="8" t="s">
-        <v>173</v>
-      </c>
+      <c r="E39" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="F39" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="G39" s="7"/>
+      <c r="H39" s="8"/>
       <c r="I39" s="9"/>
-      <c r="J39" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K39" s="6"/>
+      <c r="J39" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="K39" s="24">
+        <v>30</v>
+      </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A40" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="F40" s="7" t="str">
-        <f>CONCATENATE("http://", E40)</f>
-        <v>http://192.168.0.22</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>173</v>
-      </c>
+      <c r="A40" s="5"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24" t="s">
+        <v>351</v>
+      </c>
+      <c r="D40" s="6"/>
+      <c r="E40" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="F40" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="G40" s="7"/>
+      <c r="H40" s="8"/>
       <c r="I40" s="9"/>
-      <c r="J40" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="K40" s="12"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A41" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="F41" s="7" t="str">
-        <f>CONCATENATE("http://", E41)</f>
-        <v>http://192.168.0.23</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="H41" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I41" s="9"/>
-      <c r="J41" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="K41" s="12"/>
+      <c r="A41" s="24"/>
+      <c r="B41" s="38"/>
+      <c r="C41" s="38" t="s">
+        <v>352</v>
+      </c>
+      <c r="D41" s="25"/>
+      <c r="E41" s="38" t="s">
+        <v>297</v>
+      </c>
+      <c r="F41" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="G41" s="21"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="25"/>
+      <c r="K41" s="25"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A42" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="F42" s="7" t="str">
-        <f>CONCATENATE("http://", E42)</f>
-        <v>http://192.168.0.24</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>173</v>
-      </c>
+      <c r="A42" s="5"/>
+      <c r="B42" s="38"/>
+      <c r="C42" s="38" t="s">
+        <v>353</v>
+      </c>
+      <c r="D42" s="6"/>
+      <c r="E42" s="38" t="s">
+        <v>294</v>
+      </c>
+      <c r="F42" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="G42" s="7"/>
+      <c r="H42" s="8"/>
       <c r="I42" s="9"/>
-      <c r="J42" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="K42" s="12"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A43" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="F43" s="7" t="str">
-        <f>CONCATENATE("http://", E43)</f>
-        <v>http://192.168.0.25</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>173</v>
-      </c>
+      <c r="A43" s="5"/>
+      <c r="B43" s="38"/>
+      <c r="C43" s="38" t="s">
+        <v>354</v>
+      </c>
+      <c r="D43" s="6"/>
+      <c r="E43" s="38" t="s">
+        <v>291</v>
+      </c>
+      <c r="F43" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="G43" s="7"/>
+      <c r="H43" s="8"/>
       <c r="I43" s="9"/>
-      <c r="J43" s="6" t="s">
-        <v>128</v>
-      </c>
+      <c r="J43" s="6"/>
       <c r="K43" s="6"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A44" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F44" s="7" t="str">
-        <f>CONCATENATE("http://", E44)</f>
-        <v>http://192.168.0.26</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>173</v>
-      </c>
+      <c r="A44" s="5"/>
+      <c r="B44" s="38"/>
+      <c r="C44" s="38" t="s">
+        <v>355</v>
+      </c>
+      <c r="D44" s="6"/>
+      <c r="E44" s="38" t="s">
+        <v>298</v>
+      </c>
+      <c r="F44" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="G44" s="7"/>
+      <c r="H44" s="8"/>
       <c r="I44" s="9"/>
-      <c r="J44" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="K44" s="12"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A45" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="8" t="s">
-        <v>173</v>
-      </c>
+      <c r="A45" s="5"/>
+      <c r="B45" s="38"/>
+      <c r="C45" s="38" t="s">
+        <v>356</v>
+      </c>
+      <c r="D45" s="6"/>
+      <c r="E45" s="38" t="s">
+        <v>296</v>
+      </c>
+      <c r="F45" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="G45" s="7"/>
+      <c r="H45" s="8"/>
       <c r="I45" s="9"/>
-      <c r="J45" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K45" s="6" t="s">
-        <v>257</v>
-      </c>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A46" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C46" s="5"/>
+      <c r="A46" s="5"/>
+      <c r="B46" s="38"/>
+      <c r="C46" s="38" t="s">
+        <v>357</v>
+      </c>
       <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
+      <c r="E46" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="F46" s="38" t="s">
+        <v>289</v>
+      </c>
       <c r="G46" s="7"/>
-      <c r="H46" s="8" t="s">
-        <v>173</v>
-      </c>
+      <c r="H46" s="8"/>
       <c r="I46" s="9"/>
-      <c r="J46" s="6" t="s">
-        <v>220</v>
-      </c>
+      <c r="J46" s="6"/>
       <c r="K46" s="6"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="8" t="s">
-        <v>173</v>
-      </c>
+      <c r="A47" s="5"/>
+      <c r="B47" s="24"/>
+      <c r="C47" s="24" t="s">
+        <v>358</v>
+      </c>
+      <c r="D47" s="6"/>
+      <c r="E47" s="24" t="s">
+        <v>299</v>
+      </c>
+      <c r="F47" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="G47" s="7"/>
+      <c r="H47" s="8"/>
       <c r="I47" s="9"/>
-      <c r="J47" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K47" s="6" t="s">
-        <v>257</v>
-      </c>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A48" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C48" s="5"/>
+      <c r="A48" s="5"/>
+      <c r="B48" s="24"/>
+      <c r="C48" s="24" t="s">
+        <v>359</v>
+      </c>
       <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
+      <c r="E48" s="24" t="s">
+        <v>302</v>
+      </c>
+      <c r="F48" s="24" t="s">
+        <v>289</v>
+      </c>
       <c r="G48" s="7"/>
-      <c r="H48" s="8" t="s">
-        <v>173</v>
-      </c>
+      <c r="H48" s="8"/>
       <c r="I48" s="9"/>
-      <c r="J48" s="6" t="s">
-        <v>220</v>
-      </c>
+      <c r="J48" s="6"/>
       <c r="K48" s="6"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A49" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="6"/>
+      <c r="A49" s="5"/>
+      <c r="B49" s="24"/>
+      <c r="C49" s="24" t="s">
+        <v>360</v>
+      </c>
       <c r="D49" s="6"/>
-      <c r="E49" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
+      <c r="E49" s="24" t="s">
+        <v>293</v>
+      </c>
+      <c r="F49" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="G49" s="7"/>
       <c r="H49" s="8"/>
       <c r="I49" s="9"/>
-      <c r="J49" s="6" t="s">
-        <v>12</v>
-      </c>
+      <c r="J49" s="6"/>
       <c r="K49" s="6"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A50" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5" t="s">
-        <v>9</v>
+      <c r="A50" s="5"/>
+      <c r="B50" s="24"/>
+      <c r="C50" s="24" t="s">
+        <v>361</v>
       </c>
       <c r="D50" s="6"/>
-      <c r="E50" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="8" t="s">
-        <v>172</v>
-      </c>
+      <c r="E50" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="F50" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="G50" s="7"/>
+      <c r="H50" s="8"/>
       <c r="I50" s="9"/>
-      <c r="J50" s="6" t="s">
-        <v>232</v>
-      </c>
+      <c r="J50" s="6"/>
       <c r="K50" s="6"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A51" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I51" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="J51" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="K51" s="6" t="s">
-        <v>47</v>
-      </c>
+      <c r="A51" s="5"/>
+      <c r="B51" s="38"/>
+      <c r="C51" s="38" t="s">
+        <v>362</v>
+      </c>
+      <c r="D51" s="6"/>
+      <c r="E51" s="38" t="s">
+        <v>292</v>
+      </c>
+      <c r="F51" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="G51" s="7"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A52" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B52" s="6"/>
-      <c r="C52" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I52" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="J52" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="K52" s="6" t="s">
-        <v>47</v>
-      </c>
+      <c r="A52" s="24"/>
+      <c r="B52" s="38"/>
+      <c r="C52" s="38" t="s">
+        <v>363</v>
+      </c>
+      <c r="D52" s="25"/>
+      <c r="E52" s="38" t="s">
+        <v>288</v>
+      </c>
+      <c r="F52" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="G52" s="21"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="26"/>
+      <c r="J52" s="25"/>
+      <c r="K52" s="25"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A53" s="6" t="s">
-        <v>52</v>
+      <c r="A53" s="25" t="s">
+        <v>112</v>
       </c>
       <c r="B53" s="6"/>
-      <c r="C53" s="23" t="s">
-        <v>51</v>
+      <c r="C53" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
+        <v>109</v>
+      </c>
+      <c r="F53" s="7" t="str">
+        <f>CONCATENATE("http://", E53)</f>
+        <v>http://192.168.0.180</v>
+      </c>
+      <c r="G53" s="7"/>
       <c r="H53" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I53" s="9" t="s">
-        <v>276</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="I53" s="9"/>
       <c r="J53" s="6" t="s">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="K53" s="6" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="B54" s="6"/>
-      <c r="C54" s="23" t="s">
-        <v>48</v>
+      <c r="C54" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
+        <v>103</v>
+      </c>
+      <c r="F54" s="7" t="str">
+        <f>CONCATENATE("http://", E54)</f>
+        <v>http://192.168.0.181</v>
+      </c>
+      <c r="G54" s="7"/>
       <c r="H54" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I54" s="9" t="s">
-        <v>276</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="I54" s="9"/>
       <c r="J54" s="6" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A55" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="B55" s="10"/>
+      <c r="A55" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B55" s="6"/>
       <c r="C55" s="6" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F55" s="6" t="str">
-        <f>CONCATENATE("http://", E55, ":8080")</f>
-        <v>http://192.168.0.197:8080</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>237</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="F55" s="7" t="str">
+        <f>CONCATENATE("http://", E55)</f>
+        <v>http://192.168.0.192</v>
+      </c>
+      <c r="G55" s="7"/>
       <c r="H55" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K55" s="6"/>
+        <v>89</v>
+      </c>
+      <c r="K55" s="12" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A56" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="F56" s="7" t="str">
-        <f>CONCATENATE("http://", E56)</f>
-        <v>http://192.168.0.186</v>
+      <c r="A56" s="38" t="s">
+        <v>313</v>
+      </c>
+      <c r="B56" s="5"/>
+      <c r="C56" s="38" t="s">
+        <v>238</v>
+      </c>
+      <c r="D56" s="6"/>
+      <c r="E56" s="38" t="s">
+        <v>237</v>
+      </c>
+      <c r="F56" s="38" t="s">
+        <v>289</v>
       </c>
       <c r="G56" s="7"/>
-      <c r="H56" s="8" t="s">
-        <v>172</v>
-      </c>
+      <c r="H56" s="8"/>
       <c r="I56" s="9"/>
-      <c r="J56" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="K56" s="6" t="s">
-        <v>75</v>
+      <c r="J56" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="K56" s="24">
+        <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A57" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B57" s="6"/>
-      <c r="C57" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>40</v>
-      </c>
+      <c r="A57" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="B57" s="5"/>
+      <c r="C57" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="D57" s="6"/>
       <c r="E57" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="F57" s="7" t="str">
-        <f>CONCATENATE("http://", E57)</f>
-        <v>http://192.168.0.187</v>
-      </c>
-      <c r="G57" s="7"/>
+        <v>237</v>
+      </c>
+      <c r="F57" s="6"/>
+      <c r="G57" s="21" t="s">
+        <v>236</v>
+      </c>
       <c r="H57" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="K57" s="6" t="s">
-        <v>71</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="K57" s="6"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A58" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="F58" s="7" t="str">
-        <f>CONCATENATE("http://", E58)</f>
-        <v>http://192.168.0.188</v>
+      <c r="A58" s="41" t="s">
+        <v>204</v>
+      </c>
+      <c r="B58" s="5"/>
+      <c r="C58" s="24" t="s">
+        <v>364</v>
+      </c>
+      <c r="D58" s="6"/>
+      <c r="E58" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="F58" s="24" t="s">
+        <v>289</v>
       </c>
       <c r="G58" s="7"/>
-      <c r="H58" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I58" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="J58" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="K58" s="6" t="s">
-        <v>66</v>
-      </c>
+      <c r="H58" s="8"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A59" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>105</v>
-      </c>
+      <c r="A59" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B59" s="14"/>
+      <c r="C59" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="D59" s="6"/>
       <c r="E59" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F59" s="7" t="str">
-        <f>CONCATENATE("http://", E59)</f>
-        <v>http://192.168.0.180</v>
-      </c>
-      <c r="G59" s="7"/>
+        <v>205</v>
+      </c>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6" t="s">
+        <v>236</v>
+      </c>
       <c r="H59" s="8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I59" s="9"/>
-      <c r="J59" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="K59" s="6" t="s">
-        <v>109</v>
-      </c>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="6" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="F60" s="7" t="str">
         <f>CONCATENATE("http://", E60)</f>
-        <v>http://192.168.0.181</v>
-      </c>
-      <c r="G60" s="7"/>
+        <v>http://192.168.0.23</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>236</v>
+      </c>
       <c r="H60" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I60" s="9"/>
       <c r="J60" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="K60" s="6" t="s">
-        <v>103</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="K60" s="12"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A61" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="B61" s="5"/>
+      <c r="A61" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B61" s="6"/>
       <c r="C61" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="8" t="s">
-        <v>173</v>
+        <v>136</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E61" s="6"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="7"/>
+      <c r="H61" s="20" t="s">
+        <v>171</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="K61" s="6"/>
+        <v>137</v>
+      </c>
+      <c r="K61" s="12"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A62" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B62" s="5"/>
+      <c r="A62" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B62" s="6"/>
       <c r="C62" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D62" s="6"/>
+        <v>136</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>104</v>
+      </c>
       <c r="E62" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="21" t="s">
-        <v>172</v>
+        <v>135</v>
+      </c>
+      <c r="F62" s="7" t="str">
+        <f>CONCATENATE("http://", E62)</f>
+        <v>http://192.168.0.22</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="H62" s="20" t="s">
+        <v>171</v>
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="K62" s="6"/>
+        <v>127</v>
+      </c>
+      <c r="K62" s="12"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" s="6" t="s">
-        <v>98</v>
+        <v>11</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="6" t="s">
-        <v>283</v>
+        <v>131</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>286</v>
+        <v>130</v>
       </c>
       <c r="F63" s="7" t="str">
         <f>CONCATENATE("http://", E63)</f>
-        <v>http://192.168.201.110</v>
-      </c>
-      <c r="G63" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="H63" s="21" t="s">
-        <v>172</v>
+        <v>http://192.168.0.24</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="H63" s="20" t="s">
+        <v>171</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="K63" s="12" t="s">
-        <v>87</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="K63" s="12"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" s="6" t="s">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="6" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>88</v>
+        <v>104</v>
+      </c>
+      <c r="E64" s="15" t="s">
+        <v>128</v>
       </c>
       <c r="F64" s="7" t="str">
         <f>CONCATENATE("http://", E64)</f>
-        <v>http://192.168.0.192</v>
-      </c>
-      <c r="G64" s="7"/>
-      <c r="H64" s="21" t="s">
-        <v>173</v>
+        <v>http://192.168.0.25</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="H64" s="20" t="s">
+        <v>171</v>
       </c>
       <c r="I64" s="9"/>
       <c r="J64" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="K64" s="12" t="s">
-        <v>87</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="K64" s="6"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="6" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="21" t="s">
-        <v>173</v>
+        <v>125</v>
+      </c>
+      <c r="F65" s="7" t="str">
+        <f>CONCATENATE("http://", E65)</f>
+        <v>http://192.168.0.26</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="H65" s="20" t="s">
+        <v>171</v>
       </c>
       <c r="I65" s="9"/>
       <c r="J65" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="K65" s="6" t="s">
-        <v>92</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="K65" s="12"/>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A66" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B66" s="6"/>
+      <c r="A66" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B66" s="10"/>
       <c r="C66" s="6" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="I66" s="9" t="s">
-        <v>276</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="F66" s="6" t="str">
+        <f>CONCATENATE("http://", E66, ":8080")</f>
+        <v>http://192.168.0.197:8080</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="H66" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="I66" s="9"/>
       <c r="J66" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="K66" s="12" t="s">
-        <v>79</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="K66" s="6"/>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="6" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F67" s="7" t="str">
-        <f>CONCATENATE("ftp://", E67)</f>
-        <v>ftp://192.168.0.189</v>
-      </c>
-      <c r="G67" s="7"/>
-      <c r="H67" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="I67" s="9" t="s">
-        <v>276</v>
-      </c>
+        <f>CONCATENATE("http://", E67)</f>
+        <v>http://192.168.0.193</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="H67" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="I67" s="9"/>
       <c r="J67" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="K67" s="12" t="s">
-        <v>79</v>
+        <v>68</v>
+      </c>
+      <c r="K67" s="6" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="B68" s="6"/>
-      <c r="C68" s="6" t="s">
-        <v>81</v>
+      <c r="C68" s="18" t="s">
+        <v>118</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="F68" s="7" t="str">
-        <f>CONCATENATE("ftp://", E68)</f>
-        <v>ftp://192.168.0.190</v>
+        <f>CONCATENATE("http://", E68)</f>
+        <v>http://192.168.0.187</v>
       </c>
       <c r="G68" s="7"/>
-      <c r="H68" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="I68" s="9" t="s">
-        <v>276</v>
-      </c>
+      <c r="H68" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="I68" s="9"/>
       <c r="J68" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="K68" s="12" t="s">
-        <v>79</v>
+        <v>119</v>
+      </c>
+      <c r="K68" s="6" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="6" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="F69" s="7" t="str">
         <f>CONCATENATE("http://", E69)</f>
-        <v>http://192.168.0.183</v>
-      </c>
-      <c r="G69" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="H69" s="21" t="s">
-        <v>172</v>
+        <v>http://192.168.0.188</v>
+      </c>
+      <c r="G69" s="7"/>
+      <c r="H69" s="20" t="s">
+        <v>170</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A70" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F70" s="7" t="str">
-        <f>CONCATENATE("http://", E70)</f>
-        <v>http://192.168.0.193</v>
-      </c>
-      <c r="G70" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="H70" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="I70" s="9"/>
-      <c r="J70" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="K70" s="6" t="s">
-        <v>75</v>
-      </c>
+      <c r="A70" s="24" t="s">
+        <v>284</v>
+      </c>
+      <c r="B70" s="24"/>
+      <c r="C70" s="24" t="s">
+        <v>365</v>
+      </c>
+      <c r="D70" s="25"/>
+      <c r="E70" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="F70" s="25"/>
+      <c r="G70" s="21"/>
+      <c r="H70" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="I70" s="26"/>
+      <c r="J70" s="25" t="s">
+        <v>285</v>
+      </c>
+      <c r="K70" s="25"/>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A71" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="F71" s="7" t="str">
-        <f>CONCATENATE("http://", E71)</f>
-        <v>http://192.168.0.194</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="H71" s="21" t="s">
-        <v>173</v>
-      </c>
+      <c r="A71" s="5"/>
+      <c r="B71" s="24"/>
+      <c r="C71" s="24" t="s">
+        <v>365</v>
+      </c>
+      <c r="D71" s="6"/>
+      <c r="E71" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="F71" s="24" t="s">
+        <v>310</v>
+      </c>
+      <c r="G71" s="7"/>
+      <c r="H71" s="20"/>
       <c r="I71" s="9"/>
-      <c r="J71" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="K71" s="6" t="s">
-        <v>71</v>
+      <c r="J71" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="K71" s="38">
+        <v>12</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A72" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B72" s="6"/>
-      <c r="C72" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F72" s="7" t="str">
-        <f>CONCATENATE("http://", E72)</f>
-        <v>http://192.168.0.195</v>
-      </c>
-      <c r="G72" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="H72" s="21" t="s">
-        <v>173</v>
-      </c>
+      <c r="A72" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B72" s="5"/>
+      <c r="C72" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72" s="6"/>
+      <c r="E72" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="F72" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="G72" s="7"/>
+      <c r="H72" s="20"/>
       <c r="I72" s="9"/>
-      <c r="J72" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="K72" s="6" t="s">
-        <v>66</v>
+      <c r="J72" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="K72" s="38">
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B73" s="5"/>
-      <c r="C73" s="6" t="s">
-        <v>17</v>
+      <c r="C73" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="D73" s="6"/>
-      <c r="E73" s="6"/>
-      <c r="F73" s="6"/>
+      <c r="E73" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="G73" s="6"/>
-      <c r="H73" s="21" t="s">
-        <v>173</v>
+      <c r="H73" s="20" t="s">
+        <v>170</v>
       </c>
       <c r="I73" s="9"/>
       <c r="J73" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K73" s="6" t="s">
-        <v>16</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="K73" s="6"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="B74" s="5"/>
-      <c r="C74" s="6" t="s">
-        <v>240</v>
+        <v>7</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>184</v>
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="F74" s="6"/>
-      <c r="G74" s="22" t="s">
-        <v>238</v>
-      </c>
-      <c r="H74" s="21" t="s">
-        <v>172</v>
+        <v>185</v>
+      </c>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="H74" s="20" t="s">
+        <v>170</v>
       </c>
       <c r="I74" s="9"/>
-      <c r="J74" s="6" t="s">
-        <v>242</v>
-      </c>
+      <c r="J74" s="6"/>
       <c r="K74" s="6"/>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A75" s="5" t="s">
-        <v>243</v>
+      <c r="A75" s="19" t="s">
+        <v>231</v>
       </c>
       <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
+      <c r="C75" s="6" t="s">
+        <v>366</v>
+      </c>
       <c r="D75" s="6"/>
-      <c r="E75" s="6"/>
+      <c r="E75" s="6" t="s">
+        <v>154</v>
+      </c>
       <c r="F75" s="6"/>
-      <c r="G75" s="22"/>
-      <c r="H75" s="21" t="s">
-        <v>173</v>
+      <c r="G75" s="6"/>
+      <c r="H75" s="20" t="s">
+        <v>171</v>
       </c>
       <c r="I75" s="9"/>
-      <c r="J75" s="6"/>
+      <c r="J75" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="K75" s="6"/>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>244</v>
+        <v>155</v>
       </c>
       <c r="B76" s="5"/>
-      <c r="C76" s="5"/>
+      <c r="C76" s="6" t="s">
+        <v>367</v>
+      </c>
       <c r="D76" s="6"/>
       <c r="E76" s="6" t="s">
-        <v>246</v>
+        <v>192</v>
       </c>
       <c r="F76" s="6"/>
-      <c r="G76" s="22"/>
-      <c r="H76" s="21"/>
+      <c r="G76" s="6"/>
+      <c r="H76" s="20" t="s">
+        <v>170</v>
+      </c>
       <c r="I76" s="9"/>
-      <c r="J76" s="6"/>
+      <c r="J76" s="6" t="s">
+        <v>191</v>
+      </c>
       <c r="K76" s="6"/>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A77" s="5" t="s">
-        <v>245</v>
+      <c r="A77" s="38" t="s">
+        <v>308</v>
       </c>
       <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
+      <c r="C77" s="38" t="s">
+        <v>367</v>
+      </c>
       <c r="D77" s="6"/>
-      <c r="E77" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="F77" s="6"/>
-      <c r="G77" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="H77" s="21" t="s">
-        <v>172</v>
-      </c>
+      <c r="E77" s="38" t="s">
+        <v>192</v>
+      </c>
+      <c r="F77" s="38" t="s">
+        <v>305</v>
+      </c>
+      <c r="G77" s="7"/>
+      <c r="H77" s="20"/>
       <c r="I77" s="9"/>
-      <c r="J77" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="K77" s="6"/>
+      <c r="J77" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="K77" s="24">
+        <v>6</v>
+      </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>255</v>
+        <v>149</v>
       </c>
       <c r="B78" s="5"/>
-      <c r="C78" s="5"/>
+      <c r="C78" s="6" t="s">
+        <v>151</v>
+      </c>
       <c r="D78" s="6"/>
-      <c r="E78" s="15" t="s">
-        <v>251</v>
-      </c>
-      <c r="F78" s="6"/>
-      <c r="G78" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="H78" s="21" t="s">
-        <v>172</v>
+      <c r="E78" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F78" s="7" t="str">
+        <f>CONCATENATE("http://", E78)</f>
+        <v>http://192.168.0.208</v>
+      </c>
+      <c r="G78" s="7"/>
+      <c r="H78" s="20" t="s">
+        <v>170</v>
       </c>
       <c r="I78" s="9"/>
       <c r="J78" s="6" t="s">
-        <v>252</v>
+        <v>150</v>
       </c>
       <c r="K78" s="6"/>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="B79" s="5"/>
-      <c r="C79" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>40</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C79" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="D79" s="6"/>
       <c r="E79" s="6" t="s">
-        <v>268</v>
+        <v>180</v>
       </c>
       <c r="F79" s="6"/>
-      <c r="G79" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="H79" s="21" t="s">
-        <v>172</v>
+      <c r="G79" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="H79" s="20" t="s">
+        <v>170</v>
       </c>
       <c r="I79" s="9"/>
       <c r="J79" s="6" t="s">
-        <v>69</v>
+        <v>165</v>
       </c>
       <c r="K79" s="6"/>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A80" s="5" t="s">
-        <v>265</v>
+      <c r="A80" s="24" t="s">
+        <v>1</v>
       </c>
       <c r="B80" s="5"/>
-      <c r="C80" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="F80" s="6"/>
-      <c r="G80" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="H80" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="I80" s="9"/>
-      <c r="J80" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="K80" s="6"/>
+      <c r="C80" s="24" t="s">
+        <v>368</v>
+      </c>
+      <c r="D80" s="25"/>
+      <c r="E80" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="F80" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="G80" s="21"/>
+      <c r="H80" s="20"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="K80" s="38">
+        <v>19</v>
+      </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B81" s="5"/>
-      <c r="C81" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>270</v>
+        <v>1</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="D81" s="6"/>
+      <c r="E81" s="15" t="s">
+        <v>175</v>
       </c>
       <c r="F81" s="6"/>
-      <c r="G81" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="H81" s="21" t="s">
-        <v>172</v>
+      <c r="G81" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="H81" s="20" t="s">
+        <v>170</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="6" t="s">
-        <v>69</v>
+        <v>168</v>
       </c>
       <c r="K81" s="6"/>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A82" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="B82" s="5"/>
-      <c r="C82" s="5"/>
+      <c r="A82" s="5"/>
+      <c r="B82" s="38"/>
+      <c r="C82" s="38" t="s">
+        <v>369</v>
+      </c>
       <c r="D82" s="6"/>
-      <c r="E82" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="F82" s="6"/>
-      <c r="G82" s="22" t="s">
-        <v>238</v>
-      </c>
-      <c r="H82" s="21" t="s">
-        <v>172</v>
-      </c>
+      <c r="E82" s="38" t="s">
+        <v>309</v>
+      </c>
+      <c r="F82" s="38" t="s">
+        <v>305</v>
+      </c>
+      <c r="G82" s="7"/>
+      <c r="H82" s="20"/>
       <c r="I82" s="9"/>
-      <c r="J82" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="K82" s="6"/>
+      <c r="J82" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="K82" s="24">
+        <v>8</v>
+      </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A83" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="B83" s="5"/>
-      <c r="C83" s="5" t="s">
-        <v>278</v>
+      <c r="A83" s="5"/>
+      <c r="B83" s="24"/>
+      <c r="C83" s="24" t="s">
+        <v>370</v>
       </c>
       <c r="D83" s="6"/>
-      <c r="E83" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="F83" s="6"/>
-      <c r="G83" s="22"/>
-      <c r="H83" s="21" t="s">
-        <v>173</v>
-      </c>
+      <c r="E83" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="F83" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="G83" s="7"/>
+      <c r="H83" s="20"/>
       <c r="I83" s="9"/>
-      <c r="J83" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="K83" s="6"/>
+      <c r="J83" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="K83" s="38">
+        <v>5</v>
+      </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A84" s="5"/>
-      <c r="B84" s="5"/>
-      <c r="C84" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="D84" s="6"/>
-      <c r="E84" s="6"/>
+      <c r="A84" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="F84" s="6"/>
-      <c r="G84" s="22"/>
-      <c r="H84" s="21"/>
-      <c r="I84" s="9"/>
-      <c r="J84" s="6"/>
-      <c r="K84" s="6" t="s">
-        <v>285</v>
+      <c r="G84" s="6"/>
+      <c r="H84" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="J84" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="K84" s="12" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A85" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="B85" s="5"/>
-      <c r="C85" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="D85" s="6"/>
+      <c r="A85" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>39</v>
+      </c>
       <c r="E85" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="F85" s="6"/>
-      <c r="G85" s="22" t="s">
-        <v>238</v>
-      </c>
-      <c r="H85" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="I85" s="9"/>
+        <v>61</v>
+      </c>
+      <c r="F85" s="7" t="str">
+        <f>CONCATENATE("http://", E85)</f>
+        <v>http://192.168.0.183</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="H85" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="I85" s="9" t="s">
+        <v>270</v>
+      </c>
       <c r="J85" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="K85" s="6"/>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+      <c r="K85" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="B86" s="5"/>
       <c r="C86" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="D86" s="6"/>
+        <v>371</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>39</v>
+      </c>
       <c r="E86" s="6" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
       <c r="F86" s="6"/>
-      <c r="G86" s="22" t="s">
-        <v>238</v>
-      </c>
-      <c r="H86" s="21" t="s">
-        <v>172</v>
+      <c r="G86" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="H86" s="20" t="s">
+        <v>170</v>
       </c>
       <c r="I86" s="9"/>
       <c r="J86" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="K86" s="6"/>
+    </row>
+    <row r="87" spans="1:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="40" t="s">
+        <v>262</v>
+      </c>
+      <c r="B87" s="5"/>
+      <c r="C87" s="38" t="s">
+        <v>371</v>
+      </c>
+      <c r="D87" s="6"/>
+      <c r="E87" s="38" t="s">
+        <v>265</v>
+      </c>
+      <c r="F87" s="38" t="s">
+        <v>305</v>
+      </c>
+      <c r="G87" s="7"/>
+      <c r="H87" s="20"/>
+      <c r="I87" s="9"/>
+      <c r="J87" s="6"/>
+      <c r="K87" s="6"/>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A88" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B88" s="33"/>
+      <c r="C88" s="34" t="s">
+        <v>372</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E88" s="45" t="s">
+        <v>266</v>
+      </c>
+      <c r="F88" s="45"/>
+      <c r="G88" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="H88" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="I88" s="9"/>
+      <c r="J88" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="K88" s="6"/>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A89" s="38" t="s">
+        <v>263</v>
+      </c>
+      <c r="B89" s="30"/>
+      <c r="C89" s="28" t="s">
+        <v>372</v>
+      </c>
+      <c r="D89" s="6"/>
+      <c r="E89" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="F89" s="28" t="s">
+        <v>305</v>
+      </c>
+      <c r="G89" s="7"/>
+      <c r="H89" s="8"/>
+      <c r="I89" s="9"/>
+      <c r="J89" s="24" t="s">
         <v>290</v>
       </c>
-      <c r="K86" s="6"/>
-    </row>
-    <row r="87" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="25" t="s">
-        <v>296</v>
-      </c>
-      <c r="B87" s="25"/>
-      <c r="C87" s="25" t="s">
-        <v>294</v>
-      </c>
-      <c r="D87" s="26"/>
-      <c r="E87" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="F87" s="26"/>
-      <c r="G87" s="22"/>
-      <c r="H87" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="I87" s="27"/>
-      <c r="J87" s="26" t="s">
-        <v>297</v>
-      </c>
-      <c r="K87" s="26"/>
-    </row>
-    <row r="88" spans="1:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="28" t="s">
-        <v>298</v>
-      </c>
-      <c r="B88" s="25"/>
-      <c r="C88" s="25"/>
-      <c r="D88" s="26"/>
-      <c r="E88" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="F88" s="26"/>
-      <c r="G88" s="22"/>
-      <c r="H88" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="I88" s="27"/>
-      <c r="J88" s="26"/>
-      <c r="K88" s="26"/>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A89" s="25"/>
-      <c r="B89" s="31"/>
-      <c r="C89" s="32" t="s">
-        <v>300</v>
-      </c>
-      <c r="D89" s="26"/>
-      <c r="E89" s="32" t="s">
-        <v>301</v>
-      </c>
-      <c r="F89" s="32" t="s">
-        <v>302</v>
-      </c>
-      <c r="G89" s="22"/>
-      <c r="H89" s="21"/>
-      <c r="I89" s="27"/>
-      <c r="J89" s="26"/>
-      <c r="K89" s="26"/>
+      <c r="K89" s="24">
+        <v>2</v>
+      </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A90" s="5"/>
-      <c r="B90" s="33"/>
-      <c r="C90" s="34" t="s">
-        <v>304</v>
-      </c>
-      <c r="D90" s="6"/>
-      <c r="E90" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="F90" s="34" t="s">
-        <v>302</v>
+      <c r="A90" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B90" s="39"/>
+      <c r="C90" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E90" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F90" s="46" t="str">
+        <f>CONCATENATE("ftp://", E90)</f>
+        <v>ftp://192.168.0.189</v>
       </c>
       <c r="G90" s="7"/>
-      <c r="H90" s="8"/>
-      <c r="I90" s="9"/>
-      <c r="J90" s="6"/>
-      <c r="K90" s="6"/>
+      <c r="H90" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="J90" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K90" s="12" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A91" s="5"/>
-      <c r="B91" s="29"/>
-      <c r="C91" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="D91" s="6"/>
-      <c r="E91" s="30" t="s">
-        <v>306</v>
-      </c>
-      <c r="F91" s="30" t="s">
-        <v>302</v>
+      <c r="A91" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B91" s="39"/>
+      <c r="C91" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E91" s="43" t="s">
+        <v>79</v>
+      </c>
+      <c r="F91" s="46" t="str">
+        <f>CONCATENATE("ftp://", E91)</f>
+        <v>ftp://192.168.0.190</v>
       </c>
       <c r="G91" s="7"/>
-      <c r="H91" s="8"/>
-      <c r="I91" s="9"/>
-      <c r="J91" s="6"/>
-      <c r="K91" s="6"/>
+      <c r="H91" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I91" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="J91" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K91" s="12" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A92" s="5"/>
-      <c r="B92" s="33"/>
-      <c r="C92" s="34" t="s">
-        <v>307</v>
+      <c r="A92" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B92" s="30"/>
+      <c r="C92" s="43" t="s">
+        <v>373</v>
       </c>
       <c r="D92" s="6"/>
-      <c r="E92" s="34" t="s">
-        <v>198</v>
-      </c>
-      <c r="F92" s="34" t="s">
-        <v>302</v>
-      </c>
-      <c r="G92" s="7"/>
-      <c r="H92" s="8"/>
+      <c r="E92" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="F92" s="43"/>
+      <c r="G92" s="6"/>
+      <c r="H92" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="I92" s="9"/>
       <c r="J92" s="6"/>
       <c r="K92" s="6"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A93" s="5"/>
-      <c r="B93" s="29"/>
-      <c r="C93" s="30" t="s">
-        <v>308</v>
+      <c r="A93" s="38" t="s">
+        <v>312</v>
+      </c>
+      <c r="B93" s="30"/>
+      <c r="C93" s="28" t="s">
+        <v>373</v>
       </c>
       <c r="D93" s="6"/>
-      <c r="E93" s="30" t="s">
-        <v>309</v>
-      </c>
-      <c r="F93" s="30" t="s">
-        <v>302</v>
+      <c r="E93" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="F93" s="28" t="s">
+        <v>305</v>
       </c>
       <c r="G93" s="7"/>
       <c r="H93" s="8"/>
       <c r="I93" s="9"/>
-      <c r="J93" s="6"/>
-      <c r="K93" s="6"/>
+      <c r="J93" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="K93" s="24">
+        <v>18</v>
+      </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A94" s="5"/>
-      <c r="B94" s="33"/>
-      <c r="C94" s="34" t="s">
-        <v>310</v>
-      </c>
-      <c r="D94" s="6"/>
-      <c r="E94" s="34" t="s">
-        <v>311</v>
-      </c>
-      <c r="F94" s="34" t="s">
-        <v>302</v>
-      </c>
-      <c r="G94" s="7"/>
-      <c r="H94" s="8"/>
+      <c r="A94" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B94" s="39"/>
+      <c r="C94" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E94" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="F94" s="43"/>
+      <c r="G94" s="6"/>
+      <c r="H94" s="8" t="s">
+        <v>171</v>
+      </c>
       <c r="I94" s="9"/>
-      <c r="J94" s="6"/>
-      <c r="K94" s="6"/>
+      <c r="J94" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="K94" s="6" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A95" s="5"/>
-      <c r="B95" s="29"/>
-      <c r="C95" s="30" t="s">
-        <v>312</v>
+      <c r="A95" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B95" s="30"/>
+      <c r="C95" s="43" t="s">
+        <v>374</v>
       </c>
       <c r="D95" s="6"/>
-      <c r="E95" s="30" t="s">
-        <v>313</v>
-      </c>
-      <c r="F95" s="30" t="s">
-        <v>302</v>
-      </c>
-      <c r="G95" s="7"/>
-      <c r="H95" s="8"/>
+      <c r="E95" s="43" t="s">
+        <v>160</v>
+      </c>
+      <c r="F95" s="43"/>
+      <c r="G95" s="6"/>
+      <c r="H95" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="I95" s="9"/>
       <c r="J95" s="6"/>
       <c r="K95" s="6"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A96" s="5"/>
-      <c r="B96" s="33"/>
-      <c r="C96" s="34" t="s">
-        <v>314</v>
+      <c r="A96" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="B96" s="30"/>
+      <c r="C96" s="31" t="s">
+        <v>374</v>
       </c>
       <c r="D96" s="6"/>
-      <c r="E96" s="34" t="s">
-        <v>315</v>
-      </c>
-      <c r="F96" s="34" t="s">
-        <v>302</v>
+      <c r="E96" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="F96" s="31" t="s">
+        <v>305</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="8"/>
       <c r="I96" s="9"/>
-      <c r="J96" s="6"/>
-      <c r="K96" s="6"/>
+      <c r="J96" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="K96" s="38">
+        <v>14</v>
+      </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A97" s="5"/>
-      <c r="B97" s="29"/>
-      <c r="C97" s="30" t="s">
-        <v>316</v>
+      <c r="A97" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B97" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="C97" s="44" t="s">
+        <v>176</v>
       </c>
       <c r="D97" s="6"/>
-      <c r="E97" s="30" t="s">
-        <v>317</v>
-      </c>
-      <c r="F97" s="30" t="s">
-        <v>302</v>
-      </c>
-      <c r="G97" s="7"/>
-      <c r="H97" s="8"/>
+      <c r="E97" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="F97" s="43"/>
+      <c r="G97" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="H97" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="I97" s="9"/>
-      <c r="J97" s="6"/>
+      <c r="J97" s="6" t="s">
+        <v>181</v>
+      </c>
       <c r="K97" s="6"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A98" s="5"/>
+      <c r="A98" s="5" t="s">
+        <v>261</v>
+      </c>
       <c r="B98" s="33"/>
       <c r="C98" s="34" t="s">
-        <v>318</v>
-      </c>
-      <c r="D98" s="6"/>
-      <c r="E98" s="34" t="s">
-        <v>209</v>
-      </c>
-      <c r="F98" s="34" t="s">
-        <v>302</v>
-      </c>
-      <c r="G98" s="7"/>
-      <c r="H98" s="8"/>
+        <v>375</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E98" s="45" t="s">
+        <v>264</v>
+      </c>
+      <c r="F98" s="45"/>
+      <c r="G98" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="H98" s="20" t="s">
+        <v>170</v>
+      </c>
       <c r="I98" s="9"/>
-      <c r="J98" s="6"/>
+      <c r="J98" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="K98" s="6"/>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A99" s="25"/>
-      <c r="B99" s="31"/>
-      <c r="C99" s="32" t="s">
-        <v>319</v>
-      </c>
-      <c r="D99" s="26"/>
-      <c r="E99" s="32" t="s">
-        <v>320</v>
-      </c>
-      <c r="F99" s="32" t="s">
-        <v>302</v>
-      </c>
-      <c r="G99" s="22"/>
-      <c r="H99" s="21"/>
-      <c r="I99" s="27"/>
-      <c r="J99" s="26"/>
-      <c r="K99" s="26"/>
+      <c r="A99" s="5"/>
+      <c r="B99" s="27"/>
+      <c r="C99" s="28" t="s">
+        <v>375</v>
+      </c>
+      <c r="D99" s="6"/>
+      <c r="E99" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="F99" s="28" t="s">
+        <v>305</v>
+      </c>
+      <c r="G99" s="7"/>
+      <c r="H99" s="8"/>
+      <c r="I99" s="9"/>
+      <c r="J99" s="6"/>
+      <c r="K99" s="6"/>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A100" s="5"/>
-      <c r="B100" s="33"/>
-      <c r="C100" s="34" t="s">
-        <v>321</v>
+      <c r="A100" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B100" s="30"/>
+      <c r="C100" s="31" t="s">
+        <v>376</v>
       </c>
       <c r="D100" s="6"/>
-      <c r="E100" s="34" t="s">
-        <v>212</v>
-      </c>
-      <c r="F100" s="34" t="s">
-        <v>302</v>
-      </c>
-      <c r="G100" s="7"/>
-      <c r="H100" s="8"/>
+      <c r="E100" s="43" t="s">
+        <v>274</v>
+      </c>
+      <c r="F100" s="43"/>
+      <c r="G100" s="21"/>
+      <c r="H100" s="8" t="s">
+        <v>171</v>
+      </c>
       <c r="I100" s="9"/>
-      <c r="J100" s="6"/>
+      <c r="J100" s="6" t="s">
+        <v>273</v>
+      </c>
       <c r="K100" s="6"/>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A101" s="5"/>
-      <c r="B101" s="29"/>
-      <c r="C101" s="30" t="s">
-        <v>322</v>
+      <c r="A101" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="B101" s="30"/>
+      <c r="C101" s="31" t="s">
+        <v>377</v>
       </c>
       <c r="D101" s="6"/>
-      <c r="E101" s="30" t="s">
-        <v>323</v>
-      </c>
-      <c r="F101" s="30" t="s">
-        <v>302</v>
+      <c r="E101" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="F101" s="31" t="s">
+        <v>289</v>
       </c>
       <c r="G101" s="7"/>
       <c r="H101" s="8"/>
       <c r="I101" s="9"/>
-      <c r="J101" s="6"/>
-      <c r="K101" s="6"/>
+      <c r="J101" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="K101" s="38">
+        <v>10</v>
+      </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A102" s="5"/>
-      <c r="B102" s="33"/>
-      <c r="C102" s="34" t="s">
-        <v>324</v>
+      <c r="A102" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B102" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="C102" s="31" t="s">
+        <v>189</v>
       </c>
       <c r="D102" s="6"/>
-      <c r="E102" s="34" t="s">
-        <v>325</v>
-      </c>
-      <c r="F102" s="34" t="s">
-        <v>302</v>
-      </c>
+      <c r="E102" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="F102" s="46"/>
       <c r="G102" s="7"/>
-      <c r="H102" s="8"/>
+      <c r="H102" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="I102" s="9"/>
-      <c r="J102" s="6"/>
+      <c r="J102" s="6" t="s">
+        <v>168</v>
+      </c>
       <c r="K102" s="6"/>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A103" s="5"/>
-      <c r="B103" s="29"/>
-      <c r="C103" s="30" t="s">
-        <v>326</v>
+      <c r="A103" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B103" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="C103" s="31" t="s">
+        <v>188</v>
       </c>
       <c r="D103" s="6"/>
-      <c r="E103" s="30" t="s">
-        <v>327</v>
-      </c>
-      <c r="F103" s="30" t="s">
-        <v>328</v>
-      </c>
-      <c r="G103" s="7"/>
-      <c r="H103" s="8"/>
+      <c r="E103" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="F103" s="46"/>
+      <c r="G103" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="H103" s="8" t="s">
+        <v>171</v>
+      </c>
       <c r="I103" s="9"/>
-      <c r="J103" s="6"/>
+      <c r="J103" s="6" t="s">
+        <v>165</v>
+      </c>
       <c r="K103" s="6"/>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" s="5"/>
-      <c r="B104" s="33"/>
-      <c r="C104" s="34" t="s">
-        <v>329</v>
+      <c r="B104" s="27"/>
+      <c r="C104" s="28" t="s">
+        <v>378</v>
       </c>
       <c r="D104" s="6"/>
-      <c r="E104" s="34" t="s">
-        <v>330</v>
-      </c>
-      <c r="F104" s="34" t="s">
-        <v>302</v>
+      <c r="E104" s="28" t="s">
+        <v>267</v>
+      </c>
+      <c r="F104" s="28" t="s">
+        <v>305</v>
       </c>
       <c r="G104" s="7"/>
       <c r="H104" s="8"/>
       <c r="I104" s="9"/>
-      <c r="J104" s="6"/>
-      <c r="K104" s="6"/>
+      <c r="J104" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="K104" s="24">
+        <v>4</v>
+      </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A105" s="5"/>
-      <c r="B105" s="29"/>
-      <c r="C105" s="30" t="s">
-        <v>331</v>
-      </c>
-      <c r="D105" s="6"/>
-      <c r="E105" s="30" t="s">
-        <v>332</v>
-      </c>
-      <c r="F105" s="30" t="s">
-        <v>302</v>
-      </c>
-      <c r="G105" s="7"/>
-      <c r="H105" s="8"/>
+      <c r="A105" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B105" s="39"/>
+      <c r="C105" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E105" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="F105" s="46" t="str">
+        <f>CONCATENATE("http://", E105)</f>
+        <v>http://192.168.0.195</v>
+      </c>
+      <c r="G105" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="H105" s="8" t="s">
+        <v>171</v>
+      </c>
       <c r="I105" s="9"/>
-      <c r="J105" s="6"/>
-      <c r="K105" s="6"/>
+      <c r="J105" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="K105" s="6" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A106" s="5"/>
-      <c r="B106" s="33"/>
-      <c r="C106" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="D106" s="6"/>
-      <c r="E106" s="34" t="s">
-        <v>334</v>
-      </c>
-      <c r="F106" s="34" t="s">
-        <v>302</v>
-      </c>
-      <c r="G106" s="7"/>
-      <c r="H106" s="8"/>
+      <c r="A106" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B106" s="39"/>
+      <c r="C106" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E106" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="F106" s="46" t="str">
+        <f>CONCATENATE("http://", E106)</f>
+        <v>http://192.168.0.194</v>
+      </c>
+      <c r="G106" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="H106" s="8" t="s">
+        <v>171</v>
+      </c>
       <c r="I106" s="9"/>
-      <c r="J106" s="6"/>
-      <c r="K106" s="6"/>
+      <c r="J106" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="K106" s="6" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A107" s="5"/>
-      <c r="B107" s="29"/>
-      <c r="C107" s="30" t="s">
-        <v>264</v>
+      <c r="A107" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="B107" s="13"/>
+      <c r="C107" s="43" t="s">
+        <v>20</v>
       </c>
       <c r="D107" s="6"/>
-      <c r="E107" s="30" t="s">
-        <v>268</v>
-      </c>
-      <c r="F107" s="30" t="s">
-        <v>335</v>
-      </c>
-      <c r="G107" s="7"/>
-      <c r="H107" s="8"/>
+      <c r="E107" s="43"/>
+      <c r="F107" s="43"/>
+      <c r="G107" s="6"/>
+      <c r="H107" s="8" t="s">
+        <v>171</v>
+      </c>
       <c r="I107" s="9"/>
-      <c r="J107" s="6"/>
-      <c r="K107" s="6"/>
+      <c r="J107" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K107" s="6" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A108" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="B108" s="5"/>
-      <c r="C108" s="34" t="s">
-        <v>336</v>
-      </c>
-      <c r="D108" s="6"/>
-      <c r="E108" s="34" t="s">
-        <v>207</v>
-      </c>
-      <c r="F108" s="34" t="s">
-        <v>302</v>
+      <c r="A108" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="B108" s="6"/>
+      <c r="C108" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E108" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="F108" s="46" t="str">
+        <f>CONCATENATE("http://", E108)</f>
+        <v>http://192.168.0.186</v>
       </c>
       <c r="G108" s="7"/>
-      <c r="H108" s="8"/>
+      <c r="H108" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="I108" s="9"/>
-      <c r="J108" s="6"/>
-      <c r="K108" s="6"/>
+      <c r="J108" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K108" s="6" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A109" s="29" t="s">
-        <v>265</v>
+      <c r="A109" s="33" t="s">
+        <v>278</v>
       </c>
       <c r="B109" s="5"/>
-      <c r="C109" s="30" t="s">
-        <v>267</v>
+      <c r="C109" s="34" t="s">
+        <v>379</v>
       </c>
       <c r="D109" s="6"/>
-      <c r="E109" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="F109" s="30" t="s">
-        <v>335</v>
-      </c>
-      <c r="G109" s="7"/>
-      <c r="H109" s="8"/>
+      <c r="E109" s="45" t="s">
+        <v>281</v>
+      </c>
+      <c r="F109" s="45"/>
+      <c r="G109" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="H109" s="20" t="s">
+        <v>170</v>
+      </c>
       <c r="I109" s="9"/>
-      <c r="J109" s="6"/>
-      <c r="K109" s="6"/>
+      <c r="J109" s="45" t="s">
+        <v>280</v>
+      </c>
+      <c r="K109" s="49"/>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A110" s="36"/>
+      <c r="A110" s="30" t="s">
+        <v>279</v>
+      </c>
       <c r="B110" s="5"/>
-      <c r="C110" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="D110" s="26"/>
-      <c r="E110" s="37" t="s">
-        <v>231</v>
-      </c>
-      <c r="F110" s="37" t="s">
-        <v>302</v>
-      </c>
-      <c r="G110" s="22"/>
-      <c r="H110" s="21"/>
-      <c r="I110" s="27"/>
-      <c r="J110" s="32" t="s">
-        <v>303</v>
-      </c>
-      <c r="K110" s="38">
-        <v>1</v>
-      </c>
+      <c r="C110" s="31" t="s">
+        <v>380</v>
+      </c>
+      <c r="D110" s="6"/>
+      <c r="E110" s="43" t="s">
+        <v>282</v>
+      </c>
+      <c r="F110" s="43"/>
+      <c r="G110" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="H110" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I110" s="9"/>
+      <c r="J110" s="43" t="s">
+        <v>280</v>
+      </c>
+      <c r="K110" s="48"/>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A111" s="29" t="s">
-        <v>266</v>
+      <c r="A111" s="27" t="s">
+        <v>279</v>
       </c>
       <c r="B111" s="5"/>
-      <c r="C111" s="30" t="s">
-        <v>271</v>
+      <c r="C111" s="28" t="s">
+        <v>380</v>
       </c>
       <c r="D111" s="6"/>
-      <c r="E111" s="30" t="s">
-        <v>270</v>
-      </c>
-      <c r="F111" s="30" t="s">
-        <v>335</v>
+      <c r="E111" s="28" t="s">
+        <v>282</v>
+      </c>
+      <c r="F111" s="28" t="s">
+        <v>280</v>
       </c>
       <c r="G111" s="7"/>
       <c r="H111" s="8"/>
       <c r="I111" s="9"/>
-      <c r="J111" s="34" t="s">
-        <v>303</v>
-      </c>
-      <c r="K111" s="39">
-        <v>2</v>
+      <c r="J111" s="31" t="s">
+        <v>290</v>
+      </c>
+      <c r="K111" s="36">
+        <v>13</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A112" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="B112" s="5"/>
-      <c r="C112" s="34" t="s">
-        <v>338</v>
+      <c r="A112" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B112" s="30"/>
+      <c r="C112" s="43" t="s">
+        <v>16</v>
       </c>
       <c r="D112" s="6"/>
-      <c r="E112" s="34" t="s">
-        <v>187</v>
-      </c>
-      <c r="F112" s="34" t="s">
-        <v>302</v>
-      </c>
-      <c r="G112" s="7"/>
-      <c r="H112" s="8"/>
+      <c r="E112" s="43"/>
+      <c r="F112" s="43"/>
+      <c r="G112" s="6"/>
+      <c r="H112" s="8" t="s">
+        <v>171</v>
+      </c>
       <c r="I112" s="9"/>
-      <c r="J112" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="K112" s="35">
-        <v>3</v>
+      <c r="J112" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="K112" s="48" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A113" s="5"/>
-      <c r="B113" s="29"/>
-      <c r="C113" s="30" t="s">
-        <v>339</v>
+      <c r="A113" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B113" s="30"/>
+      <c r="C113" s="43" t="s">
+        <v>158</v>
       </c>
       <c r="D113" s="6"/>
-      <c r="E113" s="30" t="s">
-        <v>272</v>
-      </c>
-      <c r="F113" s="30" t="s">
-        <v>335</v>
-      </c>
-      <c r="G113" s="7"/>
-      <c r="H113" s="8"/>
+      <c r="E113" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="F113" s="43"/>
+      <c r="G113" s="6"/>
+      <c r="H113" s="8" t="s">
+        <v>171</v>
+      </c>
       <c r="I113" s="9"/>
-      <c r="J113" s="34" t="s">
-        <v>303</v>
-      </c>
-      <c r="K113" s="39">
-        <v>4</v>
-      </c>
+      <c r="J113" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="K113" s="48"/>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A114" s="5"/>
-      <c r="B114" s="33"/>
-      <c r="C114" s="34" t="s">
-        <v>340</v>
-      </c>
+      <c r="A114" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="B114" s="5"/>
+      <c r="C114" s="31"/>
       <c r="D114" s="6"/>
-      <c r="E114" s="34" t="s">
-        <v>341</v>
-      </c>
-      <c r="F114" s="34" t="s">
-        <v>335</v>
-      </c>
-      <c r="G114" s="7"/>
-      <c r="H114" s="8"/>
+      <c r="E114" s="43"/>
+      <c r="F114" s="43"/>
+      <c r="G114" s="21"/>
+      <c r="H114" s="8" t="s">
+        <v>171</v>
+      </c>
       <c r="I114" s="9"/>
-      <c r="J114" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="K114" s="35">
-        <v>5</v>
-      </c>
+      <c r="J114" s="43"/>
+      <c r="K114" s="48"/>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A115" s="29" t="s">
-        <v>343</v>
+      <c r="A115" s="30" t="s">
+        <v>243</v>
       </c>
       <c r="B115" s="5"/>
-      <c r="C115" s="30" t="s">
-        <v>157</v>
-      </c>
+      <c r="C115" s="31"/>
       <c r="D115" s="6"/>
-      <c r="E115" s="30" t="s">
-        <v>194</v>
-      </c>
-      <c r="F115" s="30" t="s">
-        <v>335</v>
-      </c>
-      <c r="G115" s="7"/>
-      <c r="H115" s="8"/>
+      <c r="E115" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="F115" s="43"/>
+      <c r="G115" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="H115" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="I115" s="9"/>
-      <c r="J115" s="34" t="s">
-        <v>303</v>
-      </c>
-      <c r="K115" s="39">
-        <v>6</v>
-      </c>
+      <c r="J115" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="K115" s="48"/>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A116" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="B116" s="5"/>
-      <c r="C116" s="34" t="s">
-        <v>283</v>
-      </c>
+      <c r="A116" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B116" s="30"/>
+      <c r="C116" s="31"/>
       <c r="D116" s="6"/>
-      <c r="E116" s="34" t="s">
-        <v>286</v>
-      </c>
-      <c r="F116" s="34" t="s">
-        <v>335</v>
-      </c>
-      <c r="G116" s="7"/>
+      <c r="E116" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="F116" s="43"/>
+      <c r="G116" s="21"/>
       <c r="H116" s="8"/>
       <c r="I116" s="9"/>
-      <c r="J116" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="K116" s="35">
+      <c r="J116" s="43"/>
+      <c r="K116" s="48"/>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A117" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="B117" s="5"/>
+      <c r="C117" s="31"/>
+      <c r="D117" s="6"/>
+      <c r="E117" s="44" t="s">
+        <v>249</v>
+      </c>
+      <c r="F117" s="43"/>
+      <c r="G117" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="H117" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I117" s="9"/>
+      <c r="J117" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="K117" s="48"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A118" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B118" s="30"/>
+      <c r="C118" s="31"/>
+      <c r="D118" s="6"/>
+      <c r="E118" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="F118" s="43"/>
+      <c r="G118" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="H118" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I118" s="9"/>
+      <c r="J118" s="43" t="s">
+        <v>269</v>
+      </c>
+      <c r="K118" s="48"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A119" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="B119" s="30"/>
+      <c r="C119" s="31"/>
+      <c r="D119" s="25"/>
+      <c r="E119" s="43" t="s">
+        <v>287</v>
+      </c>
+      <c r="F119" s="43"/>
+      <c r="G119" s="21"/>
+      <c r="H119" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I119" s="26"/>
+      <c r="J119" s="43"/>
+      <c r="K119" s="48"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A120" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="B120" s="6"/>
+      <c r="C120" s="43"/>
+      <c r="D120" s="6"/>
+      <c r="E120" s="44" t="s">
+        <v>183</v>
+      </c>
+      <c r="F120" s="43"/>
+      <c r="G120" s="6"/>
+      <c r="H120" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I120" s="9"/>
+      <c r="J120" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="K120" s="48"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A121" s="30" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A117" s="5"/>
-      <c r="B117" s="29"/>
-      <c r="C117" s="30" t="s">
-        <v>344</v>
-      </c>
-      <c r="D117" s="6"/>
-      <c r="E117" s="30" t="s">
-        <v>345</v>
-      </c>
-      <c r="F117" s="30" t="s">
-        <v>335</v>
-      </c>
-      <c r="G117" s="7"/>
-      <c r="H117" s="8"/>
-      <c r="I117" s="9"/>
-      <c r="J117" s="34" t="s">
-        <v>303</v>
-      </c>
-      <c r="K117" s="39">
+      <c r="B121" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C121" s="31"/>
+      <c r="D121" s="6"/>
+      <c r="E121" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="F121" s="46"/>
+      <c r="G121" s="7"/>
+      <c r="H121" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I121" s="9"/>
+      <c r="J121" s="31" t="s">
+        <v>167</v>
+      </c>
+      <c r="K121" s="48"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A122" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C122" s="31"/>
+      <c r="D122" s="6"/>
+      <c r="E122" s="43"/>
+      <c r="F122" s="46"/>
+      <c r="G122" s="7"/>
+      <c r="H122" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="I122" s="9"/>
+      <c r="J122" s="43"/>
+      <c r="K122" s="48"/>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A123" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="B123" s="5"/>
+      <c r="C123" s="34"/>
+      <c r="D123" s="6"/>
+      <c r="E123" s="45"/>
+      <c r="F123" s="47"/>
+      <c r="G123" s="7"/>
+      <c r="H123" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="J123" s="45" t="s">
+        <v>254</v>
+      </c>
+      <c r="K123" s="49"/>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A124" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B124" s="6"/>
+      <c r="C124" s="43"/>
+      <c r="D124" s="6"/>
+      <c r="E124" s="43"/>
+      <c r="F124" s="43"/>
+      <c r="G124" s="6"/>
+      <c r="H124" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="I124" s="9"/>
+      <c r="J124" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="K124" s="48"/>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A125" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B125" s="39"/>
+      <c r="C125" s="43"/>
+      <c r="D125" s="6"/>
+      <c r="E125" s="43"/>
+      <c r="F125" s="43"/>
+      <c r="G125" s="6"/>
+      <c r="H125" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="I125" s="9"/>
+      <c r="J125" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="K125" s="48"/>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A126" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B126" s="39"/>
+      <c r="C126" s="43"/>
+      <c r="D126" s="6"/>
+      <c r="E126" s="43"/>
+      <c r="F126" s="43"/>
+      <c r="G126" s="6"/>
+      <c r="H126" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="I126" s="9"/>
+      <c r="J126" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="K126" s="48"/>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A127" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="B127" s="6"/>
+      <c r="C127" s="43"/>
+      <c r="D127" s="6"/>
+      <c r="E127" s="43"/>
+      <c r="F127" s="43"/>
+      <c r="G127" s="6"/>
+      <c r="H127" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="I127" s="9"/>
+      <c r="J127" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="K127" s="48"/>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A128" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="B128" s="6"/>
+      <c r="C128" s="43"/>
+      <c r="D128" s="6"/>
+      <c r="E128" s="43"/>
+      <c r="F128" s="43"/>
+      <c r="G128" s="6"/>
+      <c r="H128" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="I128" s="9"/>
+      <c r="J128" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="K128" s="48" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A129" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="B129" s="6"/>
+      <c r="C129" s="43"/>
+      <c r="D129" s="6"/>
+      <c r="E129" s="43"/>
+      <c r="F129" s="43"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="I129" s="9"/>
+      <c r="J129" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="K129" s="48"/>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A130" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="B130" s="6"/>
+      <c r="C130" s="43"/>
+      <c r="D130" s="6"/>
+      <c r="E130" s="43"/>
+      <c r="F130" s="43"/>
+      <c r="G130" s="6"/>
+      <c r="H130" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="I130" s="9"/>
+      <c r="J130" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="K130" s="48"/>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A131" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="B131" s="6"/>
+      <c r="C131" s="43"/>
+      <c r="D131" s="6"/>
+      <c r="E131" s="43"/>
+      <c r="F131" s="43"/>
+      <c r="G131" s="6"/>
+      <c r="H131" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="I131" s="9"/>
+      <c r="J131" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="K131" s="48"/>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A132" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="B132" s="6"/>
+      <c r="C132" s="43"/>
+      <c r="D132" s="6"/>
+      <c r="E132" s="43"/>
+      <c r="F132" s="43"/>
+      <c r="G132" s="6"/>
+      <c r="H132" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="I132" s="9"/>
+      <c r="J132" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="K132" s="48"/>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A133" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C133" s="31"/>
+      <c r="D133" s="6"/>
+      <c r="E133" s="43"/>
+      <c r="F133" s="43"/>
+      <c r="G133" s="7"/>
+      <c r="H133" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="I133" s="9"/>
+      <c r="J133" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="K133" s="48"/>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A134" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C134" s="31"/>
+      <c r="D134" s="6"/>
+      <c r="E134" s="43"/>
+      <c r="F134" s="43"/>
+      <c r="G134" s="7"/>
+      <c r="H134" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="I134" s="9"/>
+      <c r="J134" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="K134" s="48"/>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A135" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B135" s="5"/>
+      <c r="C135" s="43"/>
+      <c r="D135" s="6"/>
+      <c r="E135" s="43" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A118" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="B118" s="5"/>
-      <c r="C118" s="34" t="s">
-        <v>346</v>
-      </c>
-      <c r="D118" s="6"/>
-      <c r="E118" s="34" t="s">
-        <v>192</v>
-      </c>
-      <c r="F118" s="34" t="s">
-        <v>302</v>
-      </c>
-      <c r="G118" s="7"/>
-      <c r="H118" s="8"/>
-      <c r="I118" s="9"/>
-      <c r="J118" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="K118" s="35">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A119" s="5"/>
-      <c r="B119" s="29"/>
-      <c r="C119" s="30" t="s">
-        <v>347</v>
-      </c>
-      <c r="D119" s="6"/>
-      <c r="E119" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="F119" s="30" t="s">
-        <v>302</v>
-      </c>
-      <c r="G119" s="7"/>
-      <c r="H119" s="8"/>
-      <c r="I119" s="9"/>
-      <c r="J119" s="34" t="s">
-        <v>303</v>
-      </c>
-      <c r="K119" s="39">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A120" s="5"/>
-      <c r="B120" s="33"/>
-      <c r="C120" s="34" t="s">
-        <v>294</v>
-      </c>
-      <c r="D120" s="6"/>
-      <c r="E120" s="34" t="s">
-        <v>295</v>
-      </c>
-      <c r="F120" s="34" t="s">
-        <v>348</v>
-      </c>
-      <c r="G120" s="7"/>
-      <c r="H120" s="8"/>
-      <c r="I120" s="9"/>
-      <c r="J120" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="K120" s="35">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A121" s="29" t="s">
-        <v>288</v>
-      </c>
-      <c r="B121" s="5"/>
-      <c r="C121" s="30" t="s">
-        <v>291</v>
-      </c>
-      <c r="D121" s="6"/>
-      <c r="E121" s="30" t="s">
-        <v>293</v>
-      </c>
-      <c r="F121" s="30" t="s">
-        <v>290</v>
-      </c>
-      <c r="G121" s="7"/>
-      <c r="H121" s="8"/>
-      <c r="I121" s="9"/>
-      <c r="J121" s="34" t="s">
-        <v>303</v>
-      </c>
-      <c r="K121" s="39">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A122" s="33" t="s">
-        <v>349</v>
-      </c>
-      <c r="B122" s="5"/>
-      <c r="C122" s="34" t="s">
-        <v>281</v>
-      </c>
-      <c r="D122" s="6"/>
-      <c r="E122" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="F122" s="34" t="s">
-        <v>335</v>
-      </c>
-      <c r="G122" s="7"/>
-      <c r="H122" s="8"/>
-      <c r="I122" s="9"/>
-      <c r="J122" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="K122" s="35">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A123" s="29" t="s">
-        <v>350</v>
-      </c>
-      <c r="B123" s="5"/>
-      <c r="C123" s="30" t="s">
-        <v>282</v>
-      </c>
-      <c r="D123" s="6"/>
-      <c r="E123" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="F123" s="30" t="s">
-        <v>335</v>
-      </c>
-      <c r="G123" s="7"/>
-      <c r="H123" s="8"/>
-      <c r="I123" s="9"/>
-      <c r="J123" s="34" t="s">
-        <v>303</v>
-      </c>
-      <c r="K123" s="39">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A124" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="B124" s="5"/>
-      <c r="C124" s="37" t="s">
-        <v>351</v>
-      </c>
-      <c r="D124" s="26"/>
-      <c r="E124" s="37" t="s">
-        <v>177</v>
-      </c>
-      <c r="F124" s="37" t="s">
-        <v>302</v>
-      </c>
-      <c r="G124" s="22"/>
-      <c r="H124" s="21"/>
-      <c r="I124" s="27"/>
-      <c r="J124" s="32" t="s">
-        <v>303</v>
-      </c>
-      <c r="K124" s="38">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A125" s="29" t="s">
-        <v>353</v>
-      </c>
-      <c r="B125" s="5"/>
-      <c r="C125" s="30" t="s">
-        <v>354</v>
-      </c>
-      <c r="D125" s="6"/>
-      <c r="E125" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="F125" s="30" t="s">
-        <v>302</v>
-      </c>
-      <c r="G125" s="7"/>
-      <c r="H125" s="8"/>
-      <c r="I125" s="9"/>
-      <c r="J125" s="34" t="s">
-        <v>303</v>
-      </c>
-      <c r="K125" s="39">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A126" s="5"/>
-      <c r="B126" s="33"/>
-      <c r="C126" s="34" t="s">
-        <v>355</v>
-      </c>
-      <c r="D126" s="6"/>
-      <c r="E126" s="34" t="s">
-        <v>225</v>
-      </c>
-      <c r="F126" s="34" t="s">
-        <v>302</v>
-      </c>
-      <c r="G126" s="7"/>
-      <c r="H126" s="8"/>
-      <c r="I126" s="9"/>
-      <c r="J126" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="K126" s="35">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A127" s="5"/>
-      <c r="B127" s="29"/>
-      <c r="C127" s="30" t="s">
-        <v>356</v>
-      </c>
-      <c r="D127" s="6"/>
-      <c r="E127" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="F127" s="30" t="s">
-        <v>302</v>
-      </c>
-      <c r="G127" s="7"/>
-      <c r="H127" s="8"/>
-      <c r="I127" s="9"/>
-      <c r="J127" s="34" t="s">
-        <v>303</v>
-      </c>
-      <c r="K127" s="39">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A128" s="33" t="s">
-        <v>357</v>
-      </c>
-      <c r="B128" s="5"/>
-      <c r="C128" s="34" t="s">
-        <v>358</v>
-      </c>
-      <c r="D128" s="6"/>
-      <c r="E128" s="34" t="s">
-        <v>359</v>
-      </c>
-      <c r="F128" s="34" t="s">
-        <v>302</v>
-      </c>
-      <c r="G128" s="7"/>
-      <c r="H128" s="8"/>
-      <c r="I128" s="9"/>
-      <c r="J128" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="K128" s="35">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A129" s="29" t="s">
-        <v>361</v>
-      </c>
-      <c r="B129" s="5"/>
-      <c r="C129" s="30" t="s">
-        <v>362</v>
-      </c>
-      <c r="D129" s="6"/>
-      <c r="E129" s="30" t="s">
-        <v>363</v>
-      </c>
-      <c r="F129" s="30" t="s">
-        <v>302</v>
-      </c>
-      <c r="G129" s="7"/>
-      <c r="H129" s="8"/>
-      <c r="I129" s="9"/>
-      <c r="J129" s="34" t="s">
-        <v>303</v>
-      </c>
-      <c r="K129" s="39">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A130" s="33" t="s">
-        <v>364</v>
-      </c>
-      <c r="B130" s="5"/>
-      <c r="C130" s="34" t="s">
-        <v>365</v>
-      </c>
-      <c r="D130" s="6"/>
-      <c r="E130" s="34" t="s">
-        <v>366</v>
-      </c>
-      <c r="F130" s="34" t="s">
-        <v>302</v>
-      </c>
-      <c r="G130" s="7"/>
-      <c r="H130" s="8"/>
-      <c r="I130" s="9"/>
-      <c r="J130" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="K130" s="35">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A131" s="29" t="s">
-        <v>367</v>
-      </c>
-      <c r="B131" s="5"/>
-      <c r="C131" s="30" t="s">
-        <v>368</v>
-      </c>
-      <c r="D131" s="6"/>
-      <c r="E131" s="30" t="s">
-        <v>369</v>
-      </c>
-      <c r="F131" s="30" t="s">
-        <v>302</v>
-      </c>
-      <c r="G131" s="7"/>
-      <c r="H131" s="8"/>
-      <c r="I131" s="9"/>
-      <c r="J131" s="34" t="s">
-        <v>303</v>
-      </c>
-      <c r="K131" s="39">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A132" s="33" t="s">
-        <v>370</v>
-      </c>
-      <c r="B132" s="5"/>
-      <c r="C132" s="34" t="s">
-        <v>371</v>
-      </c>
-      <c r="D132" s="6"/>
-      <c r="E132" s="34" t="s">
-        <v>372</v>
-      </c>
-      <c r="F132" s="34" t="s">
-        <v>302</v>
-      </c>
-      <c r="G132" s="7"/>
-      <c r="H132" s="8"/>
-      <c r="I132" s="9"/>
-      <c r="J132" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="K132" s="35">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A133" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="B133" s="5"/>
-      <c r="C133" s="30" t="s">
-        <v>374</v>
-      </c>
-      <c r="D133" s="6"/>
-      <c r="E133" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="F133" s="30" t="s">
-        <v>302</v>
-      </c>
-      <c r="G133" s="7"/>
-      <c r="H133" s="8"/>
-      <c r="I133" s="9"/>
-      <c r="J133" s="34" t="s">
-        <v>303</v>
-      </c>
-      <c r="K133" s="39">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A134" s="33" t="s">
-        <v>376</v>
-      </c>
-      <c r="B134" s="5"/>
-      <c r="C134" s="34" t="s">
-        <v>377</v>
-      </c>
-      <c r="D134" s="6"/>
-      <c r="E134" s="34" t="s">
-        <v>378</v>
-      </c>
-      <c r="F134" s="34" t="s">
-        <v>302</v>
-      </c>
-      <c r="G134" s="7"/>
-      <c r="H134" s="8"/>
-      <c r="I134" s="9"/>
-      <c r="J134" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="K134" s="35">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A135" s="29" t="s">
-        <v>379</v>
-      </c>
-      <c r="B135" s="5"/>
-      <c r="C135" s="30" t="s">
-        <v>380</v>
-      </c>
-      <c r="D135" s="6"/>
-      <c r="E135" s="30" t="s">
-        <v>381</v>
-      </c>
-      <c r="F135" s="30" t="s">
-        <v>302</v>
-      </c>
-      <c r="G135" s="7"/>
+      <c r="F135" s="43"/>
+      <c r="G135" s="6"/>
       <c r="H135" s="8"/>
       <c r="I135" s="9"/>
-      <c r="J135" s="34" t="s">
-        <v>342</v>
-      </c>
-      <c r="K135" s="39">
-        <v>3</v>
-      </c>
+      <c r="J135" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="K135" s="48"/>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A136" s="33" t="s">
-        <v>382</v>
-      </c>
-      <c r="B136" s="5"/>
-      <c r="C136" s="34" t="s">
-        <v>383</v>
-      </c>
-      <c r="D136" s="6"/>
-      <c r="E136" s="34" t="s">
-        <v>384</v>
-      </c>
-      <c r="F136" s="34" t="s">
-        <v>302</v>
-      </c>
-      <c r="G136" s="7"/>
-      <c r="H136" s="8"/>
-      <c r="I136" s="9"/>
-      <c r="J136" s="30" t="s">
-        <v>342</v>
-      </c>
-      <c r="K136" s="35">
-        <v>5</v>
-      </c>
+      <c r="A136" s="24"/>
+      <c r="B136" s="24"/>
+      <c r="C136" s="24"/>
+      <c r="D136" s="25"/>
+      <c r="E136" s="25"/>
+      <c r="F136" s="25"/>
+      <c r="G136" s="21"/>
+      <c r="H136" s="20"/>
+      <c r="I136" s="26"/>
+      <c r="J136" s="34"/>
+      <c r="K136" s="37"/>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A137" s="25"/>
-      <c r="B137" s="25"/>
-      <c r="C137" s="25"/>
-      <c r="D137" s="26"/>
-      <c r="E137" s="26"/>
-      <c r="F137" s="26"/>
-      <c r="G137" s="22"/>
-      <c r="H137" s="21"/>
-      <c r="I137" s="27"/>
-      <c r="J137" s="37" t="s">
-        <v>342</v>
-      </c>
-      <c r="K137" s="40">
-        <v>12</v>
-      </c>
+      <c r="A137" s="5"/>
+      <c r="B137" s="5"/>
+      <c r="C137" s="5"/>
+      <c r="D137" s="6"/>
+      <c r="E137" s="6"/>
+      <c r="F137" s="6"/>
+      <c r="G137" s="7"/>
+      <c r="H137" s="8"/>
+      <c r="I137" s="9"/>
+      <c r="J137" s="28"/>
+      <c r="K137" s="32"/>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" s="5"/>
@@ -5474,12 +5455,8 @@
       <c r="G138" s="7"/>
       <c r="H138" s="8"/>
       <c r="I138" s="9"/>
-      <c r="J138" s="30" t="s">
-        <v>342</v>
-      </c>
-      <c r="K138" s="35">
-        <v>13</v>
-      </c>
+      <c r="J138" s="31"/>
+      <c r="K138" s="36"/>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" s="5"/>
@@ -5491,12 +5468,8 @@
       <c r="G139" s="7"/>
       <c r="H139" s="8"/>
       <c r="I139" s="9"/>
-      <c r="J139" s="34" t="s">
-        <v>342</v>
-      </c>
-      <c r="K139" s="39">
-        <v>14</v>
-      </c>
+      <c r="J139" s="28"/>
+      <c r="K139" s="32"/>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" s="5"/>
@@ -5508,12 +5481,8 @@
       <c r="G140" s="7"/>
       <c r="H140" s="8"/>
       <c r="I140" s="9"/>
-      <c r="J140" s="30" t="s">
-        <v>342</v>
-      </c>
-      <c r="K140" s="35">
-        <v>17</v>
-      </c>
+      <c r="J140" s="31"/>
+      <c r="K140" s="36"/>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" s="5"/>
@@ -5525,12 +5494,8 @@
       <c r="G141" s="7"/>
       <c r="H141" s="8"/>
       <c r="I141" s="9"/>
-      <c r="J141" s="34" t="s">
-        <v>342</v>
-      </c>
-      <c r="K141" s="39">
-        <v>20</v>
-      </c>
+      <c r="J141" s="28"/>
+      <c r="K141" s="32"/>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" s="5"/>
@@ -5542,12 +5507,8 @@
       <c r="G142" s="7"/>
       <c r="H142" s="8"/>
       <c r="I142" s="9"/>
-      <c r="J142" s="30" t="s">
-        <v>342</v>
-      </c>
-      <c r="K142" s="35">
-        <v>21</v>
-      </c>
+      <c r="J142" s="31"/>
+      <c r="K142" s="36"/>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" s="5"/>
@@ -5559,12 +5520,8 @@
       <c r="G143" s="7"/>
       <c r="H143" s="8"/>
       <c r="I143" s="9"/>
-      <c r="J143" s="34" t="s">
-        <v>342</v>
-      </c>
-      <c r="K143" s="39">
-        <v>23</v>
-      </c>
+      <c r="J143" s="28"/>
+      <c r="K143" s="32"/>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144" s="5"/>
@@ -5576,46 +5533,34 @@
       <c r="G144" s="7"/>
       <c r="H144" s="8"/>
       <c r="I144" s="9"/>
-      <c r="J144" s="30" t="s">
-        <v>342</v>
-      </c>
-      <c r="K144" s="35">
-        <v>24</v>
-      </c>
+      <c r="J144" s="31"/>
+      <c r="K144" s="36"/>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A145" s="5"/>
-      <c r="B145" s="5"/>
-      <c r="C145" s="5"/>
-      <c r="D145" s="6"/>
-      <c r="E145" s="6"/>
-      <c r="F145" s="6"/>
-      <c r="G145" s="7"/>
-      <c r="H145" s="8"/>
-      <c r="I145" s="9"/>
-      <c r="J145" s="34" t="s">
-        <v>352</v>
-      </c>
-      <c r="K145" s="39">
-        <v>5</v>
-      </c>
+      <c r="A145" s="24"/>
+      <c r="B145" s="24"/>
+      <c r="C145" s="24"/>
+      <c r="D145" s="25"/>
+      <c r="E145" s="25"/>
+      <c r="F145" s="25"/>
+      <c r="G145" s="21"/>
+      <c r="H145" s="20"/>
+      <c r="I145" s="26"/>
+      <c r="J145" s="29"/>
+      <c r="K145" s="35"/>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A146" s="25"/>
-      <c r="B146" s="25"/>
-      <c r="C146" s="25"/>
-      <c r="D146" s="26"/>
-      <c r="E146" s="26"/>
-      <c r="F146" s="26"/>
-      <c r="G146" s="22"/>
-      <c r="H146" s="21"/>
-      <c r="I146" s="27"/>
-      <c r="J146" s="32" t="s">
-        <v>352</v>
-      </c>
-      <c r="K146" s="38">
-        <v>9</v>
-      </c>
+      <c r="A146" s="5"/>
+      <c r="B146" s="5"/>
+      <c r="C146" s="5"/>
+      <c r="D146" s="6"/>
+      <c r="E146" s="6"/>
+      <c r="F146" s="6"/>
+      <c r="G146" s="7"/>
+      <c r="H146" s="8"/>
+      <c r="I146" s="9"/>
+      <c r="J146" s="31"/>
+      <c r="K146" s="36"/>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A147" s="5"/>
@@ -5627,12 +5572,8 @@
       <c r="G147" s="7"/>
       <c r="H147" s="8"/>
       <c r="I147" s="9"/>
-      <c r="J147" s="34" t="s">
-        <v>352</v>
-      </c>
-      <c r="K147" s="39">
-        <v>12</v>
-      </c>
+      <c r="J147" s="28"/>
+      <c r="K147" s="32"/>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A148" s="5"/>
@@ -5644,12 +5585,8 @@
       <c r="G148" s="7"/>
       <c r="H148" s="8"/>
       <c r="I148" s="9"/>
-      <c r="J148" s="30" t="s">
-        <v>352</v>
-      </c>
-      <c r="K148" s="35">
-        <v>15</v>
-      </c>
+      <c r="J148" s="31"/>
+      <c r="K148" s="36"/>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A149" s="5"/>
@@ -5661,12 +5598,8 @@
       <c r="G149" s="7"/>
       <c r="H149" s="8"/>
       <c r="I149" s="9"/>
-      <c r="J149" s="34" t="s">
-        <v>360</v>
-      </c>
-      <c r="K149" s="39">
-        <v>2</v>
-      </c>
+      <c r="J149" s="28"/>
+      <c r="K149" s="32"/>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150" s="5"/>
@@ -5678,12 +5611,8 @@
       <c r="G150" s="7"/>
       <c r="H150" s="8"/>
       <c r="I150" s="9"/>
-      <c r="J150" s="30" t="s">
-        <v>360</v>
-      </c>
-      <c r="K150" s="35">
-        <v>3</v>
-      </c>
+      <c r="J150" s="31"/>
+      <c r="K150" s="36"/>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151" s="5"/>
@@ -5695,12 +5624,8 @@
       <c r="G151" s="7"/>
       <c r="H151" s="8"/>
       <c r="I151" s="9"/>
-      <c r="J151" s="34" t="s">
-        <v>360</v>
-      </c>
-      <c r="K151" s="39">
-        <v>4</v>
-      </c>
+      <c r="J151" s="28"/>
+      <c r="K151" s="32"/>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152" s="5"/>
@@ -5712,46 +5637,34 @@
       <c r="G152" s="7"/>
       <c r="H152" s="8"/>
       <c r="I152" s="9"/>
-      <c r="J152" s="30" t="s">
-        <v>360</v>
-      </c>
-      <c r="K152" s="35">
-        <v>5</v>
-      </c>
+      <c r="J152" s="31"/>
+      <c r="K152" s="36"/>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A153" s="5"/>
-      <c r="B153" s="5"/>
-      <c r="C153" s="5"/>
-      <c r="D153" s="6"/>
-      <c r="E153" s="6"/>
-      <c r="F153" s="6"/>
-      <c r="G153" s="7"/>
-      <c r="H153" s="8"/>
-      <c r="I153" s="9"/>
-      <c r="J153" s="34" t="s">
-        <v>360</v>
-      </c>
-      <c r="K153" s="39">
-        <v>7</v>
-      </c>
+      <c r="A153" s="24"/>
+      <c r="B153" s="24"/>
+      <c r="C153" s="24"/>
+      <c r="D153" s="25"/>
+      <c r="E153" s="25"/>
+      <c r="F153" s="25"/>
+      <c r="G153" s="21"/>
+      <c r="H153" s="20"/>
+      <c r="I153" s="26"/>
+      <c r="J153" s="29"/>
+      <c r="K153" s="35"/>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A154" s="25"/>
-      <c r="B154" s="25"/>
-      <c r="C154" s="25"/>
-      <c r="D154" s="26"/>
-      <c r="E154" s="26"/>
-      <c r="F154" s="26"/>
-      <c r="G154" s="22"/>
-      <c r="H154" s="21"/>
-      <c r="I154" s="27"/>
-      <c r="J154" s="32" t="s">
-        <v>360</v>
-      </c>
-      <c r="K154" s="38">
-        <v>8</v>
-      </c>
+      <c r="A154" s="5"/>
+      <c r="B154" s="5"/>
+      <c r="C154" s="5"/>
+      <c r="D154" s="6"/>
+      <c r="E154" s="6"/>
+      <c r="F154" s="6"/>
+      <c r="G154" s="7"/>
+      <c r="H154" s="8"/>
+      <c r="I154" s="9"/>
+      <c r="J154" s="31"/>
+      <c r="K154" s="36"/>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155" s="5"/>
@@ -5763,46 +5676,25 @@
       <c r="G155" s="7"/>
       <c r="H155" s="8"/>
       <c r="I155" s="9"/>
-      <c r="J155" s="34" t="s">
-        <v>360</v>
-      </c>
-      <c r="K155" s="39">
-        <v>9</v>
-      </c>
+      <c r="J155" s="28"/>
+      <c r="K155" s="32"/>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A156" s="5"/>
-      <c r="B156" s="5"/>
-      <c r="C156" s="5"/>
-      <c r="D156" s="6"/>
-      <c r="E156" s="6"/>
-      <c r="F156" s="6"/>
-      <c r="G156" s="7"/>
-      <c r="H156" s="8"/>
-      <c r="I156" s="9"/>
-      <c r="J156" s="30" t="s">
-        <v>360</v>
-      </c>
-      <c r="K156" s="35">
-        <v>10</v>
-      </c>
+      <c r="A156" s="24"/>
+      <c r="B156" s="24"/>
+      <c r="C156" s="24"/>
+      <c r="D156" s="25"/>
+      <c r="E156" s="25"/>
+      <c r="F156" s="25"/>
+      <c r="G156" s="21"/>
+      <c r="H156" s="20"/>
+      <c r="I156" s="26"/>
+      <c r="J156" s="34"/>
+      <c r="K156" s="37"/>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A157" s="25"/>
-      <c r="B157" s="25"/>
-      <c r="C157" s="25"/>
-      <c r="D157" s="26"/>
-      <c r="E157" s="26"/>
-      <c r="F157" s="26"/>
-      <c r="G157" s="22"/>
-      <c r="H157" s="21"/>
-      <c r="I157" s="27"/>
-      <c r="J157" s="37" t="s">
-        <v>360</v>
-      </c>
-      <c r="K157" s="40">
-        <v>11</v>
-      </c>
+      <c r="H157"/>
+      <c r="I157"/>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H158"/>
@@ -12148,23 +12040,19 @@
       <c r="H1743"/>
       <c r="I1743"/>
     </row>
-    <row r="1744" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1744"/>
-      <c r="I1744"/>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F63" r:id="rId1" display="http://192.169.0.112" xr:uid="{D2404E72-FA69-6648-ACE3-1F155CD355DD}"/>
-    <hyperlink ref="F69" r:id="rId2" display="http://192.169.0.112" xr:uid="{3F5BA59D-C194-FC49-9DCB-1F6B1CEAE85A}"/>
-    <hyperlink ref="F60" r:id="rId3" display="http://192.169.0.112" xr:uid="{80722F7C-2A8A-4A43-A5D3-BCFFE30BBC25}"/>
-    <hyperlink ref="F59" r:id="rId4" display="http://192.169.0.112" xr:uid="{7AFCBEF6-4325-D24D-B711-037F038931A3}"/>
+    <hyperlink ref="F31" r:id="rId1" display="http://192.169.0.112" xr:uid="{D2404E72-FA69-6648-ACE3-1F155CD355DD}"/>
+    <hyperlink ref="F85" r:id="rId2" display="http://192.169.0.112" xr:uid="{3F5BA59D-C194-FC49-9DCB-1F6B1CEAE85A}"/>
+    <hyperlink ref="F54" r:id="rId3" display="http://192.169.0.112" xr:uid="{80722F7C-2A8A-4A43-A5D3-BCFFE30BBC25}"/>
+    <hyperlink ref="F53" r:id="rId4" display="http://192.169.0.112" xr:uid="{7AFCBEF6-4325-D24D-B711-037F038931A3}"/>
     <hyperlink ref="F13:F15" r:id="rId5" display="http://192.169.0.112" xr:uid="{40E3D96B-FF32-1147-AA42-7A87222DBFE8}"/>
     <hyperlink ref="F4:F8" r:id="rId6" display="http://192.169.0.112" xr:uid="{EFA55FC0-66D6-5341-B122-15ED7113DE4A}"/>
-    <hyperlink ref="F64" r:id="rId7" display="http://192.169.0.112" xr:uid="{206574CD-0A69-6A49-BF19-8696C0B23754}"/>
-    <hyperlink ref="F21:F23" r:id="rId8" display="http://192.169.0.112" xr:uid="{ABAD7AC1-281C-974C-8BD8-79EEDE34950A}"/>
-    <hyperlink ref="F67" r:id="rId9" display="http://192.169.0.112" xr:uid="{2FA0DCAE-2864-024C-9351-79F3CBFD408D}"/>
-    <hyperlink ref="F68" r:id="rId10" display="http://192.169.0.112" xr:uid="{0E717F48-1348-0440-9A96-15E3AB13C8AE}"/>
-    <hyperlink ref="F2" r:id="rId11" display="http://192.169.0.112" xr:uid="{B7709A6B-F68E-6F45-9F1A-5CCF46F3BFD7}"/>
+    <hyperlink ref="F55" r:id="rId7" display="http://192.169.0.112" xr:uid="{206574CD-0A69-6A49-BF19-8696C0B23754}"/>
+    <hyperlink ref="F20:F22" r:id="rId8" display="http://192.169.0.112" xr:uid="{ABAD7AC1-281C-974C-8BD8-79EEDE34950A}"/>
+    <hyperlink ref="F90" r:id="rId9" display="http://192.169.0.112" xr:uid="{2FA0DCAE-2864-024C-9351-79F3CBFD408D}"/>
+    <hyperlink ref="F91" r:id="rId10" display="http://192.169.0.112" xr:uid="{0E717F48-1348-0440-9A96-15E3AB13C8AE}"/>
+    <hyperlink ref="F78" r:id="rId11" display="http://192.169.0.112" xr:uid="{B7709A6B-F68E-6F45-9F1A-5CCF46F3BFD7}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E67D45F-9851-E64E-9A6D-C39B48465555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DAF566-ACA1-424B-BD95-F4637559CA68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1880" yWindow="1460" windowWidth="28360" windowHeight="18180" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="384">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -1239,13 +1239,22 @@
   </si>
   <si>
     <t>D0:C8:57:82:74:B9</t>
+  </si>
+  <si>
+    <t>2603-1105</t>
+  </si>
+  <si>
+    <t>2603-1106</t>
+  </si>
+  <si>
+    <t>G2 KVM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1332,6 +1341,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1365,7 +1380,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1489,12 +1504,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9BC2E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1549,6 +1579,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="12" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5420,29 +5452,53 @@
       <c r="K135" s="48"/>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A136" s="24"/>
+      <c r="A136" s="24" t="s">
+        <v>381</v>
+      </c>
       <c r="B136" s="24"/>
-      <c r="C136" s="24"/>
-      <c r="D136" s="25"/>
-      <c r="E136" s="25"/>
+      <c r="C136" s="51" t="s">
+        <v>369</v>
+      </c>
+      <c r="D136" s="6"/>
+      <c r="E136" s="25" t="s">
+        <v>309</v>
+      </c>
       <c r="F136" s="25"/>
-      <c r="G136" s="21"/>
-      <c r="H136" s="20"/>
+      <c r="G136" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="H136" s="20" t="s">
+        <v>170</v>
+      </c>
       <c r="I136" s="26"/>
-      <c r="J136" s="34"/>
+      <c r="J136" s="34" t="s">
+        <v>383</v>
+      </c>
       <c r="K136" s="37"/>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A137" s="5"/>
+      <c r="A137" s="5" t="s">
+        <v>382</v>
+      </c>
       <c r="B137" s="5"/>
-      <c r="C137" s="5"/>
+      <c r="C137" s="51" t="s">
+        <v>370</v>
+      </c>
       <c r="D137" s="6"/>
-      <c r="E137" s="6"/>
+      <c r="E137" s="6" t="s">
+        <v>306</v>
+      </c>
       <c r="F137" s="6"/>
-      <c r="G137" s="7"/>
-      <c r="H137" s="8"/>
-      <c r="I137" s="9"/>
-      <c r="J137" s="28"/>
+      <c r="G137" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="H137" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I137" s="26"/>
+      <c r="J137" s="50" t="s">
+        <v>383</v>
+      </c>
       <c r="K137" s="32"/>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.2">

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DAF566-ACA1-424B-BD95-F4637559CA68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{649F0B39-7306-054C-A7F6-A2FDF5FD2C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1880" yWindow="1460" windowWidth="28360" windowHeight="18180" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
+    <workbookView xWindow="1880" yWindow="2960" windowWidth="28360" windowHeight="16680" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
   <sheets>
     <sheet name="network" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">network!$A$1:$K$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">network!$A$1:$K$37</definedName>
     <definedName name="taxrate">'[1]mixer costs'!$I$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="373">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -107,18 +107,6 @@
     <t>NSCU-A001</t>
   </si>
   <si>
-    <t>na</t>
-  </si>
-  <si>
-    <t>192.168.0.166</t>
-  </si>
-  <si>
-    <t>14:98:77:82:73:BD</t>
-  </si>
-  <si>
-    <t>DAW Mac</t>
-  </si>
-  <si>
     <t>CUMU-E001</t>
   </si>
   <si>
@@ -698,9 +686,6 @@
     <t>00:04:c4:11:3c:b7</t>
   </si>
   <si>
-    <t>avio-videomixer</t>
-  </si>
-  <si>
     <t>192.168.200.104</t>
   </si>
   <si>
@@ -788,9 +773,6 @@
     <t>192.168.200.114</t>
   </si>
   <si>
-    <t>Dante</t>
-  </si>
-  <si>
     <t>ZVIU-D002</t>
   </si>
   <si>
@@ -851,9 +833,6 @@
     <t>Konductor</t>
   </si>
   <si>
-    <t>port:9110</t>
-  </si>
-  <si>
     <t>midi:51325</t>
   </si>
   <si>
@@ -1022,24 +1001,9 @@
     <t>AV Balcony 2603-1203</t>
   </si>
   <si>
-    <t>ZVIU-G001 resi</t>
-  </si>
-  <si>
     <t>192.168.201.101</t>
   </si>
   <si>
-    <t>TVs</t>
-  </si>
-  <si>
-    <t>2507-0700-BMD-VideoHub</t>
-  </si>
-  <si>
-    <t>2601-2800-BMD-Cons</t>
-  </si>
-  <si>
-    <t>AV Booth TSC</t>
-  </si>
-  <si>
     <t>klang-KRB14486</t>
   </si>
   <si>
@@ -1097,18 +1061,6 @@
     <t>00:04:C4:0F:E3:C3</t>
   </si>
   <si>
-    <t>00:04:C4:11:3C:B6</t>
-  </si>
-  <si>
-    <t>00:04:C4:13:E2:61</t>
-  </si>
-  <si>
-    <t>00:04:C4:14:70:C8</t>
-  </si>
-  <si>
-    <t>00:04:C4:14:A2:0F</t>
-  </si>
-  <si>
     <t>00:04:C4:31:28:1A</t>
   </si>
   <si>
@@ -1142,15 +1094,6 @@
     <t>00:1D:56:04:CC:E3</t>
   </si>
   <si>
-    <t>00:1D:C1:51:73:2D</t>
-  </si>
-  <si>
-    <t>00:1D:C1:52:94:50</t>
-  </si>
-  <si>
-    <t>00:1D:C1:54:00:59</t>
-  </si>
-  <si>
     <t>00:1D:C1:9A:6E:02</t>
   </si>
   <si>
@@ -1190,9 +1133,6 @@
     <t>00:21:84:03:C3:DC</t>
   </si>
   <si>
-    <t>00:60:74:EE:53:EF</t>
-  </si>
-  <si>
     <t>14:3F:A6:B8:EA:5D</t>
   </si>
   <si>
@@ -1202,9 +1142,6 @@
     <t>1C:69:7A:66:87:69</t>
   </si>
   <si>
-    <t>20:A5:CB:CE:4E:B8</t>
-  </si>
-  <si>
     <t>34:1B:22:84:24:57</t>
   </si>
   <si>
@@ -1229,9 +1166,6 @@
     <t>98:BA:5F:91:07:6A</t>
   </si>
   <si>
-    <t>A4:FC:14:28:2E:B6</t>
-  </si>
-  <si>
     <t>A8:6E:84:07:E5:B1</t>
   </si>
   <si>
@@ -1248,6 +1182,39 @@
   </si>
   <si>
     <t>G2 KVM</t>
+  </si>
+  <si>
+    <t>2603-1300</t>
+  </si>
+  <si>
+    <t>CueCommander is port 1880, Companion is port 8000, media_arts_home is port 80.</t>
+  </si>
+  <si>
+    <t>osc:9110</t>
+  </si>
+  <si>
+    <t>avio-videomixer 11</t>
+  </si>
+  <si>
+    <t>unknown</t>
+  </si>
+  <si>
+    <t>Dante 1</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>-BMD-VideoHub</t>
+  </si>
+  <si>
+    <t>ATEM Constellation</t>
+  </si>
+  <si>
+    <t>Amplifier</t>
   </si>
 </sst>
 </file>
@@ -1524,7 +1491,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1539,11 +1506,9 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1556,20 +1521,15 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1577,10 +1537,55 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="12" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1598,6 +1603,7 @@
         <family val="2"/>
         <scheme val="major"/>
       </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1864,11 +1870,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K156" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K156" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K156">
-    <sortCondition ref="C2:C156"/>
-    <sortCondition ref="A2:A156"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K131" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K131" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K131">
+    <sortCondition ref="C2:C131"/>
   </sortState>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{EF2C341F-E5C1-604C-942C-FB7E9F76F1CD}" name="AssetTag" dataDxfId="10"/>
@@ -2184,3583 +2189,3186 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC7A309-0B6A-4549-9590-6CFCF97D2DB0}">
-  <dimension ref="A1:K1743"/>
+  <dimension ref="A1:K1718"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" customWidth="1"/>
     <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.1640625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="14.1640625" customWidth="1"/>
+    <col min="7" max="7" width="22.5" customWidth="1"/>
     <col min="8" max="8" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.1640625" style="4" customWidth="1"/>
     <col min="10" max="10" width="29.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="44.6640625" style="55" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.1640625" customWidth="1"/>
     <col min="13" max="13" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>142</v>
+      <c r="K1" s="43" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="5"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24" t="s">
-        <v>332</v>
+      <c r="A2" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="22" t="s">
+        <v>320</v>
       </c>
       <c r="D2" s="6"/>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="F2" s="23"/>
+      <c r="G2" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="F2" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="8"/>
+      <c r="H2" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
+      <c r="J2" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="K2" s="45"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="K3" s="6"/>
+        <v>193</v>
+      </c>
+      <c r="K3" s="44"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="5"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24" t="s">
-        <v>333</v>
+      <c r="A4" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>195</v>
       </c>
       <c r="D4" s="6"/>
-      <c r="E4" s="24" t="s">
-        <v>196</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I4" s="9"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
+      <c r="J4" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="K4" s="45"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>198</v>
+      <c r="A5" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>190</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
+      <c r="E5" s="6" t="s">
+        <v>202</v>
+      </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="K5" s="6"/>
+        <v>209</v>
+      </c>
+      <c r="K5" s="44"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="B6" s="10" t="s">
+      <c r="A6" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>208</v>
+      <c r="C6" s="22" t="s">
+        <v>204</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="E6" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="F6" s="6"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
       <c r="G6" s="6"/>
       <c r="H6" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I6" s="9"/>
-      <c r="J6" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="K6" s="6"/>
+      <c r="J6" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="K6" s="45"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="5"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24" t="s">
-        <v>334</v>
+      <c r="A7" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>219</v>
       </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="8"/>
+      <c r="E7" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I7" s="9"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
+      <c r="J7" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="K7" s="44"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>209</v>
+      <c r="A8" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>220</v>
       </c>
       <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
       <c r="G8" s="6"/>
       <c r="H8" s="8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I8" s="9"/>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="23" t="s">
         <v>217</v>
       </c>
-      <c r="K8" s="6"/>
+      <c r="K8" s="45"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>220</v>
+      <c r="A9" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="K9" s="6"/>
+        <v>210</v>
+      </c>
+      <c r="K9" s="44"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="5"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24" t="s">
-        <v>335</v>
+      <c r="A10" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>207</v>
       </c>
       <c r="D10" s="6"/>
-      <c r="E10" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="8"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I10" s="9"/>
-      <c r="J10" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="K10" s="38">
-        <v>26</v>
-      </c>
+      <c r="J10" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="K10" s="45"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>225</v>
+      <c r="A11" s="32" t="s">
+        <v>308</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="32" t="s">
+        <v>321</v>
       </c>
       <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="8" t="s">
-        <v>171</v>
-      </c>
+      <c r="E11" s="32" t="s">
+        <v>309</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H11" s="8"/>
       <c r="I11" s="9"/>
-      <c r="J11" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="K11" s="6"/>
+      <c r="J11" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="K11" s="48">
+        <v>36</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>211</v>
+      <c r="A12" s="22" t="s">
+        <v>318</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="22" t="s">
+        <v>322</v>
       </c>
       <c r="D12" s="6"/>
-      <c r="E12" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="8" t="s">
-        <v>170</v>
-      </c>
+      <c r="E12" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H12" s="8"/>
       <c r="I12" s="9"/>
-      <c r="J12" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="K12" s="6"/>
+      <c r="J12" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="K12" s="47">
+        <v>5</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="5"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24" t="s">
-        <v>336</v>
+      <c r="A13" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="22" t="s">
+        <v>323</v>
       </c>
       <c r="D13" s="6"/>
-      <c r="E13" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="F13" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="G13" s="7"/>
+      <c r="E13" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>230</v>
+      </c>
       <c r="H13" s="8"/>
       <c r="I13" s="9"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
+      <c r="J13" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="K13" s="47">
+        <v>47</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>212</v>
+      <c r="A14" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="22" t="s">
+        <v>324</v>
       </c>
       <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="8" t="s">
-        <v>171</v>
-      </c>
+      <c r="E14" s="22" t="s">
+        <v>303</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H14" s="8"/>
       <c r="I14" s="9"/>
-      <c r="J14" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="K14" s="6"/>
+      <c r="J14" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="K14" s="47">
+        <v>33</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="38" t="s">
-        <v>320</v>
+      <c r="A15" s="22" t="s">
+        <v>306</v>
       </c>
       <c r="B15" s="5"/>
-      <c r="C15" s="38" t="s">
-        <v>337</v>
+      <c r="C15" s="22" t="s">
+        <v>325</v>
       </c>
       <c r="D15" s="6"/>
-      <c r="E15" s="38" t="s">
-        <v>321</v>
-      </c>
-      <c r="F15" s="38" t="s">
-        <v>289</v>
-      </c>
-      <c r="G15" s="7"/>
+      <c r="E15" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>230</v>
+      </c>
       <c r="H15" s="8"/>
       <c r="I15" s="9"/>
-      <c r="J15" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="K15" s="24">
-        <v>36</v>
+      <c r="J15" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="K15" s="47">
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="24" t="s">
-        <v>330</v>
+      <c r="A16" s="32" t="s">
+        <v>312</v>
       </c>
       <c r="B16" s="5"/>
-      <c r="C16" s="24" t="s">
-        <v>338</v>
+      <c r="C16" s="32" t="s">
+        <v>326</v>
       </c>
       <c r="D16" s="6"/>
-      <c r="E16" s="24" t="s">
-        <v>331</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="G16" s="7"/>
+      <c r="E16" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>230</v>
+      </c>
       <c r="H16" s="8"/>
       <c r="I16" s="9"/>
-      <c r="J16" s="38" t="s">
-        <v>307</v>
-      </c>
-      <c r="K16" s="38">
-        <v>5</v>
+      <c r="J16" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="K16" s="48">
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="24" t="s">
-        <v>326</v>
+      <c r="A17" s="32" t="s">
+        <v>316</v>
       </c>
       <c r="B17" s="5"/>
-      <c r="C17" s="24" t="s">
-        <v>339</v>
+      <c r="C17" s="32" t="s">
+        <v>327</v>
       </c>
       <c r="D17" s="6"/>
-      <c r="E17" s="24" t="s">
-        <v>327</v>
-      </c>
-      <c r="F17" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="G17" s="7"/>
+      <c r="E17" s="32" t="s">
+        <v>317</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>230</v>
+      </c>
       <c r="H17" s="8"/>
       <c r="I17" s="9"/>
-      <c r="J17" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="K17" s="38">
-        <v>47</v>
+      <c r="J17" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="K17" s="48">
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="24" t="s">
-        <v>314</v>
+      <c r="A18" s="22" t="s">
+        <v>310</v>
       </c>
       <c r="B18" s="5"/>
-      <c r="C18" s="24" t="s">
-        <v>340</v>
+      <c r="C18" s="22" t="s">
+        <v>328</v>
       </c>
       <c r="D18" s="6"/>
-      <c r="E18" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="G18" s="7"/>
+      <c r="E18" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>230</v>
+      </c>
       <c r="H18" s="8"/>
       <c r="I18" s="9"/>
-      <c r="J18" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="K18" s="38">
-        <v>33</v>
+      <c r="J18" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="K18" s="47">
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="24" t="s">
-        <v>318</v>
+      <c r="A19" s="32" t="s">
+        <v>304</v>
       </c>
       <c r="B19" s="5"/>
-      <c r="C19" s="24" t="s">
-        <v>341</v>
+      <c r="C19" s="32" t="s">
+        <v>329</v>
       </c>
       <c r="D19" s="6"/>
-      <c r="E19" s="24" t="s">
-        <v>319</v>
-      </c>
-      <c r="F19" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="G19" s="7"/>
+      <c r="E19" s="32" t="s">
+        <v>305</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>230</v>
+      </c>
       <c r="H19" s="8"/>
       <c r="I19" s="9"/>
-      <c r="J19" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="K19" s="38">
-        <v>35</v>
+      <c r="J19" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="K19" s="48">
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="38" t="s">
-        <v>324</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="38" t="s">
-        <v>342</v>
+      <c r="A20" s="5"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32" t="s">
+        <v>330</v>
       </c>
       <c r="D20" s="6"/>
-      <c r="E20" s="38" t="s">
-        <v>325</v>
-      </c>
-      <c r="F20" s="38" t="s">
-        <v>289</v>
+      <c r="E20" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>294</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="8"/>
       <c r="I20" s="9"/>
-      <c r="J20" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="K20" s="24">
-        <v>38</v>
-      </c>
+      <c r="J20" s="23"/>
+      <c r="K20" s="45"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="38" t="s">
-        <v>328</v>
-      </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="38" t="s">
-        <v>343</v>
-      </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="38" t="s">
-        <v>329</v>
-      </c>
-      <c r="F21" s="38" t="s">
-        <v>289</v>
-      </c>
-      <c r="G21" s="7"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="24" t="s">
-        <v>307</v>
-      </c>
-      <c r="K21" s="24">
-        <v>3</v>
+      <c r="A21" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K21" s="44" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="24" t="s">
-        <v>322</v>
-      </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="24" t="s">
-        <v>344</v>
-      </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="24" t="s">
-        <v>323</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="G22" s="7"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="K22" s="38">
-        <v>37</v>
+      <c r="A22" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K22" s="44" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="38" t="s">
-        <v>316</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="38" t="s">
-        <v>345</v>
-      </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="38" t="s">
-        <v>317</v>
-      </c>
-      <c r="F23" s="38" t="s">
-        <v>289</v>
-      </c>
-      <c r="G23" s="7"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="K23" s="24">
-        <v>34</v>
+      <c r="A23" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K23" s="44" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="5"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="38" t="s">
-        <v>346</v>
-      </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="38" t="s">
-        <v>300</v>
-      </c>
-      <c r="F24" s="38" t="s">
-        <v>301</v>
-      </c>
-      <c r="G24" s="7"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
+      <c r="A24" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K24" s="44" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>59</v>
+        <v>137</v>
       </c>
       <c r="B25" s="6"/>
-      <c r="C25" s="22" t="s">
-        <v>58</v>
+      <c r="C25" s="11" t="s">
+        <v>135</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>256</v>
+        <v>134</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>271</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="I25" s="9"/>
       <c r="J25" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="K25" s="6" t="s">
-        <v>46</v>
+        <v>136</v>
+      </c>
+      <c r="K25" s="46" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B26" s="6"/>
+      <c r="A26" s="22"/>
+      <c r="B26" s="5"/>
       <c r="C26" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>46</v>
+        <v>268</v>
+      </c>
+      <c r="D26" s="6"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="45" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="22" t="s">
-        <v>50</v>
+        <v>93</v>
+      </c>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23" t="s">
+        <v>331</v>
       </c>
       <c r="D27" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="F27" s="19" t="str">
+        <f>CONCATENATE("http://", E27)</f>
+        <v>http://192.168.201.110</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I27" s="9"/>
+      <c r="J27" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="K27" s="46">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A28" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>271</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="I28" s="9"/>
       <c r="J28" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="K28" s="6" t="s">
-        <v>46</v>
+        <v>37</v>
+      </c>
+      <c r="K28" s="44" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="11" t="s">
-        <v>139</v>
+        <v>38</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I29" s="9"/>
       <c r="J29" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="K29" s="12" t="s">
-        <v>78</v>
+        <v>37</v>
+      </c>
+      <c r="K29" s="44" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A30" s="5"/>
+      <c r="A30" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
-        <v>275</v>
+        <v>5</v>
       </c>
       <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
+      <c r="E30" s="6" t="s">
+        <v>224</v>
+      </c>
       <c r="F30" s="6"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="8"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I30" s="9"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6" t="s">
-        <v>276</v>
-      </c>
+      <c r="J30" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="K30" s="44"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>39</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D31" s="6"/>
       <c r="E31" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="F31" s="7" t="str">
-        <f>CONCATENATE("http://", E31)</f>
-        <v>http://192.168.201.110</v>
-      </c>
-      <c r="G31" s="23" t="s">
-        <v>236</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
       <c r="H31" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I31" s="9"/>
-      <c r="J31" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="K31" s="12" t="s">
-        <v>86</v>
-      </c>
+      <c r="J31" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="K31" s="44"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>39</v>
-      </c>
+      <c r="A32" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D32" s="6"/>
       <c r="E32" s="6" t="s">
-        <v>43</v>
+        <v>222</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I32" s="9"/>
-      <c r="J32" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K32" s="6" t="s">
-        <v>255</v>
-      </c>
+      <c r="J32" s="6">
+        <v>30</v>
+      </c>
+      <c r="K32" s="44"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A33" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="8" t="s">
-        <v>171</v>
-      </c>
+      <c r="A33" s="5"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22" t="s">
+        <v>332</v>
+      </c>
+      <c r="D33" s="6"/>
+      <c r="E33" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="F33" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="G33" s="7"/>
+      <c r="H33" s="8"/>
       <c r="I33" s="9"/>
-      <c r="J33" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K33" s="6" t="s">
-        <v>255</v>
-      </c>
+      <c r="J33" s="6"/>
+      <c r="K33" s="44"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="I34" s="9"/>
-      <c r="J34" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="K34" s="6"/>
+      <c r="A34" s="22"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="32" t="s">
+        <v>333</v>
+      </c>
+      <c r="D34" s="23"/>
+      <c r="E34" s="32" t="s">
+        <v>290</v>
+      </c>
+      <c r="F34" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="G34" s="19"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="23"/>
+      <c r="K34" s="45"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" s="24"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="24" t="s">
-        <v>348</v>
-      </c>
-      <c r="D35" s="25"/>
-      <c r="E35" s="24" t="s">
-        <v>229</v>
-      </c>
-      <c r="F35" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="G35" s="21"/>
+      <c r="A35" s="5"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="D35" s="6"/>
+      <c r="E35" s="32" t="s">
+        <v>287</v>
+      </c>
+      <c r="F35" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="G35" s="7"/>
       <c r="H35" s="8"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="K35" s="38">
-        <v>1</v>
-      </c>
+      <c r="I35" s="9"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="44"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>202</v>
+      <c r="A36" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="B36" s="32"/>
+      <c r="C36" s="32" t="s">
+        <v>335</v>
       </c>
       <c r="D36" s="6"/>
-      <c r="E36" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="8" t="s">
-        <v>170</v>
-      </c>
+      <c r="E36" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="F36" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="G36" s="7"/>
+      <c r="H36" s="8"/>
       <c r="I36" s="9"/>
-      <c r="J36" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="K36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="44"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="5"/>
-      <c r="B37" s="38"/>
-      <c r="C37" s="38" t="s">
-        <v>349</v>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32" t="s">
+        <v>336</v>
       </c>
       <c r="D37" s="6"/>
-      <c r="E37" s="38" t="s">
-        <v>201</v>
-      </c>
-      <c r="F37" s="38" t="s">
-        <v>289</v>
+      <c r="E37" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="F37" s="32" t="s">
+        <v>282</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="8"/>
       <c r="I37" s="9"/>
-      <c r="J37" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="K37" s="24">
-        <v>11</v>
+      <c r="J37" s="6"/>
+      <c r="K37" s="44" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5" t="s">
-        <v>228</v>
+      <c r="A38" s="5"/>
+      <c r="B38" s="32"/>
+      <c r="C38" s="32" t="s">
+        <v>337</v>
       </c>
       <c r="D38" s="6"/>
-      <c r="E38" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="8" t="s">
-        <v>170</v>
-      </c>
+      <c r="E38" s="32" t="s">
+        <v>289</v>
+      </c>
+      <c r="F38" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="G38" s="7"/>
+      <c r="H38" s="8"/>
       <c r="I38" s="9"/>
       <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
+      <c r="K38" s="44" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="5"/>
-      <c r="B39" s="38"/>
-      <c r="C39" s="38" t="s">
-        <v>350</v>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32" t="s">
+        <v>338</v>
       </c>
       <c r="D39" s="6"/>
-      <c r="E39" s="38" t="s">
-        <v>227</v>
-      </c>
-      <c r="F39" s="38" t="s">
-        <v>289</v>
+      <c r="E39" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="F39" s="32" t="s">
+        <v>282</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="8"/>
       <c r="I39" s="9"/>
-      <c r="J39" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="K39" s="24">
-        <v>30</v>
+      <c r="J39" s="6"/>
+      <c r="K39" s="44" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="5"/>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24" t="s">
-        <v>351</v>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22" t="s">
+        <v>339</v>
       </c>
       <c r="D40" s="6"/>
-      <c r="E40" s="24" t="s">
-        <v>295</v>
-      </c>
-      <c r="F40" s="24" t="s">
-        <v>289</v>
+      <c r="E40" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="F40" s="22" t="s">
+        <v>282</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="8"/>
       <c r="I40" s="9"/>
       <c r="J40" s="6"/>
-      <c r="K40" s="6"/>
+      <c r="K40" s="44" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A41" s="24"/>
-      <c r="B41" s="38"/>
-      <c r="C41" s="38" t="s">
-        <v>352</v>
-      </c>
-      <c r="D41" s="25"/>
-      <c r="E41" s="38" t="s">
-        <v>297</v>
-      </c>
-      <c r="F41" s="38" t="s">
-        <v>289</v>
-      </c>
-      <c r="G41" s="21"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="D41" s="6"/>
+      <c r="E41" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="F41" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="G41" s="7"/>
       <c r="H41" s="8"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="25"/>
-      <c r="K41" s="25"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="44" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="5"/>
-      <c r="B42" s="38"/>
-      <c r="C42" s="38" t="s">
-        <v>353</v>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22" t="s">
+        <v>341</v>
       </c>
       <c r="D42" s="6"/>
-      <c r="E42" s="38" t="s">
-        <v>294</v>
-      </c>
-      <c r="F42" s="38" t="s">
-        <v>289</v>
+      <c r="E42" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="F42" s="22" t="s">
+        <v>282</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="8"/>
       <c r="I42" s="9"/>
       <c r="J42" s="6"/>
-      <c r="K42" s="6"/>
+      <c r="K42" s="44" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="5"/>
-      <c r="B43" s="38"/>
-      <c r="C43" s="38" t="s">
-        <v>354</v>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22" t="s">
+        <v>342</v>
       </c>
       <c r="D43" s="6"/>
-      <c r="E43" s="38" t="s">
-        <v>291</v>
-      </c>
-      <c r="F43" s="38" t="s">
-        <v>289</v>
+      <c r="E43" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="F43" s="22" t="s">
+        <v>282</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="8"/>
       <c r="I43" s="9"/>
       <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
+      <c r="K43" s="44" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="5"/>
-      <c r="B44" s="38"/>
-      <c r="C44" s="38" t="s">
-        <v>355</v>
+      <c r="B44" s="32"/>
+      <c r="C44" s="32" t="s">
+        <v>343</v>
       </c>
       <c r="D44" s="6"/>
-      <c r="E44" s="38" t="s">
-        <v>298</v>
-      </c>
-      <c r="F44" s="38" t="s">
-        <v>289</v>
+      <c r="E44" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="F44" s="32" t="s">
+        <v>282</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="8"/>
       <c r="I44" s="9"/>
       <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
+      <c r="K44" s="44" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A45" s="5"/>
-      <c r="B45" s="38"/>
-      <c r="C45" s="38" t="s">
-        <v>356</v>
-      </c>
-      <c r="D45" s="6"/>
-      <c r="E45" s="38" t="s">
-        <v>296</v>
-      </c>
-      <c r="F45" s="38" t="s">
-        <v>289</v>
-      </c>
-      <c r="G45" s="7"/>
+      <c r="A45" s="22"/>
+      <c r="B45" s="32"/>
+      <c r="C45" s="32" t="s">
+        <v>344</v>
+      </c>
+      <c r="D45" s="23"/>
+      <c r="E45" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="F45" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="G45" s="19"/>
       <c r="H45" s="8"/>
-      <c r="I45" s="9"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
+      <c r="I45" s="24"/>
+      <c r="J45" s="23"/>
+      <c r="K45" s="44" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A46" s="5"/>
-      <c r="B46" s="38"/>
-      <c r="C46" s="38" t="s">
-        <v>357</v>
-      </c>
-      <c r="D46" s="6"/>
-      <c r="E46" s="38" t="s">
-        <v>303</v>
-      </c>
-      <c r="F46" s="38" t="s">
-        <v>289</v>
+      <c r="A46" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F46" s="7" t="str">
+        <f>CONCATENATE("http://", E46)</f>
+        <v>http://192.168.0.180</v>
       </c>
       <c r="G46" s="7"/>
-      <c r="H46" s="8"/>
+      <c r="H46" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I46" s="9"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6"/>
+      <c r="J46" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="K46" s="44" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47" s="5"/>
-      <c r="B47" s="24"/>
-      <c r="C47" s="24" t="s">
-        <v>358</v>
-      </c>
-      <c r="D47" s="6"/>
-      <c r="E47" s="24" t="s">
-        <v>299</v>
-      </c>
-      <c r="F47" s="24" t="s">
-        <v>289</v>
+      <c r="A47" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F47" s="7" t="str">
+        <f>CONCATENATE("http://", E47)</f>
+        <v>http://192.168.0.181</v>
       </c>
       <c r="G47" s="7"/>
-      <c r="H47" s="8"/>
+      <c r="H47" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I47" s="9"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
+      <c r="J47" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="K47" s="44" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A48" s="5"/>
-      <c r="B48" s="24"/>
-      <c r="C48" s="24" t="s">
-        <v>359</v>
-      </c>
-      <c r="D48" s="6"/>
-      <c r="E48" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="F48" s="24" t="s">
-        <v>289</v>
+      <c r="A48" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F48" s="7" t="str">
+        <f>CONCATENATE("http://", E48)</f>
+        <v>http://192.168.0.192</v>
       </c>
       <c r="G48" s="7"/>
-      <c r="H48" s="8"/>
+      <c r="H48" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I48" s="9"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
+      <c r="J48" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="K48" s="46" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A49" s="5"/>
-      <c r="B49" s="24"/>
-      <c r="C49" s="24" t="s">
-        <v>360</v>
+      <c r="A49" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="B49" s="5"/>
+      <c r="C49" s="6" t="s">
+        <v>232</v>
       </c>
       <c r="D49" s="6"/>
-      <c r="E49" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="F49" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="G49" s="7"/>
-      <c r="H49" s="8"/>
+      <c r="E49" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="F49" s="6"/>
+      <c r="G49" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I49" s="9"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="6"/>
+      <c r="J49" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="K49" s="44">
+        <v>22</v>
+      </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A50" s="5"/>
-      <c r="B50" s="24"/>
-      <c r="C50" s="24" t="s">
-        <v>361</v>
+      <c r="A50" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="B50" s="13"/>
+      <c r="C50" s="5" t="s">
+        <v>201</v>
       </c>
       <c r="D50" s="6"/>
-      <c r="E50" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="F50" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="G50" s="7"/>
-      <c r="H50" s="8"/>
+      <c r="E50" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I50" s="9"/>
       <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
+      <c r="K50" s="44"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A51" s="5"/>
-      <c r="B51" s="38"/>
-      <c r="C51" s="38" t="s">
-        <v>362</v>
-      </c>
-      <c r="D51" s="6"/>
-      <c r="E51" s="38" t="s">
-        <v>292</v>
-      </c>
-      <c r="F51" s="38" t="s">
-        <v>289</v>
-      </c>
-      <c r="G51" s="7"/>
-      <c r="H51" s="8"/>
+      <c r="A51" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F51" s="7" t="str">
+        <f>CONCATENATE("http://", E51)</f>
+        <v>http://192.168.0.23</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I51" s="9"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
+      <c r="J51" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K51" s="46"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A52" s="24"/>
-      <c r="B52" s="38"/>
-      <c r="C52" s="38" t="s">
-        <v>363</v>
-      </c>
-      <c r="D52" s="25"/>
-      <c r="E52" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="F52" s="38" t="s">
-        <v>289</v>
-      </c>
-      <c r="G52" s="21"/>
-      <c r="H52" s="8"/>
-      <c r="I52" s="26"/>
-      <c r="J52" s="25"/>
-      <c r="K52" s="25"/>
+      <c r="A52" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F52" s="7" t="str">
+        <f>CONCATENATE("http://", E52)</f>
+        <v>http://192.168.0.22</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="I52" s="9"/>
+      <c r="J52" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K52" s="46"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A53" s="25" t="s">
-        <v>112</v>
+      <c r="A53" s="23" t="s">
+        <v>130</v>
       </c>
       <c r="B53" s="6"/>
-      <c r="C53" s="6" t="s">
-        <v>110</v>
+      <c r="C53" s="23" t="s">
+        <v>132</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F53" s="7" t="str">
-        <f>CONCATENATE("http://", E53)</f>
-        <v>http://192.168.0.180</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E53" s="23"/>
+      <c r="F53" s="19"/>
       <c r="G53" s="7"/>
-      <c r="H53" s="8" t="s">
-        <v>171</v>
+      <c r="H53" s="18" t="s">
+        <v>167</v>
       </c>
       <c r="I53" s="9"/>
-      <c r="J53" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="K53" s="6" t="s">
-        <v>108</v>
-      </c>
+      <c r="J53" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="K53" s="59"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
-        <v>107</v>
+        <v>7</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="F54" s="7" t="str">
         <f>CONCATENATE("http://", E54)</f>
-        <v>http://192.168.0.181</v>
-      </c>
-      <c r="G54" s="7"/>
-      <c r="H54" s="8" t="s">
-        <v>171</v>
+        <v>http://192.168.0.24</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H54" s="18" t="s">
+        <v>167</v>
       </c>
       <c r="I54" s="9"/>
       <c r="J54" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="K54" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="K54" s="46"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="6" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>87</v>
+        <v>100</v>
+      </c>
+      <c r="E55" s="14" t="s">
+        <v>124</v>
       </c>
       <c r="F55" s="7" t="str">
         <f>CONCATENATE("http://", E55)</f>
-        <v>http://192.168.0.192</v>
-      </c>
-      <c r="G55" s="7"/>
-      <c r="H55" s="8" t="s">
-        <v>171</v>
+        <v>http://192.168.0.25</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H55" s="18" t="s">
+        <v>167</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="K55" s="12" t="s">
-        <v>86</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="K55" s="44"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A56" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="38" t="s">
-        <v>238</v>
-      </c>
-      <c r="D56" s="6"/>
-      <c r="E56" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="F56" s="38" t="s">
-        <v>289</v>
-      </c>
-      <c r="G56" s="7"/>
-      <c r="H56" s="8"/>
+      <c r="A56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F56" s="7" t="str">
+        <f>CONCATENATE("http://", E56)</f>
+        <v>http://192.168.0.26</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H56" s="18" t="s">
+        <v>167</v>
+      </c>
       <c r="I56" s="9"/>
-      <c r="J56" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="K56" s="24">
-        <v>22</v>
-      </c>
+      <c r="J56" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K56" s="46"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A57" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="B57" s="5"/>
+      <c r="A57" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B57" s="10"/>
       <c r="C57" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="D57" s="6"/>
+        <v>51</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="E57" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="F57" s="6"/>
-      <c r="G57" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="H57" s="8" t="s">
-        <v>170</v>
+        <v>50</v>
+      </c>
+      <c r="F57" s="6" t="str">
+        <f>CONCATENATE("http://", E57, ":8080")</f>
+        <v>http://192.168.0.197:8080</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="H57" s="18" t="s">
+        <v>166</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="K57" s="6"/>
+        <v>52</v>
+      </c>
+      <c r="K57" s="44"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A58" s="41" t="s">
-        <v>204</v>
-      </c>
-      <c r="B58" s="5"/>
-      <c r="C58" s="24" t="s">
-        <v>364</v>
-      </c>
-      <c r="D58" s="6"/>
-      <c r="E58" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="F58" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="G58" s="7"/>
-      <c r="H58" s="8"/>
+      <c r="A58" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B58" s="6"/>
+      <c r="C58" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F58" s="7" t="str">
+        <f>CONCATENATE("http://", E58)</f>
+        <v>http://192.168.0.193</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="H58" s="18" t="s">
+        <v>167</v>
+      </c>
       <c r="I58" s="9"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
+      <c r="J58" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K58" s="44" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A59" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="B59" s="14"/>
-      <c r="C59" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="D59" s="6"/>
+      <c r="A59" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B59" s="6"/>
+      <c r="C59" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="E59" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="H59" s="8" t="s">
-        <v>170</v>
+        <v>113</v>
+      </c>
+      <c r="F59" s="7" t="str">
+        <f>CONCATENATE("http://", E59)</f>
+        <v>http://192.168.0.187</v>
+      </c>
+      <c r="G59" s="7"/>
+      <c r="H59" s="18" t="s">
+        <v>166</v>
       </c>
       <c r="I59" s="9"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
+      <c r="J59" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K59" s="44" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
-        <v>31</v>
+        <v>112</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="6" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F60" s="7" t="str">
         <f>CONCATENATE("http://", E60)</f>
-        <v>http://192.168.0.23</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="H60" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="I60" s="9"/>
+        <v>http://192.168.0.188</v>
+      </c>
+      <c r="G60" s="7"/>
+      <c r="H60" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>264</v>
+      </c>
       <c r="J60" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="K60" s="12"/>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A61" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E61" s="6"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="I61" s="9"/>
-      <c r="J61" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="K61" s="12"/>
+        <v>111</v>
+      </c>
+      <c r="K60" s="44" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A61" s="22" t="s">
+        <v>277</v>
+      </c>
+      <c r="B61" s="22"/>
+      <c r="C61" s="22" t="s">
+        <v>345</v>
+      </c>
+      <c r="D61" s="23"/>
+      <c r="E61" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="F61" s="23"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="I61" s="24"/>
+      <c r="J61" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="K61" s="45">
+        <v>12</v>
+      </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A62" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>104</v>
-      </c>
+      <c r="A62" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D62" s="6"/>
       <c r="E62" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="F62" s="7" t="str">
-        <f>CONCATENATE("http://", E62)</f>
-        <v>http://192.168.0.22</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="F62" s="7"/>
       <c r="G62" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="H62" s="20" t="s">
-        <v>171</v>
+        <v>242</v>
+      </c>
+      <c r="H62" s="18" t="s">
+        <v>166</v>
       </c>
       <c r="I62" s="9"/>
-      <c r="J62" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="K62" s="12"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="44">
+        <v>3</v>
+      </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A63" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B63" s="6"/>
+      <c r="A63" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="B63" s="5"/>
       <c r="C63" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>104</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="D63" s="6"/>
       <c r="E63" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="F63" s="7" t="str">
-        <f>CONCATENATE("http://", E63)</f>
-        <v>http://192.168.0.24</v>
-      </c>
-      <c r="G63" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="H63" s="20" t="s">
-        <v>171</v>
+        <v>150</v>
+      </c>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="18" t="s">
+        <v>167</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="K63" s="12"/>
+        <v>10</v>
+      </c>
+      <c r="K63" s="44"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A64" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E64" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="F64" s="7" t="str">
-        <f>CONCATENATE("http://", E64)</f>
-        <v>http://192.168.0.25</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="H64" s="20" t="s">
-        <v>171</v>
+      <c r="A64" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B64" s="22"/>
+      <c r="C64" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="D64" s="6"/>
+      <c r="E64" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="F64" s="23"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="18" t="s">
+        <v>166</v>
       </c>
       <c r="I64" s="9"/>
       <c r="J64" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="K64" s="6"/>
+        <v>187</v>
+      </c>
+      <c r="K64" s="44">
+        <v>6</v>
+      </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A65" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B65" s="6"/>
+      <c r="A65" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B65" s="5"/>
       <c r="C65" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>104</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="D65" s="6"/>
       <c r="E65" s="6" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="F65" s="7" t="str">
         <f>CONCATENATE("http://", E65)</f>
-        <v>http://192.168.0.26</v>
-      </c>
-      <c r="G65" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="H65" s="20" t="s">
-        <v>171</v>
+        <v>http://192.168.0.208</v>
+      </c>
+      <c r="G65" s="7"/>
+      <c r="H65" s="18" t="s">
+        <v>166</v>
       </c>
       <c r="I65" s="9"/>
       <c r="J65" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="K65" s="12"/>
+        <v>146</v>
+      </c>
+      <c r="K65" s="44"/>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A66" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="B66" s="10"/>
-      <c r="C66" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>39</v>
-      </c>
+      <c r="A66" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="D66" s="6"/>
       <c r="E66" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F66" s="6" t="str">
-        <f>CONCATENATE("http://", E66, ":8080")</f>
-        <v>http://192.168.0.197:8080</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="F66" s="6"/>
       <c r="G66" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="H66" s="20" t="s">
-        <v>170</v>
+        <v>241</v>
+      </c>
+      <c r="H66" s="18" t="s">
+        <v>166</v>
       </c>
       <c r="I66" s="9"/>
       <c r="J66" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="K66" s="6"/>
+        <v>161</v>
+      </c>
+      <c r="K66" s="44" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A67" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F67" s="7" t="str">
-        <f>CONCATENATE("http://", E67)</f>
-        <v>http://192.168.0.193</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="H67" s="20" t="s">
+      <c r="A67" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C67" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D67" s="6"/>
+      <c r="E67" s="14" t="s">
         <v>171</v>
+      </c>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="H67" s="18" t="s">
+        <v>166</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="K67" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="K67" s="44"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A68" s="22" t="s">
+        <v>359</v>
+      </c>
+      <c r="B68" s="22"/>
+      <c r="C68" s="57" t="s">
+        <v>348</v>
+      </c>
+      <c r="D68" s="6"/>
+      <c r="E68" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="F68" s="23"/>
+      <c r="G68" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="H68" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="I68" s="24"/>
+      <c r="J68" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="K68" s="48" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A69" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="B69" s="22"/>
+      <c r="C69" s="57" t="s">
+        <v>349</v>
+      </c>
+      <c r="D69" s="6"/>
+      <c r="E69" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="F69" s="23"/>
+      <c r="G69" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="H69" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="I69" s="24"/>
+      <c r="J69" s="41" t="s">
+        <v>361</v>
+      </c>
+      <c r="K69" s="47" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A70" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="I70" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="J70" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="K70" s="46" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A68" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B68" s="6"/>
-      <c r="C68" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E68" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="F68" s="7" t="str">
-        <f>CONCATENATE("http://", E68)</f>
-        <v>http://192.168.0.187</v>
-      </c>
-      <c r="G68" s="7"/>
-      <c r="H68" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="I68" s="9"/>
-      <c r="J68" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="K68" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A69" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E69" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="F69" s="7" t="str">
-        <f>CONCATENATE("http://", E69)</f>
-        <v>http://192.168.0.188</v>
-      </c>
-      <c r="G69" s="7"/>
-      <c r="H69" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="I69" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="J69" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="K69" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A70" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="B70" s="24"/>
-      <c r="C70" s="24" t="s">
-        <v>365</v>
-      </c>
-      <c r="D70" s="25"/>
-      <c r="E70" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="F70" s="25"/>
-      <c r="G70" s="21"/>
-      <c r="H70" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="I70" s="26"/>
-      <c r="J70" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="K70" s="25"/>
-    </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A71" s="5"/>
-      <c r="B71" s="24"/>
-      <c r="C71" s="24" t="s">
-        <v>365</v>
-      </c>
-      <c r="D71" s="6"/>
-      <c r="E71" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="F71" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="G71" s="7"/>
-      <c r="H71" s="20"/>
-      <c r="I71" s="9"/>
-      <c r="J71" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="K71" s="38">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A72" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="D72" s="6"/>
-      <c r="E72" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="F72" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="G72" s="7"/>
-      <c r="H72" s="20"/>
+      <c r="A71" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B71" s="6"/>
+      <c r="C71" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F71" s="7" t="str">
+        <f>CONCATENATE("http://", E71)</f>
+        <v>http://192.168.0.183</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="H71" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="I71" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="J71" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K71" s="44" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B72" s="22"/>
+      <c r="C72" s="22" t="s">
+        <v>350</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E72" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="F72" s="23"/>
+      <c r="G72" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="H72" s="18" t="s">
+        <v>166</v>
+      </c>
       <c r="I72" s="9"/>
-      <c r="J72" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="K72" s="38">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A73" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B73" s="5"/>
-      <c r="C73" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D73" s="6"/>
-      <c r="E73" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F73" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G73" s="6"/>
-      <c r="H73" s="20" t="s">
-        <v>170</v>
+      <c r="J72" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K72" s="44"/>
+    </row>
+    <row r="73" spans="1:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="B73" s="22"/>
+      <c r="C73" s="22" t="s">
+        <v>351</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E73" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="F73" s="23"/>
+      <c r="G73" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="H73" s="18" t="s">
+        <v>166</v>
       </c>
       <c r="I73" s="9"/>
       <c r="J73" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K73" s="6"/>
+        <v>64</v>
+      </c>
+      <c r="K73" s="44"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A74" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="H74" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="I74" s="9"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
+      <c r="A74" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" s="33"/>
+      <c r="C74" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E74" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="F74" s="39" t="str">
+        <f>CONCATENATE("ftp://", E74)</f>
+        <v>ftp://192.168.0.189</v>
+      </c>
+      <c r="G74" s="7"/>
+      <c r="H74" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="J74" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="K74" s="46" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A75" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="B75" s="5"/>
-      <c r="C75" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="D75" s="6"/>
-      <c r="E75" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="F75" s="6"/>
-      <c r="G75" s="6"/>
-      <c r="H75" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="I75" s="9"/>
+      <c r="A75" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B75" s="33"/>
+      <c r="C75" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E75" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="F75" s="39" t="str">
+        <f>CONCATENATE("ftp://", E75)</f>
+        <v>ftp://192.168.0.190</v>
+      </c>
+      <c r="G75" s="7"/>
+      <c r="H75" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>264</v>
+      </c>
       <c r="J75" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K75" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="K75" s="46" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B76" s="5"/>
-      <c r="C76" s="6" t="s">
-        <v>367</v>
+        <v>158</v>
+      </c>
+      <c r="B76" s="28"/>
+      <c r="C76" s="36" t="s">
+        <v>352</v>
       </c>
       <c r="D76" s="6"/>
-      <c r="E76" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="F76" s="6"/>
+      <c r="E76" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="F76" s="36"/>
       <c r="G76" s="6"/>
-      <c r="H76" s="20" t="s">
-        <v>170</v>
+      <c r="H76" s="8" t="s">
+        <v>166</v>
       </c>
       <c r="I76" s="9"/>
       <c r="J76" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="K76" s="6"/>
+        <v>371</v>
+      </c>
+      <c r="K76" s="44">
+        <v>18</v>
+      </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A77" s="38" t="s">
-        <v>308</v>
-      </c>
-      <c r="B77" s="5"/>
-      <c r="C77" s="38" t="s">
-        <v>367</v>
-      </c>
-      <c r="D77" s="6"/>
-      <c r="E77" s="38" t="s">
-        <v>192</v>
-      </c>
-      <c r="F77" s="38" t="s">
-        <v>305</v>
-      </c>
-      <c r="G77" s="7"/>
-      <c r="H77" s="20"/>
+      <c r="A77" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B77" s="33"/>
+      <c r="C77" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E77" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="F77" s="36"/>
+      <c r="G77" s="6"/>
+      <c r="H77" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I77" s="9"/>
-      <c r="J77" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="K77" s="24">
-        <v>6</v>
+      <c r="J77" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K77" s="44" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A78" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B78" s="5"/>
-      <c r="C78" s="6" t="s">
-        <v>151</v>
+      <c r="A78" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="B78" s="28"/>
+      <c r="C78" s="29" t="s">
+        <v>353</v>
       </c>
       <c r="D78" s="6"/>
-      <c r="E78" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F78" s="7" t="str">
-        <f>CONCATENATE("http://", E78)</f>
-        <v>http://192.168.0.208</v>
+      <c r="E78" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="F78" s="29" t="s">
+        <v>298</v>
       </c>
       <c r="G78" s="7"/>
-      <c r="H78" s="20" t="s">
-        <v>170</v>
-      </c>
+      <c r="H78" s="8"/>
       <c r="I78" s="9"/>
-      <c r="J78" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="K78" s="6"/>
+      <c r="J78" s="32" t="s">
+        <v>370</v>
+      </c>
+      <c r="K78" s="47">
+        <v>14</v>
+      </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="C79" s="17" t="s">
+        <v>362</v>
+      </c>
+      <c r="B79" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="C79" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="D79" s="6"/>
+      <c r="E79" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="F79" s="36"/>
+      <c r="G79" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="H79" s="8" t="s">
         <v>166</v>
-      </c>
-      <c r="D79" s="6"/>
-      <c r="E79" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F79" s="6"/>
-      <c r="G79" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="H79" s="20" t="s">
-        <v>170</v>
       </c>
       <c r="I79" s="9"/>
       <c r="J79" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="K79" s="6"/>
+        <v>177</v>
+      </c>
+      <c r="K79" s="44"/>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A80" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="B80" s="5"/>
-      <c r="C80" s="24" t="s">
-        <v>368</v>
-      </c>
-      <c r="D80" s="25"/>
-      <c r="E80" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="F80" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="G80" s="21"/>
-      <c r="H80" s="20"/>
-      <c r="I80" s="26"/>
-      <c r="J80" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="K80" s="38">
-        <v>19</v>
-      </c>
+      <c r="A80" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B80" s="30"/>
+      <c r="C80" s="31" t="s">
+        <v>354</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E80" s="38" t="s">
+        <v>257</v>
+      </c>
+      <c r="F80" s="38"/>
+      <c r="G80" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="H80" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="I80" s="9"/>
+      <c r="J80" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K80" s="44"/>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C81" s="15" t="s">
-        <v>152</v>
+        <v>265</v>
+      </c>
+      <c r="B81" s="28"/>
+      <c r="C81" s="29" t="s">
+        <v>355</v>
       </c>
       <c r="D81" s="6"/>
-      <c r="E81" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="F81" s="6"/>
-      <c r="G81" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="H81" s="20" t="s">
-        <v>170</v>
+      <c r="E81" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="F81" s="36"/>
+      <c r="G81" s="19"/>
+      <c r="H81" s="8" t="s">
+        <v>167</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="K81" s="44"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A82" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="K81" s="6"/>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A82" s="5"/>
-      <c r="B82" s="38"/>
-      <c r="C82" s="38" t="s">
-        <v>369</v>
+      <c r="B82" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="C82" s="29" t="s">
+        <v>185</v>
       </c>
       <c r="D82" s="6"/>
-      <c r="E82" s="38" t="s">
-        <v>309</v>
-      </c>
-      <c r="F82" s="38" t="s">
-        <v>305</v>
-      </c>
+      <c r="E82" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="F82" s="39"/>
       <c r="G82" s="7"/>
-      <c r="H82" s="20"/>
+      <c r="H82" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I82" s="9"/>
-      <c r="J82" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="K82" s="24">
-        <v>8</v>
+      <c r="J82" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="K82" s="44">
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A83" s="5"/>
-      <c r="B83" s="24"/>
-      <c r="C83" s="24" t="s">
-        <v>370</v>
+      <c r="A83" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B83" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="C83" s="29" t="s">
+        <v>184</v>
       </c>
       <c r="D83" s="6"/>
-      <c r="E83" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="F83" s="24" t="s">
-        <v>305</v>
-      </c>
-      <c r="G83" s="7"/>
-      <c r="H83" s="20"/>
+      <c r="E83" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="F83" s="39"/>
+      <c r="G83" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="H83" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I83" s="9"/>
-      <c r="J83" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="K83" s="38">
-        <v>5</v>
-      </c>
+      <c r="J83" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="K83" s="44"/>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A84" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B84" s="6"/>
-      <c r="C84" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="F84" s="6"/>
-      <c r="G84" s="6"/>
-      <c r="H84" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="I84" s="9" t="s">
+      <c r="A84" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B84" s="28"/>
+      <c r="C84" s="26" t="s">
+        <v>356</v>
+      </c>
+      <c r="D84" s="6"/>
+      <c r="E84" s="36" t="s">
+        <v>260</v>
+      </c>
+      <c r="F84" s="36"/>
+      <c r="G84" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="H84" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I84" s="9"/>
+      <c r="J84" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="K84" s="48">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A85" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B85" s="23"/>
+      <c r="C85" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E85" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="F85" s="39" t="str">
+        <f>CONCATENATE("http://", E85)</f>
+        <v>http://192.168.0.195</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="H85" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="I85" s="9"/>
+      <c r="J85" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K85" s="44" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A86" s="56" t="s">
+        <v>69</v>
+      </c>
+      <c r="B86" s="23"/>
+      <c r="C86" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E86" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="F86" s="40" t="str">
+        <f>CONCATENATE("http://", E86)</f>
+        <v>http://192.168.0.194</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="H86" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="I86" s="9"/>
+      <c r="J86" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="K86" s="49" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A87" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B87" s="12"/>
+      <c r="C87" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D87" s="6"/>
+      <c r="E87" s="36"/>
+      <c r="F87" s="36"/>
+      <c r="G87" s="6"/>
+      <c r="H87" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="I87" s="9"/>
+      <c r="J87" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="K87" s="51" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A88" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="B88" s="33"/>
+      <c r="C88" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E88" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="F88" s="39" t="str">
+        <f>CONCATENATE("http://", E88)</f>
+        <v>http://192.168.0.186</v>
+      </c>
+      <c r="G88" s="7"/>
+      <c r="H88" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I88" s="9"/>
+      <c r="J88" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="K88" s="51" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A89" s="22" t="s">
         <v>271</v>
       </c>
-      <c r="J84" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="K84" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A85" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B85" s="6"/>
-      <c r="C85" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E85" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F85" s="7" t="str">
-        <f>CONCATENATE("http://", E85)</f>
-        <v>http://192.168.0.183</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="H85" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="I85" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="J85" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="K85" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B86" s="5"/>
-      <c r="C86" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="F86" s="6"/>
-      <c r="G86" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="H86" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="I86" s="9"/>
-      <c r="J86" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="K86" s="6"/>
-    </row>
-    <row r="87" spans="1:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="40" t="s">
-        <v>262</v>
-      </c>
-      <c r="B87" s="5"/>
-      <c r="C87" s="38" t="s">
-        <v>371</v>
-      </c>
-      <c r="D87" s="6"/>
-      <c r="E87" s="38" t="s">
-        <v>265</v>
-      </c>
-      <c r="F87" s="38" t="s">
-        <v>305</v>
-      </c>
-      <c r="G87" s="7"/>
-      <c r="H87" s="20"/>
-      <c r="I87" s="9"/>
-      <c r="J87" s="6"/>
-      <c r="K87" s="6"/>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A88" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="B88" s="33"/>
-      <c r="C88" s="34" t="s">
-        <v>372</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E88" s="45" t="s">
-        <v>266</v>
-      </c>
-      <c r="F88" s="45"/>
-      <c r="G88" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="H88" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="I88" s="9"/>
-      <c r="J88" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="K88" s="6"/>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A89" s="38" t="s">
-        <v>263</v>
-      </c>
-      <c r="B89" s="30"/>
-      <c r="C89" s="28" t="s">
-        <v>372</v>
+      <c r="B89" s="28"/>
+      <c r="C89" s="29" t="s">
+        <v>357</v>
       </c>
       <c r="D89" s="6"/>
-      <c r="E89" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="F89" s="28" t="s">
-        <v>305</v>
-      </c>
-      <c r="G89" s="7"/>
-      <c r="H89" s="8"/>
+      <c r="E89" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="F89" s="36"/>
+      <c r="G89" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="H89" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I89" s="9"/>
-      <c r="J89" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="K89" s="24">
-        <v>2</v>
-      </c>
+      <c r="J89" s="36" t="s">
+        <v>273</v>
+      </c>
+      <c r="K89" s="51"/>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A90" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B90" s="39"/>
-      <c r="C90" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E90" s="43" t="s">
-        <v>83</v>
-      </c>
-      <c r="F90" s="46" t="str">
-        <f>CONCATENATE("ftp://", E90)</f>
-        <v>ftp://192.168.0.189</v>
-      </c>
-      <c r="G90" s="7"/>
+      <c r="A90" s="28" t="s">
+        <v>272</v>
+      </c>
+      <c r="B90" s="5"/>
+      <c r="C90" s="29" t="s">
+        <v>358</v>
+      </c>
+      <c r="D90" s="6"/>
+      <c r="E90" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="F90" s="36"/>
+      <c r="G90" s="19" t="s">
+        <v>230</v>
+      </c>
       <c r="H90" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="I90" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="J90" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="K90" s="12" t="s">
-        <v>78</v>
+        <v>166</v>
+      </c>
+      <c r="I90" s="9"/>
+      <c r="J90" s="36" t="s">
+        <v>273</v>
+      </c>
+      <c r="K90" s="51">
+        <v>13</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A91" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B91" s="39"/>
-      <c r="C91" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E91" s="43" t="s">
-        <v>79</v>
-      </c>
-      <c r="F91" s="46" t="str">
-        <f>CONCATENATE("ftp://", E91)</f>
-        <v>ftp://192.168.0.190</v>
-      </c>
-      <c r="G91" s="7"/>
+      <c r="A91" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B91" s="28"/>
+      <c r="C91" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D91" s="6"/>
+      <c r="E91" s="36"/>
+      <c r="F91" s="36"/>
+      <c r="G91" s="6"/>
       <c r="H91" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="I91" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="J91" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="K91" s="12" t="s">
-        <v>78</v>
+        <v>167</v>
+      </c>
+      <c r="I91" s="9"/>
+      <c r="J91" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="K91" s="51" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A92" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B92" s="30"/>
-      <c r="C92" s="43" t="s">
-        <v>373</v>
+      <c r="A92" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="B92" s="22"/>
+      <c r="C92" s="36" t="s">
+        <v>154</v>
       </c>
       <c r="D92" s="6"/>
-      <c r="E92" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="F92" s="43"/>
+      <c r="E92" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="F92" s="36"/>
       <c r="G92" s="6"/>
       <c r="H92" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I92" s="9"/>
-      <c r="J92" s="6"/>
-      <c r="K92" s="6"/>
+      <c r="J92" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="K92" s="51"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A93" s="38" t="s">
-        <v>312</v>
-      </c>
-      <c r="B93" s="30"/>
-      <c r="C93" s="28" t="s">
-        <v>373</v>
-      </c>
+      <c r="A93" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B93" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="C93" s="29"/>
       <c r="D93" s="6"/>
-      <c r="E93" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="F93" s="28" t="s">
-        <v>305</v>
-      </c>
+      <c r="E93" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="F93" s="39"/>
       <c r="G93" s="7"/>
-      <c r="H93" s="8"/>
+      <c r="H93" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I93" s="9"/>
-      <c r="J93" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="K93" s="24">
-        <v>18</v>
-      </c>
+      <c r="J93" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="K93" s="51"/>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A94" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B94" s="39"/>
-      <c r="C94" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="D94" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E94" s="43" t="s">
-        <v>92</v>
-      </c>
-      <c r="F94" s="43"/>
+      <c r="A94" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B94" s="33"/>
+      <c r="C94" s="36"/>
+      <c r="D94" s="6"/>
+      <c r="E94" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="F94" s="36"/>
       <c r="G94" s="6"/>
       <c r="H94" s="8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I94" s="9"/>
-      <c r="J94" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="K94" s="6" t="s">
-        <v>91</v>
-      </c>
+      <c r="J94" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="K94" s="51"/>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A95" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="B95" s="30"/>
-      <c r="C95" s="43" t="s">
-        <v>374</v>
-      </c>
+      <c r="A95" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="B95" s="5"/>
+      <c r="C95" s="29"/>
       <c r="D95" s="6"/>
-      <c r="E95" s="43" t="s">
-        <v>160</v>
-      </c>
-      <c r="F95" s="43"/>
-      <c r="G95" s="6"/>
+      <c r="E95" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="F95" s="36"/>
+      <c r="G95" s="19" t="s">
+        <v>364</v>
+      </c>
       <c r="H95" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I95" s="9"/>
-      <c r="J95" s="6"/>
-      <c r="K95" s="6"/>
+      <c r="J95" s="36" t="s">
+        <v>244</v>
+      </c>
+      <c r="K95" s="51"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A96" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="B96" s="30"/>
-      <c r="C96" s="31" t="s">
-        <v>374</v>
-      </c>
+      <c r="A96" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="B96" s="22"/>
+      <c r="C96" s="29"/>
       <c r="D96" s="6"/>
-      <c r="E96" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="F96" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="G96" s="7"/>
+      <c r="E96" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="F96" s="36"/>
+      <c r="G96" s="19"/>
       <c r="H96" s="8"/>
       <c r="I96" s="9"/>
-      <c r="J96" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="K96" s="38">
-        <v>14</v>
-      </c>
+      <c r="J96" s="36"/>
+      <c r="K96" s="51"/>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A97" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B97" s="30" t="s">
-        <v>178</v>
-      </c>
-      <c r="C97" s="44" t="s">
-        <v>176</v>
-      </c>
-      <c r="D97" s="6"/>
-      <c r="E97" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="F97" s="43"/>
-      <c r="G97" s="6" t="s">
+      <c r="A97" s="28" t="s">
+        <v>279</v>
+      </c>
+      <c r="B97" s="22"/>
+      <c r="C97" s="29"/>
+      <c r="D97" s="23"/>
+      <c r="E97" s="36" t="s">
+        <v>280</v>
+      </c>
+      <c r="F97" s="36"/>
+      <c r="G97" s="19"/>
+      <c r="H97" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I97" s="24"/>
+      <c r="J97" s="36"/>
+      <c r="K97" s="51"/>
+    </row>
+    <row r="98" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A98" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B98" s="5"/>
+      <c r="C98" s="38"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="38" t="s">
+        <v>4</v>
+      </c>
+      <c r="F98" s="38"/>
+      <c r="G98" s="6"/>
+      <c r="H98" s="18"/>
+      <c r="I98" s="9"/>
+      <c r="J98" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="K98" s="49"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A99" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="B99" s="5"/>
+      <c r="C99" s="29"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="36"/>
+      <c r="F99" s="36"/>
+      <c r="G99" s="19"/>
+      <c r="H99" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="I99" s="9"/>
+      <c r="J99" s="36"/>
+      <c r="K99" s="51"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A100" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B100" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="C100" s="29"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="36"/>
+      <c r="F100" s="39"/>
+      <c r="G100" s="7"/>
+      <c r="H100" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="I100" s="9"/>
+      <c r="J100" s="36"/>
+      <c r="K100" s="51"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A101" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="B101" s="28"/>
+      <c r="C101" s="29"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="36"/>
+      <c r="F101" s="39"/>
+      <c r="G101" s="7"/>
+      <c r="H101" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="J101" s="36" t="s">
         <v>247</v>
       </c>
-      <c r="H97" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="I97" s="9"/>
-      <c r="J97" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="K97" s="6"/>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A98" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="B98" s="33"/>
-      <c r="C98" s="34" t="s">
-        <v>375</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E98" s="45" t="s">
-        <v>264</v>
-      </c>
-      <c r="F98" s="45"/>
-      <c r="G98" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="H98" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="I98" s="9"/>
-      <c r="J98" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="K98" s="6"/>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A99" s="5"/>
-      <c r="B99" s="27"/>
-      <c r="C99" s="28" t="s">
-        <v>375</v>
-      </c>
-      <c r="D99" s="6"/>
-      <c r="E99" s="28" t="s">
-        <v>264</v>
-      </c>
-      <c r="F99" s="28" t="s">
-        <v>305</v>
-      </c>
-      <c r="G99" s="7"/>
-      <c r="H99" s="8"/>
-      <c r="I99" s="9"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="6"/>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A100" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="B100" s="30"/>
-      <c r="C100" s="31" t="s">
-        <v>376</v>
-      </c>
-      <c r="D100" s="6"/>
-      <c r="E100" s="43" t="s">
-        <v>274</v>
-      </c>
-      <c r="F100" s="43"/>
-      <c r="G100" s="21"/>
-      <c r="H100" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="I100" s="9"/>
-      <c r="J100" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="K100" s="6"/>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A101" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="B101" s="30"/>
-      <c r="C101" s="31" t="s">
-        <v>377</v>
-      </c>
-      <c r="D101" s="6"/>
-      <c r="E101" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="F101" s="31" t="s">
-        <v>289</v>
-      </c>
-      <c r="G101" s="7"/>
-      <c r="H101" s="8"/>
-      <c r="I101" s="9"/>
-      <c r="J101" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="K101" s="38">
-        <v>10</v>
-      </c>
+      <c r="K101" s="51"/>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A102" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B102" s="30" t="s">
-        <v>174</v>
-      </c>
-      <c r="C102" s="31" t="s">
-        <v>189</v>
-      </c>
+      <c r="A102" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B102" s="6"/>
+      <c r="C102" s="36"/>
       <c r="D102" s="6"/>
-      <c r="E102" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="F102" s="46"/>
-      <c r="G102" s="7"/>
+      <c r="E102" s="36"/>
+      <c r="F102" s="36"/>
+      <c r="G102" s="6"/>
       <c r="H102" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I102" s="9"/>
-      <c r="J102" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="K102" s="6"/>
+      <c r="J102" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="K102" s="51"/>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A103" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B103" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="C103" s="31" t="s">
-        <v>188</v>
-      </c>
+      <c r="A103" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B103" s="23"/>
+      <c r="C103" s="36"/>
       <c r="D103" s="6"/>
-      <c r="E103" s="43" t="s">
-        <v>182</v>
-      </c>
-      <c r="F103" s="46"/>
-      <c r="G103" s="7" t="s">
-        <v>234</v>
-      </c>
+      <c r="E103" s="36"/>
+      <c r="F103" s="36"/>
+      <c r="G103" s="6"/>
       <c r="H103" s="8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I103" s="9"/>
-      <c r="J103" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="K103" s="6"/>
+      <c r="J103" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="K103" s="51"/>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A104" s="5"/>
-      <c r="B104" s="27"/>
-      <c r="C104" s="28" t="s">
-        <v>378</v>
-      </c>
+      <c r="A104" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B104" s="23"/>
+      <c r="C104" s="36"/>
       <c r="D104" s="6"/>
-      <c r="E104" s="28" t="s">
-        <v>267</v>
-      </c>
-      <c r="F104" s="28" t="s">
-        <v>305</v>
-      </c>
-      <c r="G104" s="7"/>
-      <c r="H104" s="8"/>
+      <c r="E104" s="36"/>
+      <c r="F104" s="36"/>
+      <c r="G104" s="6"/>
+      <c r="H104" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I104" s="9"/>
-      <c r="J104" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="K104" s="24">
-        <v>4</v>
-      </c>
+      <c r="J104" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="K104" s="51"/>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A105" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B105" s="39"/>
-      <c r="C105" s="43" t="s">
-        <v>67</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E105" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="F105" s="46" t="str">
-        <f>CONCATENATE("http://", E105)</f>
-        <v>http://192.168.0.195</v>
-      </c>
-      <c r="G105" s="7" t="s">
-        <v>233</v>
-      </c>
+      <c r="A105" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="B105" s="6"/>
+      <c r="C105" s="36"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="36"/>
+      <c r="F105" s="36"/>
+      <c r="G105" s="6"/>
       <c r="H105" s="8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I105" s="9"/>
-      <c r="J105" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="K105" s="6" t="s">
-        <v>65</v>
-      </c>
+      <c r="J105" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="K105" s="51"/>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A106" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B106" s="39"/>
-      <c r="C106" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="D106" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E106" s="43" t="s">
-        <v>71</v>
-      </c>
-      <c r="F106" s="46" t="str">
-        <f>CONCATENATE("http://", E106)</f>
-        <v>http://192.168.0.194</v>
-      </c>
-      <c r="G106" s="7" t="s">
-        <v>233</v>
-      </c>
+      <c r="A106" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B106" s="6"/>
+      <c r="C106" s="36"/>
+      <c r="D106" s="6"/>
+      <c r="E106" s="36"/>
+      <c r="F106" s="36"/>
+      <c r="G106" s="6"/>
       <c r="H106" s="8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I106" s="9"/>
-      <c r="J106" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="K106" s="6" t="s">
-        <v>70</v>
+      <c r="J106" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="K106" s="51" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A107" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="B107" s="13"/>
-      <c r="C107" s="43" t="s">
-        <v>20</v>
-      </c>
+      <c r="A107" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B107" s="6"/>
+      <c r="C107" s="36"/>
       <c r="D107" s="6"/>
-      <c r="E107" s="43"/>
-      <c r="F107" s="43"/>
+      <c r="E107" s="36"/>
+      <c r="F107" s="36"/>
       <c r="G107" s="6"/>
       <c r="H107" s="8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I107" s="9"/>
-      <c r="J107" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K107" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="J107" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="K107" s="51"/>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A108" s="39" t="s">
-        <v>124</v>
+      <c r="A108" s="33" t="s">
+        <v>25</v>
       </c>
       <c r="B108" s="6"/>
-      <c r="C108" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E108" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="F108" s="46" t="str">
-        <f>CONCATENATE("http://", E108)</f>
-        <v>http://192.168.0.186</v>
-      </c>
-      <c r="G108" s="7"/>
+      <c r="C108" s="36"/>
+      <c r="D108" s="6"/>
+      <c r="E108" s="36"/>
+      <c r="F108" s="36"/>
+      <c r="G108" s="6"/>
       <c r="H108" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I108" s="9"/>
-      <c r="J108" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="K108" s="6" t="s">
-        <v>74</v>
-      </c>
+      <c r="J108" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="K108" s="51"/>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" s="33" t="s">
-        <v>278</v>
-      </c>
-      <c r="B109" s="5"/>
-      <c r="C109" s="34" t="s">
-        <v>379</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B109" s="6"/>
+      <c r="C109" s="36"/>
       <c r="D109" s="6"/>
-      <c r="E109" s="45" t="s">
-        <v>281</v>
-      </c>
-      <c r="F109" s="45"/>
-      <c r="G109" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="H109" s="20" t="s">
-        <v>170</v>
+      <c r="E109" s="36"/>
+      <c r="F109" s="36"/>
+      <c r="G109" s="6"/>
+      <c r="H109" s="8" t="s">
+        <v>167</v>
       </c>
       <c r="I109" s="9"/>
-      <c r="J109" s="45" t="s">
-        <v>280</v>
-      </c>
-      <c r="K109" s="49"/>
+      <c r="J109" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="K109" s="51"/>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A110" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="B110" s="5"/>
-      <c r="C110" s="31" t="s">
-        <v>380</v>
-      </c>
+      <c r="A110" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="B110" s="6"/>
+      <c r="C110" s="36"/>
       <c r="D110" s="6"/>
-      <c r="E110" s="43" t="s">
-        <v>282</v>
-      </c>
-      <c r="F110" s="43"/>
-      <c r="G110" s="21" t="s">
-        <v>236</v>
-      </c>
+      <c r="E110" s="36"/>
+      <c r="F110" s="36"/>
+      <c r="G110" s="6"/>
       <c r="H110" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I110" s="9"/>
-      <c r="J110" s="43" t="s">
-        <v>280</v>
-      </c>
-      <c r="K110" s="48"/>
+      <c r="J110" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="K110" s="51"/>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A111" s="27" t="s">
-        <v>279</v>
-      </c>
-      <c r="B111" s="5"/>
-      <c r="C111" s="28" t="s">
-        <v>380</v>
-      </c>
+      <c r="A111" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C111" s="22"/>
       <c r="D111" s="6"/>
-      <c r="E111" s="28" t="s">
-        <v>282</v>
-      </c>
-      <c r="F111" s="28" t="s">
-        <v>280</v>
-      </c>
+      <c r="E111" s="23"/>
+      <c r="F111" s="23"/>
       <c r="G111" s="7"/>
-      <c r="H111" s="8"/>
+      <c r="H111" s="18" t="s">
+        <v>167</v>
+      </c>
       <c r="I111" s="9"/>
-      <c r="J111" s="31" t="s">
-        <v>290</v>
-      </c>
-      <c r="K111" s="36">
-        <v>13</v>
-      </c>
+      <c r="J111" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="K111" s="49"/>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A112" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B112" s="30"/>
-      <c r="C112" s="43" t="s">
-        <v>16</v>
-      </c>
+      <c r="A112" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C112" s="22"/>
       <c r="D112" s="6"/>
-      <c r="E112" s="43"/>
-      <c r="F112" s="43"/>
-      <c r="G112" s="6"/>
+      <c r="E112" s="23"/>
+      <c r="F112" s="23"/>
+      <c r="G112" s="7"/>
       <c r="H112" s="8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I112" s="9"/>
-      <c r="J112" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="K112" s="48" t="s">
-        <v>15</v>
-      </c>
+      <c r="J112" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="K112" s="51"/>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A113" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B113" s="30"/>
-      <c r="C113" s="43" t="s">
-        <v>158</v>
-      </c>
+      <c r="A113" s="5"/>
+      <c r="B113" s="5"/>
+      <c r="C113" s="5"/>
       <c r="D113" s="6"/>
-      <c r="E113" s="43" t="s">
-        <v>159</v>
-      </c>
-      <c r="F113" s="43"/>
-      <c r="G113" s="6"/>
-      <c r="H113" s="8" t="s">
-        <v>171</v>
-      </c>
+      <c r="E113" s="6"/>
+      <c r="F113" s="6"/>
+      <c r="G113" s="7"/>
+      <c r="H113" s="8"/>
       <c r="I113" s="9"/>
-      <c r="J113" s="43" t="s">
-        <v>157</v>
-      </c>
-      <c r="K113" s="48"/>
+      <c r="J113" s="29"/>
+      <c r="K113" s="50"/>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A114" s="30" t="s">
-        <v>241</v>
-      </c>
+      <c r="A114" s="5"/>
       <c r="B114" s="5"/>
-      <c r="C114" s="31"/>
+      <c r="C114" s="5"/>
       <c r="D114" s="6"/>
-      <c r="E114" s="43"/>
-      <c r="F114" s="43"/>
-      <c r="G114" s="21"/>
-      <c r="H114" s="8" t="s">
-        <v>171</v>
-      </c>
+      <c r="E114" s="6"/>
+      <c r="F114" s="6"/>
+      <c r="G114" s="7"/>
+      <c r="H114" s="8"/>
       <c r="I114" s="9"/>
-      <c r="J114" s="43"/>
-      <c r="K114" s="48"/>
+      <c r="J114" s="26"/>
+      <c r="K114" s="52"/>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A115" s="30" t="s">
-        <v>243</v>
-      </c>
+      <c r="A115" s="5"/>
       <c r="B115" s="5"/>
-      <c r="C115" s="31"/>
+      <c r="C115" s="5"/>
       <c r="D115" s="6"/>
-      <c r="E115" s="43" t="s">
-        <v>245</v>
-      </c>
-      <c r="F115" s="43"/>
-      <c r="G115" s="21" t="s">
-        <v>252</v>
-      </c>
-      <c r="H115" s="8" t="s">
-        <v>170</v>
-      </c>
+      <c r="E115" s="6"/>
+      <c r="F115" s="6"/>
+      <c r="G115" s="7"/>
+      <c r="H115" s="8"/>
       <c r="I115" s="9"/>
-      <c r="J115" s="43" t="s">
-        <v>246</v>
-      </c>
-      <c r="K115" s="48"/>
+      <c r="J115" s="29"/>
+      <c r="K115" s="50"/>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A116" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B116" s="30"/>
-      <c r="C116" s="31"/>
+      <c r="A116" s="5"/>
+      <c r="B116" s="5"/>
+      <c r="C116" s="5"/>
       <c r="D116" s="6"/>
-      <c r="E116" s="43" t="s">
-        <v>244</v>
-      </c>
-      <c r="F116" s="43"/>
-      <c r="G116" s="21"/>
+      <c r="E116" s="6"/>
+      <c r="F116" s="6"/>
+      <c r="G116" s="7"/>
       <c r="H116" s="8"/>
       <c r="I116" s="9"/>
-      <c r="J116" s="43"/>
-      <c r="K116" s="48"/>
+      <c r="J116" s="26"/>
+      <c r="K116" s="52"/>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A117" s="30" t="s">
-        <v>253</v>
-      </c>
+      <c r="A117" s="5"/>
       <c r="B117" s="5"/>
-      <c r="C117" s="31"/>
+      <c r="C117" s="5"/>
       <c r="D117" s="6"/>
-      <c r="E117" s="44" t="s">
-        <v>249</v>
-      </c>
-      <c r="F117" s="43"/>
-      <c r="G117" s="21" t="s">
-        <v>251</v>
-      </c>
-      <c r="H117" s="8" t="s">
-        <v>170</v>
-      </c>
+      <c r="E117" s="6"/>
+      <c r="F117" s="6"/>
+      <c r="G117" s="7"/>
+      <c r="H117" s="8"/>
       <c r="I117" s="9"/>
-      <c r="J117" s="43" t="s">
-        <v>250</v>
-      </c>
-      <c r="K117" s="48"/>
+      <c r="J117" s="29"/>
+      <c r="K117" s="50"/>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A118" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="B118" s="30"/>
-      <c r="C118" s="31"/>
+      <c r="A118" s="5"/>
+      <c r="B118" s="5"/>
+      <c r="C118" s="5"/>
       <c r="D118" s="6"/>
-      <c r="E118" s="43" t="s">
-        <v>267</v>
-      </c>
-      <c r="F118" s="43"/>
-      <c r="G118" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="H118" s="8" t="s">
-        <v>170</v>
-      </c>
+      <c r="E118" s="6"/>
+      <c r="F118" s="6"/>
+      <c r="G118" s="7"/>
+      <c r="H118" s="8"/>
       <c r="I118" s="9"/>
-      <c r="J118" s="43" t="s">
-        <v>269</v>
-      </c>
-      <c r="K118" s="48"/>
+      <c r="J118" s="26"/>
+      <c r="K118" s="52"/>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A119" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="B119" s="30"/>
-      <c r="C119" s="31"/>
-      <c r="D119" s="25"/>
-      <c r="E119" s="43" t="s">
-        <v>287</v>
-      </c>
-      <c r="F119" s="43"/>
-      <c r="G119" s="21"/>
-      <c r="H119" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="I119" s="26"/>
-      <c r="J119" s="43"/>
-      <c r="K119" s="48"/>
+      <c r="A119" s="5"/>
+      <c r="B119" s="5"/>
+      <c r="C119" s="5"/>
+      <c r="D119" s="6"/>
+      <c r="E119" s="6"/>
+      <c r="F119" s="6"/>
+      <c r="G119" s="7"/>
+      <c r="H119" s="8"/>
+      <c r="I119" s="9"/>
+      <c r="J119" s="29"/>
+      <c r="K119" s="50"/>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A120" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="B120" s="6"/>
-      <c r="C120" s="43"/>
-      <c r="D120" s="6"/>
-      <c r="E120" s="44" t="s">
-        <v>183</v>
-      </c>
-      <c r="F120" s="43"/>
-      <c r="G120" s="6"/>
-      <c r="H120" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="I120" s="9"/>
-      <c r="J120" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="K120" s="48"/>
+      <c r="A120" s="22"/>
+      <c r="B120" s="22"/>
+      <c r="C120" s="22"/>
+      <c r="D120" s="23"/>
+      <c r="E120" s="23"/>
+      <c r="F120" s="23"/>
+      <c r="G120" s="19"/>
+      <c r="H120" s="18"/>
+      <c r="I120" s="24"/>
+      <c r="J120" s="27"/>
+      <c r="K120" s="53"/>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A121" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="C121" s="31"/>
+      <c r="A121" s="5"/>
+      <c r="B121" s="5"/>
+      <c r="C121" s="5"/>
       <c r="D121" s="6"/>
-      <c r="E121" s="43" t="s">
-        <v>186</v>
-      </c>
-      <c r="F121" s="46"/>
+      <c r="E121" s="6"/>
+      <c r="F121" s="6"/>
       <c r="G121" s="7"/>
-      <c r="H121" s="8" t="s">
-        <v>170</v>
-      </c>
+      <c r="H121" s="8"/>
       <c r="I121" s="9"/>
-      <c r="J121" s="31" t="s">
-        <v>167</v>
-      </c>
-      <c r="K121" s="48"/>
+      <c r="J121" s="29"/>
+      <c r="K121" s="50"/>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A122" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="C122" s="31"/>
+      <c r="A122" s="5"/>
+      <c r="B122" s="5"/>
+      <c r="C122" s="5"/>
       <c r="D122" s="6"/>
-      <c r="E122" s="43"/>
-      <c r="F122" s="46"/>
+      <c r="E122" s="6"/>
+      <c r="F122" s="6"/>
       <c r="G122" s="7"/>
-      <c r="H122" s="8" t="s">
-        <v>171</v>
-      </c>
+      <c r="H122" s="8"/>
       <c r="I122" s="9"/>
-      <c r="J122" s="43"/>
-      <c r="K122" s="48"/>
+      <c r="J122" s="26"/>
+      <c r="K122" s="52"/>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A123" s="33" t="s">
-        <v>172</v>
-      </c>
+      <c r="A123" s="5"/>
       <c r="B123" s="5"/>
-      <c r="C123" s="34"/>
+      <c r="C123" s="5"/>
       <c r="D123" s="6"/>
-      <c r="E123" s="45"/>
-      <c r="F123" s="47"/>
+      <c r="E123" s="6"/>
+      <c r="F123" s="6"/>
       <c r="G123" s="7"/>
-      <c r="H123" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="I123" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="J123" s="45" t="s">
-        <v>254</v>
-      </c>
-      <c r="K123" s="49"/>
+      <c r="H123" s="8"/>
+      <c r="I123" s="9"/>
+      <c r="J123" s="29"/>
+      <c r="K123" s="50"/>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A124" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="B124" s="6"/>
-      <c r="C124" s="43"/>
+      <c r="A124" s="5"/>
+      <c r="B124" s="5"/>
+      <c r="C124" s="5"/>
       <c r="D124" s="6"/>
-      <c r="E124" s="43"/>
-      <c r="F124" s="43"/>
-      <c r="G124" s="6"/>
-      <c r="H124" s="8" t="s">
-        <v>171</v>
-      </c>
+      <c r="E124" s="6"/>
+      <c r="F124" s="6"/>
+      <c r="G124" s="7"/>
+      <c r="H124" s="8"/>
       <c r="I124" s="9"/>
-      <c r="J124" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="K124" s="48"/>
+      <c r="J124" s="26"/>
+      <c r="K124" s="52"/>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A125" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B125" s="39"/>
-      <c r="C125" s="43"/>
+      <c r="A125" s="5"/>
+      <c r="B125" s="5"/>
+      <c r="C125" s="5"/>
       <c r="D125" s="6"/>
-      <c r="E125" s="43"/>
-      <c r="F125" s="43"/>
-      <c r="G125" s="6"/>
-      <c r="H125" s="8" t="s">
-        <v>171</v>
-      </c>
+      <c r="E125" s="6"/>
+      <c r="F125" s="6"/>
+      <c r="G125" s="7"/>
+      <c r="H125" s="8"/>
       <c r="I125" s="9"/>
-      <c r="J125" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="K125" s="48"/>
+      <c r="J125" s="29"/>
+      <c r="K125" s="50"/>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A126" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B126" s="39"/>
-      <c r="C126" s="43"/>
+      <c r="A126" s="5"/>
+      <c r="B126" s="5"/>
+      <c r="C126" s="5"/>
       <c r="D126" s="6"/>
-      <c r="E126" s="43"/>
-      <c r="F126" s="43"/>
-      <c r="G126" s="6"/>
-      <c r="H126" s="8" t="s">
-        <v>171</v>
-      </c>
+      <c r="E126" s="6"/>
+      <c r="F126" s="6"/>
+      <c r="G126" s="7"/>
+      <c r="H126" s="8"/>
       <c r="I126" s="9"/>
-      <c r="J126" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="K126" s="48"/>
+      <c r="J126" s="26"/>
+      <c r="K126" s="52"/>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A127" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="B127" s="6"/>
-      <c r="C127" s="43"/>
+      <c r="A127" s="5"/>
+      <c r="B127" s="5"/>
+      <c r="C127" s="5"/>
       <c r="D127" s="6"/>
-      <c r="E127" s="43"/>
-      <c r="F127" s="43"/>
-      <c r="G127" s="6"/>
-      <c r="H127" s="8" t="s">
-        <v>171</v>
-      </c>
+      <c r="E127" s="6"/>
+      <c r="F127" s="6"/>
+      <c r="G127" s="7"/>
+      <c r="H127" s="8"/>
       <c r="I127" s="9"/>
-      <c r="J127" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="K127" s="48"/>
+      <c r="J127" s="29"/>
+      <c r="K127" s="50"/>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A128" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B128" s="6"/>
-      <c r="C128" s="43"/>
-      <c r="D128" s="6"/>
-      <c r="E128" s="43"/>
-      <c r="F128" s="43"/>
-      <c r="G128" s="6"/>
-      <c r="H128" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="I128" s="9"/>
-      <c r="J128" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="K128" s="48" t="s">
-        <v>25</v>
-      </c>
+      <c r="A128" s="22"/>
+      <c r="B128" s="22"/>
+      <c r="C128" s="22"/>
+      <c r="D128" s="23"/>
+      <c r="E128" s="23"/>
+      <c r="F128" s="23"/>
+      <c r="G128" s="19"/>
+      <c r="H128" s="18"/>
+      <c r="I128" s="24"/>
+      <c r="J128" s="27"/>
+      <c r="K128" s="53"/>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A129" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="B129" s="6"/>
-      <c r="C129" s="43"/>
+      <c r="A129" s="5"/>
+      <c r="B129" s="5"/>
+      <c r="C129" s="5"/>
       <c r="D129" s="6"/>
-      <c r="E129" s="43"/>
-      <c r="F129" s="43"/>
-      <c r="G129" s="6"/>
-      <c r="H129" s="8" t="s">
-        <v>171</v>
-      </c>
+      <c r="E129" s="6"/>
+      <c r="F129" s="6"/>
+      <c r="G129" s="7"/>
+      <c r="H129" s="8"/>
       <c r="I129" s="9"/>
-      <c r="J129" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="K129" s="48"/>
+      <c r="J129" s="29"/>
+      <c r="K129" s="50"/>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A130" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="B130" s="6"/>
-      <c r="C130" s="43"/>
+      <c r="A130" s="5"/>
+      <c r="B130" s="5"/>
+      <c r="C130" s="5"/>
       <c r="D130" s="6"/>
-      <c r="E130" s="43"/>
-      <c r="F130" s="43"/>
-      <c r="G130" s="6"/>
-      <c r="H130" s="8" t="s">
-        <v>171</v>
-      </c>
+      <c r="E130" s="6"/>
+      <c r="F130" s="6"/>
+      <c r="G130" s="7"/>
+      <c r="H130" s="8"/>
       <c r="I130" s="9"/>
-      <c r="J130" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="K130" s="48"/>
+      <c r="J130" s="26"/>
+      <c r="K130" s="52"/>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A131" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="B131" s="6"/>
-      <c r="C131" s="43"/>
-      <c r="D131" s="6"/>
-      <c r="E131" s="43"/>
-      <c r="F131" s="43"/>
-      <c r="G131" s="6"/>
-      <c r="H131" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="I131" s="9"/>
-      <c r="J131" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="K131" s="48"/>
+      <c r="A131" s="22"/>
+      <c r="B131" s="22"/>
+      <c r="C131" s="22"/>
+      <c r="D131" s="23"/>
+      <c r="E131" s="23"/>
+      <c r="F131" s="23"/>
+      <c r="G131" s="19"/>
+      <c r="H131" s="18"/>
+      <c r="I131" s="24"/>
+      <c r="J131" s="31"/>
+      <c r="K131" s="54"/>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A132" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="B132" s="6"/>
-      <c r="C132" s="43"/>
-      <c r="D132" s="6"/>
-      <c r="E132" s="43"/>
-      <c r="F132" s="43"/>
-      <c r="G132" s="6"/>
-      <c r="H132" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="I132" s="9"/>
-      <c r="J132" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="K132" s="48"/>
+      <c r="H132"/>
+      <c r="I132"/>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A133" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="B133" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C133" s="31"/>
-      <c r="D133" s="6"/>
-      <c r="E133" s="43"/>
-      <c r="F133" s="43"/>
-      <c r="G133" s="7"/>
-      <c r="H133" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="I133" s="9"/>
-      <c r="J133" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="K133" s="48"/>
+      <c r="H133"/>
+      <c r="I133"/>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A134" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="B134" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C134" s="31"/>
-      <c r="D134" s="6"/>
-      <c r="E134" s="43"/>
-      <c r="F134" s="43"/>
-      <c r="G134" s="7"/>
-      <c r="H134" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="I134" s="9"/>
-      <c r="J134" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="K134" s="48"/>
+      <c r="H134"/>
+      <c r="I134"/>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A135" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="B135" s="5"/>
-      <c r="C135" s="43"/>
-      <c r="D135" s="6"/>
-      <c r="E135" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F135" s="43"/>
-      <c r="G135" s="6"/>
-      <c r="H135" s="8"/>
-      <c r="I135" s="9"/>
-      <c r="J135" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="K135" s="48"/>
+      <c r="H135"/>
+      <c r="I135"/>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A136" s="24" t="s">
-        <v>381</v>
-      </c>
-      <c r="B136" s="24"/>
-      <c r="C136" s="51" t="s">
-        <v>369</v>
-      </c>
-      <c r="D136" s="6"/>
-      <c r="E136" s="25" t="s">
-        <v>309</v>
-      </c>
-      <c r="F136" s="25"/>
-      <c r="G136" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="H136" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="I136" s="26"/>
-      <c r="J136" s="34" t="s">
-        <v>383</v>
-      </c>
-      <c r="K136" s="37"/>
+      <c r="H136"/>
+      <c r="I136"/>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A137" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="B137" s="5"/>
-      <c r="C137" s="51" t="s">
-        <v>370</v>
-      </c>
-      <c r="D137" s="6"/>
-      <c r="E137" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="F137" s="6"/>
-      <c r="G137" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="H137" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="I137" s="26"/>
-      <c r="J137" s="50" t="s">
-        <v>383</v>
-      </c>
-      <c r="K137" s="32"/>
+      <c r="H137"/>
+      <c r="I137"/>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A138" s="5"/>
-      <c r="B138" s="5"/>
-      <c r="C138" s="5"/>
-      <c r="D138" s="6"/>
-      <c r="E138" s="6"/>
-      <c r="F138" s="6"/>
-      <c r="G138" s="7"/>
-      <c r="H138" s="8"/>
-      <c r="I138" s="9"/>
-      <c r="J138" s="31"/>
-      <c r="K138" s="36"/>
+      <c r="H138"/>
+      <c r="I138"/>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A139" s="5"/>
-      <c r="B139" s="5"/>
-      <c r="C139" s="5"/>
-      <c r="D139" s="6"/>
-      <c r="E139" s="6"/>
-      <c r="F139" s="6"/>
-      <c r="G139" s="7"/>
-      <c r="H139" s="8"/>
-      <c r="I139" s="9"/>
-      <c r="J139" s="28"/>
-      <c r="K139" s="32"/>
+      <c r="H139"/>
+      <c r="I139"/>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A140" s="5"/>
-      <c r="B140" s="5"/>
-      <c r="C140" s="5"/>
-      <c r="D140" s="6"/>
-      <c r="E140" s="6"/>
-      <c r="F140" s="6"/>
-      <c r="G140" s="7"/>
-      <c r="H140" s="8"/>
-      <c r="I140" s="9"/>
-      <c r="J140" s="31"/>
-      <c r="K140" s="36"/>
+      <c r="H140"/>
+      <c r="I140"/>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A141" s="5"/>
-      <c r="B141" s="5"/>
-      <c r="C141" s="5"/>
-      <c r="D141" s="6"/>
-      <c r="E141" s="6"/>
-      <c r="F141" s="6"/>
-      <c r="G141" s="7"/>
-      <c r="H141" s="8"/>
-      <c r="I141" s="9"/>
-      <c r="J141" s="28"/>
-      <c r="K141" s="32"/>
+      <c r="H141"/>
+      <c r="I141"/>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A142" s="5"/>
-      <c r="B142" s="5"/>
-      <c r="C142" s="5"/>
-      <c r="D142" s="6"/>
-      <c r="E142" s="6"/>
-      <c r="F142" s="6"/>
-      <c r="G142" s="7"/>
-      <c r="H142" s="8"/>
-      <c r="I142" s="9"/>
-      <c r="J142" s="31"/>
-      <c r="K142" s="36"/>
+      <c r="H142"/>
+      <c r="I142"/>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A143" s="5"/>
-      <c r="B143" s="5"/>
-      <c r="C143" s="5"/>
-      <c r="D143" s="6"/>
-      <c r="E143" s="6"/>
-      <c r="F143" s="6"/>
-      <c r="G143" s="7"/>
-      <c r="H143" s="8"/>
-      <c r="I143" s="9"/>
-      <c r="J143" s="28"/>
-      <c r="K143" s="32"/>
+      <c r="H143"/>
+      <c r="I143"/>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A144" s="5"/>
-      <c r="B144" s="5"/>
-      <c r="C144" s="5"/>
-      <c r="D144" s="6"/>
-      <c r="E144" s="6"/>
-      <c r="F144" s="6"/>
-      <c r="G144" s="7"/>
-      <c r="H144" s="8"/>
-      <c r="I144" s="9"/>
-      <c r="J144" s="31"/>
-      <c r="K144" s="36"/>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A145" s="24"/>
-      <c r="B145" s="24"/>
-      <c r="C145" s="24"/>
-      <c r="D145" s="25"/>
-      <c r="E145" s="25"/>
-      <c r="F145" s="25"/>
-      <c r="G145" s="21"/>
-      <c r="H145" s="20"/>
-      <c r="I145" s="26"/>
-      <c r="J145" s="29"/>
-      <c r="K145" s="35"/>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A146" s="5"/>
-      <c r="B146" s="5"/>
-      <c r="C146" s="5"/>
-      <c r="D146" s="6"/>
-      <c r="E146" s="6"/>
-      <c r="F146" s="6"/>
-      <c r="G146" s="7"/>
-      <c r="H146" s="8"/>
-      <c r="I146" s="9"/>
-      <c r="J146" s="31"/>
-      <c r="K146" s="36"/>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A147" s="5"/>
-      <c r="B147" s="5"/>
-      <c r="C147" s="5"/>
-      <c r="D147" s="6"/>
-      <c r="E147" s="6"/>
-      <c r="F147" s="6"/>
-      <c r="G147" s="7"/>
-      <c r="H147" s="8"/>
-      <c r="I147" s="9"/>
-      <c r="J147" s="28"/>
-      <c r="K147" s="32"/>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A148" s="5"/>
-      <c r="B148" s="5"/>
-      <c r="C148" s="5"/>
-      <c r="D148" s="6"/>
-      <c r="E148" s="6"/>
-      <c r="F148" s="6"/>
-      <c r="G148" s="7"/>
-      <c r="H148" s="8"/>
-      <c r="I148" s="9"/>
-      <c r="J148" s="31"/>
-      <c r="K148" s="36"/>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A149" s="5"/>
-      <c r="B149" s="5"/>
-      <c r="C149" s="5"/>
-      <c r="D149" s="6"/>
-      <c r="E149" s="6"/>
-      <c r="F149" s="6"/>
-      <c r="G149" s="7"/>
-      <c r="H149" s="8"/>
-      <c r="I149" s="9"/>
-      <c r="J149" s="28"/>
-      <c r="K149" s="32"/>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A150" s="5"/>
-      <c r="B150" s="5"/>
-      <c r="C150" s="5"/>
-      <c r="D150" s="6"/>
-      <c r="E150" s="6"/>
-      <c r="F150" s="6"/>
-      <c r="G150" s="7"/>
-      <c r="H150" s="8"/>
-      <c r="I150" s="9"/>
-      <c r="J150" s="31"/>
-      <c r="K150" s="36"/>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A151" s="5"/>
-      <c r="B151" s="5"/>
-      <c r="C151" s="5"/>
-      <c r="D151" s="6"/>
-      <c r="E151" s="6"/>
-      <c r="F151" s="6"/>
-      <c r="G151" s="7"/>
-      <c r="H151" s="8"/>
-      <c r="I151" s="9"/>
-      <c r="J151" s="28"/>
-      <c r="K151" s="32"/>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A152" s="5"/>
-      <c r="B152" s="5"/>
-      <c r="C152" s="5"/>
-      <c r="D152" s="6"/>
-      <c r="E152" s="6"/>
-      <c r="F152" s="6"/>
-      <c r="G152" s="7"/>
-      <c r="H152" s="8"/>
-      <c r="I152" s="9"/>
-      <c r="J152" s="31"/>
-      <c r="K152" s="36"/>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A153" s="24"/>
-      <c r="B153" s="24"/>
-      <c r="C153" s="24"/>
-      <c r="D153" s="25"/>
-      <c r="E153" s="25"/>
-      <c r="F153" s="25"/>
-      <c r="G153" s="21"/>
-      <c r="H153" s="20"/>
-      <c r="I153" s="26"/>
-      <c r="J153" s="29"/>
-      <c r="K153" s="35"/>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A154" s="5"/>
-      <c r="B154" s="5"/>
-      <c r="C154" s="5"/>
-      <c r="D154" s="6"/>
-      <c r="E154" s="6"/>
-      <c r="F154" s="6"/>
-      <c r="G154" s="7"/>
-      <c r="H154" s="8"/>
-      <c r="I154" s="9"/>
-      <c r="J154" s="31"/>
-      <c r="K154" s="36"/>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A155" s="5"/>
-      <c r="B155" s="5"/>
-      <c r="C155" s="5"/>
-      <c r="D155" s="6"/>
-      <c r="E155" s="6"/>
-      <c r="F155" s="6"/>
-      <c r="G155" s="7"/>
-      <c r="H155" s="8"/>
-      <c r="I155" s="9"/>
-      <c r="J155" s="28"/>
-      <c r="K155" s="32"/>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A156" s="24"/>
-      <c r="B156" s="24"/>
-      <c r="C156" s="24"/>
-      <c r="D156" s="25"/>
-      <c r="E156" s="25"/>
-      <c r="F156" s="25"/>
-      <c r="G156" s="21"/>
-      <c r="H156" s="20"/>
-      <c r="I156" s="26"/>
-      <c r="J156" s="34"/>
-      <c r="K156" s="37"/>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H144"/>
+      <c r="I144"/>
+    </row>
+    <row r="145" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H145"/>
+      <c r="I145"/>
+    </row>
+    <row r="146" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H146"/>
+      <c r="I146"/>
+    </row>
+    <row r="147" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H147"/>
+      <c r="I147"/>
+    </row>
+    <row r="148" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H148"/>
+      <c r="I148"/>
+    </row>
+    <row r="149" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H149"/>
+      <c r="I149"/>
+    </row>
+    <row r="150" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H150"/>
+      <c r="I150"/>
+    </row>
+    <row r="151" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H151"/>
+      <c r="I151"/>
+    </row>
+    <row r="152" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H152"/>
+      <c r="I152"/>
+    </row>
+    <row r="153" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H153"/>
+      <c r="I153"/>
+    </row>
+    <row r="154" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H154"/>
+      <c r="I154"/>
+    </row>
+    <row r="155" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H155"/>
+      <c r="I155"/>
+    </row>
+    <row r="156" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H156"/>
+      <c r="I156"/>
+    </row>
+    <row r="157" spans="8:9" x14ac:dyDescent="0.2">
       <c r="H157"/>
       <c r="I157"/>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="8:9" x14ac:dyDescent="0.2">
       <c r="H158"/>
       <c r="I158"/>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="8:9" x14ac:dyDescent="0.2">
       <c r="H159"/>
       <c r="I159"/>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="8:9" x14ac:dyDescent="0.2">
       <c r="H160"/>
       <c r="I160"/>
     </row>
@@ -11996,119 +11604,19 @@
       <c r="H1718"/>
       <c r="I1718"/>
     </row>
-    <row r="1719" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1719"/>
-      <c r="I1719"/>
-    </row>
-    <row r="1720" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1720"/>
-      <c r="I1720"/>
-    </row>
-    <row r="1721" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1721"/>
-      <c r="I1721"/>
-    </row>
-    <row r="1722" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1722"/>
-      <c r="I1722"/>
-    </row>
-    <row r="1723" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1723"/>
-      <c r="I1723"/>
-    </row>
-    <row r="1724" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1724"/>
-      <c r="I1724"/>
-    </row>
-    <row r="1725" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1725"/>
-      <c r="I1725"/>
-    </row>
-    <row r="1726" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1726"/>
-      <c r="I1726"/>
-    </row>
-    <row r="1727" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1727"/>
-      <c r="I1727"/>
-    </row>
-    <row r="1728" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1728"/>
-      <c r="I1728"/>
-    </row>
-    <row r="1729" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1729"/>
-      <c r="I1729"/>
-    </row>
-    <row r="1730" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1730"/>
-      <c r="I1730"/>
-    </row>
-    <row r="1731" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1731"/>
-      <c r="I1731"/>
-    </row>
-    <row r="1732" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1732"/>
-      <c r="I1732"/>
-    </row>
-    <row r="1733" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1733"/>
-      <c r="I1733"/>
-    </row>
-    <row r="1734" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1734"/>
-      <c r="I1734"/>
-    </row>
-    <row r="1735" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1735"/>
-      <c r="I1735"/>
-    </row>
-    <row r="1736" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1736"/>
-      <c r="I1736"/>
-    </row>
-    <row r="1737" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1737"/>
-      <c r="I1737"/>
-    </row>
-    <row r="1738" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1738"/>
-      <c r="I1738"/>
-    </row>
-    <row r="1739" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1739"/>
-      <c r="I1739"/>
-    </row>
-    <row r="1740" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1740"/>
-      <c r="I1740"/>
-    </row>
-    <row r="1741" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1741"/>
-      <c r="I1741"/>
-    </row>
-    <row r="1742" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1742"/>
-      <c r="I1742"/>
-    </row>
-    <row r="1743" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H1743"/>
-      <c r="I1743"/>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F31" r:id="rId1" display="http://192.169.0.112" xr:uid="{D2404E72-FA69-6648-ACE3-1F155CD355DD}"/>
-    <hyperlink ref="F85" r:id="rId2" display="http://192.169.0.112" xr:uid="{3F5BA59D-C194-FC49-9DCB-1F6B1CEAE85A}"/>
-    <hyperlink ref="F54" r:id="rId3" display="http://192.169.0.112" xr:uid="{80722F7C-2A8A-4A43-A5D3-BCFFE30BBC25}"/>
-    <hyperlink ref="F53" r:id="rId4" display="http://192.169.0.112" xr:uid="{7AFCBEF6-4325-D24D-B711-037F038931A3}"/>
-    <hyperlink ref="F13:F15" r:id="rId5" display="http://192.169.0.112" xr:uid="{40E3D96B-FF32-1147-AA42-7A87222DBFE8}"/>
+    <hyperlink ref="F27" r:id="rId1" display="http://192.169.0.112" xr:uid="{D2404E72-FA69-6648-ACE3-1F155CD355DD}"/>
+    <hyperlink ref="F71" r:id="rId2" display="http://192.169.0.112" xr:uid="{3F5BA59D-C194-FC49-9DCB-1F6B1CEAE85A}"/>
+    <hyperlink ref="F47" r:id="rId3" display="http://192.169.0.112" xr:uid="{80722F7C-2A8A-4A43-A5D3-BCFFE30BBC25}"/>
+    <hyperlink ref="F46" r:id="rId4" display="http://192.169.0.112" xr:uid="{7AFCBEF6-4325-D24D-B711-037F038931A3}"/>
+    <hyperlink ref="F12:F14" r:id="rId5" display="http://192.169.0.112" xr:uid="{40E3D96B-FF32-1147-AA42-7A87222DBFE8}"/>
     <hyperlink ref="F4:F8" r:id="rId6" display="http://192.169.0.112" xr:uid="{EFA55FC0-66D6-5341-B122-15ED7113DE4A}"/>
-    <hyperlink ref="F55" r:id="rId7" display="http://192.169.0.112" xr:uid="{206574CD-0A69-6A49-BF19-8696C0B23754}"/>
-    <hyperlink ref="F20:F22" r:id="rId8" display="http://192.169.0.112" xr:uid="{ABAD7AC1-281C-974C-8BD8-79EEDE34950A}"/>
-    <hyperlink ref="F90" r:id="rId9" display="http://192.169.0.112" xr:uid="{2FA0DCAE-2864-024C-9351-79F3CBFD408D}"/>
-    <hyperlink ref="F91" r:id="rId10" display="http://192.169.0.112" xr:uid="{0E717F48-1348-0440-9A96-15E3AB13C8AE}"/>
-    <hyperlink ref="F78" r:id="rId11" display="http://192.169.0.112" xr:uid="{B7709A6B-F68E-6F45-9F1A-5CCF46F3BFD7}"/>
+    <hyperlink ref="F48" r:id="rId7" display="http://192.169.0.112" xr:uid="{206574CD-0A69-6A49-BF19-8696C0B23754}"/>
+    <hyperlink ref="F19:F21" r:id="rId8" display="http://192.169.0.112" xr:uid="{ABAD7AC1-281C-974C-8BD8-79EEDE34950A}"/>
+    <hyperlink ref="F74" r:id="rId9" display="http://192.169.0.112" xr:uid="{2FA0DCAE-2864-024C-9351-79F3CBFD408D}"/>
+    <hyperlink ref="F75" r:id="rId10" display="http://192.169.0.112" xr:uid="{0E717F48-1348-0440-9A96-15E3AB13C8AE}"/>
+    <hyperlink ref="F65" r:id="rId11" display="http://192.169.0.112" xr:uid="{B7709A6B-F68E-6F45-9F1A-5CCF46F3BFD7}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{649F0B39-7306-054C-A7F6-A2FDF5FD2C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA37C41-0AE7-BB40-AD36-3D15171DB6E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1880" yWindow="2960" windowWidth="28360" windowHeight="16680" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="373">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -1187,9 +1187,6 @@
     <t>2603-1300</t>
   </si>
   <si>
-    <t>CueCommander is port 1880, Companion is port 8000, media_arts_home is port 80.</t>
-  </si>
-  <si>
     <t>osc:9110</t>
   </si>
   <si>
@@ -1215,6 +1212,9 @@
   </si>
   <si>
     <t>Amplifier</t>
+  </si>
+  <si>
+    <t>cuecommander:1880, companion:8000, media_arts_home:80</t>
   </si>
 </sst>
 </file>
@@ -1491,7 +1491,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1586,6 +1586,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2250,7 +2251,9 @@
       <c r="C2" s="22" t="s">
         <v>320</v>
       </c>
-      <c r="D2" s="6"/>
+      <c r="D2" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E2" s="23" t="s">
         <v>239</v>
       </c>
@@ -2277,7 +2280,9 @@
       <c r="C3" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="D3" s="6"/>
+      <c r="D3" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E3" s="6" t="s">
         <v>192</v>
       </c>
@@ -2302,7 +2307,9 @@
       <c r="C4" s="22" t="s">
         <v>195</v>
       </c>
-      <c r="D4" s="6"/>
+      <c r="D4" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E4" s="23"/>
       <c r="F4" s="23"/>
       <c r="G4" s="6"/>
@@ -2325,7 +2332,9 @@
       <c r="C5" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="D5" s="6"/>
+      <c r="D5" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E5" s="6" t="s">
         <v>202</v>
       </c>
@@ -2350,7 +2359,9 @@
       <c r="C6" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="D6" s="6"/>
+      <c r="D6" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E6" s="23"/>
       <c r="F6" s="23"/>
       <c r="G6" s="6"/>
@@ -2373,7 +2384,9 @@
       <c r="C7" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E7" s="6" t="s">
         <v>218</v>
       </c>
@@ -2400,7 +2413,9 @@
       <c r="C8" s="22" t="s">
         <v>220</v>
       </c>
-      <c r="D8" s="6"/>
+      <c r="D8" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
       <c r="G8" s="6"/>
@@ -2423,7 +2438,9 @@
       <c r="C9" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="D9" s="6"/>
+      <c r="D9" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E9" s="6" t="s">
         <v>205</v>
       </c>
@@ -2448,7 +2465,9 @@
       <c r="C10" s="22" t="s">
         <v>207</v>
       </c>
-      <c r="D10" s="6"/>
+      <c r="D10" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E10" s="23"/>
       <c r="F10" s="23"/>
       <c r="G10" s="6"/>
@@ -2469,7 +2488,9 @@
       <c r="C11" s="32" t="s">
         <v>321</v>
       </c>
-      <c r="D11" s="6"/>
+      <c r="D11" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E11" s="32" t="s">
         <v>309</v>
       </c>
@@ -2496,7 +2517,9 @@
       <c r="C12" s="22" t="s">
         <v>322</v>
       </c>
-      <c r="D12" s="6"/>
+      <c r="D12" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E12" s="22" t="s">
         <v>319</v>
       </c>
@@ -2523,7 +2546,9 @@
       <c r="C13" s="22" t="s">
         <v>323</v>
       </c>
-      <c r="D13" s="6"/>
+      <c r="D13" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E13" s="22" t="s">
         <v>315</v>
       </c>
@@ -2550,7 +2575,9 @@
       <c r="C14" s="22" t="s">
         <v>324</v>
       </c>
-      <c r="D14" s="6"/>
+      <c r="D14" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E14" s="22" t="s">
         <v>303</v>
       </c>
@@ -2577,7 +2604,9 @@
       <c r="C15" s="22" t="s">
         <v>325</v>
       </c>
-      <c r="D15" s="6"/>
+      <c r="D15" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E15" s="22" t="s">
         <v>307</v>
       </c>
@@ -2604,7 +2633,9 @@
       <c r="C16" s="32" t="s">
         <v>326</v>
       </c>
-      <c r="D16" s="6"/>
+      <c r="D16" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E16" s="32" t="s">
         <v>313</v>
       </c>
@@ -2631,7 +2662,9 @@
       <c r="C17" s="32" t="s">
         <v>327</v>
       </c>
-      <c r="D17" s="6"/>
+      <c r="D17" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E17" s="32" t="s">
         <v>317</v>
       </c>
@@ -2658,7 +2691,9 @@
       <c r="C18" s="22" t="s">
         <v>328</v>
       </c>
-      <c r="D18" s="6"/>
+      <c r="D18" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E18" s="22" t="s">
         <v>311</v>
       </c>
@@ -2685,7 +2720,9 @@
       <c r="C19" s="32" t="s">
         <v>329</v>
       </c>
-      <c r="D19" s="6"/>
+      <c r="D19" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E19" s="32" t="s">
         <v>305</v>
       </c>
@@ -2710,7 +2747,9 @@
       <c r="C20" s="32" t="s">
         <v>330</v>
       </c>
-      <c r="D20" s="6"/>
+      <c r="D20" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E20" s="32" t="s">
         <v>293</v>
       </c>
@@ -2872,7 +2911,9 @@
       <c r="C26" s="22" t="s">
         <v>268</v>
       </c>
-      <c r="D26" s="6"/>
+      <c r="D26" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E26" s="23"/>
       <c r="F26" s="23"/>
       <c r="G26" s="19"/>
@@ -2981,7 +3022,9 @@
       <c r="C30" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D30" s="6"/>
+      <c r="D30" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E30" s="6" t="s">
         <v>224</v>
       </c>
@@ -2992,7 +3035,7 @@
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="K30" s="44"/>
     </row>
@@ -3006,7 +3049,9 @@
       <c r="C31" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="D31" s="6"/>
+      <c r="D31" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E31" s="6" t="s">
         <v>196</v>
       </c>
@@ -3017,7 +3062,7 @@
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="K31" s="44"/>
     </row>
@@ -3029,7 +3074,9 @@
       <c r="C32" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D32" s="6"/>
+      <c r="D32" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E32" s="6" t="s">
         <v>222</v>
       </c>
@@ -3050,7 +3097,9 @@
       <c r="C33" s="22" t="s">
         <v>332</v>
       </c>
-      <c r="D33" s="6"/>
+      <c r="D33" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E33" s="22" t="s">
         <v>288</v>
       </c>
@@ -3069,7 +3118,9 @@
       <c r="C34" s="32" t="s">
         <v>333</v>
       </c>
-      <c r="D34" s="23"/>
+      <c r="D34" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E34" s="32" t="s">
         <v>290</v>
       </c>
@@ -3088,7 +3139,9 @@
       <c r="C35" s="32" t="s">
         <v>334</v>
       </c>
-      <c r="D35" s="6"/>
+      <c r="D35" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E35" s="32" t="s">
         <v>287</v>
       </c>
@@ -3103,13 +3156,15 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B36" s="32"/>
       <c r="C36" s="32" t="s">
         <v>335</v>
       </c>
-      <c r="D36" s="6"/>
+      <c r="D36" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E36" s="32" t="s">
         <v>284</v>
       </c>
@@ -3128,7 +3183,9 @@
       <c r="C37" s="32" t="s">
         <v>336</v>
       </c>
-      <c r="D37" s="6"/>
+      <c r="D37" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E37" s="32" t="s">
         <v>291</v>
       </c>
@@ -3140,7 +3197,7 @@
       <c r="I37" s="9"/>
       <c r="J37" s="6"/>
       <c r="K37" s="44" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
@@ -3149,7 +3206,9 @@
       <c r="C38" s="32" t="s">
         <v>337</v>
       </c>
-      <c r="D38" s="6"/>
+      <c r="D38" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E38" s="32" t="s">
         <v>289</v>
       </c>
@@ -3161,7 +3220,7 @@
       <c r="I38" s="9"/>
       <c r="J38" s="6"/>
       <c r="K38" s="44" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
@@ -3170,7 +3229,9 @@
       <c r="C39" s="32" t="s">
         <v>338</v>
       </c>
-      <c r="D39" s="6"/>
+      <c r="D39" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E39" s="32" t="s">
         <v>296</v>
       </c>
@@ -3182,7 +3243,7 @@
       <c r="I39" s="9"/>
       <c r="J39" s="6"/>
       <c r="K39" s="44" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
@@ -3191,7 +3252,9 @@
       <c r="C40" s="22" t="s">
         <v>339</v>
       </c>
-      <c r="D40" s="6"/>
+      <c r="D40" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E40" s="22" t="s">
         <v>292</v>
       </c>
@@ -3203,7 +3266,7 @@
       <c r="I40" s="9"/>
       <c r="J40" s="6"/>
       <c r="K40" s="44" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
@@ -3212,7 +3275,9 @@
       <c r="C41" s="22" t="s">
         <v>340</v>
       </c>
-      <c r="D41" s="6"/>
+      <c r="D41" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E41" s="22" t="s">
         <v>295</v>
       </c>
@@ -3224,7 +3289,7 @@
       <c r="I41" s="9"/>
       <c r="J41" s="6"/>
       <c r="K41" s="44" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
@@ -3233,7 +3298,9 @@
       <c r="C42" s="22" t="s">
         <v>341</v>
       </c>
-      <c r="D42" s="6"/>
+      <c r="D42" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E42" s="22" t="s">
         <v>286</v>
       </c>
@@ -3245,7 +3312,7 @@
       <c r="I42" s="9"/>
       <c r="J42" s="6"/>
       <c r="K42" s="44" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
@@ -3254,7 +3321,9 @@
       <c r="C43" s="22" t="s">
         <v>342</v>
       </c>
-      <c r="D43" s="6"/>
+      <c r="D43" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E43" s="22" t="s">
         <v>297</v>
       </c>
@@ -3266,7 +3335,7 @@
       <c r="I43" s="9"/>
       <c r="J43" s="6"/>
       <c r="K43" s="44" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
@@ -3275,7 +3344,9 @@
       <c r="C44" s="32" t="s">
         <v>343</v>
       </c>
-      <c r="D44" s="6"/>
+      <c r="D44" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E44" s="32" t="s">
         <v>285</v>
       </c>
@@ -3287,7 +3358,7 @@
       <c r="I44" s="9"/>
       <c r="J44" s="6"/>
       <c r="K44" s="44" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
@@ -3296,7 +3367,9 @@
       <c r="C45" s="32" t="s">
         <v>344</v>
       </c>
-      <c r="D45" s="23"/>
+      <c r="D45" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E45" s="32" t="s">
         <v>281</v>
       </c>
@@ -3308,7 +3381,7 @@
       <c r="I45" s="24"/>
       <c r="J45" s="23"/>
       <c r="K45" s="44" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
@@ -3409,7 +3482,9 @@
       <c r="C49" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="D49" s="6"/>
+      <c r="D49" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E49" s="6" t="s">
         <v>231</v>
       </c>
@@ -3436,7 +3511,9 @@
       <c r="C50" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="D50" s="6"/>
+      <c r="D50" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E50" s="6" t="s">
         <v>200</v>
       </c>
@@ -3756,7 +3833,9 @@
       <c r="C61" s="22" t="s">
         <v>345</v>
       </c>
-      <c r="D61" s="23"/>
+      <c r="D61" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E61" s="58" t="s">
         <v>276</v>
       </c>
@@ -3783,7 +3862,9 @@
       <c r="C62" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="D62" s="6"/>
+      <c r="D62" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="E62" s="6" t="s">
         <v>181</v>
       </c>
@@ -3808,7 +3889,9 @@
       <c r="C63" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="D63" s="6"/>
+      <c r="D63" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E63" s="6" t="s">
         <v>150</v>
       </c>
@@ -3831,7 +3914,9 @@
       <c r="C64" s="23" t="s">
         <v>347</v>
       </c>
-      <c r="D64" s="6"/>
+      <c r="D64" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E64" s="23" t="s">
         <v>188</v>
       </c>
@@ -3856,7 +3941,9 @@
       <c r="C65" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D65" s="6"/>
+      <c r="D65" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E65" s="6" t="s">
         <v>149</v>
       </c>
@@ -3884,13 +3971,15 @@
       <c r="C66" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="D66" s="6"/>
+      <c r="D66" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E66" s="6" t="s">
         <v>176</v>
       </c>
       <c r="F66" s="6"/>
       <c r="G66" s="6" t="s">
-        <v>241</v>
+        <v>372</v>
       </c>
       <c r="H66" s="18" t="s">
         <v>166</v>
@@ -3899,9 +3988,7 @@
       <c r="J66" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="K66" s="44" t="s">
-        <v>363</v>
-      </c>
+      <c r="K66" s="44"/>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
@@ -3913,13 +4000,15 @@
       <c r="C67" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="D67" s="6"/>
+      <c r="D67" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="E67" s="14" t="s">
         <v>171</v>
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="6" t="s">
-        <v>241</v>
+        <v>372</v>
       </c>
       <c r="H67" s="18" t="s">
         <v>166</v>
@@ -3938,7 +4027,9 @@
       <c r="C68" s="57" t="s">
         <v>348</v>
       </c>
-      <c r="D68" s="6"/>
+      <c r="D68" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E68" s="23" t="s">
         <v>301</v>
       </c>
@@ -3954,7 +4045,7 @@
         <v>361</v>
       </c>
       <c r="K68" s="48" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
@@ -3965,7 +4056,9 @@
       <c r="C69" s="57" t="s">
         <v>349</v>
       </c>
-      <c r="D69" s="6"/>
+      <c r="D69" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E69" s="23" t="s">
         <v>299</v>
       </c>
@@ -3981,7 +4074,7 @@
         <v>361</v>
       </c>
       <c r="K69" s="47" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
@@ -4173,7 +4266,9 @@
       <c r="C76" s="36" t="s">
         <v>352</v>
       </c>
-      <c r="D76" s="6"/>
+      <c r="D76" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E76" s="36" t="s">
         <v>157</v>
       </c>
@@ -4184,7 +4279,7 @@
       </c>
       <c r="I76" s="9"/>
       <c r="J76" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="K76" s="44">
         <v>18</v>
@@ -4225,7 +4320,9 @@
       <c r="C78" s="29" t="s">
         <v>353</v>
       </c>
-      <c r="D78" s="6"/>
+      <c r="D78" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E78" s="29" t="s">
         <v>156</v>
       </c>
@@ -4236,7 +4333,7 @@
       <c r="H78" s="8"/>
       <c r="I78" s="9"/>
       <c r="J78" s="32" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="K78" s="47">
         <v>14</v>
@@ -4252,7 +4349,9 @@
       <c r="C79" s="37" t="s">
         <v>172</v>
       </c>
-      <c r="D79" s="6"/>
+      <c r="D79" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E79" s="37" t="s">
         <v>173</v>
       </c>
@@ -4304,7 +4403,9 @@
       <c r="C81" s="29" t="s">
         <v>355</v>
       </c>
-      <c r="D81" s="6"/>
+      <c r="D81" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E81" s="36" t="s">
         <v>267</v>
       </c>
@@ -4329,7 +4430,9 @@
       <c r="C82" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="D82" s="6"/>
+      <c r="D82" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E82" s="36" t="s">
         <v>186</v>
       </c>
@@ -4356,7 +4459,9 @@
       <c r="C83" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="D83" s="6"/>
+      <c r="D83" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="E83" s="36" t="s">
         <v>178</v>
       </c>
@@ -4381,7 +4486,9 @@
       <c r="C84" s="26" t="s">
         <v>356</v>
       </c>
-      <c r="D84" s="6"/>
+      <c r="D84" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E84" s="36" t="s">
         <v>260</v>
       </c>
@@ -4472,7 +4579,9 @@
       <c r="C87" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="D87" s="6"/>
+      <c r="D87" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E87" s="36"/>
       <c r="F87" s="36"/>
       <c r="G87" s="6"/>
@@ -4517,7 +4626,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" s="22" t="s">
         <v>271</v>
       </c>
@@ -4525,7 +4634,9 @@
       <c r="C89" s="29" t="s">
         <v>357</v>
       </c>
-      <c r="D89" s="6"/>
+      <c r="D89" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="E89" s="36" t="s">
         <v>274</v>
       </c>
@@ -4550,7 +4661,9 @@
       <c r="C90" s="29" t="s">
         <v>358</v>
       </c>
-      <c r="D90" s="6"/>
+      <c r="D90" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="E90" s="36" t="s">
         <v>275</v>
       </c>
@@ -4577,7 +4690,9 @@
       <c r="C91" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="D91" s="6"/>
+      <c r="D91" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E91" s="36"/>
       <c r="F91" s="36"/>
       <c r="G91" s="6"/>
@@ -4600,7 +4715,9 @@
       <c r="C92" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="D92" s="6"/>
+      <c r="D92" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E92" s="36" t="s">
         <v>155</v>
       </c>
@@ -4623,7 +4740,9 @@
         <v>183</v>
       </c>
       <c r="C93" s="29"/>
-      <c r="D93" s="6"/>
+      <c r="D93" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E93" s="36" t="s">
         <v>182</v>
       </c>
@@ -4644,7 +4763,9 @@
       </c>
       <c r="B94" s="33"/>
       <c r="C94" s="36"/>
-      <c r="D94" s="6"/>
+      <c r="D94" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E94" s="37" t="s">
         <v>179</v>
       </c>
@@ -4665,13 +4786,15 @@
       </c>
       <c r="B95" s="5"/>
       <c r="C95" s="29"/>
-      <c r="D95" s="6"/>
+      <c r="D95" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E95" s="37" t="s">
         <v>243</v>
       </c>
       <c r="F95" s="36"/>
       <c r="G95" s="19" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H95" s="8" t="s">
         <v>166</v>
@@ -4688,7 +4811,9 @@
       </c>
       <c r="B96" s="22"/>
       <c r="C96" s="29"/>
-      <c r="D96" s="6"/>
+      <c r="D96" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E96" s="36" t="s">
         <v>238</v>
       </c>
@@ -4705,7 +4830,9 @@
       </c>
       <c r="B97" s="22"/>
       <c r="C97" s="29"/>
-      <c r="D97" s="23"/>
+      <c r="D97" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E97" s="36" t="s">
         <v>280</v>
       </c>
@@ -4718,13 +4845,15 @@
       <c r="J97" s="36"/>
       <c r="K97" s="51"/>
     </row>
-    <row r="98" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="30" t="s">
         <v>9</v>
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="38"/>
-      <c r="D98" s="6"/>
+      <c r="D98" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E98" s="38" t="s">
         <v>4</v>
       </c>
@@ -4743,7 +4872,9 @@
       </c>
       <c r="B99" s="5"/>
       <c r="C99" s="29"/>
-      <c r="D99" s="6"/>
+      <c r="D99" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E99" s="36"/>
       <c r="F99" s="36"/>
       <c r="G99" s="19"/>
@@ -4762,7 +4893,9 @@
         <v>161</v>
       </c>
       <c r="C100" s="29"/>
-      <c r="D100" s="6"/>
+      <c r="D100" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E100" s="36"/>
       <c r="F100" s="39"/>
       <c r="G100" s="7"/>
@@ -4773,13 +4906,15 @@
       <c r="J100" s="36"/>
       <c r="K100" s="51"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A101" s="22" t="s">
         <v>168</v>
       </c>
       <c r="B101" s="28"/>
       <c r="C101" s="29"/>
-      <c r="D101" s="6"/>
+      <c r="D101" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E101" s="36"/>
       <c r="F101" s="39"/>
       <c r="G101" s="7"/>
@@ -4800,7 +4935,9 @@
       </c>
       <c r="B102" s="6"/>
       <c r="C102" s="36"/>
-      <c r="D102" s="6"/>
+      <c r="D102" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E102" s="36"/>
       <c r="F102" s="36"/>
       <c r="G102" s="6"/>
@@ -4819,7 +4956,9 @@
       </c>
       <c r="B103" s="23"/>
       <c r="C103" s="36"/>
-      <c r="D103" s="6"/>
+      <c r="D103" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E103" s="36"/>
       <c r="F103" s="36"/>
       <c r="G103" s="6"/>
@@ -4838,7 +4977,9 @@
       </c>
       <c r="B104" s="23"/>
       <c r="C104" s="36"/>
-      <c r="D104" s="6"/>
+      <c r="D104" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E104" s="36"/>
       <c r="F104" s="36"/>
       <c r="G104" s="6"/>
@@ -4857,7 +4998,9 @@
       </c>
       <c r="B105" s="6"/>
       <c r="C105" s="36"/>
-      <c r="D105" s="6"/>
+      <c r="D105" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E105" s="36"/>
       <c r="F105" s="36"/>
       <c r="G105" s="6"/>
@@ -4876,7 +5019,9 @@
       </c>
       <c r="B106" s="6"/>
       <c r="C106" s="36"/>
-      <c r="D106" s="6"/>
+      <c r="D106" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E106" s="36"/>
       <c r="F106" s="36"/>
       <c r="G106" s="6"/>
@@ -4897,7 +5042,9 @@
       </c>
       <c r="B107" s="6"/>
       <c r="C107" s="36"/>
-      <c r="D107" s="6"/>
+      <c r="D107" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E107" s="36"/>
       <c r="F107" s="36"/>
       <c r="G107" s="6"/>
@@ -4916,7 +5063,9 @@
       </c>
       <c r="B108" s="6"/>
       <c r="C108" s="36"/>
-      <c r="D108" s="6"/>
+      <c r="D108" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E108" s="36"/>
       <c r="F108" s="36"/>
       <c r="G108" s="6"/>
@@ -4935,7 +5084,9 @@
       </c>
       <c r="B109" s="6"/>
       <c r="C109" s="36"/>
-      <c r="D109" s="6"/>
+      <c r="D109" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E109" s="36"/>
       <c r="F109" s="36"/>
       <c r="G109" s="6"/>
@@ -4954,7 +5105,9 @@
       </c>
       <c r="B110" s="6"/>
       <c r="C110" s="36"/>
-      <c r="D110" s="6"/>
+      <c r="D110" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E110" s="36"/>
       <c r="F110" s="36"/>
       <c r="G110" s="6"/>
@@ -4975,7 +5128,9 @@
         <v>194</v>
       </c>
       <c r="C111" s="22"/>
-      <c r="D111" s="6"/>
+      <c r="D111" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E111" s="23"/>
       <c r="F111" s="23"/>
       <c r="G111" s="7"/>
@@ -4996,7 +5151,9 @@
         <v>194</v>
       </c>
       <c r="C112" s="22"/>
-      <c r="D112" s="6"/>
+      <c r="D112" s="60" t="s">
+        <v>100</v>
+      </c>
       <c r="E112" s="23"/>
       <c r="F112" s="23"/>
       <c r="G112" s="7"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA37C41-0AE7-BB40-AD36-3D15171DB6E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9C1C04-0C35-2340-B8FA-73CABF26C156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1880" yWindow="2960" windowWidth="28360" windowHeight="16680" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -1491,7 +1491,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1518,9 +1518,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1528,7 +1525,7 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1537,7 +1534,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1545,16 +1542,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1579,13 +1573,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1872,7 +1860,43 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K131" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K131" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
+  <autoFilter ref="A1:K131" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="192.168.0.103"/>
+        <filter val="192.168.0.122"/>
+        <filter val="192.168.0.130"/>
+        <filter val="192.168.0.145"/>
+        <filter val="192.168.0.180"/>
+        <filter val="192.168.0.181"/>
+        <filter val="192.168.0.183"/>
+        <filter val="192.168.0.185"/>
+        <filter val="192.168.0.186"/>
+        <filter val="192.168.0.187"/>
+        <filter val="192.168.0.188"/>
+        <filter val="192.168.0.189"/>
+        <filter val="192.168.0.190"/>
+        <filter val="192.168.0.191"/>
+        <filter val="192.168.0.192"/>
+        <filter val="192.168.0.193"/>
+        <filter val="192.168.0.194"/>
+        <filter val="192.168.0.195"/>
+        <filter val="192.168.0.197"/>
+        <filter val="192.168.0.201"/>
+        <filter val="192.168.0.202"/>
+        <filter val="192.168.0.207"/>
+        <filter val="192.168.0.208"/>
+        <filter val="192.168.0.210"/>
+        <filter val="192.168.0.22"/>
+        <filter val="192.168.0.23"/>
+        <filter val="192.168.0.239"/>
+        <filter val="192.168.0.24"/>
+        <filter val="192.168.0.25"/>
+        <filter val="192.168.0.26"/>
+        <filter val="192.168.0.53"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K131">
     <sortCondition ref="C2:C131"/>
   </sortState>
@@ -2203,7 +2227,7 @@
     <col min="8" max="8" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.1640625" style="4" customWidth="1"/>
     <col min="10" max="10" width="29.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="44.6640625" style="55" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="44.6640625" style="51" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.1640625" customWidth="1"/>
     <col min="13" max="13" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -2239,25 +2263,25 @@
       <c r="J1" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="K1" s="43" t="s">
+      <c r="K1" s="40" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>237</v>
       </c>
       <c r="B2" s="5"/>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="5" t="s">
         <v>320</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="F2" s="23"/>
+      <c r="F2" s="6"/>
       <c r="G2" s="19" t="s">
         <v>245</v>
       </c>
@@ -2265,12 +2289,12 @@
         <v>166</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="23" t="s">
+      <c r="J2" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="K2" s="45"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K2" s="41"/>
+    </row>
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>189</v>
       </c>
@@ -2295,34 +2319,34 @@
       <c r="J3" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="K3" s="44"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K3" s="41"/>
+    </row>
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="5" t="s">
         <v>195</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I4" s="9"/>
-      <c r="J4" s="23" t="s">
+      <c r="J4" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="K4" s="45"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K4" s="41"/>
+    </row>
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>208</v>
       </c>
@@ -2347,34 +2371,34 @@
       <c r="J5" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="K5" s="44"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="23" t="s">
+      <c r="K5" s="41"/>
+    </row>
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
         <v>208</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="5" t="s">
         <v>204</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I6" s="9"/>
-      <c r="J6" s="23" t="s">
+      <c r="J6" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="K6" s="45"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K6" s="41"/>
+    </row>
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>215</v>
       </c>
@@ -2401,34 +2425,34 @@
       <c r="J7" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="K7" s="44"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K7" s="41"/>
+    </row>
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="5" t="s">
         <v>220</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I8" s="9"/>
-      <c r="J8" s="23" t="s">
+      <c r="J8" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="K8" s="45"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K8" s="41"/>
+    </row>
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>214</v>
       </c>
@@ -2453,48 +2477,48 @@
       <c r="J9" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="K9" s="44"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K9" s="41"/>
+    </row>
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="5" t="s">
         <v>207</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I10" s="9"/>
-      <c r="J10" s="23" t="s">
+      <c r="J10" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="K10" s="45"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="32" t="s">
+      <c r="K10" s="41"/>
+    </row>
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="29" t="s">
         <v>308</v>
       </c>
       <c r="B11" s="5"/>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="29" t="s">
         <v>321</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="29" t="s">
         <v>309</v>
       </c>
-      <c r="F11" s="32" t="s">
+      <c r="F11" s="29" t="s">
         <v>282</v>
       </c>
       <c r="G11" s="7" t="s">
@@ -2502,28 +2526,28 @@
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="9"/>
-      <c r="J11" s="22" t="s">
+      <c r="J11" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="K11" s="48">
+      <c r="K11" s="44">
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="22" t="s">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
         <v>318</v>
       </c>
       <c r="B12" s="5"/>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="5" t="s">
         <v>322</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="5" t="s">
         <v>282</v>
       </c>
       <c r="G12" s="7" t="s">
@@ -2531,28 +2555,28 @@
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="9"/>
-      <c r="J12" s="32" t="s">
+      <c r="J12" s="29" t="s">
         <v>300</v>
       </c>
-      <c r="K12" s="47">
+      <c r="K12" s="43">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="22" t="s">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
         <v>314</v>
       </c>
       <c r="B13" s="5"/>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="5" t="s">
         <v>323</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="5" t="s">
         <v>282</v>
       </c>
       <c r="G13" s="7" t="s">
@@ -2560,28 +2584,28 @@
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="9"/>
-      <c r="J13" s="32" t="s">
+      <c r="J13" s="29" t="s">
         <v>283</v>
       </c>
-      <c r="K13" s="47">
+      <c r="K13" s="43">
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="22" t="s">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
         <v>302</v>
       </c>
       <c r="B14" s="5"/>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="5" t="s">
         <v>324</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="5" t="s">
         <v>282</v>
       </c>
       <c r="G14" s="7" t="s">
@@ -2589,28 +2613,28 @@
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="9"/>
-      <c r="J14" s="32" t="s">
+      <c r="J14" s="29" t="s">
         <v>283</v>
       </c>
-      <c r="K14" s="47">
+      <c r="K14" s="43">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="22" t="s">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
         <v>306</v>
       </c>
       <c r="B15" s="5"/>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="5" t="s">
         <v>325</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="5" t="s">
         <v>282</v>
       </c>
       <c r="G15" s="7" t="s">
@@ -2618,28 +2642,28 @@
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="9"/>
-      <c r="J15" s="32" t="s">
+      <c r="J15" s="29" t="s">
         <v>283</v>
       </c>
-      <c r="K15" s="47">
+      <c r="K15" s="43">
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="32" t="s">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="29" t="s">
         <v>312</v>
       </c>
       <c r="B16" s="5"/>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="29" t="s">
         <v>326</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="29" t="s">
         <v>313</v>
       </c>
-      <c r="F16" s="32" t="s">
+      <c r="F16" s="29" t="s">
         <v>282</v>
       </c>
       <c r="G16" s="7" t="s">
@@ -2647,28 +2671,28 @@
       </c>
       <c r="H16" s="8"/>
       <c r="I16" s="9"/>
-      <c r="J16" s="22" t="s">
+      <c r="J16" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="K16" s="48">
+      <c r="K16" s="44">
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="32" t="s">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="29" t="s">
         <v>316</v>
       </c>
       <c r="B17" s="5"/>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="29" t="s">
         <v>327</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E17" s="32" t="s">
+      <c r="E17" s="29" t="s">
         <v>317</v>
       </c>
-      <c r="F17" s="32" t="s">
+      <c r="F17" s="29" t="s">
         <v>282</v>
       </c>
       <c r="G17" s="7" t="s">
@@ -2676,28 +2700,28 @@
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="9"/>
-      <c r="J17" s="22" t="s">
+      <c r="J17" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="K17" s="48">
+      <c r="K17" s="44">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="22" t="s">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
         <v>310</v>
       </c>
       <c r="B18" s="5"/>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="5" t="s">
         <v>328</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="F18" s="22" t="s">
+      <c r="F18" s="5" t="s">
         <v>282</v>
       </c>
       <c r="G18" s="7" t="s">
@@ -2705,28 +2729,28 @@
       </c>
       <c r="H18" s="8"/>
       <c r="I18" s="9"/>
-      <c r="J18" s="32" t="s">
+      <c r="J18" s="29" t="s">
         <v>283</v>
       </c>
-      <c r="K18" s="47">
+      <c r="K18" s="43">
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="32" t="s">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="29" t="s">
         <v>304</v>
       </c>
       <c r="B19" s="5"/>
-      <c r="C19" s="32" t="s">
+      <c r="C19" s="29" t="s">
         <v>329</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E19" s="32" t="s">
+      <c r="E19" s="29" t="s">
         <v>305</v>
       </c>
-      <c r="F19" s="32" t="s">
+      <c r="F19" s="29" t="s">
         <v>282</v>
       </c>
       <c r="G19" s="7" t="s">
@@ -2734,36 +2758,36 @@
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="9"/>
-      <c r="J19" s="22" t="s">
+      <c r="J19" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="K19" s="48">
+      <c r="K19" s="44">
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="32" t="s">
+      <c r="B20" s="29"/>
+      <c r="C20" s="29" t="s">
         <v>330</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E20" s="32" t="s">
+      <c r="E20" s="29" t="s">
         <v>293</v>
       </c>
-      <c r="F20" s="32" t="s">
+      <c r="F20" s="29" t="s">
         <v>294</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="8"/>
       <c r="I20" s="9"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="45"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="23" t="s">
+      <c r="J20" s="6"/>
+      <c r="K20" s="41"/>
+    </row>
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
         <v>55</v>
       </c>
       <c r="B21" s="6"/>
@@ -2787,11 +2811,11 @@
       <c r="J21" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="K21" s="44" t="s">
+      <c r="K21" s="41" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
         <v>45</v>
       </c>
@@ -2816,11 +2840,11 @@
       <c r="J22" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="K22" s="44" t="s">
+      <c r="K22" s="41" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
         <v>47</v>
       </c>
@@ -2845,11 +2869,11 @@
       <c r="J23" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="K23" s="44" t="s">
+      <c r="K23" s="41" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
         <v>49</v>
       </c>
@@ -2874,7 +2898,7 @@
       <c r="J24" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="K24" s="44" t="s">
+      <c r="K24" s="41" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2901,41 +2925,41 @@
       <c r="J25" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="K25" s="46" t="s">
+      <c r="K25" s="42" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" s="22"/>
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="5"/>
       <c r="B26" s="5"/>
-      <c r="C26" s="22" t="s">
+      <c r="C26" s="5" t="s">
         <v>268</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
       <c r="G26" s="19"/>
       <c r="H26" s="8"/>
       <c r="I26" s="9"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="45" t="s">
+      <c r="J26" s="6"/>
+      <c r="K26" s="41" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23" t="s">
+      <c r="B27" s="6"/>
+      <c r="C27" s="6" t="s">
         <v>331</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E27" s="23" t="s">
+      <c r="E27" s="6" t="s">
         <v>270</v>
       </c>
       <c r="F27" s="19" t="str">
@@ -2952,7 +2976,7 @@
       <c r="J27" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="K27" s="46">
+      <c r="K27" s="42">
         <v>4</v>
       </c>
     </row>
@@ -2981,7 +3005,7 @@
       <c r="J28" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K28" s="44" t="s">
+      <c r="K28" s="41" t="s">
         <v>248</v>
       </c>
     </row>
@@ -3010,11 +3034,11 @@
       <c r="J29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K29" s="44" t="s">
+      <c r="K29" s="41" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>6</v>
       </c>
@@ -3037,9 +3061,9 @@
       <c r="J30" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="K30" s="44"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="41"/>
+    </row>
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>198</v>
       </c>
@@ -3064,9 +3088,9 @@
       <c r="J31" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="K31" s="44"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="41"/>
+    </row>
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>221</v>
       </c>
@@ -3089,303 +3113,303 @@
       <c r="J32" s="6">
         <v>30</v>
       </c>
-      <c r="K32" s="44"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K32" s="41"/>
+    </row>
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22" t="s">
+      <c r="B33" s="5"/>
+      <c r="C33" s="5" t="s">
         <v>332</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="E33" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="F33" s="22" t="s">
+      <c r="F33" s="5" t="s">
         <v>282</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="8"/>
       <c r="I33" s="9"/>
       <c r="J33" s="6"/>
-      <c r="K33" s="44"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" s="22"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="32" t="s">
+      <c r="K33" s="41"/>
+    </row>
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="5"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29" t="s">
         <v>333</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E34" s="32" t="s">
+      <c r="E34" s="29" t="s">
         <v>290</v>
       </c>
-      <c r="F34" s="32" t="s">
+      <c r="F34" s="29" t="s">
         <v>282</v>
       </c>
       <c r="G34" s="19"/>
       <c r="H34" s="8"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="23"/>
-      <c r="K34" s="45"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I34" s="9"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="41"/>
+    </row>
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="32" t="s">
+      <c r="B35" s="29"/>
+      <c r="C35" s="29" t="s">
         <v>334</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E35" s="32" t="s">
+      <c r="E35" s="29" t="s">
         <v>287</v>
       </c>
-      <c r="F35" s="32" t="s">
+      <c r="F35" s="29" t="s">
         <v>282</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="8"/>
       <c r="I35" s="9"/>
       <c r="J35" s="6"/>
-      <c r="K35" s="44"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K35" s="41"/>
+    </row>
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="B36" s="32"/>
-      <c r="C36" s="32" t="s">
+      <c r="B36" s="29"/>
+      <c r="C36" s="29" t="s">
         <v>335</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E36" s="32" t="s">
+      <c r="E36" s="29" t="s">
         <v>284</v>
       </c>
-      <c r="F36" s="32" t="s">
+      <c r="F36" s="29" t="s">
         <v>282</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="8"/>
       <c r="I36" s="9"/>
       <c r="J36" s="6"/>
-      <c r="K36" s="44"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K36" s="41"/>
+    </row>
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32" t="s">
+      <c r="B37" s="29"/>
+      <c r="C37" s="29" t="s">
         <v>336</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E37" s="32" t="s">
+      <c r="E37" s="29" t="s">
         <v>291</v>
       </c>
-      <c r="F37" s="32" t="s">
+      <c r="F37" s="29" t="s">
         <v>282</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="8"/>
       <c r="I37" s="9"/>
       <c r="J37" s="6"/>
-      <c r="K37" s="44" t="s">
+      <c r="K37" s="41" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5"/>
-      <c r="B38" s="32"/>
-      <c r="C38" s="32" t="s">
+      <c r="B38" s="29"/>
+      <c r="C38" s="29" t="s">
         <v>337</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E38" s="32" t="s">
+      <c r="E38" s="29" t="s">
         <v>289</v>
       </c>
-      <c r="F38" s="32" t="s">
+      <c r="F38" s="29" t="s">
         <v>282</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="8"/>
       <c r="I38" s="9"/>
       <c r="J38" s="6"/>
-      <c r="K38" s="44" t="s">
+      <c r="K38" s="41" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5"/>
-      <c r="B39" s="32"/>
-      <c r="C39" s="32" t="s">
+      <c r="B39" s="29"/>
+      <c r="C39" s="29" t="s">
         <v>338</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E39" s="32" t="s">
+      <c r="E39" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="F39" s="32" t="s">
+      <c r="F39" s="29" t="s">
         <v>282</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="8"/>
       <c r="I39" s="9"/>
       <c r="J39" s="6"/>
-      <c r="K39" s="44" t="s">
+      <c r="K39" s="41" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="22" t="s">
+      <c r="B40" s="5"/>
+      <c r="C40" s="5" t="s">
         <v>339</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E40" s="22" t="s">
+      <c r="E40" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="F40" s="22" t="s">
+      <c r="F40" s="5" t="s">
         <v>282</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="8"/>
       <c r="I40" s="9"/>
       <c r="J40" s="6"/>
-      <c r="K40" s="44" t="s">
+      <c r="K40" s="41" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22" t="s">
+      <c r="B41" s="5"/>
+      <c r="C41" s="5" t="s">
         <v>340</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E41" s="22" t="s">
+      <c r="E41" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="F41" s="22" t="s">
+      <c r="F41" s="5" t="s">
         <v>282</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="8"/>
       <c r="I41" s="9"/>
       <c r="J41" s="6"/>
-      <c r="K41" s="44" t="s">
+      <c r="K41" s="41" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22" t="s">
+      <c r="B42" s="5"/>
+      <c r="C42" s="5" t="s">
         <v>341</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E42" s="22" t="s">
+      <c r="E42" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="F42" s="22" t="s">
+      <c r="F42" s="5" t="s">
         <v>282</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="8"/>
       <c r="I42" s="9"/>
       <c r="J42" s="6"/>
-      <c r="K42" s="44" t="s">
+      <c r="K42" s="41" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="5"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22" t="s">
+      <c r="B43" s="5"/>
+      <c r="C43" s="5" t="s">
         <v>342</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E43" s="22" t="s">
+      <c r="E43" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="F43" s="22" t="s">
+      <c r="F43" s="5" t="s">
         <v>282</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="8"/>
       <c r="I43" s="9"/>
       <c r="J43" s="6"/>
-      <c r="K43" s="44" t="s">
+      <c r="K43" s="41" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5"/>
-      <c r="B44" s="32"/>
-      <c r="C44" s="32" t="s">
+      <c r="B44" s="29"/>
+      <c r="C44" s="29" t="s">
         <v>343</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E44" s="32" t="s">
+      <c r="E44" s="29" t="s">
         <v>285</v>
       </c>
-      <c r="F44" s="32" t="s">
+      <c r="F44" s="29" t="s">
         <v>282</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="8"/>
       <c r="I44" s="9"/>
       <c r="J44" s="6"/>
-      <c r="K44" s="44" t="s">
+      <c r="K44" s="41" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A45" s="22"/>
-      <c r="B45" s="32"/>
-      <c r="C45" s="32" t="s">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="5"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="29" t="s">
         <v>344</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E45" s="32" t="s">
+      <c r="E45" s="29" t="s">
         <v>281</v>
       </c>
-      <c r="F45" s="32" t="s">
+      <c r="F45" s="29" t="s">
         <v>282</v>
       </c>
       <c r="G45" s="19"/>
       <c r="H45" s="8"/>
-      <c r="I45" s="24"/>
-      <c r="J45" s="23"/>
-      <c r="K45" s="44" t="s">
+      <c r="I45" s="9"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="41" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A46" s="23" t="s">
+      <c r="A46" s="6" t="s">
         <v>108</v>
       </c>
       <c r="B46" s="6"/>
@@ -3410,7 +3434,7 @@
       <c r="J46" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="K46" s="44" t="s">
+      <c r="K46" s="41" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3440,7 +3464,7 @@
       <c r="J47" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="K47" s="44" t="s">
+      <c r="K47" s="41" t="s">
         <v>98</v>
       </c>
     </row>
@@ -3470,12 +3494,12 @@
       <c r="J48" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="K48" s="46" t="s">
+      <c r="K48" s="42" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A49" s="22" t="s">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="5" t="s">
         <v>233</v>
       </c>
       <c r="B49" s="5"/>
@@ -3499,12 +3523,12 @@
       <c r="J49" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="K49" s="44">
+      <c r="K49" s="41">
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A50" s="34" t="s">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="31" t="s">
         <v>199</v>
       </c>
       <c r="B50" s="13"/>
@@ -3526,7 +3550,7 @@
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="6"/>
-      <c r="K50" s="44"/>
+      <c r="K50" s="41"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
@@ -3537,7 +3561,7 @@
         <v>129</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>128</v>
@@ -3556,7 +3580,7 @@
       <c r="J51" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="K51" s="46"/>
+      <c r="K51" s="42"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
@@ -3567,7 +3591,7 @@
         <v>132</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>131</v>
@@ -3586,30 +3610,30 @@
       <c r="J52" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="K52" s="46"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A53" s="23" t="s">
+      <c r="K52" s="42"/>
+    </row>
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="6" t="s">
         <v>130</v>
       </c>
       <c r="B53" s="6"/>
-      <c r="C53" s="23" t="s">
+      <c r="C53" s="6" t="s">
         <v>132</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E53" s="23"/>
+      <c r="E53" s="6"/>
       <c r="F53" s="19"/>
       <c r="G53" s="7"/>
       <c r="H53" s="18" t="s">
         <v>167</v>
       </c>
       <c r="I53" s="9"/>
-      <c r="J53" s="23" t="s">
+      <c r="J53" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="K53" s="59"/>
+      <c r="K53" s="42"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
@@ -3620,7 +3644,7 @@
         <v>127</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>126</v>
@@ -3639,7 +3663,7 @@
       <c r="J54" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="K54" s="46"/>
+      <c r="K54" s="42"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -3650,7 +3674,7 @@
         <v>125</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>124</v>
@@ -3669,7 +3693,7 @@
       <c r="J55" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="K55" s="44"/>
+      <c r="K55" s="41"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
@@ -3680,7 +3704,7 @@
         <v>122</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>121</v>
@@ -3699,7 +3723,7 @@
       <c r="J56" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="K56" s="46"/>
+      <c r="K56" s="42"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="10" t="s">
@@ -3729,7 +3753,7 @@
       <c r="J57" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="K57" s="44"/>
+      <c r="K57" s="41"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
@@ -3759,7 +3783,7 @@
       <c r="J58" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K58" s="44" t="s">
+      <c r="K58" s="41" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3789,7 +3813,7 @@
       <c r="J59" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="K59" s="44" t="s">
+      <c r="K59" s="41" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3821,38 +3845,38 @@
       <c r="J60" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="K60" s="44" t="s">
+      <c r="K60" s="41" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A61" s="22" t="s">
+    <row r="61" spans="1:11" ht="17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="B61" s="22"/>
-      <c r="C61" s="22" t="s">
+      <c r="B61" s="5"/>
+      <c r="C61" s="5" t="s">
         <v>345</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E61" s="58" t="s">
+      <c r="E61" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="F61" s="23"/>
+      <c r="F61" s="6"/>
       <c r="G61" s="19"/>
       <c r="H61" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I61" s="24"/>
-      <c r="J61" s="23" t="s">
+      <c r="I61" s="9"/>
+      <c r="J61" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="K61" s="45">
+      <c r="K61" s="41">
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
         <v>3</v>
       </c>
@@ -3877,7 +3901,7 @@
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="6"/>
-      <c r="K62" s="44">
+      <c r="K62" s="41">
         <v>3</v>
       </c>
     </row>
@@ -3904,23 +3928,23 @@
       <c r="J63" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K63" s="44"/>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="41"/>
+    </row>
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B64" s="22"/>
-      <c r="C64" s="23" t="s">
+      <c r="B64" s="5"/>
+      <c r="C64" s="6" t="s">
         <v>347</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E64" s="23" t="s">
+      <c r="E64" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="F64" s="23"/>
+      <c r="F64" s="6"/>
       <c r="G64" s="6"/>
       <c r="H64" s="18" t="s">
         <v>166</v>
@@ -3929,7 +3953,7 @@
       <c r="J64" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="K64" s="44">
+      <c r="K64" s="41">
         <v>6</v>
       </c>
     </row>
@@ -3959,7 +3983,7 @@
       <c r="J65" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="K65" s="44"/>
+      <c r="K65" s="41"/>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
@@ -3972,7 +3996,7 @@
         <v>162</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>176</v>
@@ -3988,9 +4012,9 @@
       <c r="J66" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="K66" s="44"/>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K66" s="41"/>
+    </row>
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
         <v>1</v>
       </c>
@@ -4017,63 +4041,63 @@
       <c r="J67" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="K67" s="44"/>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A68" s="22" t="s">
+      <c r="K67" s="41"/>
+    </row>
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="B68" s="22"/>
-      <c r="C68" s="57" t="s">
+      <c r="B68" s="5"/>
+      <c r="C68" s="53" t="s">
         <v>348</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E68" s="23" t="s">
+      <c r="E68" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="F68" s="23"/>
+      <c r="F68" s="6"/>
       <c r="G68" s="19" t="s">
         <v>230</v>
       </c>
       <c r="H68" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I68" s="24"/>
-      <c r="J68" s="22" t="s">
+      <c r="I68" s="9"/>
+      <c r="J68" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="K68" s="48" t="s">
+      <c r="K68" s="44" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="B69" s="22"/>
-      <c r="C69" s="57" t="s">
+      <c r="B69" s="5"/>
+      <c r="C69" s="53" t="s">
         <v>349</v>
       </c>
-      <c r="D69" s="60" t="s">
+      <c r="D69" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E69" s="23" t="s">
+      <c r="E69" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="F69" s="23"/>
+      <c r="F69" s="6"/>
       <c r="G69" s="19" t="s">
         <v>230</v>
       </c>
       <c r="H69" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I69" s="24"/>
-      <c r="J69" s="41" t="s">
+      <c r="I69" s="9"/>
+      <c r="J69" s="38" t="s">
         <v>361</v>
       </c>
-      <c r="K69" s="47" t="s">
+      <c r="K69" s="43" t="s">
         <v>367</v>
       </c>
     </row>
@@ -4102,7 +4126,7 @@
       <c r="J70" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="K70" s="46" t="s">
+      <c r="K70" s="42" t="s">
         <v>74</v>
       </c>
     </row>
@@ -4136,25 +4160,25 @@
       <c r="J71" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K71" s="44" t="s">
+      <c r="K71" s="41" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="B72" s="22"/>
-      <c r="C72" s="22" t="s">
+      <c r="B72" s="5"/>
+      <c r="C72" s="5" t="s">
         <v>350</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E72" s="23" t="s">
+      <c r="E72" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="F72" s="23"/>
+      <c r="F72" s="6"/>
       <c r="G72" s="7" t="s">
         <v>227</v>
       </c>
@@ -4165,23 +4189,23 @@
       <c r="J72" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K72" s="44"/>
-    </row>
-    <row r="73" spans="1:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="25" t="s">
+      <c r="K72" s="41"/>
+    </row>
+    <row r="73" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="22" t="s">
         <v>256</v>
       </c>
-      <c r="B73" s="22"/>
-      <c r="C73" s="22" t="s">
+      <c r="B73" s="5"/>
+      <c r="C73" s="5" t="s">
         <v>351</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E73" s="23" t="s">
+      <c r="E73" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="F73" s="23"/>
+      <c r="F73" s="6"/>
       <c r="G73" s="7" t="s">
         <v>227</v>
       </c>
@@ -4192,23 +4216,23 @@
       <c r="J73" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K73" s="44"/>
+      <c r="K73" s="41"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B74" s="33"/>
-      <c r="C74" s="36" t="s">
+      <c r="B74" s="30"/>
+      <c r="C74" s="33" t="s">
         <v>80</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E74" s="36" t="s">
+      <c r="E74" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="F74" s="39" t="str">
+      <c r="F74" s="36" t="str">
         <f>CONCATENATE("ftp://", E74)</f>
         <v>ftp://192.168.0.189</v>
       </c>
@@ -4222,7 +4246,7 @@
       <c r="J74" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="K74" s="46" t="s">
+      <c r="K74" s="42" t="s">
         <v>74</v>
       </c>
     </row>
@@ -4230,17 +4254,17 @@
       <c r="A75" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B75" s="33"/>
-      <c r="C75" s="36" t="s">
+      <c r="B75" s="30"/>
+      <c r="C75" s="33" t="s">
         <v>76</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E75" s="36" t="s">
+      <c r="E75" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="F75" s="39" t="str">
+      <c r="F75" s="36" t="str">
         <f>CONCATENATE("ftp://", E75)</f>
         <v>ftp://192.168.0.190</v>
       </c>
@@ -4254,25 +4278,25 @@
       <c r="J75" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="K75" s="46" t="s">
+      <c r="K75" s="42" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B76" s="28"/>
-      <c r="C76" s="36" t="s">
+      <c r="B76" s="25"/>
+      <c r="C76" s="33" t="s">
         <v>352</v>
       </c>
-      <c r="D76" s="60" t="s">
+      <c r="D76" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E76" s="36" t="s">
+      <c r="E76" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="F76" s="36"/>
+      <c r="F76" s="33"/>
       <c r="G76" s="6"/>
       <c r="H76" s="8" t="s">
         <v>166</v>
@@ -4281,7 +4305,7 @@
       <c r="J76" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="K76" s="44">
+      <c r="K76" s="41">
         <v>18</v>
       </c>
     </row>
@@ -4289,17 +4313,17 @@
       <c r="A77" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B77" s="33"/>
-      <c r="C77" s="36" t="s">
+      <c r="B77" s="30"/>
+      <c r="C77" s="33" t="s">
         <v>89</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E77" s="36" t="s">
+      <c r="E77" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="F77" s="36"/>
+      <c r="F77" s="33"/>
       <c r="G77" s="6"/>
       <c r="H77" s="8" t="s">
         <v>167</v>
@@ -4308,34 +4332,34 @@
       <c r="J77" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="K77" s="44" t="s">
+      <c r="K77" s="41" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A78" s="22" t="s">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B78" s="28"/>
-      <c r="C78" s="29" t="s">
+      <c r="B78" s="25"/>
+      <c r="C78" s="26" t="s">
         <v>353</v>
       </c>
-      <c r="D78" s="60" t="s">
+      <c r="D78" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E78" s="29" t="s">
+      <c r="E78" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="F78" s="29" t="s">
+      <c r="F78" s="26" t="s">
         <v>298</v>
       </c>
       <c r="G78" s="7"/>
       <c r="H78" s="8"/>
       <c r="I78" s="9"/>
-      <c r="J78" s="32" t="s">
+      <c r="J78" s="29" t="s">
         <v>369</v>
       </c>
-      <c r="K78" s="47">
+      <c r="K78" s="43">
         <v>14</v>
       </c>
     </row>
@@ -4343,19 +4367,19 @@
       <c r="A79" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="B79" s="28" t="s">
+      <c r="B79" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="C79" s="37" t="s">
+      <c r="C79" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="D79" s="60" t="s">
+      <c r="D79" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E79" s="37" t="s">
+      <c r="E79" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="F79" s="36"/>
+      <c r="F79" s="33"/>
       <c r="G79" s="6" t="s">
         <v>241</v>
       </c>
@@ -4366,23 +4390,23 @@
       <c r="J79" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="K79" s="44"/>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K79" s="41"/>
+    </row>
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="B80" s="30"/>
-      <c r="C80" s="31" t="s">
+      <c r="B80" s="27"/>
+      <c r="C80" s="28" t="s">
         <v>354</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E80" s="38" t="s">
+      <c r="E80" s="35" t="s">
         <v>257</v>
       </c>
-      <c r="F80" s="38"/>
+      <c r="F80" s="35"/>
       <c r="G80" s="7" t="s">
         <v>227</v>
       </c>
@@ -4393,23 +4417,23 @@
       <c r="J80" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K80" s="44"/>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K80" s="41"/>
+    </row>
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="B81" s="28"/>
-      <c r="C81" s="29" t="s">
+      <c r="B81" s="25"/>
+      <c r="C81" s="26" t="s">
         <v>355</v>
       </c>
-      <c r="D81" s="60" t="s">
+      <c r="D81" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E81" s="36" t="s">
+      <c r="E81" s="33" t="s">
         <v>267</v>
       </c>
-      <c r="F81" s="36"/>
+      <c r="F81" s="33"/>
       <c r="G81" s="19"/>
       <c r="H81" s="8" t="s">
         <v>167</v>
@@ -4418,25 +4442,25 @@
       <c r="J81" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="K81" s="44"/>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K81" s="41"/>
+    </row>
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="B82" s="28" t="s">
+      <c r="B82" s="25" t="s">
         <v>170</v>
       </c>
-      <c r="C82" s="29" t="s">
+      <c r="C82" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="D82" s="60" t="s">
+      <c r="D82" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E82" s="36" t="s">
+      <c r="E82" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="F82" s="39"/>
+      <c r="F82" s="36"/>
       <c r="G82" s="7"/>
       <c r="H82" s="8" t="s">
         <v>166</v>
@@ -4445,7 +4469,7 @@
       <c r="J82" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="K82" s="44">
+      <c r="K82" s="41">
         <v>10</v>
       </c>
     </row>
@@ -4453,19 +4477,19 @@
       <c r="A83" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="B83" s="28" t="s">
+      <c r="B83" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="C83" s="29" t="s">
+      <c r="C83" s="26" t="s">
         <v>184</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E83" s="36" t="s">
+      <c r="E83" s="33" t="s">
         <v>178</v>
       </c>
-      <c r="F83" s="39"/>
+      <c r="F83" s="36"/>
       <c r="G83" s="7" t="s">
         <v>228</v>
       </c>
@@ -4476,23 +4500,23 @@
       <c r="J83" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="K83" s="44"/>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K83" s="41"/>
+    </row>
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="B84" s="28"/>
-      <c r="C84" s="26" t="s">
+      <c r="B84" s="25"/>
+      <c r="C84" s="23" t="s">
         <v>356</v>
       </c>
-      <c r="D84" s="60" t="s">
+      <c r="D84" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E84" s="36" t="s">
+      <c r="E84" s="33" t="s">
         <v>260</v>
       </c>
-      <c r="F84" s="36"/>
+      <c r="F84" s="33"/>
       <c r="G84" s="19" t="s">
         <v>230</v>
       </c>
@@ -4500,28 +4524,28 @@
         <v>166</v>
       </c>
       <c r="I84" s="9"/>
-      <c r="J84" s="23" t="s">
+      <c r="J84" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="K84" s="48">
+      <c r="K84" s="44">
         <v>4</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A85" s="33" t="s">
+      <c r="A85" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="B85" s="23"/>
-      <c r="C85" s="36" t="s">
+      <c r="B85" s="6"/>
+      <c r="C85" s="33" t="s">
         <v>63</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E85" s="36" t="s">
+      <c r="E85" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="F85" s="39" t="str">
+      <c r="F85" s="36" t="str">
         <f>CONCATENATE("http://", E85)</f>
         <v>http://192.168.0.195</v>
       </c>
@@ -4535,25 +4559,25 @@
       <c r="J85" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K85" s="44" t="s">
+      <c r="K85" s="41" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A86" s="56" t="s">
+      <c r="A86" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="B86" s="23"/>
-      <c r="C86" s="38" t="s">
+      <c r="B86" s="6"/>
+      <c r="C86" s="35" t="s">
         <v>68</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E86" s="38" t="s">
+      <c r="E86" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="F86" s="40" t="str">
+      <c r="F86" s="37" t="str">
         <f>CONCATENATE("http://", E86)</f>
         <v>http://192.168.0.194</v>
       </c>
@@ -4564,53 +4588,53 @@
         <v>167</v>
       </c>
       <c r="I86" s="9"/>
-      <c r="J86" s="38" t="s">
+      <c r="J86" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="K86" s="49" t="s">
+      <c r="K86" s="45" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A87" s="35" t="s">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="32" t="s">
         <v>18</v>
       </c>
       <c r="B87" s="12"/>
-      <c r="C87" s="36" t="s">
+      <c r="C87" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D87" s="60" t="s">
+      <c r="D87" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E87" s="36"/>
-      <c r="F87" s="36"/>
+      <c r="E87" s="33"/>
+      <c r="F87" s="33"/>
       <c r="G87" s="6"/>
       <c r="H87" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I87" s="9"/>
-      <c r="J87" s="36" t="s">
+      <c r="J87" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="K87" s="51" t="s">
+      <c r="K87" s="47" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A88" s="23" t="s">
+      <c r="A88" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="B88" s="33"/>
-      <c r="C88" s="36" t="s">
+      <c r="B88" s="30"/>
+      <c r="C88" s="33" t="s">
         <v>118</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E88" s="36" t="s">
+      <c r="E88" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="F88" s="39" t="str">
+      <c r="F88" s="36" t="str">
         <f>CONCATENATE("http://", E88)</f>
         <v>http://192.168.0.186</v>
       </c>
@@ -4619,28 +4643,28 @@
         <v>166</v>
       </c>
       <c r="I88" s="9"/>
-      <c r="J88" s="36" t="s">
+      <c r="J88" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="K88" s="51" t="s">
+      <c r="K88" s="47" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A89" s="22" t="s">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="B89" s="28"/>
-      <c r="C89" s="29" t="s">
+      <c r="B89" s="25"/>
+      <c r="C89" s="26" t="s">
         <v>357</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E89" s="36" t="s">
+      <c r="E89" s="33" t="s">
         <v>274</v>
       </c>
-      <c r="F89" s="36"/>
+      <c r="F89" s="33"/>
       <c r="G89" s="19" t="s">
         <v>230</v>
       </c>
@@ -4648,26 +4672,26 @@
         <v>166</v>
       </c>
       <c r="I89" s="9"/>
-      <c r="J89" s="36" t="s">
+      <c r="J89" s="33" t="s">
         <v>273</v>
       </c>
-      <c r="K89" s="51"/>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A90" s="28" t="s">
+      <c r="K89" s="47"/>
+    </row>
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="25" t="s">
         <v>272</v>
       </c>
       <c r="B90" s="5"/>
-      <c r="C90" s="29" t="s">
+      <c r="C90" s="26" t="s">
         <v>358</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E90" s="36" t="s">
+      <c r="E90" s="33" t="s">
         <v>275</v>
       </c>
-      <c r="F90" s="36"/>
+      <c r="F90" s="33"/>
       <c r="G90" s="19" t="s">
         <v>230</v>
       </c>
@@ -4675,124 +4699,124 @@
         <v>166</v>
       </c>
       <c r="I90" s="9"/>
-      <c r="J90" s="36" t="s">
+      <c r="J90" s="33" t="s">
         <v>273</v>
       </c>
-      <c r="K90" s="51">
+      <c r="K90" s="47">
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A91" s="22" t="s">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B91" s="28"/>
-      <c r="C91" s="36" t="s">
+      <c r="B91" s="25"/>
+      <c r="C91" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="D91" s="60" t="s">
+      <c r="D91" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E91" s="36"/>
-      <c r="F91" s="36"/>
+      <c r="E91" s="33"/>
+      <c r="F91" s="33"/>
       <c r="G91" s="6"/>
       <c r="H91" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I91" s="9"/>
-      <c r="J91" s="36" t="s">
+      <c r="J91" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="K91" s="51" t="s">
+      <c r="K91" s="47" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A92" s="28" t="s">
+      <c r="A92" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="B92" s="22"/>
-      <c r="C92" s="36" t="s">
+      <c r="B92" s="5"/>
+      <c r="C92" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="D92" s="60" t="s">
+      <c r="D92" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E92" s="36" t="s">
+      <c r="E92" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="F92" s="36"/>
+      <c r="F92" s="33"/>
       <c r="G92" s="6"/>
       <c r="H92" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I92" s="9"/>
-      <c r="J92" s="36" t="s">
+      <c r="J92" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="K92" s="51"/>
+      <c r="K92" s="47"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A93" s="22" t="s">
+      <c r="A93" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B93" s="28" t="s">
+      <c r="B93" s="25" t="s">
         <v>183</v>
       </c>
-      <c r="C93" s="29"/>
-      <c r="D93" s="60" t="s">
+      <c r="C93" s="26"/>
+      <c r="D93" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E93" s="36" t="s">
+      <c r="E93" s="33" t="s">
         <v>182</v>
       </c>
-      <c r="F93" s="39"/>
+      <c r="F93" s="36"/>
       <c r="G93" s="7"/>
       <c r="H93" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I93" s="9"/>
-      <c r="J93" s="29" t="s">
+      <c r="J93" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="K93" s="51"/>
+      <c r="K93" s="47"/>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A94" s="23" t="s">
+      <c r="A94" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B94" s="33"/>
-      <c r="C94" s="36"/>
-      <c r="D94" s="60" t="s">
+      <c r="B94" s="30"/>
+      <c r="C94" s="33"/>
+      <c r="D94" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E94" s="37" t="s">
+      <c r="E94" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="F94" s="36"/>
+      <c r="F94" s="33"/>
       <c r="G94" s="6"/>
       <c r="H94" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I94" s="9"/>
-      <c r="J94" s="36" t="s">
+      <c r="J94" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="K94" s="51"/>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A95" s="28" t="s">
+      <c r="K94" s="47"/>
+    </row>
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="25" t="s">
         <v>246</v>
       </c>
       <c r="B95" s="5"/>
-      <c r="C95" s="29"/>
-      <c r="D95" s="60" t="s">
+      <c r="C95" s="26"/>
+      <c r="D95" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E95" s="37" t="s">
+      <c r="E95" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="F95" s="36"/>
+      <c r="F95" s="33"/>
       <c r="G95" s="19" t="s">
         <v>363</v>
       </c>
@@ -4800,123 +4824,123 @@
         <v>166</v>
       </c>
       <c r="I95" s="9"/>
-      <c r="J95" s="36" t="s">
+      <c r="J95" s="33" t="s">
         <v>244</v>
       </c>
-      <c r="K95" s="51"/>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A96" s="28" t="s">
+      <c r="K95" s="47"/>
+    </row>
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="B96" s="22"/>
-      <c r="C96" s="29"/>
-      <c r="D96" s="60" t="s">
+      <c r="B96" s="5"/>
+      <c r="C96" s="26"/>
+      <c r="D96" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E96" s="36" t="s">
+      <c r="E96" s="33" t="s">
         <v>238</v>
       </c>
-      <c r="F96" s="36"/>
+      <c r="F96" s="33"/>
       <c r="G96" s="19"/>
       <c r="H96" s="8"/>
       <c r="I96" s="9"/>
-      <c r="J96" s="36"/>
-      <c r="K96" s="51"/>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A97" s="28" t="s">
+      <c r="J96" s="33"/>
+      <c r="K96" s="47"/>
+    </row>
+    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="B97" s="22"/>
-      <c r="C97" s="29"/>
-      <c r="D97" s="60" t="s">
+      <c r="B97" s="5"/>
+      <c r="C97" s="26"/>
+      <c r="D97" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E97" s="36" t="s">
+      <c r="E97" s="33" t="s">
         <v>280</v>
       </c>
-      <c r="F97" s="36"/>
+      <c r="F97" s="33"/>
       <c r="G97" s="19"/>
       <c r="H97" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="I97" s="24"/>
-      <c r="J97" s="36"/>
-      <c r="K97" s="51"/>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A98" s="30" t="s">
+      <c r="I97" s="9"/>
+      <c r="J97" s="33"/>
+      <c r="K97" s="47"/>
+    </row>
+    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="27" t="s">
         <v>9</v>
       </c>
       <c r="B98" s="5"/>
-      <c r="C98" s="38"/>
-      <c r="D98" s="60" t="s">
+      <c r="C98" s="35"/>
+      <c r="D98" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E98" s="38" t="s">
+      <c r="E98" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F98" s="38"/>
+      <c r="F98" s="35"/>
       <c r="G98" s="6"/>
       <c r="H98" s="18"/>
       <c r="I98" s="9"/>
-      <c r="J98" s="38" t="s">
+      <c r="J98" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="K98" s="49"/>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A99" s="28" t="s">
+      <c r="K98" s="45"/>
+    </row>
+    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="25" t="s">
         <v>235</v>
       </c>
       <c r="B99" s="5"/>
-      <c r="C99" s="29"/>
-      <c r="D99" s="60" t="s">
+      <c r="C99" s="26"/>
+      <c r="D99" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E99" s="36"/>
-      <c r="F99" s="36"/>
+      <c r="E99" s="33"/>
+      <c r="F99" s="33"/>
       <c r="G99" s="19"/>
       <c r="H99" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I99" s="9"/>
-      <c r="J99" s="36"/>
-      <c r="K99" s="51"/>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A100" s="22" t="s">
+      <c r="J99" s="33"/>
+      <c r="K99" s="47"/>
+    </row>
+    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B100" s="28" t="s">
+      <c r="B100" s="25" t="s">
         <v>161</v>
       </c>
-      <c r="C100" s="29"/>
-      <c r="D100" s="60" t="s">
+      <c r="C100" s="26"/>
+      <c r="D100" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E100" s="36"/>
-      <c r="F100" s="39"/>
+      <c r="E100" s="33"/>
+      <c r="F100" s="36"/>
       <c r="G100" s="7"/>
       <c r="H100" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I100" s="9"/>
-      <c r="J100" s="36"/>
-      <c r="K100" s="51"/>
-    </row>
-    <row r="101" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A101" s="22" t="s">
+      <c r="J100" s="33"/>
+      <c r="K100" s="47"/>
+    </row>
+    <row r="101" spans="1:11" ht="17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="B101" s="28"/>
-      <c r="C101" s="29"/>
-      <c r="D101" s="60" t="s">
+      <c r="B101" s="25"/>
+      <c r="C101" s="26"/>
+      <c r="D101" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E101" s="36"/>
-      <c r="F101" s="39"/>
+      <c r="E101" s="33"/>
+      <c r="F101" s="36"/>
       <c r="G101" s="7"/>
       <c r="H101" s="8" t="s">
         <v>166</v>
@@ -4924,249 +4948,249 @@
       <c r="I101" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="J101" s="36" t="s">
+      <c r="J101" s="33" t="s">
         <v>247</v>
       </c>
-      <c r="K101" s="51"/>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A102" s="33" t="s">
+      <c r="K101" s="47"/>
+    </row>
+    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="30" t="s">
         <v>33</v>
       </c>
       <c r="B102" s="6"/>
-      <c r="C102" s="36"/>
-      <c r="D102" s="60" t="s">
+      <c r="C102" s="33"/>
+      <c r="D102" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E102" s="36"/>
-      <c r="F102" s="36"/>
+      <c r="E102" s="33"/>
+      <c r="F102" s="33"/>
       <c r="G102" s="6"/>
       <c r="H102" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I102" s="9"/>
-      <c r="J102" s="36" t="s">
+      <c r="J102" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="K102" s="51"/>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A103" s="33" t="s">
+      <c r="K102" s="47"/>
+    </row>
+    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="B103" s="23"/>
-      <c r="C103" s="36"/>
-      <c r="D103" s="60" t="s">
+      <c r="B103" s="6"/>
+      <c r="C103" s="33"/>
+      <c r="D103" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E103" s="36"/>
-      <c r="F103" s="36"/>
+      <c r="E103" s="33"/>
+      <c r="F103" s="33"/>
       <c r="G103" s="6"/>
       <c r="H103" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I103" s="9"/>
-      <c r="J103" s="36" t="s">
+      <c r="J103" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="K103" s="51"/>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A104" s="33" t="s">
+      <c r="K103" s="47"/>
+    </row>
+    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="B104" s="23"/>
-      <c r="C104" s="36"/>
-      <c r="D104" s="60" t="s">
+      <c r="B104" s="6"/>
+      <c r="C104" s="33"/>
+      <c r="D104" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E104" s="36"/>
-      <c r="F104" s="36"/>
+      <c r="E104" s="33"/>
+      <c r="F104" s="33"/>
       <c r="G104" s="6"/>
       <c r="H104" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I104" s="9"/>
-      <c r="J104" s="36" t="s">
+      <c r="J104" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="K104" s="51"/>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A105" s="33" t="s">
+      <c r="K104" s="47"/>
+    </row>
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="30" t="s">
         <v>28</v>
       </c>
       <c r="B105" s="6"/>
-      <c r="C105" s="36"/>
-      <c r="D105" s="60" t="s">
+      <c r="C105" s="33"/>
+      <c r="D105" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E105" s="36"/>
-      <c r="F105" s="36"/>
+      <c r="E105" s="33"/>
+      <c r="F105" s="33"/>
       <c r="G105" s="6"/>
       <c r="H105" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I105" s="9"/>
-      <c r="J105" s="36" t="s">
+      <c r="J105" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="K105" s="51"/>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A106" s="33" t="s">
+      <c r="K105" s="47"/>
+    </row>
+    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="30" t="s">
         <v>23</v>
       </c>
       <c r="B106" s="6"/>
-      <c r="C106" s="36"/>
-      <c r="D106" s="60" t="s">
+      <c r="C106" s="33"/>
+      <c r="D106" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E106" s="36"/>
-      <c r="F106" s="36"/>
+      <c r="E106" s="33"/>
+      <c r="F106" s="33"/>
       <c r="G106" s="6"/>
       <c r="H106" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I106" s="9"/>
-      <c r="J106" s="36" t="s">
+      <c r="J106" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="K106" s="51" t="s">
+      <c r="K106" s="47" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A107" s="33" t="s">
+    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="30" t="s">
         <v>31</v>
       </c>
       <c r="B107" s="6"/>
-      <c r="C107" s="36"/>
-      <c r="D107" s="60" t="s">
+      <c r="C107" s="33"/>
+      <c r="D107" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E107" s="36"/>
-      <c r="F107" s="36"/>
+      <c r="E107" s="33"/>
+      <c r="F107" s="33"/>
       <c r="G107" s="6"/>
       <c r="H107" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I107" s="9"/>
-      <c r="J107" s="36" t="s">
+      <c r="J107" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="K107" s="51"/>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A108" s="33" t="s">
+      <c r="K107" s="47"/>
+    </row>
+    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="30" t="s">
         <v>25</v>
       </c>
       <c r="B108" s="6"/>
-      <c r="C108" s="36"/>
-      <c r="D108" s="60" t="s">
+      <c r="C108" s="33"/>
+      <c r="D108" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E108" s="36"/>
-      <c r="F108" s="36"/>
+      <c r="E108" s="33"/>
+      <c r="F108" s="33"/>
       <c r="G108" s="6"/>
       <c r="H108" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I108" s="9"/>
-      <c r="J108" s="36" t="s">
+      <c r="J108" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="K108" s="51"/>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A109" s="33" t="s">
+      <c r="K108" s="47"/>
+    </row>
+    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="30" t="s">
         <v>30</v>
       </c>
       <c r="B109" s="6"/>
-      <c r="C109" s="36"/>
-      <c r="D109" s="60" t="s">
+      <c r="C109" s="33"/>
+      <c r="D109" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E109" s="36"/>
-      <c r="F109" s="36"/>
+      <c r="E109" s="33"/>
+      <c r="F109" s="33"/>
       <c r="G109" s="6"/>
       <c r="H109" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I109" s="9"/>
-      <c r="J109" s="36" t="s">
+      <c r="J109" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="K109" s="51"/>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A110" s="33" t="s">
+      <c r="K109" s="47"/>
+    </row>
+    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B110" s="6"/>
-      <c r="C110" s="36"/>
-      <c r="D110" s="60" t="s">
+      <c r="C110" s="33"/>
+      <c r="D110" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E110" s="36"/>
-      <c r="F110" s="36"/>
+      <c r="E110" s="33"/>
+      <c r="F110" s="33"/>
       <c r="G110" s="6"/>
       <c r="H110" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I110" s="9"/>
-      <c r="J110" s="36" t="s">
+      <c r="J110" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="K110" s="51"/>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A111" s="23" t="s">
+      <c r="K110" s="47"/>
+    </row>
+    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C111" s="22"/>
-      <c r="D111" s="60" t="s">
+      <c r="C111" s="5"/>
+      <c r="D111" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E111" s="23"/>
-      <c r="F111" s="23"/>
+      <c r="E111" s="6"/>
+      <c r="F111" s="6"/>
       <c r="G111" s="7"/>
       <c r="H111" s="18" t="s">
         <v>167</v>
       </c>
       <c r="I111" s="9"/>
-      <c r="J111" s="38" t="s">
+      <c r="J111" s="35" t="s">
         <v>213</v>
       </c>
-      <c r="K111" s="49"/>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A112" s="23" t="s">
+      <c r="K111" s="45"/>
+    </row>
+    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="6" t="s">
         <v>38</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C112" s="22"/>
-      <c r="D112" s="60" t="s">
+      <c r="C112" s="5"/>
+      <c r="D112" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E112" s="23"/>
-      <c r="F112" s="23"/>
+      <c r="E112" s="6"/>
+      <c r="F112" s="6"/>
       <c r="G112" s="7"/>
       <c r="H112" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I112" s="9"/>
-      <c r="J112" s="42" t="s">
+      <c r="J112" s="39" t="s">
         <v>213</v>
       </c>
-      <c r="K112" s="51"/>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K112" s="47"/>
+    </row>
+    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="5"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -5176,10 +5200,10 @@
       <c r="G113" s="7"/>
       <c r="H113" s="8"/>
       <c r="I113" s="9"/>
-      <c r="J113" s="29"/>
-      <c r="K113" s="50"/>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J113" s="26"/>
+      <c r="K113" s="46"/>
+    </row>
+    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="5"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -5189,10 +5213,10 @@
       <c r="G114" s="7"/>
       <c r="H114" s="8"/>
       <c r="I114" s="9"/>
-      <c r="J114" s="26"/>
-      <c r="K114" s="52"/>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J114" s="23"/>
+      <c r="K114" s="48"/>
+    </row>
+    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="5"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -5202,10 +5226,10 @@
       <c r="G115" s="7"/>
       <c r="H115" s="8"/>
       <c r="I115" s="9"/>
-      <c r="J115" s="29"/>
-      <c r="K115" s="50"/>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J115" s="26"/>
+      <c r="K115" s="46"/>
+    </row>
+    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="5"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -5215,10 +5239,10 @@
       <c r="G116" s="7"/>
       <c r="H116" s="8"/>
       <c r="I116" s="9"/>
-      <c r="J116" s="26"/>
-      <c r="K116" s="52"/>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J116" s="23"/>
+      <c r="K116" s="48"/>
+    </row>
+    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="5"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -5228,10 +5252,10 @@
       <c r="G117" s="7"/>
       <c r="H117" s="8"/>
       <c r="I117" s="9"/>
-      <c r="J117" s="29"/>
-      <c r="K117" s="50"/>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J117" s="26"/>
+      <c r="K117" s="46"/>
+    </row>
+    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="5"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -5241,10 +5265,10 @@
       <c r="G118" s="7"/>
       <c r="H118" s="8"/>
       <c r="I118" s="9"/>
-      <c r="J118" s="26"/>
-      <c r="K118" s="52"/>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J118" s="23"/>
+      <c r="K118" s="48"/>
+    </row>
+    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="5"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -5254,23 +5278,23 @@
       <c r="G119" s="7"/>
       <c r="H119" s="8"/>
       <c r="I119" s="9"/>
-      <c r="J119" s="29"/>
-      <c r="K119" s="50"/>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A120" s="22"/>
-      <c r="B120" s="22"/>
-      <c r="C120" s="22"/>
-      <c r="D120" s="23"/>
-      <c r="E120" s="23"/>
-      <c r="F120" s="23"/>
+      <c r="J119" s="26"/>
+      <c r="K119" s="46"/>
+    </row>
+    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="5"/>
+      <c r="B120" s="5"/>
+      <c r="C120" s="5"/>
+      <c r="D120" s="6"/>
+      <c r="E120" s="6"/>
+      <c r="F120" s="6"/>
       <c r="G120" s="19"/>
       <c r="H120" s="18"/>
-      <c r="I120" s="24"/>
-      <c r="J120" s="27"/>
-      <c r="K120" s="53"/>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I120" s="9"/>
+      <c r="J120" s="24"/>
+      <c r="K120" s="49"/>
+    </row>
+    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="5"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -5280,10 +5304,10 @@
       <c r="G121" s="7"/>
       <c r="H121" s="8"/>
       <c r="I121" s="9"/>
-      <c r="J121" s="29"/>
-      <c r="K121" s="50"/>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J121" s="26"/>
+      <c r="K121" s="46"/>
+    </row>
+    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="5"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -5293,10 +5317,10 @@
       <c r="G122" s="7"/>
       <c r="H122" s="8"/>
       <c r="I122" s="9"/>
-      <c r="J122" s="26"/>
-      <c r="K122" s="52"/>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J122" s="23"/>
+      <c r="K122" s="48"/>
+    </row>
+    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="5"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -5306,10 +5330,10 @@
       <c r="G123" s="7"/>
       <c r="H123" s="8"/>
       <c r="I123" s="9"/>
-      <c r="J123" s="29"/>
-      <c r="K123" s="50"/>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J123" s="26"/>
+      <c r="K123" s="46"/>
+    </row>
+    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="5"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -5319,10 +5343,10 @@
       <c r="G124" s="7"/>
       <c r="H124" s="8"/>
       <c r="I124" s="9"/>
-      <c r="J124" s="26"/>
-      <c r="K124" s="52"/>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J124" s="23"/>
+      <c r="K124" s="48"/>
+    </row>
+    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="5"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -5332,10 +5356,10 @@
       <c r="G125" s="7"/>
       <c r="H125" s="8"/>
       <c r="I125" s="9"/>
-      <c r="J125" s="29"/>
-      <c r="K125" s="50"/>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J125" s="26"/>
+      <c r="K125" s="46"/>
+    </row>
+    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="5"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -5345,10 +5369,10 @@
       <c r="G126" s="7"/>
       <c r="H126" s="8"/>
       <c r="I126" s="9"/>
-      <c r="J126" s="26"/>
-      <c r="K126" s="52"/>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J126" s="23"/>
+      <c r="K126" s="48"/>
+    </row>
+    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="5"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -5358,23 +5382,23 @@
       <c r="G127" s="7"/>
       <c r="H127" s="8"/>
       <c r="I127" s="9"/>
-      <c r="J127" s="29"/>
-      <c r="K127" s="50"/>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A128" s="22"/>
-      <c r="B128" s="22"/>
-      <c r="C128" s="22"/>
-      <c r="D128" s="23"/>
-      <c r="E128" s="23"/>
-      <c r="F128" s="23"/>
+      <c r="J127" s="26"/>
+      <c r="K127" s="46"/>
+    </row>
+    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="5"/>
+      <c r="B128" s="5"/>
+      <c r="C128" s="5"/>
+      <c r="D128" s="6"/>
+      <c r="E128" s="6"/>
+      <c r="F128" s="6"/>
       <c r="G128" s="19"/>
       <c r="H128" s="18"/>
-      <c r="I128" s="24"/>
-      <c r="J128" s="27"/>
-      <c r="K128" s="53"/>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I128" s="9"/>
+      <c r="J128" s="24"/>
+      <c r="K128" s="49"/>
+    </row>
+    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="5"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -5384,10 +5408,10 @@
       <c r="G129" s="7"/>
       <c r="H129" s="8"/>
       <c r="I129" s="9"/>
-      <c r="J129" s="29"/>
-      <c r="K129" s="50"/>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J129" s="26"/>
+      <c r="K129" s="46"/>
+    </row>
+    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -5397,21 +5421,21 @@
       <c r="G130" s="7"/>
       <c r="H130" s="8"/>
       <c r="I130" s="9"/>
-      <c r="J130" s="26"/>
-      <c r="K130" s="52"/>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A131" s="22"/>
-      <c r="B131" s="22"/>
-      <c r="C131" s="22"/>
-      <c r="D131" s="23"/>
-      <c r="E131" s="23"/>
-      <c r="F131" s="23"/>
+      <c r="J130" s="23"/>
+      <c r="K130" s="48"/>
+    </row>
+    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="5"/>
+      <c r="B131" s="5"/>
+      <c r="C131" s="5"/>
+      <c r="D131" s="6"/>
+      <c r="E131" s="6"/>
+      <c r="F131" s="6"/>
       <c r="G131" s="19"/>
       <c r="H131" s="18"/>
-      <c r="I131" s="24"/>
-      <c r="J131" s="31"/>
-      <c r="K131" s="54"/>
+      <c r="I131" s="9"/>
+      <c r="J131" s="28"/>
+      <c r="K131" s="50"/>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H132"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9C1C04-0C35-2340-B8FA-73CABF26C156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{538832C3-E8E8-C249-9893-1081B677E08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1880" yWindow="2960" windowWidth="28360" windowHeight="16680" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">network!$A$1:$K$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">network!$A$1:$K$38</definedName>
     <definedName name="taxrate">'[1]mixer costs'!$I$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="392">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -947,9 +947,6 @@
     <t>AV Network</t>
   </si>
   <si>
-    <t>AV Amp 2603-1200</t>
-  </si>
-  <si>
     <t>192.168.200.102</t>
   </si>
   <si>
@@ -998,96 +995,33 @@
     <t>192.168.201.100</t>
   </si>
   <si>
-    <t>AV Balcony 2603-1203</t>
-  </si>
-  <si>
     <t>192.168.201.101</t>
   </si>
   <si>
-    <t>klang-KRB14486</t>
-  </si>
-  <si>
     <t>192.168.200.199</t>
   </si>
   <si>
-    <t>klang-KRB14514</t>
-  </si>
-  <si>
     <t>192.168.200.123</t>
   </si>
   <si>
-    <t>klang-KRB14506</t>
-  </si>
-  <si>
-    <t>192.168.200.149</t>
-  </si>
-  <si>
-    <t>klang-KRB14070</t>
-  </si>
-  <si>
     <t>192.168.200.150</t>
   </si>
   <si>
-    <t>klang-KRB14513</t>
-  </si>
-  <si>
     <t>192.168.200.100</t>
   </si>
   <si>
-    <t>klang-KRB14510</t>
-  </si>
-  <si>
-    <t>192.168.200.147</t>
-  </si>
-  <si>
-    <t>klang-KRB14415</t>
-  </si>
-  <si>
     <t>192.168.200.138</t>
   </si>
   <si>
-    <t>klang-KRB14512</t>
-  </si>
-  <si>
     <t>192.168.200.130</t>
   </si>
   <si>
-    <t>klang-KRB14072</t>
-  </si>
-  <si>
     <t>192.168.200.148</t>
   </si>
   <si>
     <t>00:04:C4:0F:E3:C3</t>
   </si>
   <si>
-    <t>00:04:C4:31:28:1A</t>
-  </si>
-  <si>
-    <t>00:04:C4:31:28:1C</t>
-  </si>
-  <si>
-    <t>00:04:C4:31:29:73</t>
-  </si>
-  <si>
-    <t>00:04:C4:31:29:BA</t>
-  </si>
-  <si>
-    <t>00:04:C4:31:29:CE</t>
-  </si>
-  <si>
-    <t>00:04:C4:31:29:D2</t>
-  </si>
-  <si>
-    <t>00:04:C4:31:29:D4</t>
-  </si>
-  <si>
-    <t>00:04:C4:31:29:D5</t>
-  </si>
-  <si>
-    <t>00:04:C4:31:29:D6</t>
-  </si>
-  <si>
     <t>00:0C:15:06:B9:31</t>
   </si>
   <si>
@@ -1193,9 +1127,6 @@
     <t>avio-videomixer 11</t>
   </si>
   <si>
-    <t>unknown</t>
-  </si>
-  <si>
     <t>Dante 1</t>
   </si>
   <si>
@@ -1215,13 +1146,139 @@
   </si>
   <si>
     <t>cuecommander:1880, companion:8000, media_arts_home:80</t>
+  </si>
+  <si>
+    <t>2510-0401</t>
+  </si>
+  <si>
+    <t>2510-0402</t>
+  </si>
+  <si>
+    <t>2510-0403</t>
+  </si>
+  <si>
+    <t>2510-0411</t>
+  </si>
+  <si>
+    <t>2510-0405</t>
+  </si>
+  <si>
+    <t>2510-0406</t>
+  </si>
+  <si>
+    <t>2510-0407</t>
+  </si>
+  <si>
+    <t>2510-0408</t>
+  </si>
+  <si>
+    <t>2510-0409</t>
+  </si>
+  <si>
+    <t>2510-0410</t>
+  </si>
+  <si>
+    <t>Klang Kontroller</t>
+  </si>
+  <si>
+    <t>00-04-C4-31-29-D2</t>
+  </si>
+  <si>
+    <t>00-04-C4-31-29-D5</t>
+  </si>
+  <si>
+    <t>00-04-C4-31-29-D4</t>
+  </si>
+  <si>
+    <t>00-04-C4-31-28-1A</t>
+  </si>
+  <si>
+    <t>00-04-C4-31-28-1C</t>
+  </si>
+  <si>
+    <t>00-04-C4-31-29-73</t>
+  </si>
+  <si>
+    <t>00-04-C4-31-29-BA</t>
+  </si>
+  <si>
+    <t>00-04-C4-31-29-CE</t>
+  </si>
+  <si>
+    <t>00-04-C4-31-29-D6</t>
+  </si>
+  <si>
+    <t>192.168.200.151</t>
+  </si>
+  <si>
+    <t>192.168.200.157</t>
+  </si>
+  <si>
+    <t>notag20</t>
+  </si>
+  <si>
+    <t>notag26</t>
+  </si>
+  <si>
+    <t>notag33</t>
+  </si>
+  <si>
+    <t>notag34</t>
+  </si>
+  <si>
+    <t>notag35</t>
+  </si>
+  <si>
+    <t>notag36</t>
+  </si>
+  <si>
+    <t>notag37</t>
+  </si>
+  <si>
+    <t>notag38</t>
+  </si>
+  <si>
+    <t>notag39</t>
+  </si>
+  <si>
+    <t>notag40</t>
+  </si>
+  <si>
+    <t>notag41</t>
+  </si>
+  <si>
+    <t>notag42</t>
+  </si>
+  <si>
+    <t>notag43</t>
+  </si>
+  <si>
+    <t>notag44</t>
+  </si>
+  <si>
+    <t>notag45</t>
+  </si>
+  <si>
+    <t>pending93</t>
+  </si>
+  <si>
+    <t>pending100</t>
+  </si>
+  <si>
+    <t>dante_control</t>
+  </si>
+  <si>
+    <t>192.168.200.105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00-04-C4-31-29-CF </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1313,6 +1370,19 @@
       <color rgb="FF000000"/>
       <name val="Calibri Light"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1491,7 +1561,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1575,6 +1645,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1859,46 +1936,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K131" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K131" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="192.168.0.103"/>
-        <filter val="192.168.0.122"/>
-        <filter val="192.168.0.130"/>
-        <filter val="192.168.0.145"/>
-        <filter val="192.168.0.180"/>
-        <filter val="192.168.0.181"/>
-        <filter val="192.168.0.183"/>
-        <filter val="192.168.0.185"/>
-        <filter val="192.168.0.186"/>
-        <filter val="192.168.0.187"/>
-        <filter val="192.168.0.188"/>
-        <filter val="192.168.0.189"/>
-        <filter val="192.168.0.190"/>
-        <filter val="192.168.0.191"/>
-        <filter val="192.168.0.192"/>
-        <filter val="192.168.0.193"/>
-        <filter val="192.168.0.194"/>
-        <filter val="192.168.0.195"/>
-        <filter val="192.168.0.197"/>
-        <filter val="192.168.0.201"/>
-        <filter val="192.168.0.202"/>
-        <filter val="192.168.0.207"/>
-        <filter val="192.168.0.208"/>
-        <filter val="192.168.0.210"/>
-        <filter val="192.168.0.22"/>
-        <filter val="192.168.0.23"/>
-        <filter val="192.168.0.239"/>
-        <filter val="192.168.0.24"/>
-        <filter val="192.168.0.25"/>
-        <filter val="192.168.0.26"/>
-        <filter val="192.168.0.53"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K131">
-    <sortCondition ref="C2:C131"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K135" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K135" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K132">
+    <sortCondition ref="C2:C132"/>
   </sortState>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{EF2C341F-E5C1-604C-942C-FB7E9F76F1CD}" name="AssetTag" dataDxfId="10"/>
@@ -2214,7 +2255,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC7A309-0B6A-4549-9590-6CFCF97D2DB0}">
-  <dimension ref="A1:K1718"/>
+  <dimension ref="A1:K1719"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
@@ -2267,13 +2308,13 @@
         <v>138</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>237</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>100</v>
@@ -2294,7 +2335,7 @@
       </c>
       <c r="K2" s="41"/>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>189</v>
       </c>
@@ -2321,7 +2362,7 @@
       </c>
       <c r="K3" s="41"/>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>189</v>
       </c>
@@ -2346,7 +2387,7 @@
       </c>
       <c r="K4" s="41"/>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>208</v>
       </c>
@@ -2373,7 +2414,7 @@
       </c>
       <c r="K5" s="41"/>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>208</v>
       </c>
@@ -2398,7 +2439,7 @@
       </c>
       <c r="K6" s="41"/>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>215</v>
       </c>
@@ -2427,7 +2468,7 @@
       </c>
       <c r="K7" s="41"/>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>215</v>
       </c>
@@ -2452,7 +2493,7 @@
       </c>
       <c r="K8" s="41"/>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>214</v>
       </c>
@@ -2479,7 +2520,7 @@
       </c>
       <c r="K9" s="41"/>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>214</v>
       </c>
@@ -2504,19 +2545,21 @@
       </c>
       <c r="K10" s="41"/>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="29" t="s">
-        <v>308</v>
-      </c>
-      <c r="B11" s="5"/>
+        <v>357</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>389</v>
+      </c>
       <c r="C11" s="29" t="s">
-        <v>321</v>
+        <v>364</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="F11" s="29" t="s">
         <v>282</v>
@@ -2524,28 +2567,30 @@
       <c r="G11" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="H11" s="8"/>
+      <c r="H11" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I11" s="9"/>
       <c r="J11" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="K11" s="44">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+        <v>360</v>
+      </c>
+      <c r="K11" s="44"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="B12" s="5"/>
+        <v>358</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>389</v>
+      </c>
       <c r="C12" s="5" t="s">
-        <v>322</v>
+        <v>365</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>282</v>
@@ -2553,57 +2598,59 @@
       <c r="G12" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="H12" s="8"/>
+      <c r="H12" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I12" s="9"/>
-      <c r="J12" s="29" t="s">
-        <v>300</v>
-      </c>
-      <c r="K12" s="43">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="J12" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="K12" s="43"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="B13" s="5"/>
+        <v>354</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>389</v>
+      </c>
       <c r="C13" s="5" t="s">
-        <v>323</v>
+        <v>391</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>282</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="F13" s="5"/>
       <c r="G13" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="H13" s="8"/>
+      <c r="H13" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I13" s="9"/>
-      <c r="J13" s="29" t="s">
-        <v>283</v>
-      </c>
-      <c r="K13" s="43">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="J13" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="K13" s="43"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="B14" s="5"/>
+        <v>355</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>389</v>
+      </c>
       <c r="C14" s="5" t="s">
-        <v>324</v>
+        <v>366</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>282</v>
@@ -2611,28 +2658,30 @@
       <c r="G14" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="H14" s="8"/>
+      <c r="H14" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I14" s="9"/>
-      <c r="J14" s="29" t="s">
-        <v>283</v>
-      </c>
-      <c r="K14" s="43">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="J14" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="K14" s="43"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B15" s="5"/>
+        <v>353</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>389</v>
+      </c>
       <c r="C15" s="5" t="s">
-        <v>325</v>
+        <v>367</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>282</v>
@@ -2640,57 +2689,61 @@
       <c r="G15" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="H15" s="8"/>
+      <c r="H15" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I15" s="9"/>
-      <c r="J15" s="29" t="s">
-        <v>283</v>
-      </c>
-      <c r="K15" s="43">
+      <c r="J15" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="K15" s="43"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="29" t="s">
-        <v>312</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="29" t="s">
-        <v>326</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16" s="29" t="s">
-        <v>313</v>
-      </c>
-      <c r="F16" s="29" t="s">
+      <c r="E16" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>282</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="H16" s="8"/>
+      <c r="H16" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I16" s="9"/>
       <c r="J16" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="K16" s="44">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+        <v>360</v>
+      </c>
+      <c r="K16" s="43"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="29" t="s">
-        <v>316</v>
-      </c>
-      <c r="B17" s="5"/>
+        <v>350</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>389</v>
+      </c>
       <c r="C17" s="29" t="s">
-        <v>327</v>
+        <v>361</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>317</v>
+        <v>370</v>
       </c>
       <c r="F17" s="29" t="s">
         <v>282</v>
@@ -2698,136 +2751,144 @@
       <c r="G17" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="H17" s="8"/>
+      <c r="H17" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I17" s="9"/>
       <c r="J17" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="K17" s="44">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5" t="s">
-        <v>328</v>
+        <v>360</v>
+      </c>
+      <c r="K17" s="44"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="29" t="s">
+        <v>352</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>363</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="F18" s="5" t="s">
+      <c r="E18" s="29" t="s">
+        <v>305</v>
+      </c>
+      <c r="F18" s="29" t="s">
         <v>282</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="H18" s="8"/>
+      <c r="H18" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I18" s="9"/>
-      <c r="J18" s="29" t="s">
-        <v>283</v>
-      </c>
-      <c r="K18" s="43">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="29" t="s">
-        <v>304</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="29" t="s">
-        <v>329</v>
+      <c r="J18" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="K18" s="44"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>362</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E19" s="29" t="s">
-        <v>305</v>
-      </c>
-      <c r="F19" s="29" t="s">
+      <c r="E19" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>282</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="H19" s="8"/>
+      <c r="H19" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I19" s="9"/>
       <c r="J19" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="K19" s="44">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="5"/>
-      <c r="B20" s="29"/>
+        <v>360</v>
+      </c>
+      <c r="K19" s="43"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="29" t="s">
+        <v>359</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>389</v>
+      </c>
       <c r="C20" s="29" t="s">
-        <v>330</v>
+        <v>369</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E20" s="29" t="s">
+        <v>301</v>
+      </c>
+      <c r="F20" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I20" s="9"/>
+      <c r="J20" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="K20" s="44"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29" t="s">
+        <v>308</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>292</v>
+      </c>
+      <c r="F21" s="29" t="s">
         <v>293</v>
       </c>
-      <c r="F20" s="29" t="s">
-        <v>294</v>
-      </c>
-      <c r="G20" s="7"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="41"/>
-    </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
+      <c r="G21" s="7"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="41"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="K21" s="41" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
-        <v>45</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="20" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
@@ -2844,19 +2905,19 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="20" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
@@ -2873,19 +2934,19 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
@@ -2904,126 +2965,128 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>137</v>
+        <v>49</v>
       </c>
       <c r="B25" s="6"/>
-      <c r="C25" s="11" t="s">
-        <v>135</v>
+      <c r="C25" s="20" t="s">
+        <v>48</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>134</v>
+        <v>250</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="I25" s="9"/>
+      <c r="I25" s="9" t="s">
+        <v>264</v>
+      </c>
       <c r="J25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K25" s="41" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I26" s="9"/>
+      <c r="J26" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="K25" s="42" t="s">
+      <c r="K26" s="42" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5" t="s">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D27" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="41" t="s">
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="41" t="s">
         <v>269</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="F27" s="19" t="str">
-        <f>CONCATENATE("http://", E27)</f>
-        <v>http://192.168.201.110</v>
-      </c>
-      <c r="G27" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="I27" s="9"/>
-      <c r="J27" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="K27" s="42">
-        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>190</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>40</v>
+        <v>309</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
+        <v>270</v>
+      </c>
+      <c r="F28" s="19" t="str">
+        <f>CONCATENATE("http://", E28)</f>
+        <v>http://192.168.201.110</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>230</v>
+      </c>
       <c r="H28" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I28" s="9"/>
       <c r="J28" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K28" s="41" t="s">
-        <v>248</v>
+        <v>92</v>
+      </c>
+      <c r="K28" s="42">
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>190</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
@@ -3038,46 +3101,48 @@
         <v>248</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5" t="s">
-        <v>5</v>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>224</v>
+        <v>34</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="K30" s="41"/>
-    </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>190</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="K30" s="41" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="5"/>
       <c r="C31" s="5" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>196</v>
+        <v>224</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
@@ -3085,24 +3150,26 @@
         <v>166</v>
       </c>
       <c r="I31" s="9"/>
-      <c r="J31" s="5" t="s">
-        <v>364</v>
+      <c r="J31" s="6" t="s">
+        <v>343</v>
       </c>
       <c r="K31" s="41"/>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="B32" s="5"/>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>190</v>
+      </c>
       <c r="C32" s="5" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
@@ -3110,87 +3177,95 @@
         <v>166</v>
       </c>
       <c r="I32" s="9"/>
-      <c r="J32" s="6">
-        <v>30</v>
+      <c r="J32" s="5" t="s">
+        <v>342</v>
       </c>
       <c r="K32" s="41"/>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="5"/>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>221</v>
+      </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5" t="s">
-        <v>332</v>
+        <v>223</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="G33" s="7"/>
-      <c r="H33" s="8"/>
+      <c r="E33" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I33" s="9"/>
-      <c r="J33" s="6"/>
+      <c r="J33" s="6">
+        <v>30</v>
+      </c>
       <c r="K33" s="41"/>
     </row>
-    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="5"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="29" t="s">
-        <v>333</v>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5" t="s">
+        <v>310</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E34" s="29" t="s">
-        <v>290</v>
-      </c>
-      <c r="F34" s="29" t="s">
+      <c r="E34" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="F34" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="G34" s="19"/>
+      <c r="G34" s="7"/>
       <c r="H34" s="8"/>
       <c r="I34" s="9"/>
       <c r="J34" s="6"/>
       <c r="K34" s="41"/>
     </row>
-    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="5"/>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
+        <v>375</v>
+      </c>
       <c r="B35" s="29"/>
       <c r="C35" s="29" t="s">
-        <v>334</v>
+        <v>311</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F35" s="29" t="s">
         <v>282</v>
       </c>
-      <c r="G35" s="7"/>
+      <c r="G35" s="19"/>
       <c r="H35" s="8"/>
       <c r="I35" s="9"/>
       <c r="J35" s="6"/>
       <c r="K35" s="41"/>
     </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="B36" s="29"/>
       <c r="C36" s="29" t="s">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F36" s="29" t="s">
         <v>282</v>
@@ -3201,17 +3276,19 @@
       <c r="J36" s="6"/>
       <c r="K36" s="41"/>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="5"/>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37" s="5" t="s">
+        <v>377</v>
+      </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29" t="s">
-        <v>336</v>
+        <v>313</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="F37" s="29" t="s">
         <v>282</v>
@@ -3220,21 +3297,21 @@
       <c r="H37" s="8"/>
       <c r="I37" s="9"/>
       <c r="J37" s="6"/>
-      <c r="K37" s="41" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="5"/>
+      <c r="K37" s="41"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" s="5" t="s">
+        <v>378</v>
+      </c>
       <c r="B38" s="29"/>
       <c r="C38" s="29" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F38" s="29" t="s">
         <v>282</v>
@@ -3244,20 +3321,22 @@
       <c r="I38" s="9"/>
       <c r="J38" s="6"/>
       <c r="K38" s="41" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="5"/>
+        <v>348</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A39" s="5" t="s">
+        <v>379</v>
+      </c>
       <c r="B39" s="29"/>
       <c r="C39" s="29" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F39" s="29" t="s">
         <v>282</v>
@@ -3267,22 +3346,24 @@
       <c r="I39" s="9"/>
       <c r="J39" s="6"/>
       <c r="K39" s="41" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5" t="s">
-        <v>339</v>
+        <v>348</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29" t="s">
+        <v>316</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="F40" s="5" t="s">
+      <c r="E40" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="F40" s="29" t="s">
         <v>282</v>
       </c>
       <c r="G40" s="7"/>
@@ -3290,20 +3371,22 @@
       <c r="I40" s="9"/>
       <c r="J40" s="6"/>
       <c r="K40" s="41" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="5"/>
+        <v>348</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" s="5" t="s">
+        <v>381</v>
+      </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
-        <v>340</v>
+        <v>317</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>282</v>
@@ -3313,20 +3396,22 @@
       <c r="I41" s="9"/>
       <c r="J41" s="6"/>
       <c r="K41" s="41" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="5"/>
+        <v>348</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" s="5" t="s">
+        <v>382</v>
+      </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>282</v>
@@ -3336,20 +3421,22 @@
       <c r="I42" s="9"/>
       <c r="J42" s="6"/>
       <c r="K42" s="41" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="5"/>
+        <v>348</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" s="5" t="s">
+        <v>383</v>
+      </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>282</v>
@@ -3359,22 +3446,24 @@
       <c r="I43" s="9"/>
       <c r="J43" s="6"/>
       <c r="K43" s="41" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="5"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="29" t="s">
-        <v>343</v>
+        <v>348</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5" t="s">
+        <v>320</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E44" s="29" t="s">
-        <v>285</v>
-      </c>
-      <c r="F44" s="29" t="s">
+      <c r="E44" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="F44" s="5" t="s">
         <v>282</v>
       </c>
       <c r="G44" s="7"/>
@@ -3382,79 +3471,76 @@
       <c r="I44" s="9"/>
       <c r="J44" s="6"/>
       <c r="K44" s="41" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="5"/>
+        <v>348</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A45" s="5" t="s">
+        <v>385</v>
+      </c>
       <c r="B45" s="29"/>
       <c r="C45" s="29" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E45" s="29" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F45" s="29" t="s">
         <v>282</v>
       </c>
-      <c r="G45" s="19"/>
+      <c r="G45" s="7"/>
       <c r="H45" s="8"/>
       <c r="I45" s="9"/>
       <c r="J45" s="6"/>
       <c r="K45" s="41" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A46" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6" t="s">
-        <v>106</v>
+      <c r="A46" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29" t="s">
+        <v>322</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E46" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="F46" s="7" t="str">
-        <f>CONCATENATE("http://", E46)</f>
-        <v>http://192.168.0.180</v>
-      </c>
-      <c r="G46" s="7"/>
-      <c r="H46" s="8" t="s">
-        <v>167</v>
-      </c>
+      <c r="E46" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="F46" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="G46" s="19"/>
+      <c r="H46" s="8"/>
       <c r="I46" s="9"/>
-      <c r="J46" s="6" t="s">
-        <v>107</v>
-      </c>
+      <c r="J46" s="6"/>
       <c r="K46" s="41" t="s">
-        <v>104</v>
+        <v>348</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F47" s="7" t="str">
         <f>CONCATENATE("http://", E47)</f>
-        <v>http://192.168.0.181</v>
+        <v>http://192.168.0.180</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="8" t="s">
@@ -3462,29 +3548,29 @@
       </c>
       <c r="I47" s="9"/>
       <c r="J47" s="6" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="K47" s="41" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="F48" s="7" t="str">
         <f>CONCATENATE("http://", E48)</f>
-        <v>http://192.168.0.192</v>
+        <v>http://192.168.0.181</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="8" t="s">
@@ -3492,113 +3578,113 @@
       </c>
       <c r="I48" s="9"/>
       <c r="J48" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="K48" s="42" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="B49" s="5"/>
+        <v>102</v>
+      </c>
+      <c r="K48" s="41" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A49" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B49" s="6"/>
       <c r="C49" s="6" t="s">
-        <v>232</v>
+        <v>84</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="F49" s="6"/>
-      <c r="G49" s="19" t="s">
-        <v>230</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="F49" s="7" t="str">
+        <f>CONCATENATE("http://", E49)</f>
+        <v>http://192.168.0.192</v>
+      </c>
+      <c r="G49" s="7"/>
       <c r="H49" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="K49" s="41">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="5" t="s">
-        <v>201</v>
+        <v>85</v>
+      </c>
+      <c r="K49" s="42" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A50" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="6" t="s">
+        <v>232</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="F50" s="6"/>
-      <c r="G50" s="6" t="s">
+      <c r="G50" s="19" t="s">
         <v>230</v>
       </c>
       <c r="H50" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I50" s="9"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="41"/>
+      <c r="J50" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="K50" s="41">
+        <v>22</v>
+      </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A51" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6" t="s">
-        <v>129</v>
+      <c r="A51" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="B51" s="13"/>
+      <c r="C51" s="5" t="s">
+        <v>201</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="F51" s="7" t="str">
-        <f>CONCATENATE("http://", E51)</f>
-        <v>http://192.168.0.23</v>
-      </c>
-      <c r="G51" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6" t="s">
         <v>230</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I51" s="9"/>
-      <c r="J51" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="K51" s="42"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="41"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F52" s="7" t="str">
         <f>CONCATENATE("http://", E52)</f>
-        <v>http://192.168.0.22</v>
+        <v>http://192.168.0.23</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>230</v>
@@ -3612,76 +3698,76 @@
       </c>
       <c r="K52" s="42"/>
     </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
-        <v>130</v>
+        <v>2</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6" t="s">
         <v>132</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E53" s="6"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F53" s="7" t="str">
+        <f>CONCATENATE("http://", E53)</f>
+        <v>http://192.168.0.22</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H53" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="6" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="K53" s="42"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F54" s="7" t="str">
-        <f>CONCATENATE("http://", E54)</f>
-        <v>http://192.168.0.24</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>230</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E54" s="6"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="7"/>
       <c r="H54" s="18" t="s">
         <v>167</v>
       </c>
       <c r="I54" s="9"/>
       <c r="J54" s="6" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="K54" s="42"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E55" s="14" t="s">
-        <v>124</v>
+      <c r="E55" s="6" t="s">
+        <v>126</v>
       </c>
       <c r="F55" s="7" t="str">
         <f>CONCATENATE("http://", E55)</f>
-        <v>http://192.168.0.25</v>
+        <v>http://192.168.0.24</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>230</v>
@@ -3693,25 +3779,25 @@
       <c r="J55" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="K55" s="41"/>
+      <c r="K55" s="42"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E56" s="6" t="s">
-        <v>121</v>
+      <c r="E56" s="14" t="s">
+        <v>124</v>
       </c>
       <c r="F56" s="7" t="str">
         <f>CONCATENATE("http://", E56)</f>
-        <v>http://192.168.0.26</v>
+        <v>http://192.168.0.25</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>230</v>
@@ -3723,364 +3809,365 @@
       <c r="J56" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="K56" s="42"/>
+      <c r="K56" s="41"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A57" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="B57" s="10"/>
+      <c r="A57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B57" s="6"/>
       <c r="C57" s="6" t="s">
-        <v>51</v>
+        <v>122</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F57" s="6" t="str">
-        <f>CONCATENATE("http://", E57, ":8080")</f>
-        <v>http://192.168.0.197:8080</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>229</v>
+        <v>121</v>
+      </c>
+      <c r="F57" s="7" t="str">
+        <f>CONCATENATE("http://", E57)</f>
+        <v>http://192.168.0.26</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>230</v>
       </c>
       <c r="H57" s="18" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="K57" s="41"/>
+        <v>123</v>
+      </c>
+      <c r="K57" s="42"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A58" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B58" s="6"/>
+      <c r="A58" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B58" s="10"/>
       <c r="C58" s="6" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="F58" s="7" t="str">
-        <f>CONCATENATE("http://", E58)</f>
-        <v>http://192.168.0.193</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>227</v>
+        <v>50</v>
+      </c>
+      <c r="F58" s="6" t="str">
+        <f>CONCATENATE("http://", E58, ":8080")</f>
+        <v>http://192.168.0.197:8080</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>229</v>
       </c>
       <c r="H58" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I58" s="9"/>
       <c r="J58" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="K58" s="41" t="s">
-        <v>70</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="K58" s="41"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="B59" s="6"/>
-      <c r="C59" s="16" t="s">
-        <v>114</v>
+      <c r="C59" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="F59" s="7" t="str">
         <f>CONCATENATE("http://", E59)</f>
-        <v>http://192.168.0.187</v>
-      </c>
-      <c r="G59" s="7"/>
+        <v>http://192.168.0.193</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>227</v>
+      </c>
       <c r="H59" s="18" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="6" t="s">
-        <v>115</v>
+        <v>64</v>
       </c>
       <c r="K59" s="41" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B60" s="6"/>
-      <c r="C60" s="6" t="s">
-        <v>110</v>
+      <c r="C60" s="16" t="s">
+        <v>114</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F60" s="7" t="str">
         <f>CONCATENATE("http://", E60)</f>
-        <v>http://192.168.0.188</v>
+        <v>http://192.168.0.187</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I60" s="9" t="s">
-        <v>264</v>
-      </c>
+      <c r="I60" s="9"/>
       <c r="J60" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K60" s="41" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5" t="s">
-        <v>345</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A61" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="F61" s="6"/>
-      <c r="G61" s="19"/>
+        <v>35</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F61" s="7" t="str">
+        <f>CONCATENATE("http://", E61)</f>
+        <v>http://192.168.0.188</v>
+      </c>
+      <c r="G61" s="7"/>
       <c r="H61" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I61" s="9"/>
+      <c r="I61" s="9" t="s">
+        <v>264</v>
+      </c>
       <c r="J61" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="K61" s="41">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+      <c r="K61" s="41" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>170</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="B62" s="5"/>
       <c r="C62" s="5" t="s">
-        <v>180</v>
+        <v>323</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="F62" s="7"/>
-      <c r="G62" s="7" t="s">
-        <v>242</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F62" s="6"/>
+      <c r="G62" s="19"/>
       <c r="H62" s="18" t="s">
         <v>166</v>
       </c>
       <c r="I62" s="9"/>
-      <c r="J62" s="6"/>
+      <c r="J62" s="6" t="s">
+        <v>278</v>
+      </c>
       <c r="K62" s="41">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A63" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A63" s="17" t="s">
+      <c r="B63" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="F63" s="7"/>
+      <c r="G63" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="H63" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="I63" s="9"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A64" s="17" t="s">
         <v>225</v>
-      </c>
-      <c r="B63" s="5"/>
-      <c r="C63" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="I63" s="9"/>
-      <c r="J63" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="K63" s="41"/>
-    </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="5" t="s">
-        <v>151</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="6" t="s">
-        <v>347</v>
+        <v>324</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="F64" s="6"/>
       <c r="G64" s="6"/>
       <c r="H64" s="18" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I64" s="9"/>
       <c r="J64" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="K64" s="41">
-        <v>6</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="K64" s="41"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="6" t="s">
-        <v>147</v>
+        <v>325</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="F65" s="7" t="str">
-        <f>CONCATENATE("http://", E65)</f>
-        <v>http://192.168.0.208</v>
-      </c>
-      <c r="G65" s="7"/>
+        <v>188</v>
+      </c>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
       <c r="H65" s="18" t="s">
         <v>166</v>
       </c>
       <c r="I65" s="9"/>
       <c r="J65" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K65" s="41"/>
+        <v>187</v>
+      </c>
+      <c r="K65" s="41">
+        <v>6</v>
+      </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C66" s="15" t="s">
-        <v>162</v>
+        <v>145</v>
+      </c>
+      <c r="B66" s="5"/>
+      <c r="C66" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6" t="s">
-        <v>372</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="F66" s="7" t="str">
+        <f>CONCATENATE("http://", E66)</f>
+        <v>http://192.168.0.208</v>
+      </c>
+      <c r="G66" s="7"/>
       <c r="H66" s="18" t="s">
         <v>166</v>
       </c>
       <c r="I66" s="9"/>
       <c r="J66" s="6" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="K66" s="41"/>
     </row>
-    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C67" s="14" t="s">
-        <v>148</v>
+        <v>175</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>162</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E67" s="14" t="s">
-        <v>171</v>
+      <c r="E67" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="6" t="s">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="H67" s="18" t="s">
         <v>166</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="K67" s="41"/>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="B68" s="5"/>
-      <c r="C68" s="53" t="s">
-        <v>348</v>
+        <v>1</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>148</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E68" s="6" t="s">
-        <v>301</v>
+        <v>35</v>
+      </c>
+      <c r="E68" s="14" t="s">
+        <v>171</v>
       </c>
       <c r="F68" s="6"/>
-      <c r="G68" s="19" t="s">
-        <v>230</v>
+      <c r="G68" s="6" t="s">
+        <v>349</v>
       </c>
       <c r="H68" s="18" t="s">
         <v>166</v>
       </c>
       <c r="I68" s="9"/>
-      <c r="J68" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="K68" s="44" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="J68" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="K68" s="41"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="53" t="s">
-        <v>349</v>
-      </c>
-      <c r="D69" s="54" t="s">
+        <v>326</v>
+      </c>
+      <c r="D69" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E69" s="6" t="s">
@@ -4094,116 +4181,118 @@
         <v>166</v>
       </c>
       <c r="I69" s="9"/>
-      <c r="J69" s="38" t="s">
-        <v>361</v>
-      </c>
-      <c r="K69" s="43" t="s">
-        <v>367</v>
+      <c r="J69" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="K69" s="44" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A70" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>35</v>
+      <c r="A70" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="B70" s="5"/>
+      <c r="C70" s="53" t="s">
+        <v>327</v>
+      </c>
+      <c r="D70" s="54" t="s">
+        <v>100</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>94</v>
+        <v>298</v>
       </c>
       <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
+      <c r="G70" s="19" t="s">
+        <v>230</v>
+      </c>
       <c r="H70" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I70" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="J70" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="K70" s="42" t="s">
-        <v>74</v>
+      <c r="I70" s="9"/>
+      <c r="J70" s="38" t="s">
+        <v>339</v>
+      </c>
+      <c r="K70" s="43" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="6" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F71" s="7" t="str">
-        <f>CONCATENATE("http://", E71)</f>
-        <v>http://192.168.0.183</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>227</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="F71" s="6"/>
+      <c r="G71" s="6"/>
       <c r="H71" s="18" t="s">
         <v>166</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="K71" s="41" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5" t="s">
-        <v>350</v>
+        <v>96</v>
+      </c>
+      <c r="K71" s="42" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A72" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B72" s="6"/>
+      <c r="C72" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="F72" s="6"/>
+        <v>57</v>
+      </c>
+      <c r="F72" s="7" t="str">
+        <f>CONCATENATE("http://", E72)</f>
+        <v>http://192.168.0.183</v>
+      </c>
       <c r="G72" s="7" t="s">
         <v>227</v>
       </c>
       <c r="H72" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I72" s="9"/>
+      <c r="I72" s="9" t="s">
+        <v>263</v>
+      </c>
       <c r="J72" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="K72" s="41"/>
-    </row>
-    <row r="73" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="22" t="s">
-        <v>256</v>
+        <v>59</v>
+      </c>
+      <c r="K72" s="41" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="5" t="s">
+        <v>255</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5" t="s">
-        <v>351</v>
+        <v>328</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F73" s="6"/>
       <c r="G73" s="7" t="s">
@@ -4218,55 +4307,50 @@
       </c>
       <c r="K73" s="41"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A74" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B74" s="30"/>
-      <c r="C74" s="33" t="s">
-        <v>80</v>
+    <row r="74" spans="1:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5" t="s">
+        <v>329</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E74" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="F74" s="36" t="str">
-        <f>CONCATENATE("ftp://", E74)</f>
-        <v>ftp://192.168.0.189</v>
-      </c>
-      <c r="G74" s="7"/>
-      <c r="H74" s="8" t="s">
+      <c r="E74" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F74" s="6"/>
+      <c r="G74" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="H74" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I74" s="9" t="s">
-        <v>264</v>
-      </c>
+      <c r="I74" s="9"/>
       <c r="J74" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="K74" s="42" t="s">
-        <v>74</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="K74" s="41"/>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B75" s="30"/>
       <c r="C75" s="33" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E75" s="33" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F75" s="36" t="str">
         <f>CONCATENATE("ftp://", E75)</f>
-        <v>ftp://192.168.0.190</v>
+        <v>ftp://192.168.0.189</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="8" t="s">
@@ -4282,414 +4366,419 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="B76" s="25"/>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A76" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B76" s="30"/>
       <c r="C76" s="33" t="s">
-        <v>352</v>
-      </c>
-      <c r="D76" s="54" t="s">
-        <v>100</v>
+        <v>76</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="E76" s="33" t="s">
-        <v>157</v>
-      </c>
-      <c r="F76" s="33"/>
-      <c r="G76" s="6"/>
+        <v>75</v>
+      </c>
+      <c r="F76" s="36" t="str">
+        <f>CONCATENATE("ftp://", E76)</f>
+        <v>ftp://192.168.0.190</v>
+      </c>
+      <c r="G76" s="7"/>
       <c r="H76" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="I76" s="9"/>
+      <c r="I76" s="9" t="s">
+        <v>264</v>
+      </c>
       <c r="J76" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="K76" s="41">
-        <v>18</v>
+        <v>77</v>
+      </c>
+      <c r="K76" s="42" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A77" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B77" s="30"/>
+      <c r="A77" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B77" s="25"/>
       <c r="C77" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>35</v>
+        <v>330</v>
+      </c>
+      <c r="D77" s="54" t="s">
+        <v>100</v>
       </c>
       <c r="E77" s="33" t="s">
-        <v>88</v>
+        <v>157</v>
       </c>
       <c r="F77" s="33"/>
       <c r="G77" s="6"/>
       <c r="H77" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="K77" s="41">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A78" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B78" s="30"/>
+      <c r="C78" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E78" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="F78" s="33"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="I78" s="9"/>
+      <c r="J78" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="K77" s="41" t="s">
+      <c r="K78" s="41" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B78" s="25"/>
-      <c r="C78" s="26" t="s">
-        <v>353</v>
-      </c>
-      <c r="D78" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="E78" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="F78" s="26" t="s">
-        <v>298</v>
-      </c>
-      <c r="G78" s="7"/>
-      <c r="H78" s="8"/>
-      <c r="I78" s="9"/>
-      <c r="J78" s="29" t="s">
-        <v>369</v>
-      </c>
-      <c r="K78" s="43">
-        <v>14</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="B79" s="25" t="s">
-        <v>174</v>
-      </c>
-      <c r="C79" s="34" t="s">
-        <v>172</v>
+        <v>159</v>
+      </c>
+      <c r="B79" s="25"/>
+      <c r="C79" s="26" t="s">
+        <v>331</v>
       </c>
       <c r="D79" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E79" s="34" t="s">
+      <c r="E79" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F79" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="G79" s="7"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="9"/>
+      <c r="J79" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="K79" s="43">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A80" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="B80" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C80" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="D80" s="54" t="s">
+        <v>100</v>
+      </c>
+      <c r="E80" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="F79" s="33"/>
-      <c r="G79" s="6" t="s">
+      <c r="F80" s="33"/>
+      <c r="G80" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="H79" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="I79" s="9"/>
-      <c r="J79" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="K79" s="41"/>
-    </row>
-    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="B80" s="27"/>
-      <c r="C80" s="28" t="s">
-        <v>354</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E80" s="35" t="s">
-        <v>257</v>
-      </c>
-      <c r="F80" s="35"/>
-      <c r="G80" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="H80" s="18" t="s">
+      <c r="H80" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I80" s="9"/>
       <c r="J80" s="6" t="s">
-        <v>64</v>
+        <v>177</v>
       </c>
       <c r="K80" s="41"/>
     </row>
-    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B81" s="25"/>
-      <c r="C81" s="26" t="s">
-        <v>355</v>
-      </c>
-      <c r="D81" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="E81" s="33" t="s">
-        <v>267</v>
-      </c>
-      <c r="F81" s="33"/>
-      <c r="G81" s="19"/>
-      <c r="H81" s="8" t="s">
-        <v>167</v>
+        <v>254</v>
+      </c>
+      <c r="B81" s="27"/>
+      <c r="C81" s="28" t="s">
+        <v>332</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E81" s="35" t="s">
+        <v>257</v>
+      </c>
+      <c r="F81" s="35"/>
+      <c r="G81" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="H81" s="18" t="s">
+        <v>166</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="6" t="s">
-        <v>266</v>
+        <v>64</v>
       </c>
       <c r="K81" s="41"/>
     </row>
-    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B82" s="25" t="s">
-        <v>170</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="B82" s="25"/>
       <c r="C82" s="26" t="s">
-        <v>185</v>
+        <v>333</v>
       </c>
       <c r="D82" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E82" s="33" t="s">
-        <v>186</v>
-      </c>
-      <c r="F82" s="36"/>
-      <c r="G82" s="7"/>
+        <v>267</v>
+      </c>
+      <c r="F82" s="33"/>
+      <c r="G82" s="19"/>
       <c r="H82" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I82" s="9"/>
       <c r="J82" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="K82" s="41">
-        <v>10</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="K82" s="41"/>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
         <v>168</v>
       </c>
       <c r="B83" s="25" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C83" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>35</v>
+        <v>185</v>
+      </c>
+      <c r="D83" s="54" t="s">
+        <v>100</v>
       </c>
       <c r="E83" s="33" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="F83" s="36"/>
-      <c r="G83" s="7" t="s">
-        <v>228</v>
-      </c>
+      <c r="G83" s="7"/>
       <c r="H83" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="K83" s="41"/>
-    </row>
-    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+      <c r="K83" s="41">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="B84" s="25"/>
-      <c r="C84" s="23" t="s">
-        <v>356</v>
-      </c>
-      <c r="D84" s="54" t="s">
-        <v>100</v>
+        <v>168</v>
+      </c>
+      <c r="B84" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="C84" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="E84" s="33" t="s">
-        <v>260</v>
-      </c>
-      <c r="F84" s="33"/>
-      <c r="G84" s="19" t="s">
-        <v>230</v>
+        <v>178</v>
+      </c>
+      <c r="F84" s="36"/>
+      <c r="G84" s="7" t="s">
+        <v>228</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I84" s="9"/>
       <c r="J84" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="K84" s="44">
-        <v>4</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="K84" s="41"/>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A85" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="B85" s="6"/>
-      <c r="C85" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>35</v>
+      <c r="A85" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B85" s="25"/>
+      <c r="C85" s="23" t="s">
+        <v>334</v>
+      </c>
+      <c r="D85" s="54" t="s">
+        <v>100</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="F85" s="36" t="str">
-        <f>CONCATENATE("http://", E85)</f>
-        <v>http://192.168.0.195</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>227</v>
+        <v>260</v>
+      </c>
+      <c r="F85" s="33"/>
+      <c r="G85" s="19" t="s">
+        <v>230</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I85" s="9"/>
       <c r="J85" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="K85" s="41" t="s">
-        <v>61</v>
+        <v>262</v>
+      </c>
+      <c r="K85" s="44">
+        <v>4</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A86" s="52" t="s">
-        <v>69</v>
+      <c r="A86" s="30" t="s">
+        <v>65</v>
       </c>
       <c r="B86" s="6"/>
-      <c r="C86" s="35" t="s">
-        <v>68</v>
+      <c r="C86" s="33" t="s">
+        <v>63</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E86" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="F86" s="37" t="str">
+      <c r="E86" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="F86" s="36" t="str">
         <f>CONCATENATE("http://", E86)</f>
-        <v>http://192.168.0.194</v>
+        <v>http://192.168.0.195</v>
       </c>
       <c r="G86" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="H86" s="18" t="s">
+      <c r="H86" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I86" s="9"/>
-      <c r="J86" s="35" t="s">
+      <c r="J86" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K86" s="45" t="s">
+      <c r="K86" s="41" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A87" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="B87" s="6"/>
+      <c r="C87" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E87" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="F87" s="37" t="str">
+        <f>CONCATENATE("http://", E87)</f>
+        <v>http://192.168.0.194</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="H87" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="I87" s="9"/>
+      <c r="J87" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="K87" s="45" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="32" t="s">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A88" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="B87" s="12"/>
-      <c r="C87" s="33" t="s">
+      <c r="B88" s="12"/>
+      <c r="C88" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D87" s="54" t="s">
+      <c r="D88" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E87" s="33"/>
-      <c r="F87" s="33"/>
-      <c r="G87" s="6"/>
-      <c r="H87" s="8" t="s">
+      <c r="E88" s="33"/>
+      <c r="F88" s="33"/>
+      <c r="G88" s="6"/>
+      <c r="H88" s="8" t="s">
         <v>167</v>
-      </c>
-      <c r="I87" s="9"/>
-      <c r="J87" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="K87" s="47" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A88" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B88" s="30"/>
-      <c r="C88" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E88" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="F88" s="36" t="str">
-        <f>CONCATENATE("http://", E88)</f>
-        <v>http://192.168.0.186</v>
-      </c>
-      <c r="G88" s="7"/>
-      <c r="H88" s="8" t="s">
-        <v>166</v>
       </c>
       <c r="I88" s="9"/>
       <c r="J88" s="33" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="K88" s="47" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="B89" s="25"/>
-      <c r="C89" s="26" t="s">
-        <v>357</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A89" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B89" s="30"/>
+      <c r="C89" s="33" t="s">
+        <v>118</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E89" s="33" t="s">
-        <v>274</v>
-      </c>
-      <c r="F89" s="33"/>
-      <c r="G89" s="19" t="s">
-        <v>230</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="F89" s="36" t="str">
+        <f>CONCATENATE("http://", E89)</f>
+        <v>http://192.168.0.186</v>
+      </c>
+      <c r="G89" s="7"/>
       <c r="H89" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="33" t="s">
-        <v>273</v>
-      </c>
-      <c r="K89" s="47"/>
-    </row>
-    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="25" t="s">
-        <v>272</v>
-      </c>
-      <c r="B90" s="5"/>
+        <v>119</v>
+      </c>
+      <c r="K89" s="47" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A90" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B90" s="25"/>
       <c r="C90" s="26" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E90" s="33" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F90" s="33"/>
       <c r="G90" s="19" t="s">
@@ -4702,49 +4791,49 @@
       <c r="J90" s="33" t="s">
         <v>273</v>
       </c>
-      <c r="K90" s="47">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B91" s="25"/>
-      <c r="C91" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="D91" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="E91" s="33"/>
+      <c r="K90" s="47"/>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A91" s="25" t="s">
+        <v>272</v>
+      </c>
+      <c r="B91" s="5"/>
+      <c r="C91" s="26" t="s">
+        <v>336</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E91" s="33" t="s">
+        <v>275</v>
+      </c>
       <c r="F91" s="33"/>
-      <c r="G91" s="6"/>
+      <c r="G91" s="19" t="s">
+        <v>230</v>
+      </c>
       <c r="H91" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I91" s="9"/>
       <c r="J91" s="33" t="s">
+        <v>273</v>
+      </c>
+      <c r="K91" s="47">
         <v>13</v>
       </c>
-      <c r="K91" s="47" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A92" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="B92" s="5"/>
+      <c r="A92" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B92" s="25"/>
       <c r="C92" s="33" t="s">
-        <v>154</v>
+        <v>12</v>
       </c>
       <c r="D92" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E92" s="33" t="s">
-        <v>155</v>
-      </c>
+      <c r="E92" s="33"/>
       <c r="F92" s="33"/>
       <c r="G92" s="6"/>
       <c r="H92" s="8" t="s">
@@ -4752,105 +4841,115 @@
       </c>
       <c r="I92" s="9"/>
       <c r="J92" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="K92" s="47"/>
+        <v>13</v>
+      </c>
+      <c r="K92" s="47" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A93" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B93" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="C93" s="26"/>
+      <c r="A93" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="B93" s="5"/>
+      <c r="C93" s="33" t="s">
+        <v>154</v>
+      </c>
       <c r="D93" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E93" s="33" t="s">
-        <v>182</v>
-      </c>
-      <c r="F93" s="36"/>
-      <c r="G93" s="7"/>
+        <v>155</v>
+      </c>
+      <c r="F93" s="33"/>
+      <c r="G93" s="6"/>
       <c r="H93" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I93" s="9"/>
-      <c r="J93" s="26" t="s">
-        <v>163</v>
+      <c r="J93" s="33" t="s">
+        <v>153</v>
       </c>
       <c r="K93" s="47"/>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A94" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B94" s="30"/>
-      <c r="C94" s="33"/>
+      <c r="A94" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B94" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="C94" s="26" t="s">
+        <v>387</v>
+      </c>
       <c r="D94" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E94" s="34" t="s">
-        <v>179</v>
-      </c>
-      <c r="F94" s="33"/>
-      <c r="G94" s="6"/>
+      <c r="E94" s="33" t="s">
+        <v>182</v>
+      </c>
+      <c r="F94" s="36"/>
+      <c r="G94" s="7"/>
       <c r="H94" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I94" s="9"/>
-      <c r="J94" s="33" t="s">
-        <v>19</v>
+      <c r="J94" s="26" t="s">
+        <v>163</v>
       </c>
       <c r="K94" s="47"/>
     </row>
-    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="25" t="s">
-        <v>246</v>
-      </c>
-      <c r="B95" s="5"/>
-      <c r="C95" s="26"/>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A95" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B95" s="30"/>
+      <c r="C95" s="33"/>
       <c r="D95" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E95" s="34" t="s">
-        <v>243</v>
+        <v>179</v>
       </c>
       <c r="F95" s="33"/>
-      <c r="G95" s="19" t="s">
-        <v>363</v>
-      </c>
+      <c r="G95" s="6"/>
       <c r="H95" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="33" t="s">
-        <v>244</v>
+        <v>19</v>
       </c>
       <c r="K95" s="47"/>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" s="25" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B96" s="5"/>
       <c r="C96" s="26"/>
       <c r="D96" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E96" s="33" t="s">
-        <v>238</v>
+      <c r="E96" s="34" t="s">
+        <v>243</v>
       </c>
       <c r="F96" s="33"/>
-      <c r="G96" s="19"/>
-      <c r="H96" s="8"/>
+      <c r="G96" s="19" t="s">
+        <v>341</v>
+      </c>
+      <c r="H96" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I96" s="9"/>
-      <c r="J96" s="33"/>
+      <c r="J96" s="33" t="s">
+        <v>244</v>
+      </c>
       <c r="K96" s="47"/>
     </row>
-    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" s="25" t="s">
-        <v>279</v>
+        <v>236</v>
       </c>
       <c r="B97" s="5"/>
       <c r="C97" s="26"/>
@@ -4858,71 +4957,69 @@
         <v>100</v>
       </c>
       <c r="E97" s="33" t="s">
-        <v>280</v>
+        <v>238</v>
       </c>
       <c r="F97" s="33"/>
       <c r="G97" s="19"/>
-      <c r="H97" s="8" t="s">
-        <v>166</v>
-      </c>
+      <c r="H97" s="8"/>
       <c r="I97" s="9"/>
       <c r="J97" s="33"/>
       <c r="K97" s="47"/>
     </row>
-    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="27" t="s">
-        <v>9</v>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A98" s="25" t="s">
+        <v>279</v>
       </c>
       <c r="B98" s="5"/>
-      <c r="C98" s="35"/>
+      <c r="C98" s="26"/>
       <c r="D98" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E98" s="35" t="s">
-        <v>4</v>
-      </c>
-      <c r="F98" s="35"/>
-      <c r="G98" s="6"/>
-      <c r="H98" s="18"/>
+      <c r="E98" s="33" t="s">
+        <v>280</v>
+      </c>
+      <c r="F98" s="33"/>
+      <c r="G98" s="19"/>
+      <c r="H98" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I98" s="9"/>
-      <c r="J98" s="35" t="s">
-        <v>8</v>
-      </c>
-      <c r="K98" s="45"/>
-    </row>
-    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="25" t="s">
-        <v>235</v>
+      <c r="J98" s="33"/>
+      <c r="K98" s="47"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A99" s="27" t="s">
+        <v>9</v>
       </c>
       <c r="B99" s="5"/>
-      <c r="C99" s="26"/>
+      <c r="C99" s="35"/>
       <c r="D99" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E99" s="33"/>
-      <c r="F99" s="33"/>
-      <c r="G99" s="19"/>
-      <c r="H99" s="8" t="s">
-        <v>167</v>
-      </c>
+      <c r="E99" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F99" s="35"/>
+      <c r="G99" s="6"/>
+      <c r="H99" s="18"/>
       <c r="I99" s="9"/>
-      <c r="J99" s="33"/>
-      <c r="K99" s="47"/>
-    </row>
-    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B100" s="25" t="s">
-        <v>161</v>
-      </c>
+      <c r="J99" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="K99" s="45"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A100" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="B100" s="5"/>
       <c r="C100" s="26"/>
       <c r="D100" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E100" s="33"/>
-      <c r="F100" s="36"/>
-      <c r="G100" s="7"/>
+      <c r="F100" s="33"/>
+      <c r="G100" s="19"/>
       <c r="H100" s="8" t="s">
         <v>167</v>
       </c>
@@ -4930,12 +5027,16 @@
       <c r="J100" s="33"/>
       <c r="K100" s="47"/>
     </row>
-    <row r="101" spans="1:11" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B101" s="25"/>
-      <c r="C101" s="26"/>
+        <v>3</v>
+      </c>
+      <c r="B101" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="C101" s="26" t="s">
+        <v>388</v>
+      </c>
       <c r="D101" s="54" t="s">
         <v>100</v>
       </c>
@@ -4943,40 +5044,38 @@
       <c r="F101" s="36"/>
       <c r="G101" s="7"/>
       <c r="H101" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="J101" s="33" t="s">
-        <v>247</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="I101" s="9"/>
+      <c r="J101" s="33"/>
       <c r="K101" s="47"/>
     </row>
-    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="B102" s="6"/>
-      <c r="C102" s="33"/>
+    <row r="102" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A102" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B102" s="25"/>
+      <c r="C102" s="26"/>
       <c r="D102" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E102" s="33"/>
-      <c r="F102" s="33"/>
-      <c r="G102" s="6"/>
+      <c r="F102" s="36"/>
+      <c r="G102" s="7"/>
       <c r="H102" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="I102" s="9"/>
+        <v>166</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J102" s="33" t="s">
-        <v>22</v>
+        <v>247</v>
       </c>
       <c r="K102" s="47"/>
     </row>
-    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B103" s="6"/>
       <c r="C103" s="33"/>
@@ -4995,9 +5094,9 @@
       </c>
       <c r="K103" s="47"/>
     </row>
-    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" s="30" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B104" s="6"/>
       <c r="C104" s="33"/>
@@ -5016,9 +5115,9 @@
       </c>
       <c r="K104" s="47"/>
     </row>
-    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B105" s="6"/>
       <c r="C105" s="33"/>
@@ -5037,9 +5136,9 @@
       </c>
       <c r="K105" s="47"/>
     </row>
-    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" s="30" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B106" s="6"/>
       <c r="C106" s="33"/>
@@ -5056,13 +5155,11 @@
       <c r="J106" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="K106" s="47" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="K106" s="47"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" s="30" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B107" s="6"/>
       <c r="C107" s="33"/>
@@ -5079,11 +5176,13 @@
       <c r="J107" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="K107" s="47"/>
-    </row>
-    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="K107" s="47" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" s="30" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B108" s="6"/>
       <c r="C108" s="33"/>
@@ -5102,9 +5201,9 @@
       </c>
       <c r="K108" s="47"/>
     </row>
-    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" s="30" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B109" s="6"/>
       <c r="C109" s="33"/>
@@ -5123,9 +5222,9 @@
       </c>
       <c r="K109" s="47"/>
     </row>
-    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" s="30" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B110" s="6"/>
       <c r="C110" s="33"/>
@@ -5144,32 +5243,30 @@
       </c>
       <c r="K110" s="47"/>
     </row>
-    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="C111" s="5"/>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A111" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B111" s="6"/>
+      <c r="C111" s="33"/>
       <c r="D111" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E111" s="6"/>
-      <c r="F111" s="6"/>
-      <c r="G111" s="7"/>
-      <c r="H111" s="18" t="s">
+      <c r="E111" s="33"/>
+      <c r="F111" s="33"/>
+      <c r="G111" s="6"/>
+      <c r="H111" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I111" s="9"/>
-      <c r="J111" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="K111" s="45"/>
-    </row>
-    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="J111" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="K111" s="47"/>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>194</v>
@@ -5181,30 +5278,40 @@
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
       <c r="G112" s="7"/>
-      <c r="H112" s="8" t="s">
+      <c r="H112" s="18" t="s">
         <v>167</v>
       </c>
       <c r="I112" s="9"/>
-      <c r="J112" s="39" t="s">
+      <c r="J112" s="35" t="s">
         <v>213</v>
       </c>
-      <c r="K112" s="47"/>
-    </row>
-    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="5"/>
-      <c r="B113" s="5"/>
+      <c r="K112" s="45"/>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A113" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>194</v>
+      </c>
       <c r="C113" s="5"/>
-      <c r="D113" s="6"/>
+      <c r="D113" s="54" t="s">
+        <v>100</v>
+      </c>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
       <c r="G113" s="7"/>
-      <c r="H113" s="8"/>
+      <c r="H113" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I113" s="9"/>
-      <c r="J113" s="26"/>
-      <c r="K113" s="46"/>
-    </row>
-    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="5"/>
+      <c r="J113" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="K113" s="47"/>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A114" s="59"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
       <c r="D114" s="6"/>
@@ -5213,11 +5320,11 @@
       <c r="G114" s="7"/>
       <c r="H114" s="8"/>
       <c r="I114" s="9"/>
-      <c r="J114" s="23"/>
-      <c r="K114" s="48"/>
-    </row>
-    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="5"/>
+      <c r="J114" s="26"/>
+      <c r="K114" s="46"/>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A115" s="59"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
       <c r="D115" s="6"/>
@@ -5226,11 +5333,11 @@
       <c r="G115" s="7"/>
       <c r="H115" s="8"/>
       <c r="I115" s="9"/>
-      <c r="J115" s="26"/>
-      <c r="K115" s="46"/>
-    </row>
-    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="5"/>
+      <c r="J115" s="23"/>
+      <c r="K115" s="48"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A116" s="59"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
       <c r="D116" s="6"/>
@@ -5239,11 +5346,11 @@
       <c r="G116" s="7"/>
       <c r="H116" s="8"/>
       <c r="I116" s="9"/>
-      <c r="J116" s="23"/>
-      <c r="K116" s="48"/>
-    </row>
-    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="5"/>
+      <c r="J116" s="26"/>
+      <c r="K116" s="46"/>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A117" s="59"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
       <c r="D117" s="6"/>
@@ -5252,11 +5359,11 @@
       <c r="G117" s="7"/>
       <c r="H117" s="8"/>
       <c r="I117" s="9"/>
-      <c r="J117" s="26"/>
-      <c r="K117" s="46"/>
-    </row>
-    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="5"/>
+      <c r="J117" s="23"/>
+      <c r="K117" s="48"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A118" s="59"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
       <c r="D118" s="6"/>
@@ -5265,11 +5372,11 @@
       <c r="G118" s="7"/>
       <c r="H118" s="8"/>
       <c r="I118" s="9"/>
-      <c r="J118" s="23"/>
-      <c r="K118" s="48"/>
-    </row>
-    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="5"/>
+      <c r="J118" s="26"/>
+      <c r="K118" s="46"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A119" s="59"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
       <c r="D119" s="6"/>
@@ -5278,37 +5385,37 @@
       <c r="G119" s="7"/>
       <c r="H119" s="8"/>
       <c r="I119" s="9"/>
-      <c r="J119" s="26"/>
-      <c r="K119" s="46"/>
-    </row>
-    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="5"/>
+      <c r="J119" s="23"/>
+      <c r="K119" s="48"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A120" s="59"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
       <c r="D120" s="6"/>
       <c r="E120" s="6"/>
       <c r="F120" s="6"/>
-      <c r="G120" s="19"/>
-      <c r="H120" s="18"/>
+      <c r="G120" s="7"/>
+      <c r="H120" s="8"/>
       <c r="I120" s="9"/>
-      <c r="J120" s="24"/>
-      <c r="K120" s="49"/>
-    </row>
-    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="5"/>
+      <c r="J120" s="26"/>
+      <c r="K120" s="46"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A121" s="59"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
       <c r="F121" s="6"/>
-      <c r="G121" s="7"/>
-      <c r="H121" s="8"/>
+      <c r="G121" s="19"/>
+      <c r="H121" s="18"/>
       <c r="I121" s="9"/>
-      <c r="J121" s="26"/>
-      <c r="K121" s="46"/>
-    </row>
-    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="5"/>
+      <c r="J121" s="24"/>
+      <c r="K121" s="49"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A122" s="59"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
       <c r="D122" s="6"/>
@@ -5317,11 +5424,11 @@
       <c r="G122" s="7"/>
       <c r="H122" s="8"/>
       <c r="I122" s="9"/>
-      <c r="J122" s="23"/>
-      <c r="K122" s="48"/>
-    </row>
-    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="5"/>
+      <c r="J122" s="26"/>
+      <c r="K122" s="46"/>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A123" s="59"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
       <c r="D123" s="6"/>
@@ -5330,11 +5437,11 @@
       <c r="G123" s="7"/>
       <c r="H123" s="8"/>
       <c r="I123" s="9"/>
-      <c r="J123" s="26"/>
-      <c r="K123" s="46"/>
-    </row>
-    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="5"/>
+      <c r="J123" s="23"/>
+      <c r="K123" s="48"/>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A124" s="59"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
       <c r="D124" s="6"/>
@@ -5343,11 +5450,11 @@
       <c r="G124" s="7"/>
       <c r="H124" s="8"/>
       <c r="I124" s="9"/>
-      <c r="J124" s="23"/>
-      <c r="K124" s="48"/>
-    </row>
-    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="5"/>
+      <c r="J124" s="26"/>
+      <c r="K124" s="46"/>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A125" s="59"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
       <c r="D125" s="6"/>
@@ -5356,11 +5463,11 @@
       <c r="G125" s="7"/>
       <c r="H125" s="8"/>
       <c r="I125" s="9"/>
-      <c r="J125" s="26"/>
-      <c r="K125" s="46"/>
-    </row>
-    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="5"/>
+      <c r="J125" s="23"/>
+      <c r="K125" s="48"/>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A126" s="59"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
       <c r="D126" s="6"/>
@@ -5369,11 +5476,11 @@
       <c r="G126" s="7"/>
       <c r="H126" s="8"/>
       <c r="I126" s="9"/>
-      <c r="J126" s="23"/>
-      <c r="K126" s="48"/>
-    </row>
-    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="5"/>
+      <c r="J126" s="26"/>
+      <c r="K126" s="46"/>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A127" s="59"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
       <c r="D127" s="6"/>
@@ -5382,36 +5489,36 @@
       <c r="G127" s="7"/>
       <c r="H127" s="8"/>
       <c r="I127" s="9"/>
-      <c r="J127" s="26"/>
-      <c r="K127" s="46"/>
-    </row>
-    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="J127" s="23"/>
+      <c r="K127" s="48"/>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" s="5"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
       <c r="D128" s="6"/>
       <c r="E128" s="6"/>
       <c r="F128" s="6"/>
-      <c r="G128" s="19"/>
-      <c r="H128" s="18"/>
+      <c r="G128" s="7"/>
+      <c r="H128" s="8"/>
       <c r="I128" s="9"/>
-      <c r="J128" s="24"/>
-      <c r="K128" s="49"/>
-    </row>
-    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="J128" s="26"/>
+      <c r="K128" s="46"/>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" s="5"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
       <c r="D129" s="6"/>
       <c r="E129" s="6"/>
       <c r="F129" s="6"/>
-      <c r="G129" s="7"/>
-      <c r="H129" s="8"/>
+      <c r="G129" s="19"/>
+      <c r="H129" s="18"/>
       <c r="I129" s="9"/>
-      <c r="J129" s="26"/>
-      <c r="K129" s="46"/>
-    </row>
-    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="J129" s="24"/>
+      <c r="K129" s="49"/>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -5421,37 +5528,73 @@
       <c r="G130" s="7"/>
       <c r="H130" s="8"/>
       <c r="I130" s="9"/>
-      <c r="J130" s="23"/>
-      <c r="K130" s="48"/>
-    </row>
-    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="J130" s="26"/>
+      <c r="K130" s="46"/>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" s="5"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
       <c r="D131" s="6"/>
       <c r="E131" s="6"/>
       <c r="F131" s="6"/>
-      <c r="G131" s="19"/>
-      <c r="H131" s="18"/>
+      <c r="G131" s="7"/>
+      <c r="H131" s="8"/>
       <c r="I131" s="9"/>
-      <c r="J131" s="28"/>
-      <c r="K131" s="50"/>
+      <c r="J131" s="23"/>
+      <c r="K131" s="48"/>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H132"/>
-      <c r="I132"/>
+      <c r="A132" s="5"/>
+      <c r="B132" s="5"/>
+      <c r="C132" s="5"/>
+      <c r="D132" s="6"/>
+      <c r="E132" s="6"/>
+      <c r="F132" s="6"/>
+      <c r="G132" s="19"/>
+      <c r="H132" s="18"/>
+      <c r="I132" s="9"/>
+      <c r="J132" s="28"/>
+      <c r="K132" s="50"/>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H133"/>
-      <c r="I133"/>
+      <c r="A133" s="55"/>
+      <c r="B133" s="55"/>
+      <c r="C133" s="55"/>
+      <c r="D133" s="56"/>
+      <c r="E133" s="56"/>
+      <c r="F133" s="56"/>
+      <c r="G133" s="19"/>
+      <c r="H133" s="18"/>
+      <c r="I133" s="57"/>
+      <c r="J133" s="56"/>
+      <c r="K133" s="58"/>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H134"/>
-      <c r="I134"/>
+      <c r="A134" s="55"/>
+      <c r="B134" s="55"/>
+      <c r="C134" s="55"/>
+      <c r="D134" s="56"/>
+      <c r="E134" s="56"/>
+      <c r="F134" s="56"/>
+      <c r="G134" s="19"/>
+      <c r="H134" s="18"/>
+      <c r="I134" s="57"/>
+      <c r="J134" s="56"/>
+      <c r="K134" s="58"/>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H135"/>
-      <c r="I135"/>
+      <c r="A135" s="55"/>
+      <c r="B135" s="55"/>
+      <c r="C135" s="55"/>
+      <c r="D135" s="56"/>
+      <c r="E135" s="56"/>
+      <c r="F135" s="56"/>
+      <c r="G135" s="19"/>
+      <c r="H135" s="18"/>
+      <c r="I135" s="57"/>
+      <c r="J135" s="56"/>
+      <c r="K135" s="58"/>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H136"/>
@@ -11785,19 +11928,24 @@
       <c r="H1718"/>
       <c r="I1718"/>
     </row>
+    <row r="1719" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H1719"/>
+      <c r="I1719"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="14" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F27" r:id="rId1" display="http://192.169.0.112" xr:uid="{D2404E72-FA69-6648-ACE3-1F155CD355DD}"/>
-    <hyperlink ref="F71" r:id="rId2" display="http://192.169.0.112" xr:uid="{3F5BA59D-C194-FC49-9DCB-1F6B1CEAE85A}"/>
-    <hyperlink ref="F47" r:id="rId3" display="http://192.169.0.112" xr:uid="{80722F7C-2A8A-4A43-A5D3-BCFFE30BBC25}"/>
-    <hyperlink ref="F46" r:id="rId4" display="http://192.169.0.112" xr:uid="{7AFCBEF6-4325-D24D-B711-037F038931A3}"/>
-    <hyperlink ref="F12:F14" r:id="rId5" display="http://192.169.0.112" xr:uid="{40E3D96B-FF32-1147-AA42-7A87222DBFE8}"/>
+    <hyperlink ref="F28" r:id="rId1" display="http://192.169.0.112" xr:uid="{D2404E72-FA69-6648-ACE3-1F155CD355DD}"/>
+    <hyperlink ref="F72" r:id="rId2" display="http://192.169.0.112" xr:uid="{3F5BA59D-C194-FC49-9DCB-1F6B1CEAE85A}"/>
+    <hyperlink ref="F48" r:id="rId3" display="http://192.169.0.112" xr:uid="{80722F7C-2A8A-4A43-A5D3-BCFFE30BBC25}"/>
+    <hyperlink ref="F47" r:id="rId4" display="http://192.169.0.112" xr:uid="{7AFCBEF6-4325-D24D-B711-037F038931A3}"/>
+    <hyperlink ref="F12:F15" r:id="rId5" display="http://192.169.0.112" xr:uid="{40E3D96B-FF32-1147-AA42-7A87222DBFE8}"/>
     <hyperlink ref="F4:F8" r:id="rId6" display="http://192.169.0.112" xr:uid="{EFA55FC0-66D6-5341-B122-15ED7113DE4A}"/>
-    <hyperlink ref="F48" r:id="rId7" display="http://192.169.0.112" xr:uid="{206574CD-0A69-6A49-BF19-8696C0B23754}"/>
-    <hyperlink ref="F19:F21" r:id="rId8" display="http://192.169.0.112" xr:uid="{ABAD7AC1-281C-974C-8BD8-79EEDE34950A}"/>
-    <hyperlink ref="F74" r:id="rId9" display="http://192.169.0.112" xr:uid="{2FA0DCAE-2864-024C-9351-79F3CBFD408D}"/>
-    <hyperlink ref="F75" r:id="rId10" display="http://192.169.0.112" xr:uid="{0E717F48-1348-0440-9A96-15E3AB13C8AE}"/>
-    <hyperlink ref="F65" r:id="rId11" display="http://192.169.0.112" xr:uid="{B7709A6B-F68E-6F45-9F1A-5CCF46F3BFD7}"/>
+    <hyperlink ref="F49" r:id="rId7" display="http://192.169.0.112" xr:uid="{206574CD-0A69-6A49-BF19-8696C0B23754}"/>
+    <hyperlink ref="F20:F22" r:id="rId8" display="http://192.169.0.112" xr:uid="{ABAD7AC1-281C-974C-8BD8-79EEDE34950A}"/>
+    <hyperlink ref="F75" r:id="rId9" display="http://192.169.0.112" xr:uid="{2FA0DCAE-2864-024C-9351-79F3CBFD408D}"/>
+    <hyperlink ref="F76" r:id="rId10" display="http://192.169.0.112" xr:uid="{0E717F48-1348-0440-9A96-15E3AB13C8AE}"/>
+    <hyperlink ref="F66" r:id="rId11" display="http://192.169.0.112" xr:uid="{B7709A6B-F68E-6F45-9F1A-5CCF46F3BFD7}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{538832C3-E8E8-C249-9893-1081B677E08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E9EA51-B4D8-FA49-9B2A-929AD094B732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1880" yWindow="2960" windowWidth="28360" windowHeight="16680" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -695,9 +695,6 @@
     <t>2308-1124</t>
   </si>
   <si>
-    <t>Core-53ee</t>
-  </si>
-  <si>
     <t>192.168.200.50</t>
   </si>
   <si>
@@ -1004,9 +1001,6 @@
     <t>192.168.200.123</t>
   </si>
   <si>
-    <t>192.168.200.150</t>
-  </si>
-  <si>
     <t>192.168.200.100</t>
   </si>
   <si>
@@ -1272,6 +1266,12 @@
   </si>
   <si>
     <t xml:space="preserve">00-04-C4-31-29-CF </t>
+  </si>
+  <si>
+    <t>192.168.200.158</t>
+  </si>
+  <si>
+    <t>2408-2700</t>
   </si>
 </sst>
 </file>
@@ -2293,7 +2293,7 @@
         <v>139</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>165</v>
@@ -2310,28 +2310,28 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="19" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K2" s="41"/>
     </row>
@@ -2383,25 +2383,25 @@
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K4" s="41"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>190</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -2410,19 +2410,19 @@
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K5" s="41"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>194</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>100</v>
@@ -2435,48 +2435,48 @@
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K6" s="41"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>190</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K7" s="41"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>194</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>100</v>
@@ -2489,25 +2489,25 @@
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K8" s="41"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>190</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -2516,19 +2516,19 @@
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K9" s="41"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>194</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>100</v>
@@ -2541,334 +2541,334 @@
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K10" s="41"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="29" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>302</v>
+        <v>390</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="K11" s="44"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="K12" s="43"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>389</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>391</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="K13" s="43"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="K14" s="43"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="K15" s="43"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="K16" s="43"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="29" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="K17" s="44"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="29" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F18" s="29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="K18" s="44"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="K19" s="43"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="29" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="K20" s="44"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B21" s="29"/>
       <c r="C21" s="29" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E21" s="29" t="s">
+        <v>291</v>
+      </c>
+      <c r="F21" s="29" t="s">
         <v>292</v>
-      </c>
-      <c r="F21" s="29" t="s">
-        <v>293</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="8"/>
@@ -2888,7 +2888,7 @@
         <v>35</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
@@ -2896,7 +2896,7 @@
         <v>166</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>44</v>
@@ -2917,7 +2917,7 @@
         <v>35</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
@@ -2925,7 +2925,7 @@
         <v>166</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>44</v>
@@ -2946,7 +2946,7 @@
         <v>35</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
@@ -2954,7 +2954,7 @@
         <v>166</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>44</v>
@@ -2975,7 +2975,7 @@
         <v>35</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
@@ -2983,7 +2983,7 @@
         <v>166</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>44</v>
@@ -3021,11 +3021,11 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>100</v>
@@ -3037,7 +3037,7 @@
       <c r="I27" s="9"/>
       <c r="J27" s="6"/>
       <c r="K27" s="41" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
@@ -3046,20 +3046,20 @@
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F28" s="19" t="str">
         <f>CONCATENATE("http://", E28)</f>
         <v>http://192.168.201.110</v>
       </c>
       <c r="G28" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H28" s="8" t="s">
         <v>166</v>
@@ -3098,7 +3098,7 @@
         <v>37</v>
       </c>
       <c r="K29" s="41" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -3127,7 +3127,7 @@
         <v>37</v>
       </c>
       <c r="K30" s="41" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
@@ -3142,7 +3142,7 @@
         <v>100</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="K31" s="41"/>
     </row>
@@ -3178,23 +3178,23 @@
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="K32" s="41"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
@@ -3209,20 +3209,20 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="8"/>
@@ -3232,20 +3232,20 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B35" s="29"/>
       <c r="C35" s="29" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G35" s="19"/>
       <c r="H35" s="8"/>
@@ -3255,20 +3255,20 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B36" s="29"/>
       <c r="C36" s="29" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="8"/>
@@ -3278,20 +3278,20 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="8"/>
@@ -3301,227 +3301,227 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B38" s="29"/>
       <c r="C38" s="29" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="8"/>
       <c r="I38" s="9"/>
       <c r="J38" s="6"/>
       <c r="K38" s="41" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B39" s="29"/>
       <c r="C39" s="29" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F39" s="29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="8"/>
       <c r="I39" s="9"/>
       <c r="J39" s="6"/>
       <c r="K39" s="41" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="29" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F40" s="29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="8"/>
       <c r="I40" s="9"/>
       <c r="J40" s="6"/>
       <c r="K40" s="41" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="8"/>
       <c r="I41" s="9"/>
       <c r="J41" s="6"/>
       <c r="K41" s="41" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="8"/>
       <c r="I42" s="9"/>
       <c r="J42" s="6"/>
       <c r="K42" s="41" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="8"/>
       <c r="I43" s="9"/>
       <c r="J43" s="6"/>
       <c r="K43" s="41" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="8"/>
       <c r="I44" s="9"/>
       <c r="J44" s="6"/>
       <c r="K44" s="41" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B45" s="29"/>
       <c r="C45" s="29" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E45" s="29" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F45" s="29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="8"/>
       <c r="I45" s="9"/>
       <c r="J45" s="6"/>
       <c r="K45" s="41" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B46" s="29"/>
       <c r="C46" s="29" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E46" s="29" t="s">
+        <v>280</v>
+      </c>
+      <c r="F46" s="29" t="s">
         <v>281</v>
-      </c>
-      <c r="F46" s="29" t="s">
-        <v>282</v>
       </c>
       <c r="G46" s="19"/>
       <c r="H46" s="8"/>
       <c r="I46" s="9"/>
       <c r="J46" s="6"/>
       <c r="K46" s="41" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
@@ -3616,28 +3616,28 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H50" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K50" s="41">
         <v>22</v>
@@ -3645,21 +3645,21 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="31" t="s">
-        <v>199</v>
+        <v>391</v>
       </c>
       <c r="B51" s="13"/>
       <c r="C51" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H51" s="8" t="s">
         <v>166</v>
@@ -3687,7 +3687,7 @@
         <v>http://192.168.0.23</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H52" s="8" t="s">
         <v>167</v>
@@ -3717,7 +3717,7 @@
         <v>http://192.168.0.22</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H53" s="8" t="s">
         <v>167</v>
@@ -3770,7 +3770,7 @@
         <v>http://192.168.0.24</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H55" s="18" t="s">
         <v>167</v>
@@ -3800,7 +3800,7 @@
         <v>http://192.168.0.25</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H56" s="18" t="s">
         <v>167</v>
@@ -3830,7 +3830,7 @@
         <v>http://192.168.0.26</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H57" s="18" t="s">
         <v>167</v>
@@ -3860,7 +3860,7 @@
         <v>http://192.168.0.197:8080</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H58" s="18" t="s">
         <v>166</v>
@@ -3890,7 +3890,7 @@
         <v>http://192.168.0.193</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H59" s="18" t="s">
         <v>167</v>
@@ -3956,7 +3956,7 @@
         <v>166</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J61" s="6" t="s">
         <v>111</v>
@@ -3967,17 +3967,17 @@
     </row>
     <row r="62" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="19"/>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K62" s="41">
         <v>12</v>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="F63" s="7"/>
       <c r="G63" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H63" s="18" t="s">
         <v>166</v>
@@ -4023,11 +4023,11 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" s="17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>100</v>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>100</v>
@@ -4119,7 +4119,7 @@
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H67" s="18" t="s">
         <v>166</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F68" s="6"/>
       <c r="G68" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H68" s="18" t="s">
         <v>166</v>
@@ -4161,60 +4161,60 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="53" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F69" s="6"/>
       <c r="G69" s="19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H69" s="18" t="s">
         <v>166</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="K69" s="44" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="53" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D70" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F70" s="6"/>
       <c r="G70" s="19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H70" s="18" t="s">
         <v>166</v>
       </c>
       <c r="I70" s="9"/>
       <c r="J70" s="38" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="K70" s="43" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
@@ -4237,7 +4237,7 @@
         <v>166</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J71" s="6" t="s">
         <v>96</v>
@@ -4265,13 +4265,13 @@
         <v>http://192.168.0.183</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H72" s="18" t="s">
         <v>166</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J72" s="6" t="s">
         <v>59</v>
@@ -4282,21 +4282,21 @@
     </row>
     <row r="73" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F73" s="6"/>
       <c r="G73" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H73" s="18" t="s">
         <v>166</v>
@@ -4309,21 +4309,21 @@
     </row>
     <row r="74" spans="1:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A74" s="22" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F74" s="6"/>
       <c r="G74" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H74" s="18" t="s">
         <v>166</v>
@@ -4357,7 +4357,7 @@
         <v>166</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J75" s="6" t="s">
         <v>77</v>
@@ -4389,7 +4389,7 @@
         <v>166</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J76" s="6" t="s">
         <v>77</v>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="B77" s="25"/>
       <c r="C77" s="33" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D77" s="54" t="s">
         <v>100</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K77" s="41">
         <v>18</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B79" s="25"/>
       <c r="C79" s="26" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D79" s="54" t="s">
         <v>100</v>
@@ -4467,13 +4467,13 @@
         <v>156</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="8"/>
       <c r="I79" s="9"/>
       <c r="J79" s="29" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K79" s="43">
         <v>14</v>
@@ -4481,7 +4481,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B80" s="25" t="s">
         <v>174</v>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="F80" s="33"/>
       <c r="G80" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H80" s="8" t="s">
         <v>166</v>
@@ -4510,21 +4510,21 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B81" s="27"/>
       <c r="C81" s="28" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E81" s="35" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F81" s="35"/>
       <c r="G81" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H81" s="18" t="s">
         <v>166</v>
@@ -4537,17 +4537,17 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B82" s="25"/>
       <c r="C82" s="26" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D82" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E82" s="33" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F82" s="33"/>
       <c r="G82" s="19"/>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="I82" s="9"/>
       <c r="J82" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K82" s="41"/>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="F84" s="36"/>
       <c r="G84" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H84" s="8" t="s">
         <v>167</v>
@@ -4620,28 +4620,28 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B85" s="25"/>
       <c r="C85" s="23" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D85" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F85" s="33"/>
       <c r="G85" s="19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H85" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I85" s="9"/>
       <c r="J85" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K85" s="44">
         <v>4</v>
@@ -4666,7 +4666,7 @@
         <v>http://192.168.0.195</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H86" s="8" t="s">
         <v>167</v>
@@ -4698,7 +4698,7 @@
         <v>http://192.168.0.194</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H87" s="18" t="s">
         <v>167</v>
@@ -4768,55 +4768,55 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B90" s="25"/>
       <c r="C90" s="26" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E90" s="33" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F90" s="33"/>
       <c r="G90" s="19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H90" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I90" s="9"/>
       <c r="J90" s="33" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K90" s="47"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" s="25" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B91" s="5"/>
       <c r="C91" s="26" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E91" s="33" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F91" s="33"/>
       <c r="G91" s="19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H91" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I91" s="9"/>
       <c r="J91" s="33" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K91" s="47">
         <v>13</v>
@@ -4880,7 +4880,7 @@
         <v>183</v>
       </c>
       <c r="C94" s="26" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D94" s="54" t="s">
         <v>100</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" s="25" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B96" s="5"/>
       <c r="C96" s="26"/>
@@ -4932,24 +4932,24 @@
         <v>100</v>
       </c>
       <c r="E96" s="34" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F96" s="33"/>
       <c r="G96" s="19" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H96" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I96" s="9"/>
       <c r="J96" s="33" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K96" s="47"/>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" s="25" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B97" s="5"/>
       <c r="C97" s="26"/>
@@ -4957,7 +4957,7 @@
         <v>100</v>
       </c>
       <c r="E97" s="33" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F97" s="33"/>
       <c r="G97" s="19"/>
@@ -4968,7 +4968,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="25" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="26"/>
@@ -4976,7 +4976,7 @@
         <v>100</v>
       </c>
       <c r="E98" s="33" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F98" s="33"/>
       <c r="G98" s="19"/>
@@ -5010,7 +5010,7 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" s="25" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B100" s="5"/>
       <c r="C100" s="26"/>
@@ -5035,7 +5035,7 @@
         <v>161</v>
       </c>
       <c r="C101" s="26" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D101" s="54" t="s">
         <v>100</v>
@@ -5066,10 +5066,10 @@
         <v>166</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J102" s="33" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K102" s="47"/>
     </row>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="I112" s="9"/>
       <c r="J112" s="35" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K112" s="45"/>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="I113" s="9"/>
       <c r="J113" s="39" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K113" s="47"/>
     </row>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E9EA51-B4D8-FA49-9B2A-929AD094B732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F3D613-8BD4-5143-8AC8-92673D0E6EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1880" yWindow="2960" windowWidth="28360" windowHeight="16680" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="401">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -1272,6 +1272,33 @@
   </si>
   <si>
     <t>2408-2700</t>
+  </si>
+  <si>
+    <t>2605-0500</t>
+  </si>
+  <si>
+    <t>LAN</t>
+  </si>
+  <si>
+    <t>38:8c:ef:4d:85:78</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t>Stage Display TV.</t>
+  </si>
+  <si>
+    <t>control:8002</t>
+  </si>
+  <si>
+    <t>b8-a0-b8-4c-93-d4</t>
+  </si>
+  <si>
+    <t>192.168.207.101</t>
+  </si>
+  <si>
+    <t>None</t>
   </si>
 </sst>
 </file>
@@ -5311,29 +5338,57 @@
       <c r="K113" s="47"/>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A114" s="59"/>
-      <c r="B114" s="5"/>
-      <c r="C114" s="5"/>
-      <c r="D114" s="6"/>
-      <c r="E114" s="6"/>
+      <c r="A114" s="59" t="s">
+        <v>392</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="E114" s="6" t="s">
+        <v>395</v>
+      </c>
       <c r="F114" s="6"/>
       <c r="G114" s="7"/>
-      <c r="H114" s="8"/>
+      <c r="H114" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I114" s="9"/>
       <c r="J114" s="26"/>
       <c r="K114" s="46"/>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A115" s="59"/>
-      <c r="B115" s="5"/>
-      <c r="C115" s="5"/>
-      <c r="D115" s="6"/>
-      <c r="E115" s="6"/>
+      <c r="A115" s="59" t="s">
+        <v>392</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E115" s="6" t="s">
+        <v>399</v>
+      </c>
       <c r="F115" s="6"/>
-      <c r="G115" s="7"/>
-      <c r="H115" s="8"/>
+      <c r="G115" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="H115" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I115" s="9"/>
-      <c r="J115" s="23"/>
+      <c r="J115" s="23" t="s">
+        <v>396</v>
+      </c>
       <c r="K115" s="48"/>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F3D613-8BD4-5143-8AC8-92673D0E6EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7826427-D20E-2B4F-B2F3-A253EA5A5785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1880" yWindow="2960" windowWidth="28360" windowHeight="16680" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -2400,7 +2400,7 @@
         <v>195</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -2452,7 +2452,7 @@
         <v>203</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -2506,7 +2506,7 @@
         <v>219</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -2558,7 +2558,7 @@
         <v>206</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7826427-D20E-2B4F-B2F3-A253EA5A5785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1FF6446-C2B6-EE49-A2A7-C44B88E6F63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1880" yWindow="2960" windowWidth="28360" windowHeight="16680" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
+    <workbookView xWindow="320" yWindow="3740" windowWidth="28360" windowHeight="16680" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
   <sheets>
     <sheet name="network" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="409">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -1299,6 +1299,30 @@
   </si>
   <si>
     <t>None</t>
+  </si>
+  <si>
+    <t>2605-1503</t>
+  </si>
+  <si>
+    <t>80:7B:1E:03:9C:BD</t>
+  </si>
+  <si>
+    <t>2605-2500</t>
+  </si>
+  <si>
+    <t>80:7B:1E:03:9C:BB</t>
+  </si>
+  <si>
+    <t>ProP Stream Deck Dock</t>
+  </si>
+  <si>
+    <t>Nursery Stream Deck Dock</t>
+  </si>
+  <si>
+    <t>192.168.201.115</t>
+  </si>
+  <si>
+    <t>Dynamic</t>
   </si>
 </sst>
 </file>
@@ -1588,7 +1612,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1672,12 +1696,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -5338,7 +5356,7 @@
       <c r="K113" s="47"/>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A114" s="59" t="s">
+      <c r="A114" s="55" t="s">
         <v>392</v>
       </c>
       <c r="B114" s="5" t="s">
@@ -5363,7 +5381,7 @@
       <c r="K114" s="46"/>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A115" s="59" t="s">
+      <c r="A115" s="55" t="s">
         <v>392</v>
       </c>
       <c r="B115" s="5" t="s">
@@ -5392,33 +5410,59 @@
       <c r="K115" s="48"/>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A116" s="59"/>
-      <c r="B116" s="5"/>
-      <c r="C116" s="5"/>
-      <c r="D116" s="6"/>
+      <c r="A116" s="55" t="s">
+        <v>401</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="E116" s="6"/>
       <c r="F116" s="6"/>
       <c r="G116" s="7"/>
-      <c r="H116" s="8"/>
+      <c r="H116" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I116" s="9"/>
-      <c r="J116" s="26"/>
+      <c r="J116" s="26" t="s">
+        <v>406</v>
+      </c>
       <c r="K116" s="46"/>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A117" s="59"/>
-      <c r="B117" s="5"/>
-      <c r="C117" s="5"/>
-      <c r="D117" s="6"/>
-      <c r="E117" s="6"/>
+      <c r="A117" s="55" t="s">
+        <v>403</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>407</v>
+      </c>
       <c r="F117" s="6"/>
       <c r="G117" s="7"/>
-      <c r="H117" s="8"/>
+      <c r="H117" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I117" s="9"/>
-      <c r="J117" s="23"/>
+      <c r="J117" s="23" t="s">
+        <v>405</v>
+      </c>
       <c r="K117" s="48"/>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A118" s="59"/>
+      <c r="A118" s="55"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
       <c r="D118" s="6"/>
@@ -5431,7 +5475,7 @@
       <c r="K118" s="46"/>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A119" s="59"/>
+      <c r="A119" s="55"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
       <c r="D119" s="6"/>
@@ -5444,7 +5488,7 @@
       <c r="K119" s="48"/>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A120" s="59"/>
+      <c r="A120" s="55"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
       <c r="D120" s="6"/>
@@ -5457,7 +5501,7 @@
       <c r="K120" s="46"/>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A121" s="59"/>
+      <c r="A121" s="55"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
       <c r="D121" s="6"/>
@@ -5470,7 +5514,7 @@
       <c r="K121" s="49"/>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A122" s="59"/>
+      <c r="A122" s="55"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
       <c r="D122" s="6"/>
@@ -5483,7 +5527,7 @@
       <c r="K122" s="46"/>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A123" s="59"/>
+      <c r="A123" s="55"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
       <c r="D123" s="6"/>
@@ -5496,7 +5540,7 @@
       <c r="K123" s="48"/>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A124" s="59"/>
+      <c r="A124" s="55"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
       <c r="D124" s="6"/>
@@ -5509,7 +5553,7 @@
       <c r="K124" s="46"/>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A125" s="59"/>
+      <c r="A125" s="55"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
       <c r="D125" s="6"/>
@@ -5522,7 +5566,7 @@
       <c r="K125" s="48"/>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A126" s="59"/>
+      <c r="A126" s="55"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
       <c r="D126" s="6"/>
@@ -5535,7 +5579,7 @@
       <c r="K126" s="46"/>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A127" s="59"/>
+      <c r="A127" s="55"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
       <c r="D127" s="6"/>
@@ -5613,43 +5657,43 @@
       <c r="K132" s="50"/>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A133" s="55"/>
-      <c r="B133" s="55"/>
-      <c r="C133" s="55"/>
-      <c r="D133" s="56"/>
-      <c r="E133" s="56"/>
-      <c r="F133" s="56"/>
+      <c r="A133" s="5"/>
+      <c r="B133" s="5"/>
+      <c r="C133" s="5"/>
+      <c r="D133" s="6"/>
+      <c r="E133" s="6"/>
+      <c r="F133" s="6"/>
       <c r="G133" s="19"/>
       <c r="H133" s="18"/>
-      <c r="I133" s="57"/>
-      <c r="J133" s="56"/>
-      <c r="K133" s="58"/>
+      <c r="I133" s="9"/>
+      <c r="J133" s="6"/>
+      <c r="K133" s="41"/>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A134" s="55"/>
-      <c r="B134" s="55"/>
-      <c r="C134" s="55"/>
-      <c r="D134" s="56"/>
-      <c r="E134" s="56"/>
-      <c r="F134" s="56"/>
+      <c r="A134" s="5"/>
+      <c r="B134" s="5"/>
+      <c r="C134" s="5"/>
+      <c r="D134" s="6"/>
+      <c r="E134" s="6"/>
+      <c r="F134" s="6"/>
       <c r="G134" s="19"/>
       <c r="H134" s="18"/>
-      <c r="I134" s="57"/>
-      <c r="J134" s="56"/>
-      <c r="K134" s="58"/>
+      <c r="I134" s="9"/>
+      <c r="J134" s="6"/>
+      <c r="K134" s="41"/>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A135" s="55"/>
-      <c r="B135" s="55"/>
-      <c r="C135" s="55"/>
-      <c r="D135" s="56"/>
-      <c r="E135" s="56"/>
-      <c r="F135" s="56"/>
+      <c r="A135" s="5"/>
+      <c r="B135" s="5"/>
+      <c r="C135" s="5"/>
+      <c r="D135" s="6"/>
+      <c r="E135" s="6"/>
+      <c r="F135" s="6"/>
       <c r="G135" s="19"/>
       <c r="H135" s="18"/>
-      <c r="I135" s="57"/>
-      <c r="J135" s="56"/>
-      <c r="K135" s="58"/>
+      <c r="I135" s="9"/>
+      <c r="J135" s="6"/>
+      <c r="K135" s="41"/>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H136"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1FF6446-C2B6-EE49-A2A7-C44B88E6F63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1545CA0B-0815-7F43-8ECB-87B63DDE743E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="320" yWindow="3740" windowWidth="28360" windowHeight="16680" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
+    <workbookView xWindow="320" yWindow="2960" windowWidth="29920" windowHeight="16680" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
   <sheets>
     <sheet name="network" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="410">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -908,15 +908,9 @@
     <t>192.168.201.110</t>
   </si>
   <si>
-    <t>2411-1330</t>
-  </si>
-  <si>
     <t>2507-1000</t>
   </si>
   <si>
-    <t>NDI</t>
-  </si>
-  <si>
     <t>192.168.204.32</t>
   </si>
   <si>
@@ -1323,6 +1317,15 @@
   </si>
   <si>
     <t>Dynamic</t>
+  </si>
+  <si>
+    <t>2411-1300</t>
+  </si>
+  <si>
+    <t>SDI2NDI</t>
+  </si>
+  <si>
+    <t>NDI2HDMI</t>
   </si>
 </sst>
 </file>
@@ -1983,9 +1986,6 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K135" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="A1:K135" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K132">
-    <sortCondition ref="C2:C132"/>
-  </sortState>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{EF2C341F-E5C1-604C-942C-FB7E9F76F1CD}" name="AssetTag" dataDxfId="10"/>
     <tableColumn id="13" xr3:uid="{41250547-1480-7146-952C-14798A4748DA}" name="NIC" dataDxfId="9"/>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>100</v>
@@ -2418,7 +2418,7 @@
         <v>195</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -2470,7 +2470,7 @@
         <v>203</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -2524,7 +2524,7 @@
         <v>219</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -2576,7 +2576,7 @@
         <v>206</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -2592,22 +2592,22 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="29" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>229</v>
@@ -2617,28 +2617,28 @@
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K11" s="44"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>229</v>
@@ -2648,25 +2648,25 @@
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K12" s="43"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>387</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>389</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="7" t="s">
@@ -2677,28 +2677,28 @@
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K13" s="43"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>229</v>
@@ -2708,28 +2708,28 @@
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K14" s="43"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>229</v>
@@ -2739,28 +2739,28 @@
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K15" s="43"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>229</v>
@@ -2770,28 +2770,28 @@
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K16" s="43"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="29" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>229</v>
@@ -2801,28 +2801,28 @@
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K17" s="44"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="29" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F18" s="29" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>229</v>
@@ -2832,28 +2832,28 @@
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K18" s="44"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>229</v>
@@ -2863,28 +2863,28 @@
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K19" s="43"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="29" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>229</v>
@@ -2894,26 +2894,26 @@
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K20" s="44"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B21" s="29"/>
       <c r="C21" s="29" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F21" s="29" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="8"/>
@@ -3066,7 +3066,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5" t="s">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>35</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="K31" s="41"/>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="K32" s="41"/>
     </row>
@@ -3254,20 +3254,20 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="8"/>
@@ -3277,20 +3277,20 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B35" s="29"/>
       <c r="C35" s="29" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G35" s="19"/>
       <c r="H35" s="8"/>
@@ -3300,20 +3300,20 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B36" s="29"/>
       <c r="C36" s="29" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="8"/>
@@ -3323,20 +3323,20 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="8"/>
@@ -3346,227 +3346,227 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B38" s="29"/>
       <c r="C38" s="29" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="8"/>
       <c r="I38" s="9"/>
       <c r="J38" s="6"/>
       <c r="K38" s="41" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B39" s="29"/>
       <c r="C39" s="29" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F39" s="29" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="8"/>
       <c r="I39" s="9"/>
       <c r="J39" s="6"/>
       <c r="K39" s="41" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="29" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F40" s="29" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="8"/>
       <c r="I40" s="9"/>
       <c r="J40" s="6"/>
       <c r="K40" s="41" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="8"/>
       <c r="I41" s="9"/>
       <c r="J41" s="6"/>
       <c r="K41" s="41" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="8"/>
       <c r="I42" s="9"/>
       <c r="J42" s="6"/>
       <c r="K42" s="41" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="8"/>
       <c r="I43" s="9"/>
       <c r="J43" s="6"/>
       <c r="K43" s="41" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="8"/>
       <c r="I44" s="9"/>
       <c r="J44" s="6"/>
       <c r="K44" s="41" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B45" s="29"/>
       <c r="C45" s="29" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E45" s="29" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F45" s="29" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="8"/>
       <c r="I45" s="9"/>
       <c r="J45" s="6"/>
       <c r="K45" s="41" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B46" s="29"/>
       <c r="C46" s="29" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E46" s="29" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G46" s="19"/>
       <c r="H46" s="8"/>
       <c r="I46" s="9"/>
       <c r="J46" s="6"/>
       <c r="K46" s="41" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
@@ -3690,7 +3690,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="31" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B51" s="13"/>
       <c r="C51" s="5" t="s">
@@ -4012,17 +4012,17 @@
     </row>
     <row r="62" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="19"/>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K62" s="41">
         <v>12</v>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>100</v>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>100</v>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H67" s="18" t="s">
         <v>166</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="F68" s="6"/>
       <c r="G68" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H68" s="18" t="s">
         <v>166</v>
@@ -4206,17 +4206,17 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="53" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F69" s="6"/>
       <c r="G69" s="19" t="s">
@@ -4227,25 +4227,25 @@
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="K69" s="44" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="53" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D70" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F70" s="6"/>
       <c r="G70" s="19" t="s">
@@ -4256,10 +4256,10 @@
       </c>
       <c r="I70" s="9"/>
       <c r="J70" s="38" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="K70" s="43" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>35</v>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>35</v>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="B77" s="25"/>
       <c r="C77" s="33" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D77" s="54" t="s">
         <v>100</v>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="K77" s="41">
         <v>18</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="B79" s="25"/>
       <c r="C79" s="26" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D79" s="54" t="s">
         <v>100</v>
@@ -4512,13 +4512,13 @@
         <v>156</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="8"/>
       <c r="I79" s="9"/>
       <c r="J79" s="29" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="K79" s="43">
         <v>14</v>
@@ -4526,7 +4526,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B80" s="25" t="s">
         <v>174</v>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="B81" s="27"/>
       <c r="C81" s="28" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>35</v>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B82" s="25"/>
       <c r="C82" s="26" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D82" s="54" t="s">
         <v>100</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="B85" s="25"/>
       <c r="C85" s="23" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D85" s="54" t="s">
         <v>100</v>
@@ -4813,17 +4813,17 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>270</v>
+        <v>407</v>
       </c>
       <c r="B90" s="25"/>
       <c r="C90" s="26" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E90" s="33" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F90" s="33"/>
       <c r="G90" s="19" t="s">
@@ -4834,23 +4834,23 @@
       </c>
       <c r="I90" s="9"/>
       <c r="J90" s="33" t="s">
-        <v>272</v>
+        <v>408</v>
       </c>
       <c r="K90" s="47"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" s="25" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B91" s="5"/>
       <c r="C91" s="26" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E91" s="33" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F91" s="33"/>
       <c r="G91" s="19" t="s">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="I91" s="9"/>
       <c r="J91" s="33" t="s">
-        <v>272</v>
+        <v>409</v>
       </c>
       <c r="K91" s="47">
         <v>13</v>
@@ -4925,7 +4925,7 @@
         <v>183</v>
       </c>
       <c r="C94" s="26" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D94" s="54" t="s">
         <v>100</v>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="F96" s="33"/>
       <c r="G96" s="19" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H96" s="8" t="s">
         <v>166</v>
@@ -5013,7 +5013,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="25" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="26"/>
@@ -5021,7 +5021,7 @@
         <v>100</v>
       </c>
       <c r="E98" s="33" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F98" s="33"/>
       <c r="G98" s="19"/>
@@ -5080,7 +5080,7 @@
         <v>161</v>
       </c>
       <c r="C101" s="26" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D101" s="54" t="s">
         <v>100</v>
@@ -5357,19 +5357,19 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="55" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>161</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F114" s="6"/>
       <c r="G114" s="7"/>
@@ -5382,42 +5382,42 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="55" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F115" s="6"/>
       <c r="G115" s="7" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H115" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I115" s="9"/>
       <c r="J115" s="23" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="K115" s="48"/>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" s="55" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>100</v>
@@ -5430,25 +5430,25 @@
       </c>
       <c r="I116" s="9"/>
       <c r="J116" s="26" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="K116" s="46"/>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" s="55" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="F117" s="6"/>
       <c r="G117" s="7"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="23" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="K117" s="48"/>
     </row>

--- a/network.xlsx
+++ b/network.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1545CA0B-0815-7F43-8ECB-87B63DDE743E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC0DBB0-CD25-D446-8C82-2C50AABAB715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="320" yWindow="2960" windowWidth="29920" windowHeight="16680" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="418">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -1316,9 +1316,6 @@
     <t>192.168.201.115</t>
   </si>
   <si>
-    <t>Dynamic</t>
-  </si>
-  <si>
     <t>2411-1300</t>
   </si>
   <si>
@@ -1326,6 +1323,33 @@
   </si>
   <si>
     <t>NDI2HDMI</t>
+  </si>
+  <si>
+    <t>2603-1204</t>
+  </si>
+  <si>
+    <t>60-83-E7-42-0F-D7</t>
+  </si>
+  <si>
+    <t>192.168.201.1</t>
+  </si>
+  <si>
+    <t>AVNet Router</t>
+  </si>
+  <si>
+    <t>LAN5</t>
+  </si>
+  <si>
+    <t>WAN1</t>
+  </si>
+  <si>
+    <t>60-83-E7-42-0F-D8</t>
+  </si>
+  <si>
+    <t>192.168.0.220</t>
+  </si>
+  <si>
+    <t>Bridge to ITNet</t>
   </si>
 </sst>
 </file>
@@ -4813,7 +4837,7 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B90" s="25"/>
       <c r="C90" s="26" t="s">
@@ -4834,7 +4858,7 @@
       </c>
       <c r="I90" s="9"/>
       <c r="J90" s="33" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K90" s="47"/>
     </row>
@@ -4861,7 +4885,7 @@
       </c>
       <c r="I91" s="9"/>
       <c r="J91" s="33" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K91" s="47">
         <v>13</v>
@@ -5445,7 +5469,7 @@
         <v>402</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>406</v>
+        <v>35</v>
       </c>
       <c r="E117" s="6" t="s">
         <v>405</v>
@@ -5462,29 +5486,55 @@
       <c r="K117" s="48"/>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A118" s="55"/>
-      <c r="B118" s="5"/>
-      <c r="C118" s="5"/>
-      <c r="D118" s="6"/>
-      <c r="E118" s="6"/>
+      <c r="A118" s="55" t="s">
+        <v>409</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>411</v>
+      </c>
       <c r="F118" s="6"/>
       <c r="G118" s="7"/>
-      <c r="H118" s="8"/>
+      <c r="H118" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I118" s="9"/>
-      <c r="J118" s="26"/>
+      <c r="J118" s="26" t="s">
+        <v>412</v>
+      </c>
       <c r="K118" s="46"/>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A119" s="55"/>
-      <c r="B119" s="5"/>
-      <c r="C119" s="5"/>
-      <c r="D119" s="6"/>
-      <c r="E119" s="6"/>
+      <c r="A119" s="55" t="s">
+        <v>409</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>416</v>
+      </c>
       <c r="F119" s="6"/>
       <c r="G119" s="7"/>
       <c r="H119" s="8"/>
       <c r="I119" s="9"/>
-      <c r="J119" s="23"/>
+      <c r="J119" s="23" t="s">
+        <v>417</v>
+      </c>
       <c r="K119" s="48"/>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">

--- a/network.xlsx
+++ b/network.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC0DBB0-CD25-D446-8C82-2C50AABAB715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FA0AE8-5F8C-D641-A85B-057DEC6DFE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="320" yWindow="2960" windowWidth="29920" windowHeight="16680" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="420">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -1350,6 +1350,12 @@
   </si>
   <si>
     <t>Bridge to ITNet</t>
+  </si>
+  <si>
+    <t>192.169.201.114</t>
+  </si>
+  <si>
+    <t>Not sure the IP will be picked up correcty</t>
   </si>
 </sst>
 </file>
@@ -5444,9 +5450,11 @@
         <v>400</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E116" s="6"/>
+        <v>35</v>
+      </c>
+      <c r="E116" s="6" t="s">
+        <v>418</v>
+      </c>
       <c r="F116" s="6"/>
       <c r="G116" s="7"/>
       <c r="H116" s="8" t="s">
@@ -5456,7 +5464,9 @@
       <c r="J116" s="26" t="s">
         <v>404</v>
       </c>
-      <c r="K116" s="46"/>
+      <c r="K116" s="46" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" s="55" t="s">

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FA0AE8-5F8C-D641-A85B-057DEC6DFE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175679B4-B78B-5B4B-9E36-8C37992ABEA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="320" yWindow="2960" windowWidth="29920" windowHeight="16680" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="429">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -836,9 +836,6 @@
     <t>2602-2200</t>
   </si>
   <si>
-    <t>USBNIC for PremNet</t>
-  </si>
-  <si>
     <t>Manage via Dante Controller.</t>
   </si>
   <si>
@@ -1356,6 +1353,36 @@
   </si>
   <si>
     <t>Not sure the IP will be picked up correcty</t>
+  </si>
+  <si>
+    <t>2601-0600</t>
+  </si>
+  <si>
+    <t>192.168.207.102</t>
+  </si>
+  <si>
+    <t>Library TV Control</t>
+  </si>
+  <si>
+    <t>B0:F2:F6:78:9E:BC</t>
+  </si>
+  <si>
+    <t>2410-1607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USBNIC for cumu-g002 on ITNet </t>
+  </si>
+  <si>
+    <t>192.168.0.119</t>
+  </si>
+  <si>
+    <t>en1 wifi</t>
+  </si>
+  <si>
+    <t>80:6d:97:20:a7:89</t>
+  </si>
+  <si>
+    <t>builtin AVNET</t>
   </si>
 </sst>
 </file>
@@ -2015,7 +2042,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K135" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K135" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
+  <autoFilter ref="A1:K135" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="CUMU-G002"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{EF2C341F-E5C1-604C-942C-FB7E9F76F1CD}" name="AssetTag" dataDxfId="10"/>
     <tableColumn id="13" xr3:uid="{41250547-1480-7146-952C-14798A4748DA}" name="NIC" dataDxfId="9"/>
@@ -2336,7 +2369,7 @@
     <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1640625" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.1640625" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="22.5" customWidth="1"/>
@@ -2383,13 +2416,13 @@
         <v>138</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>236</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>100</v>
@@ -2410,7 +2443,7 @@
       </c>
       <c r="K2" s="41"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>189</v>
       </c>
@@ -2437,7 +2470,7 @@
       </c>
       <c r="K3" s="41"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>189</v>
       </c>
@@ -2448,7 +2481,7 @@
         <v>195</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -2462,7 +2495,7 @@
       </c>
       <c r="K4" s="41"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>207</v>
       </c>
@@ -2489,7 +2522,7 @@
       </c>
       <c r="K5" s="41"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>207</v>
       </c>
@@ -2500,7 +2533,7 @@
         <v>203</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -2514,7 +2547,7 @@
       </c>
       <c r="K6" s="41"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>214</v>
       </c>
@@ -2543,7 +2576,7 @@
       </c>
       <c r="K7" s="41"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>214</v>
       </c>
@@ -2554,7 +2587,7 @@
         <v>219</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -2568,7 +2601,7 @@
       </c>
       <c r="K8" s="41"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>213</v>
       </c>
@@ -2595,7 +2628,7 @@
       </c>
       <c r="K9" s="41"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>213</v>
       </c>
@@ -2606,7 +2639,7 @@
         <v>206</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -2620,24 +2653,24 @@
       </c>
       <c r="K10" s="41"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="29" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>229</v>
@@ -2647,28 +2680,28 @@
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K11" s="44"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>229</v>
@@ -2678,25 +2711,25 @@
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K12" s="43"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="7" t="s">
@@ -2707,28 +2740,28 @@
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K13" s="43"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>229</v>
@@ -2738,28 +2771,28 @@
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K14" s="43"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>229</v>
@@ -2769,28 +2802,28 @@
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K15" s="43"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>229</v>
@@ -2800,28 +2833,28 @@
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="K16" s="43"/>
+    </row>
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="29" t="s">
+        <v>345</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="C17" s="29" t="s">
         <v>356</v>
-      </c>
-      <c r="K16" s="43"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="29" t="s">
-        <v>346</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="C17" s="29" t="s">
-        <v>357</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>229</v>
@@ -2831,28 +2864,28 @@
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K17" s="44"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="29" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F18" s="29" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>229</v>
@@ -2862,28 +2895,28 @@
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K18" s="44"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>229</v>
@@ -2893,28 +2926,28 @@
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K19" s="43"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="29" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>229</v>
@@ -2924,26 +2957,26 @@
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K20" s="44"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B21" s="29"/>
       <c r="C21" s="29" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E21" s="29" t="s">
+        <v>288</v>
+      </c>
+      <c r="F21" s="29" t="s">
         <v>289</v>
-      </c>
-      <c r="F21" s="29" t="s">
-        <v>290</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="8"/>
@@ -2951,7 +2984,7 @@
       <c r="J21" s="6"/>
       <c r="K21" s="41"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
         <v>55</v>
       </c>
@@ -2963,7 +2996,7 @@
         <v>35</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
@@ -2971,7 +3004,7 @@
         <v>166</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>44</v>
@@ -2980,7 +3013,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
         <v>45</v>
       </c>
@@ -2992,7 +3025,7 @@
         <v>35</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
@@ -3000,7 +3033,7 @@
         <v>166</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>44</v>
@@ -3009,7 +3042,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
         <v>47</v>
       </c>
@@ -3021,7 +3054,7 @@
         <v>35</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
@@ -3029,7 +3062,7 @@
         <v>166</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>44</v>
@@ -3038,7 +3071,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>49</v>
       </c>
@@ -3050,7 +3083,7 @@
         <v>35</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
@@ -3058,7 +3091,7 @@
         <v>166</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>44</v>
@@ -3067,7 +3100,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>137</v>
       </c>
@@ -3094,13 +3127,13 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>100</v>
@@ -3112,22 +3145,22 @@
       <c r="I27" s="9"/>
       <c r="J27" s="6"/>
       <c r="K27" s="41" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>93</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F28" s="19" t="str">
         <f>CONCATENATE("http://", E28)</f>
@@ -3147,7 +3180,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>41</v>
       </c>
@@ -3173,10 +3206,10 @@
         <v>37</v>
       </c>
       <c r="K29" s="41" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>38</v>
       </c>
@@ -3202,10 +3235,10 @@
         <v>37</v>
       </c>
       <c r="K30" s="41" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>6</v>
       </c>
@@ -3226,11 +3259,11 @@
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="K31" s="41"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>198</v>
       </c>
@@ -3253,11 +3286,11 @@
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K32" s="41"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>220</v>
       </c>
@@ -3282,22 +3315,22 @@
       </c>
       <c r="K33" s="41"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="8"/>
@@ -3305,22 +3338,22 @@
       <c r="J34" s="6"/>
       <c r="K34" s="41"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B35" s="29"/>
       <c r="C35" s="29" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G35" s="19"/>
       <c r="H35" s="8"/>
@@ -3328,22 +3361,22 @@
       <c r="J35" s="6"/>
       <c r="K35" s="41"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B36" s="29"/>
       <c r="C36" s="29" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="8"/>
@@ -3351,22 +3384,22 @@
       <c r="J36" s="6"/>
       <c r="K36" s="41"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="8"/>
@@ -3374,232 +3407,232 @@
       <c r="J37" s="6"/>
       <c r="K37" s="41"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B38" s="29"/>
       <c r="C38" s="29" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="8"/>
       <c r="I38" s="9"/>
       <c r="J38" s="6"/>
       <c r="K38" s="41" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B39" s="29"/>
       <c r="C39" s="29" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F39" s="29" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="8"/>
       <c r="I39" s="9"/>
       <c r="J39" s="6"/>
       <c r="K39" s="41" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="29" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F40" s="29" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="8"/>
       <c r="I40" s="9"/>
       <c r="J40" s="6"/>
       <c r="K40" s="41" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="8"/>
       <c r="I41" s="9"/>
       <c r="J41" s="6"/>
       <c r="K41" s="41" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="8"/>
       <c r="I42" s="9"/>
       <c r="J42" s="6"/>
       <c r="K42" s="41" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="8"/>
       <c r="I43" s="9"/>
       <c r="J43" s="6"/>
       <c r="K43" s="41" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="8"/>
       <c r="I44" s="9"/>
       <c r="J44" s="6"/>
       <c r="K44" s="41" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B45" s="29"/>
       <c r="C45" s="29" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E45" s="29" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F45" s="29" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="8"/>
       <c r="I45" s="9"/>
       <c r="J45" s="6"/>
       <c r="K45" s="41" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B46" s="29"/>
       <c r="C46" s="29" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E46" s="29" t="s">
+        <v>277</v>
+      </c>
+      <c r="F46" s="29" t="s">
         <v>278</v>
-      </c>
-      <c r="F46" s="29" t="s">
-        <v>279</v>
       </c>
       <c r="G46" s="19"/>
       <c r="H46" s="8"/>
       <c r="I46" s="9"/>
       <c r="J46" s="6"/>
       <c r="K46" s="41" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>108</v>
       </c>
@@ -3629,7 +3662,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>103</v>
       </c>
@@ -3659,7 +3692,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>86</v>
       </c>
@@ -3689,7 +3722,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>232</v>
       </c>
@@ -3718,9 +3751,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="31" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B51" s="13"/>
       <c r="C51" s="5" t="s">
@@ -3743,7 +3776,7 @@
       <c r="J51" s="6"/>
       <c r="K51" s="41"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
         <v>27</v>
       </c>
@@ -3773,7 +3806,7 @@
       </c>
       <c r="K52" s="42"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
         <v>2</v>
       </c>
@@ -3803,7 +3836,7 @@
       </c>
       <c r="K53" s="42"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
         <v>130</v>
       </c>
@@ -3826,7 +3859,7 @@
       </c>
       <c r="K54" s="42"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
         <v>7</v>
       </c>
@@ -3856,7 +3889,7 @@
       </c>
       <c r="K55" s="42"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
         <v>0</v>
       </c>
@@ -3886,7 +3919,7 @@
       </c>
       <c r="K56" s="41"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
         <v>24</v>
       </c>
@@ -3916,7 +3949,7 @@
       </c>
       <c r="K57" s="42"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="10" t="s">
         <v>53</v>
       </c>
@@ -3946,7 +3979,7 @@
       </c>
       <c r="K58" s="41"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
         <v>73</v>
       </c>
@@ -3978,7 +4011,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
         <v>116</v>
       </c>
@@ -4008,7 +4041,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
         <v>112</v>
       </c>
@@ -4031,7 +4064,7 @@
         <v>166</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J61" s="6" t="s">
         <v>111</v>
@@ -4040,19 +4073,19 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" ht="17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="19"/>
@@ -4061,13 +4094,13 @@
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K62" s="41">
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
         <v>3</v>
       </c>
@@ -4096,13 +4129,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="17" t="s">
         <v>224</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>100</v>
@@ -4121,13 +4154,13 @@
       </c>
       <c r="K64" s="41"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
         <v>151</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>100</v>
@@ -4148,7 +4181,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
         <v>145</v>
       </c>
@@ -4176,7 +4209,7 @@
       </c>
       <c r="K66" s="41"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
         <v>1</v>
       </c>
@@ -4194,7 +4227,7 @@
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H67" s="18" t="s">
         <v>166</v>
@@ -4205,7 +4238,7 @@
       </c>
       <c r="K67" s="41"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
         <v>1</v>
       </c>
@@ -4223,7 +4256,7 @@
       </c>
       <c r="F68" s="6"/>
       <c r="G68" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H68" s="18" t="s">
         <v>166</v>
@@ -4234,19 +4267,19 @@
       </c>
       <c r="K68" s="41"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="53" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F69" s="6"/>
       <c r="G69" s="19" t="s">
@@ -4257,25 +4290,25 @@
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K69" s="44" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="53" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D70" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F70" s="6"/>
       <c r="G70" s="19" t="s">
@@ -4286,13 +4319,13 @@
       </c>
       <c r="I70" s="9"/>
       <c r="J70" s="38" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K70" s="43" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
         <v>97</v>
       </c>
@@ -4312,7 +4345,7 @@
         <v>166</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J71" s="6" t="s">
         <v>96</v>
@@ -4321,7 +4354,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
         <v>60</v>
       </c>
@@ -4346,7 +4379,7 @@
         <v>166</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J72" s="6" t="s">
         <v>59</v>
@@ -4355,19 +4388,19 @@
         <v>56</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F73" s="6"/>
       <c r="G73" s="7" t="s">
@@ -4382,19 +4415,19 @@
       </c>
       <c r="K73" s="41"/>
     </row>
-    <row r="74" spans="1:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A74" s="22" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F74" s="6"/>
       <c r="G74" s="7" t="s">
@@ -4409,7 +4442,7 @@
       </c>
       <c r="K74" s="41"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
         <v>81</v>
       </c>
@@ -4432,7 +4465,7 @@
         <v>166</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J75" s="6" t="s">
         <v>77</v>
@@ -4441,7 +4474,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="6" t="s">
         <v>78</v>
       </c>
@@ -4464,7 +4497,7 @@
         <v>166</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J76" s="6" t="s">
         <v>77</v>
@@ -4473,13 +4506,13 @@
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
         <v>158</v>
       </c>
       <c r="B77" s="25"/>
       <c r="C77" s="33" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D77" s="54" t="s">
         <v>100</v>
@@ -4494,13 +4527,13 @@
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K77" s="41">
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="6" t="s">
         <v>91</v>
       </c>
@@ -4527,13 +4560,13 @@
         <v>87</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
         <v>159</v>
       </c>
       <c r="B79" s="25"/>
       <c r="C79" s="26" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D79" s="54" t="s">
         <v>100</v>
@@ -4542,21 +4575,21 @@
         <v>156</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="8"/>
       <c r="I79" s="9"/>
       <c r="J79" s="29" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K79" s="43">
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B80" s="25" t="s">
         <v>174</v>
@@ -4583,19 +4616,19 @@
       </c>
       <c r="K80" s="41"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B81" s="27"/>
       <c r="C81" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E81" s="35" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F81" s="35"/>
       <c r="G81" s="7" t="s">
@@ -4610,19 +4643,19 @@
       </c>
       <c r="K81" s="41"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B82" s="25"/>
       <c r="C82" s="26" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D82" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E82" s="33" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F82" s="33"/>
       <c r="G82" s="19"/>
@@ -4631,7 +4664,7 @@
       </c>
       <c r="I82" s="9"/>
       <c r="J82" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K82" s="41"/>
     </row>
@@ -4658,7 +4691,7 @@
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="6" t="s">
-        <v>164</v>
+        <v>428</v>
       </c>
       <c r="K83" s="41">
         <v>10</v>
@@ -4669,7 +4702,7 @@
         <v>168</v>
       </c>
       <c r="B84" s="25" t="s">
-        <v>175</v>
+        <v>426</v>
       </c>
       <c r="C84" s="26" t="s">
         <v>184</v>
@@ -4693,19 +4726,19 @@
       </c>
       <c r="K84" s="41"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B85" s="25"/>
       <c r="C85" s="23" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D85" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F85" s="33"/>
       <c r="G85" s="19" t="s">
@@ -4716,13 +4749,13 @@
       </c>
       <c r="I85" s="9"/>
       <c r="J85" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K85" s="44">
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="30" t="s">
         <v>65</v>
       </c>
@@ -4754,7 +4787,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="52" t="s">
         <v>69</v>
       </c>
@@ -4786,7 +4819,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="32" t="s">
         <v>18</v>
       </c>
@@ -4811,7 +4844,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6" t="s">
         <v>120</v>
       </c>
@@ -4841,19 +4874,19 @@
         <v>70</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B90" s="25"/>
       <c r="C90" s="26" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E90" s="33" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F90" s="33"/>
       <c r="G90" s="19" t="s">
@@ -4864,23 +4897,23 @@
       </c>
       <c r="I90" s="9"/>
       <c r="J90" s="33" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="K90" s="47"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="25" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B91" s="5"/>
       <c r="C91" s="26" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E91" s="33" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F91" s="33"/>
       <c r="G91" s="19" t="s">
@@ -4891,13 +4924,13 @@
       </c>
       <c r="I91" s="9"/>
       <c r="J91" s="33" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K91" s="47">
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
         <v>14</v>
       </c>
@@ -4922,7 +4955,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="25" t="s">
         <v>152</v>
       </c>
@@ -4947,7 +4980,7 @@
       </c>
       <c r="K93" s="47"/>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
         <v>3</v>
       </c>
@@ -4955,7 +4988,7 @@
         <v>183</v>
       </c>
       <c r="C94" s="26" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D94" s="54" t="s">
         <v>100</v>
@@ -4974,7 +5007,7 @@
       </c>
       <c r="K94" s="47"/>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6" t="s">
         <v>20</v>
       </c>
@@ -4997,7 +5030,7 @@
       </c>
       <c r="K95" s="47"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="25" t="s">
         <v>245</v>
       </c>
@@ -5011,7 +5044,7 @@
       </c>
       <c r="F96" s="33"/>
       <c r="G96" s="19" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H96" s="8" t="s">
         <v>166</v>
@@ -5022,7 +5055,7 @@
       </c>
       <c r="K96" s="47"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="25" t="s">
         <v>235</v>
       </c>
@@ -5041,9 +5074,9 @@
       <c r="J97" s="33"/>
       <c r="K97" s="47"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="25" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="26"/>
@@ -5051,7 +5084,7 @@
         <v>100</v>
       </c>
       <c r="E98" s="33" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F98" s="33"/>
       <c r="G98" s="19"/>
@@ -5062,7 +5095,7 @@
       <c r="J98" s="33"/>
       <c r="K98" s="47"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="27" t="s">
         <v>9</v>
       </c>
@@ -5083,7 +5116,7 @@
       </c>
       <c r="K99" s="45"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="25" t="s">
         <v>234</v>
       </c>
@@ -5102,7 +5135,7 @@
       <c r="J100" s="33"/>
       <c r="K100" s="47"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
         <v>3</v>
       </c>
@@ -5110,7 +5143,7 @@
         <v>161</v>
       </c>
       <c r="C101" s="26" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D101" s="54" t="s">
         <v>100</v>
@@ -5127,28 +5160,34 @@
     </row>
     <row r="102" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B102" s="25"/>
-      <c r="C102" s="26"/>
+        <v>423</v>
+      </c>
+      <c r="B102" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C102" s="26" t="s">
+        <v>427</v>
+      </c>
       <c r="D102" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E102" s="33"/>
+      <c r="E102" s="33" t="s">
+        <v>425</v>
+      </c>
       <c r="F102" s="36"/>
       <c r="G102" s="7"/>
       <c r="H102" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J102" s="33" t="s">
-        <v>246</v>
+        <v>424</v>
       </c>
       <c r="K102" s="47"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="30" t="s">
         <v>33</v>
       </c>
@@ -5169,7 +5208,7 @@
       </c>
       <c r="K103" s="47"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="30" t="s">
         <v>32</v>
       </c>
@@ -5190,7 +5229,7 @@
       </c>
       <c r="K104" s="47"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="30" t="s">
         <v>29</v>
       </c>
@@ -5211,7 +5250,7 @@
       </c>
       <c r="K105" s="47"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="30" t="s">
         <v>28</v>
       </c>
@@ -5232,7 +5271,7 @@
       </c>
       <c r="K106" s="47"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="30" t="s">
         <v>23</v>
       </c>
@@ -5255,7 +5294,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="30" t="s">
         <v>31</v>
       </c>
@@ -5276,7 +5315,7 @@
       </c>
       <c r="K108" s="47"/>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="30" t="s">
         <v>25</v>
       </c>
@@ -5297,7 +5336,7 @@
       </c>
       <c r="K109" s="47"/>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="30" t="s">
         <v>30</v>
       </c>
@@ -5318,7 +5357,7 @@
       </c>
       <c r="K110" s="47"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="30" t="s">
         <v>26</v>
       </c>
@@ -5339,7 +5378,7 @@
       </c>
       <c r="K111" s="47"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="6" t="s">
         <v>41</v>
       </c>
@@ -5362,7 +5401,7 @@
       </c>
       <c r="K112" s="45"/>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="6" t="s">
         <v>38</v>
       </c>
@@ -5385,21 +5424,21 @@
       </c>
       <c r="K113" s="47"/>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>161</v>
       </c>
       <c r="C114" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="E114" s="6" t="s">
         <v>392</v>
-      </c>
-      <c r="D114" s="6" t="s">
-        <v>398</v>
-      </c>
-      <c r="E114" s="6" t="s">
-        <v>393</v>
       </c>
       <c r="F114" s="6"/>
       <c r="G114" s="7"/>
@@ -5410,50 +5449,50 @@
       <c r="J114" s="26"/>
       <c r="K114" s="46"/>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="55" t="s">
+        <v>389</v>
+      </c>
+      <c r="B115" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="B115" s="5" t="s">
-        <v>391</v>
-      </c>
       <c r="C115" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F115" s="6"/>
       <c r="G115" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H115" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I115" s="9"/>
       <c r="J115" s="23" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K115" s="48"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="55" t="s">
+        <v>398</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="C116" s="5" t="s">
         <v>399</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>400</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F116" s="6"/>
       <c r="G116" s="7"/>
@@ -5462,27 +5501,27 @@
       </c>
       <c r="I116" s="9"/>
       <c r="J116" s="26" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K116" s="46" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="55" t="s">
+        <v>400</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="C117" s="5" t="s">
         <v>401</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>402</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F117" s="6"/>
       <c r="G117" s="7"/>
@@ -5491,25 +5530,25 @@
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="23" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K117" s="48"/>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="55" t="s">
+        <v>408</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="C118" s="5" t="s">
         <v>409</v>
-      </c>
-      <c r="B118" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>410</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F118" s="6"/>
       <c r="G118" s="7"/>
@@ -5518,49 +5557,63 @@
       </c>
       <c r="I118" s="9"/>
       <c r="J118" s="26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="K118" s="46"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="55" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B119" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="C119" s="5" t="s">
         <v>414</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>415</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F119" s="6"/>
       <c r="G119" s="7"/>
       <c r="H119" s="8"/>
       <c r="I119" s="9"/>
       <c r="J119" s="23" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="K119" s="48"/>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A120" s="55"/>
-      <c r="B120" s="5"/>
-      <c r="C120" s="5"/>
-      <c r="D120" s="6"/>
-      <c r="E120" s="6"/>
+    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="55" t="s">
+        <v>419</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>420</v>
+      </c>
       <c r="F120" s="6"/>
       <c r="G120" s="7"/>
-      <c r="H120" s="8"/>
+      <c r="H120" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I120" s="9"/>
-      <c r="J120" s="26"/>
+      <c r="J120" s="26" t="s">
+        <v>421</v>
+      </c>
       <c r="K120" s="46"/>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="55"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -5573,7 +5626,7 @@
       <c r="J121" s="24"/>
       <c r="K121" s="49"/>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="55"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -5586,7 +5639,7 @@
       <c r="J122" s="26"/>
       <c r="K122" s="46"/>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="55"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -5599,7 +5652,7 @@
       <c r="J123" s="23"/>
       <c r="K123" s="48"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="55"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -5612,7 +5665,7 @@
       <c r="J124" s="26"/>
       <c r="K124" s="46"/>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="55"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -5625,7 +5678,7 @@
       <c r="J125" s="23"/>
       <c r="K125" s="48"/>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="55"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -5638,7 +5691,7 @@
       <c r="J126" s="26"/>
       <c r="K126" s="46"/>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="55"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -5651,7 +5704,7 @@
       <c r="J127" s="23"/>
       <c r="K127" s="48"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="5"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -5664,7 +5717,7 @@
       <c r="J128" s="26"/>
       <c r="K128" s="46"/>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="5"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -5677,7 +5730,7 @@
       <c r="J129" s="24"/>
       <c r="K129" s="49"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -5690,7 +5743,7 @@
       <c r="J130" s="26"/>
       <c r="K130" s="46"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="5"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -5703,7 +5756,7 @@
       <c r="J131" s="23"/>
       <c r="K131" s="48"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="5"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -5716,7 +5769,7 @@
       <c r="J132" s="28"/>
       <c r="K132" s="50"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="5"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -5729,7 +5782,7 @@
       <c r="J133" s="6"/>
       <c r="K133" s="41"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="5"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -5742,7 +5795,7 @@
       <c r="J134" s="6"/>
       <c r="K134" s="41"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="5"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175679B4-B78B-5B4B-9E36-8C37992ABEA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FF314F-24EB-D54E-8C05-752BA5BAE09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="320" yWindow="2960" windowWidth="29920" windowHeight="16680" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="438">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -839,18 +839,6 @@
     <t>Manage via Dante Controller.</t>
   </si>
   <si>
-    <t>192.168.200.134</t>
-  </si>
-  <si>
-    <t>192.168.200.154</t>
-  </si>
-  <si>
-    <t>192.168.200.132</t>
-  </si>
-  <si>
-    <t>192.168.200.170</t>
-  </si>
-  <si>
     <t>KB0034</t>
   </si>
   <si>
@@ -1244,12 +1232,6 @@
     <t>notag45</t>
   </si>
   <si>
-    <t>pending93</t>
-  </si>
-  <si>
-    <t>pending100</t>
-  </si>
-  <si>
     <t>dante_control</t>
   </si>
   <si>
@@ -1383,6 +1365,51 @@
   </si>
   <si>
     <t>builtin AVNET</t>
+  </si>
+  <si>
+    <t>80:6d: 97:20:a7:8e</t>
+  </si>
+  <si>
+    <t>14:98:77:81:27:3f</t>
+  </si>
+  <si>
+    <t>172.31.99.182</t>
+  </si>
+  <si>
+    <t>SSID UAC</t>
+  </si>
+  <si>
+    <t>2509-1704</t>
+  </si>
+  <si>
+    <t>2509-1705</t>
+  </si>
+  <si>
+    <t>00-0E-DD-2C-03-83</t>
+  </si>
+  <si>
+    <t>00-0E-DD-2C-02-C8</t>
+  </si>
+  <si>
+    <t>192.168.200.116</t>
+  </si>
+  <si>
+    <t>192.168.200.117</t>
+  </si>
+  <si>
+    <t>IEM xmtr</t>
+  </si>
+  <si>
+    <t>unused</t>
+  </si>
+  <si>
+    <t>192.168.200.150</t>
+  </si>
+  <si>
+    <t>192.168.200.152</t>
+  </si>
+  <si>
+    <t>192.168.200.153</t>
   </si>
 </sst>
 </file>
@@ -2042,13 +2069,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K135" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K135" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="CUMU-G002"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K135" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{EF2C341F-E5C1-604C-942C-FB7E9F76F1CD}" name="AssetTag" dataDxfId="10"/>
     <tableColumn id="13" xr3:uid="{41250547-1480-7146-952C-14798A4748DA}" name="NIC" dataDxfId="9"/>
@@ -2369,7 +2390,7 @@
     <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1640625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" customWidth="1"/>
     <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.1640625" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="22.5" customWidth="1"/>
@@ -2416,13 +2437,13 @@
         <v>138</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>236</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>100</v>
@@ -2443,7 +2464,7 @@
       </c>
       <c r="K2" s="41"/>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>189</v>
       </c>
@@ -2470,7 +2491,7 @@
       </c>
       <c r="K3" s="41"/>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>189</v>
       </c>
@@ -2481,7 +2502,7 @@
         <v>195</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -2495,7 +2516,7 @@
       </c>
       <c r="K4" s="41"/>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>207</v>
       </c>
@@ -2522,7 +2543,7 @@
       </c>
       <c r="K5" s="41"/>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>207</v>
       </c>
@@ -2533,7 +2554,7 @@
         <v>203</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -2547,7 +2568,7 @@
       </c>
       <c r="K6" s="41"/>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>214</v>
       </c>
@@ -2576,7 +2597,7 @@
       </c>
       <c r="K7" s="41"/>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>214</v>
       </c>
@@ -2587,7 +2608,7 @@
         <v>219</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -2601,7 +2622,7 @@
       </c>
       <c r="K8" s="41"/>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>213</v>
       </c>
@@ -2628,7 +2649,7 @@
       </c>
       <c r="K9" s="41"/>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>213</v>
       </c>
@@ -2639,7 +2660,7 @@
         <v>206</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -2653,24 +2674,24 @@
       </c>
       <c r="K10" s="41"/>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="29" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>229</v>
@@ -2680,28 +2701,28 @@
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="5" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="K11" s="44"/>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>229</v>
@@ -2711,25 +2732,25 @@
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="5" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="K12" s="43"/>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="7" t="s">
@@ -2740,28 +2761,28 @@
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="5" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="K13" s="43"/>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>229</v>
@@ -2771,28 +2792,28 @@
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="5" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="K14" s="43"/>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>229</v>
@@ -2802,28 +2823,28 @@
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="5" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="K15" s="43"/>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>229</v>
@@ -2833,28 +2854,28 @@
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="5" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="K16" s="43"/>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="29" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>229</v>
@@ -2864,28 +2885,28 @@
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="5" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="K17" s="44"/>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="29" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F18" s="29" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>229</v>
@@ -2895,28 +2916,28 @@
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="5" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="K18" s="44"/>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>229</v>
@@ -2926,28 +2947,28 @@
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="5" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="K19" s="43"/>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="29" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>229</v>
@@ -2957,26 +2978,26 @@
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="5" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="K20" s="44"/>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B21" s="29"/>
       <c r="C21" s="29" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F21" s="29" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="8"/>
@@ -2984,11 +3005,13 @@
       <c r="J21" s="6"/>
       <c r="K21" s="41"/>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="6"/>
+      <c r="B22" s="6" t="s">
+        <v>190</v>
+      </c>
       <c r="C22" s="20" t="s">
         <v>54</v>
       </c>
@@ -2996,7 +3019,7 @@
         <v>35</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>247</v>
+        <v>435</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
@@ -3004,7 +3027,7 @@
         <v>166</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>44</v>
@@ -3013,11 +3036,13 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="6"/>
+      <c r="B23" s="6" t="s">
+        <v>190</v>
+      </c>
       <c r="C23" s="20" t="s">
         <v>43</v>
       </c>
@@ -3025,7 +3050,7 @@
         <v>35</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>250</v>
+        <v>437</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
@@ -3033,7 +3058,7 @@
         <v>166</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>44</v>
@@ -3042,11 +3067,13 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="6"/>
+      <c r="B24" s="6" t="s">
+        <v>190</v>
+      </c>
       <c r="C24" s="20" t="s">
         <v>46</v>
       </c>
@@ -3054,7 +3081,7 @@
         <v>35</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>249</v>
+        <v>436</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
@@ -3062,7 +3089,7 @@
         <v>166</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>44</v>
@@ -3071,11 +3098,13 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="6"/>
+      <c r="B25" s="6" t="s">
+        <v>190</v>
+      </c>
       <c r="C25" s="20" t="s">
         <v>48</v>
       </c>
@@ -3083,7 +3112,7 @@
         <v>35</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>248</v>
+        <v>361</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
@@ -3091,7 +3120,7 @@
         <v>166</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>44</v>
@@ -3100,7 +3129,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>137</v>
       </c>
@@ -3127,13 +3156,13 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>100</v>
@@ -3145,22 +3174,22 @@
       <c r="I27" s="9"/>
       <c r="J27" s="6"/>
       <c r="K27" s="41" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>93</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F28" s="19" t="str">
         <f>CONCATENATE("http://", E28)</f>
@@ -3180,7 +3209,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>41</v>
       </c>
@@ -3209,7 +3238,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>38</v>
       </c>
@@ -3238,7 +3267,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>6</v>
       </c>
@@ -3259,11 +3288,11 @@
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="K31" s="41"/>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>198</v>
       </c>
@@ -3286,11 +3315,11 @@
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="5" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="K32" s="41"/>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>220</v>
       </c>
@@ -3315,22 +3344,22 @@
       </c>
       <c r="K33" s="41"/>
     </row>
-    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="8"/>
@@ -3338,22 +3367,22 @@
       <c r="J34" s="6"/>
       <c r="K34" s="41"/>
     </row>
-    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B35" s="29"/>
       <c r="C35" s="29" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G35" s="19"/>
       <c r="H35" s="8"/>
@@ -3361,22 +3390,22 @@
       <c r="J35" s="6"/>
       <c r="K35" s="41"/>
     </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B36" s="29"/>
       <c r="C36" s="29" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="8"/>
@@ -3384,22 +3413,22 @@
       <c r="J36" s="6"/>
       <c r="K36" s="41"/>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="8"/>
@@ -3407,232 +3436,232 @@
       <c r="J37" s="6"/>
       <c r="K37" s="41"/>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B38" s="29"/>
       <c r="C38" s="29" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="8"/>
       <c r="I38" s="9"/>
       <c r="J38" s="6"/>
       <c r="K38" s="41" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B39" s="29"/>
       <c r="C39" s="29" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F39" s="29" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="8"/>
       <c r="I39" s="9"/>
       <c r="J39" s="6"/>
       <c r="K39" s="41" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="29" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="F40" s="29" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="8"/>
       <c r="I40" s="9"/>
       <c r="J40" s="6"/>
       <c r="K40" s="41" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="8"/>
       <c r="I41" s="9"/>
       <c r="J41" s="6"/>
       <c r="K41" s="41" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="8"/>
       <c r="I42" s="9"/>
       <c r="J42" s="6"/>
       <c r="K42" s="41" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="8"/>
       <c r="I43" s="9"/>
       <c r="J43" s="6"/>
       <c r="K43" s="41" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="8"/>
       <c r="I44" s="9"/>
       <c r="J44" s="6"/>
       <c r="K44" s="41" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B45" s="29"/>
       <c r="C45" s="29" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E45" s="29" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F45" s="29" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="8"/>
       <c r="I45" s="9"/>
       <c r="J45" s="6"/>
       <c r="K45" s="41" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B46" s="29"/>
       <c r="C46" s="29" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E46" s="29" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G46" s="19"/>
       <c r="H46" s="8"/>
       <c r="I46" s="9"/>
       <c r="J46" s="6"/>
       <c r="K46" s="41" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>108</v>
       </c>
@@ -3662,7 +3691,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>103</v>
       </c>
@@ -3692,7 +3721,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>86</v>
       </c>
@@ -3722,7 +3751,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>232</v>
       </c>
@@ -3751,9 +3780,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="31" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="B51" s="13"/>
       <c r="C51" s="5" t="s">
@@ -3776,7 +3805,7 @@
       <c r="J51" s="6"/>
       <c r="K51" s="41"/>
     </row>
-    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
         <v>27</v>
       </c>
@@ -3806,7 +3835,7 @@
       </c>
       <c r="K52" s="42"/>
     </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
         <v>2</v>
       </c>
@@ -3836,7 +3865,7 @@
       </c>
       <c r="K53" s="42"/>
     </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
         <v>130</v>
       </c>
@@ -3859,7 +3888,7 @@
       </c>
       <c r="K54" s="42"/>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
         <v>7</v>
       </c>
@@ -3889,7 +3918,7 @@
       </c>
       <c r="K55" s="42"/>
     </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
         <v>0</v>
       </c>
@@ -3919,7 +3948,7 @@
       </c>
       <c r="K56" s="41"/>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
         <v>24</v>
       </c>
@@ -3949,7 +3978,7 @@
       </c>
       <c r="K57" s="42"/>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="10" t="s">
         <v>53</v>
       </c>
@@ -3979,7 +4008,7 @@
       </c>
       <c r="K58" s="41"/>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
         <v>73</v>
       </c>
@@ -4011,7 +4040,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
         <v>116</v>
       </c>
@@ -4041,7 +4070,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
         <v>112</v>
       </c>
@@ -4064,7 +4093,7 @@
         <v>166</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J61" s="6" t="s">
         <v>111</v>
@@ -4073,19 +4102,19 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="19"/>
@@ -4094,13 +4123,13 @@
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="6" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="K62" s="41">
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
         <v>3</v>
       </c>
@@ -4125,17 +4154,15 @@
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="6"/>
-      <c r="K63" s="41">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="K63" s="41"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" s="17" t="s">
         <v>224</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="6" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>100</v>
@@ -4154,13 +4181,13 @@
       </c>
       <c r="K64" s="41"/>
     </row>
-    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
         <v>151</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="6" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>100</v>
@@ -4181,7 +4208,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
         <v>145</v>
       </c>
@@ -4209,7 +4236,7 @@
       </c>
       <c r="K66" s="41"/>
     </row>
-    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
         <v>1</v>
       </c>
@@ -4227,7 +4254,7 @@
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="6" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="H67" s="18" t="s">
         <v>166</v>
@@ -4238,7 +4265,7 @@
       </c>
       <c r="K67" s="41"/>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
         <v>1</v>
       </c>
@@ -4256,7 +4283,7 @@
       </c>
       <c r="F68" s="6"/>
       <c r="G68" s="6" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="H68" s="18" t="s">
         <v>166</v>
@@ -4267,19 +4294,19 @@
       </c>
       <c r="K68" s="41"/>
     </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="53" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F69" s="6"/>
       <c r="G69" s="19" t="s">
@@ -4290,25 +4317,25 @@
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="5" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="K69" s="44" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="53" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D70" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F70" s="6"/>
       <c r="G70" s="19" t="s">
@@ -4319,13 +4346,13 @@
       </c>
       <c r="I70" s="9"/>
       <c r="J70" s="38" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="K70" s="43" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
         <v>97</v>
       </c>
@@ -4345,7 +4372,7 @@
         <v>166</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J71" s="6" t="s">
         <v>96</v>
@@ -4354,7 +4381,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
         <v>60</v>
       </c>
@@ -4379,7 +4406,7 @@
         <v>166</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="J72" s="6" t="s">
         <v>59</v>
@@ -4388,19 +4415,19 @@
         <v>56</v>
       </c>
     </row>
-    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F73" s="6"/>
       <c r="G73" s="7" t="s">
@@ -4415,19 +4442,19 @@
       </c>
       <c r="K73" s="41"/>
     </row>
-    <row r="74" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A74" s="22" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F74" s="6"/>
       <c r="G74" s="7" t="s">
@@ -4442,7 +4469,7 @@
       </c>
       <c r="K74" s="41"/>
     </row>
-    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
         <v>81</v>
       </c>
@@ -4465,7 +4492,7 @@
         <v>166</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J75" s="6" t="s">
         <v>77</v>
@@ -4474,7 +4501,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" s="6" t="s">
         <v>78</v>
       </c>
@@ -4497,7 +4524,7 @@
         <v>166</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J76" s="6" t="s">
         <v>77</v>
@@ -4506,13 +4533,13 @@
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
         <v>158</v>
       </c>
       <c r="B77" s="25"/>
       <c r="C77" s="33" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D77" s="54" t="s">
         <v>100</v>
@@ -4527,13 +4554,13 @@
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="6" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="K77" s="41">
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" s="6" t="s">
         <v>91</v>
       </c>
@@ -4560,13 +4587,13 @@
         <v>87</v>
       </c>
     </row>
-    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
         <v>159</v>
       </c>
       <c r="B79" s="25"/>
       <c r="C79" s="26" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D79" s="54" t="s">
         <v>100</v>
@@ -4575,21 +4602,21 @@
         <v>156</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="8"/>
       <c r="I79" s="9"/>
       <c r="J79" s="29" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="K79" s="43">
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B80" s="25" t="s">
         <v>174</v>
@@ -4616,19 +4643,19 @@
       </c>
       <c r="K80" s="41"/>
     </row>
-    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B81" s="27"/>
       <c r="C81" s="28" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E81" s="35" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F81" s="35"/>
       <c r="G81" s="7" t="s">
@@ -4643,19 +4670,19 @@
       </c>
       <c r="K81" s="41"/>
     </row>
-    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B82" s="25"/>
       <c r="C82" s="26" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D82" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E82" s="33" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F82" s="33"/>
       <c r="G82" s="19"/>
@@ -4664,7 +4691,7 @@
       </c>
       <c r="I82" s="9"/>
       <c r="J82" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="K82" s="41"/>
     </row>
@@ -4691,7 +4718,7 @@
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="6" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="K83" s="41">
         <v>10</v>
@@ -4702,7 +4729,7 @@
         <v>168</v>
       </c>
       <c r="B84" s="25" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C84" s="26" t="s">
         <v>184</v>
@@ -4726,19 +4753,19 @@
       </c>
       <c r="K84" s="41"/>
     </row>
-    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B85" s="25"/>
       <c r="C85" s="23" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D85" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F85" s="33"/>
       <c r="G85" s="19" t="s">
@@ -4749,13 +4776,13 @@
       </c>
       <c r="I85" s="9"/>
       <c r="J85" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K85" s="44">
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" s="30" t="s">
         <v>65</v>
       </c>
@@ -4787,7 +4814,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" s="52" t="s">
         <v>69</v>
       </c>
@@ -4819,7 +4846,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" s="32" t="s">
         <v>18</v>
       </c>
@@ -4844,7 +4871,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" s="6" t="s">
         <v>120</v>
       </c>
@@ -4874,19 +4901,19 @@
         <v>70</v>
       </c>
     </row>
-    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B90" s="25"/>
       <c r="C90" s="26" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E90" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="F90" s="33"/>
       <c r="G90" s="19" t="s">
@@ -4897,23 +4924,23 @@
       </c>
       <c r="I90" s="9"/>
       <c r="J90" s="33" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="K90" s="47"/>
     </row>
-    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" s="25" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B91" s="5"/>
       <c r="C91" s="26" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E91" s="33" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F91" s="33"/>
       <c r="G91" s="19" t="s">
@@ -4924,13 +4951,13 @@
       </c>
       <c r="I91" s="9"/>
       <c r="J91" s="33" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="K91" s="47">
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
         <v>14</v>
       </c>
@@ -4955,7 +4982,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" s="25" t="s">
         <v>152</v>
       </c>
@@ -4980,7 +5007,7 @@
       </c>
       <c r="K93" s="47"/>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
         <v>3</v>
       </c>
@@ -4988,7 +5015,7 @@
         <v>183</v>
       </c>
       <c r="C94" s="26" t="s">
-        <v>382</v>
+        <v>423</v>
       </c>
       <c r="D94" s="54" t="s">
         <v>100</v>
@@ -5007,7 +5034,7 @@
       </c>
       <c r="K94" s="47"/>
     </row>
-    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" s="6" t="s">
         <v>20</v>
       </c>
@@ -5030,7 +5057,7 @@
       </c>
       <c r="K95" s="47"/>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" s="25" t="s">
         <v>245</v>
       </c>
@@ -5044,7 +5071,7 @@
       </c>
       <c r="F96" s="33"/>
       <c r="G96" s="19" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="H96" s="8" t="s">
         <v>166</v>
@@ -5055,7 +5082,7 @@
       </c>
       <c r="K96" s="47"/>
     </row>
-    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" s="25" t="s">
         <v>235</v>
       </c>
@@ -5074,9 +5101,9 @@
       <c r="J97" s="33"/>
       <c r="K97" s="47"/>
     </row>
-    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="25" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="26"/>
@@ -5084,7 +5111,7 @@
         <v>100</v>
       </c>
       <c r="E98" s="33" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F98" s="33"/>
       <c r="G98" s="19"/>
@@ -5095,7 +5122,7 @@
       <c r="J98" s="33"/>
       <c r="K98" s="47"/>
     </row>
-    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" s="27" t="s">
         <v>9</v>
       </c>
@@ -5116,7 +5143,7 @@
       </c>
       <c r="K99" s="45"/>
     </row>
-    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" s="25" t="s">
         <v>234</v>
       </c>
@@ -5135,44 +5162,48 @@
       <c r="J100" s="33"/>
       <c r="K100" s="47"/>
     </row>
-    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B101" s="25" t="s">
-        <v>161</v>
+        <v>420</v>
       </c>
       <c r="C101" s="26" t="s">
-        <v>383</v>
+        <v>424</v>
       </c>
       <c r="D101" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="E101" s="33"/>
+      <c r="E101" s="33" t="s">
+        <v>425</v>
+      </c>
       <c r="F101" s="36"/>
       <c r="G101" s="7"/>
       <c r="H101" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I101" s="9"/>
-      <c r="J101" s="33"/>
+      <c r="J101" s="33" t="s">
+        <v>426</v>
+      </c>
       <c r="K101" s="47"/>
     </row>
     <row r="102" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="B102" s="25" t="s">
         <v>174</v>
       </c>
       <c r="C102" s="26" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="D102" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E102" s="33" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="F102" s="36"/>
       <c r="G102" s="7"/>
@@ -5180,14 +5211,14 @@
         <v>166</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="J102" s="33" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="K102" s="47"/>
     </row>
-    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" s="30" t="s">
         <v>33</v>
       </c>
@@ -5208,7 +5239,7 @@
       </c>
       <c r="K103" s="47"/>
     </row>
-    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" s="30" t="s">
         <v>32</v>
       </c>
@@ -5229,7 +5260,7 @@
       </c>
       <c r="K104" s="47"/>
     </row>
-    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" s="30" t="s">
         <v>29</v>
       </c>
@@ -5250,7 +5281,7 @@
       </c>
       <c r="K105" s="47"/>
     </row>
-    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" s="30" t="s">
         <v>28</v>
       </c>
@@ -5271,7 +5302,7 @@
       </c>
       <c r="K106" s="47"/>
     </row>
-    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" s="30" t="s">
         <v>23</v>
       </c>
@@ -5294,7 +5325,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" s="30" t="s">
         <v>31</v>
       </c>
@@ -5315,7 +5346,7 @@
       </c>
       <c r="K108" s="47"/>
     </row>
-    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" s="30" t="s">
         <v>25</v>
       </c>
@@ -5336,7 +5367,7 @@
       </c>
       <c r="K109" s="47"/>
     </row>
-    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" s="30" t="s">
         <v>30</v>
       </c>
@@ -5357,7 +5388,7 @@
       </c>
       <c r="K110" s="47"/>
     </row>
-    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" s="30" t="s">
         <v>26</v>
       </c>
@@ -5378,7 +5409,7 @@
       </c>
       <c r="K111" s="47"/>
     </row>
-    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="6" t="s">
         <v>41</v>
       </c>
@@ -5401,7 +5432,7 @@
       </c>
       <c r="K112" s="45"/>
     </row>
-    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" s="6" t="s">
         <v>38</v>
       </c>
@@ -5424,21 +5455,21 @@
       </c>
       <c r="K113" s="47"/>
     </row>
-    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="55" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>161</v>
       </c>
       <c r="C114" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="D114" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="D114" s="6" t="s">
-        <v>397</v>
-      </c>
       <c r="E114" s="6" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="F114" s="6"/>
       <c r="G114" s="7"/>
@@ -5449,50 +5480,50 @@
       <c r="J114" s="26"/>
       <c r="K114" s="46"/>
     </row>
-    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="55" t="s">
+        <v>383</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="C115" s="5" t="s">
         <v>389</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>395</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="F115" s="6"/>
       <c r="G115" s="7" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="H115" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I115" s="9"/>
       <c r="J115" s="23" t="s">
+        <v>387</v>
+      </c>
+      <c r="K115" s="48"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A116" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="C116" s="5" t="s">
         <v>393</v>
-      </c>
-      <c r="K115" s="48"/>
-    </row>
-    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="55" t="s">
-        <v>398</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>399</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="F116" s="6"/>
       <c r="G116" s="7"/>
@@ -5501,27 +5532,27 @@
       </c>
       <c r="I116" s="9"/>
       <c r="J116" s="26" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="K116" s="46" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" s="55" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="F117" s="6"/>
       <c r="G117" s="7"/>
@@ -5530,25 +5561,25 @@
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="23" t="s">
+        <v>396</v>
+      </c>
+      <c r="K117" s="48"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A118" s="55" t="s">
         <v>402</v>
       </c>
-      <c r="K117" s="48"/>
-    </row>
-    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="55" t="s">
-        <v>408</v>
-      </c>
       <c r="B118" s="5" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="F118" s="6"/>
       <c r="G118" s="7"/>
@@ -5557,50 +5588,50 @@
       </c>
       <c r="I118" s="9"/>
       <c r="J118" s="26" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="K118" s="46"/>
     </row>
-    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" s="55" t="s">
+        <v>402</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C119" s="5" t="s">
         <v>408</v>
-      </c>
-      <c r="B119" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>414</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="F119" s="6"/>
       <c r="G119" s="7"/>
       <c r="H119" s="8"/>
       <c r="I119" s="9"/>
       <c r="J119" s="23" t="s">
+        <v>410</v>
+      </c>
+      <c r="K119" s="48"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A120" s="55" t="s">
+        <v>413</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="C120" s="5" t="s">
         <v>416</v>
-      </c>
-      <c r="K119" s="48"/>
-    </row>
-    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="55" t="s">
-        <v>419</v>
-      </c>
-      <c r="B120" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>422</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="F120" s="6"/>
       <c r="G120" s="7"/>
@@ -5609,63 +5640,107 @@
       </c>
       <c r="I120" s="9"/>
       <c r="J120" s="26" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="K120" s="46"/>
     </row>
-    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="55"/>
-      <c r="B121" s="5"/>
-      <c r="C121" s="5"/>
-      <c r="D121" s="6"/>
-      <c r="E121" s="6"/>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A121" s="55" t="s">
+        <v>427</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>431</v>
+      </c>
       <c r="F121" s="6"/>
       <c r="G121" s="19"/>
-      <c r="H121" s="18"/>
+      <c r="H121" s="18" t="s">
+        <v>166</v>
+      </c>
       <c r="I121" s="9"/>
-      <c r="J121" s="24"/>
+      <c r="J121" s="24" t="s">
+        <v>433</v>
+      </c>
       <c r="K121" s="49"/>
     </row>
-    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="55"/>
-      <c r="B122" s="5"/>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A122" s="55" t="s">
+        <v>427</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>194</v>
+      </c>
       <c r="C122" s="5"/>
-      <c r="D122" s="6"/>
+      <c r="D122" s="54" t="s">
+        <v>100</v>
+      </c>
       <c r="E122" s="6"/>
       <c r="F122" s="6"/>
       <c r="G122" s="7"/>
       <c r="H122" s="8"/>
       <c r="I122" s="9"/>
-      <c r="J122" s="26"/>
+      <c r="J122" s="26" t="s">
+        <v>434</v>
+      </c>
       <c r="K122" s="46"/>
     </row>
-    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="55"/>
-      <c r="B123" s="5"/>
-      <c r="C123" s="5"/>
-      <c r="D123" s="6"/>
-      <c r="E123" s="6"/>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A123" s="55" t="s">
+        <v>428</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>432</v>
+      </c>
       <c r="F123" s="6"/>
       <c r="G123" s="7"/>
-      <c r="H123" s="8"/>
+      <c r="H123" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="I123" s="9"/>
-      <c r="J123" s="23"/>
+      <c r="J123" s="23" t="s">
+        <v>433</v>
+      </c>
       <c r="K123" s="48"/>
     </row>
-    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="55"/>
-      <c r="B124" s="5"/>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A124" s="55" t="s">
+        <v>428</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>194</v>
+      </c>
       <c r="C124" s="5"/>
-      <c r="D124" s="6"/>
+      <c r="D124" s="54" t="s">
+        <v>100</v>
+      </c>
       <c r="E124" s="6"/>
       <c r="F124" s="6"/>
       <c r="G124" s="7"/>
       <c r="H124" s="8"/>
       <c r="I124" s="9"/>
-      <c r="J124" s="26"/>
+      <c r="J124" s="26" t="s">
+        <v>434</v>
+      </c>
       <c r="K124" s="46"/>
     </row>
-    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125" s="55"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -5678,7 +5753,7 @@
       <c r="J125" s="23"/>
       <c r="K125" s="48"/>
     </row>
-    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126" s="55"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -5691,7 +5766,7 @@
       <c r="J126" s="26"/>
       <c r="K126" s="46"/>
     </row>
-    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127" s="55"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -5704,7 +5779,7 @@
       <c r="J127" s="23"/>
       <c r="K127" s="48"/>
     </row>
-    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" s="5"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -5717,7 +5792,7 @@
       <c r="J128" s="26"/>
       <c r="K128" s="46"/>
     </row>
-    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" s="5"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -5730,7 +5805,7 @@
       <c r="J129" s="24"/>
       <c r="K129" s="49"/>
     </row>
-    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -5743,7 +5818,7 @@
       <c r="J130" s="26"/>
       <c r="K130" s="46"/>
     </row>
-    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" s="5"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -5756,7 +5831,7 @@
       <c r="J131" s="23"/>
       <c r="K131" s="48"/>
     </row>
-    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" s="5"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -5769,7 +5844,7 @@
       <c r="J132" s="28"/>
       <c r="K132" s="50"/>
     </row>
-    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" s="5"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -5782,7 +5857,7 @@
       <c r="J133" s="6"/>
       <c r="K133" s="41"/>
     </row>
-    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" s="5"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -5795,7 +5870,7 @@
       <c r="J134" s="6"/>
       <c r="K134" s="41"/>
     </row>
-    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" s="5"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FF314F-24EB-D54E-8C05-752BA5BAE09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC8F5C25-01B6-0046-ACA1-F6957BDAFC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="320" yWindow="2960" windowWidth="29920" windowHeight="16680" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
+    <workbookView xWindow="33320" yWindow="-29420" windowWidth="43300" windowHeight="26180" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
   <sheets>
     <sheet name="network" sheetId="1" r:id="rId1"/>
@@ -629,9 +629,6 @@
     <t>192.168.0.207</t>
   </si>
   <si>
-    <t>USB Nic</t>
-  </si>
-  <si>
     <t>192.168.0.210</t>
   </si>
   <si>
@@ -1091,9 +1088,6 @@
     <t>G2 KVM</t>
   </si>
   <si>
-    <t>2603-1300</t>
-  </si>
-  <si>
     <t>osc:9110</t>
   </si>
   <si>
@@ -1410,6 +1404,12 @@
   </si>
   <si>
     <t>192.168.200.153</t>
+  </si>
+  <si>
+    <t>2410-1606</t>
+  </si>
+  <si>
+    <t>USB Nic for cumu-g001</t>
   </si>
 </sst>
 </file>
@@ -2069,7 +2069,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K135" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K135" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
+  <autoFilter ref="A1:K135" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="CUMU-E001"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{EF2C341F-E5C1-604C-942C-FB7E9F76F1CD}" name="AssetTag" dataDxfId="10"/>
     <tableColumn id="13" xr3:uid="{41250547-1480-7146-952C-14798A4748DA}" name="NIC" dataDxfId="9"/>
@@ -2422,7 +2428,7 @@
         <v>139</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>165</v>
@@ -2437,48 +2443,48 @@
         <v>138</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K2" s="41"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="C3" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>191</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -2487,22 +2493,22 @@
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="K3" s="41"/>
+    </row>
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="K3" s="41"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>195</v>
-      </c>
       <c r="D4" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -2512,25 +2518,25 @@
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K4" s="41"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -2539,22 +2545,22 @@
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K5" s="41"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -2564,51 +2570,51 @@
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K6" s="41"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K7" s="41"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -2618,25 +2624,25 @@
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K8" s="41"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -2645,22 +2651,22 @@
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K9" s="41"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -2670,334 +2676,334 @@
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K10" s="41"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="29" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="K11" s="44"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="K12" s="43"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>378</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>380</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="K13" s="43"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="K14" s="43"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="K15" s="43"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="K16" s="43"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="29" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="K17" s="44"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="29" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F18" s="29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="K18" s="44"/>
+    </row>
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>351</v>
-      </c>
-      <c r="K18" s="44"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>353</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="K19" s="43"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="29" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="K20" s="44"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B21" s="29"/>
       <c r="C21" s="29" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E21" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="F21" s="29" t="s">
         <v>284</v>
-      </c>
-      <c r="F21" s="29" t="s">
-        <v>285</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="8"/>
@@ -3005,12 +3011,12 @@
       <c r="J21" s="6"/>
       <c r="K21" s="41"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
         <v>55</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>54</v>
@@ -3019,7 +3025,7 @@
         <v>35</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
@@ -3027,7 +3033,7 @@
         <v>166</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>44</v>
@@ -3036,12 +3042,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>43</v>
@@ -3050,7 +3056,7 @@
         <v>35</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
@@ -3058,7 +3064,7 @@
         <v>166</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>44</v>
@@ -3067,12 +3073,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C24" s="20" t="s">
         <v>46</v>
@@ -3081,7 +3087,7 @@
         <v>35</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
@@ -3089,7 +3095,7 @@
         <v>166</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>44</v>
@@ -3098,12 +3104,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C25" s="20" t="s">
         <v>48</v>
@@ -3112,7 +3118,7 @@
         <v>35</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
@@ -3120,7 +3126,7 @@
         <v>166</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>44</v>
@@ -3129,7 +3135,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>137</v>
       </c>
@@ -3156,13 +3162,13 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>100</v>
@@ -3174,29 +3180,29 @@
       <c r="I27" s="9"/>
       <c r="J27" s="6"/>
       <c r="K27" s="41" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>93</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F28" s="19" t="str">
         <f>CONCATENATE("http://", E28)</f>
         <v>http://192.168.201.110</v>
       </c>
       <c r="G28" s="21" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H28" s="8" t="s">
         <v>166</v>
@@ -3209,12 +3215,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>40</v>
@@ -3235,15 +3241,15 @@
         <v>37</v>
       </c>
       <c r="K29" s="41" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>38</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>36</v>
@@ -3264,10 +3270,10 @@
         <v>37</v>
       </c>
       <c r="K30" s="41" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>6</v>
       </c>
@@ -3279,7 +3285,7 @@
         <v>100</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
@@ -3288,25 +3294,25 @@
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="K31" s="41"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
@@ -3315,23 +3321,23 @@
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="K32" s="41"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
@@ -3344,22 +3350,22 @@
       </c>
       <c r="K33" s="41"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="8"/>
@@ -3367,22 +3373,22 @@
       <c r="J34" s="6"/>
       <c r="K34" s="41"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B35" s="29"/>
       <c r="C35" s="29" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G35" s="19"/>
       <c r="H35" s="8"/>
@@ -3390,22 +3396,22 @@
       <c r="J35" s="6"/>
       <c r="K35" s="41"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B36" s="29"/>
       <c r="C36" s="29" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="8"/>
@@ -3413,22 +3419,22 @@
       <c r="J36" s="6"/>
       <c r="K36" s="41"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="8"/>
@@ -3436,232 +3442,232 @@
       <c r="J37" s="6"/>
       <c r="K37" s="41"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B38" s="29"/>
       <c r="C38" s="29" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="8"/>
       <c r="I38" s="9"/>
       <c r="J38" s="6"/>
       <c r="K38" s="41" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B39" s="29"/>
       <c r="C39" s="29" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F39" s="29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="8"/>
       <c r="I39" s="9"/>
       <c r="J39" s="6"/>
       <c r="K39" s="41" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="29" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F40" s="29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="8"/>
       <c r="I40" s="9"/>
       <c r="J40" s="6"/>
       <c r="K40" s="41" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="8"/>
       <c r="I41" s="9"/>
       <c r="J41" s="6"/>
       <c r="K41" s="41" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="8"/>
       <c r="I42" s="9"/>
       <c r="J42" s="6"/>
       <c r="K42" s="41" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="8"/>
       <c r="I43" s="9"/>
       <c r="J43" s="6"/>
       <c r="K43" s="41" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="8"/>
       <c r="I44" s="9"/>
       <c r="J44" s="6"/>
       <c r="K44" s="41" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B45" s="29"/>
       <c r="C45" s="29" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E45" s="29" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F45" s="29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="8"/>
       <c r="I45" s="9"/>
       <c r="J45" s="6"/>
       <c r="K45" s="41" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B46" s="29"/>
       <c r="C46" s="29" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E46" s="29" t="s">
+        <v>272</v>
+      </c>
+      <c r="F46" s="29" t="s">
         <v>273</v>
-      </c>
-      <c r="F46" s="29" t="s">
-        <v>274</v>
       </c>
       <c r="G46" s="19"/>
       <c r="H46" s="8"/>
       <c r="I46" s="9"/>
       <c r="J46" s="6"/>
       <c r="K46" s="41" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>108</v>
       </c>
@@ -3691,7 +3697,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>103</v>
       </c>
@@ -3721,7 +3727,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>86</v>
       </c>
@@ -3751,52 +3757,52 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H50" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K50" s="41">
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="31" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B51" s="13"/>
       <c r="C51" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H51" s="8" t="s">
         <v>166</v>
@@ -3805,7 +3811,7 @@
       <c r="J51" s="6"/>
       <c r="K51" s="41"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
         <v>27</v>
       </c>
@@ -3824,7 +3830,7 @@
         <v>http://192.168.0.23</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H52" s="8" t="s">
         <v>167</v>
@@ -3835,7 +3841,7 @@
       </c>
       <c r="K52" s="42"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
         <v>2</v>
       </c>
@@ -3854,7 +3860,7 @@
         <v>http://192.168.0.22</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H53" s="8" t="s">
         <v>167</v>
@@ -3865,7 +3871,7 @@
       </c>
       <c r="K53" s="42"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
         <v>130</v>
       </c>
@@ -3888,7 +3894,7 @@
       </c>
       <c r="K54" s="42"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
         <v>7</v>
       </c>
@@ -3907,7 +3913,7 @@
         <v>http://192.168.0.24</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H55" s="18" t="s">
         <v>167</v>
@@ -3918,7 +3924,7 @@
       </c>
       <c r="K55" s="42"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
         <v>0</v>
       </c>
@@ -3937,7 +3943,7 @@
         <v>http://192.168.0.25</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H56" s="18" t="s">
         <v>167</v>
@@ -3948,7 +3954,7 @@
       </c>
       <c r="K56" s="41"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
         <v>24</v>
       </c>
@@ -3967,7 +3973,7 @@
         <v>http://192.168.0.26</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H57" s="18" t="s">
         <v>167</v>
@@ -3978,7 +3984,7 @@
       </c>
       <c r="K57" s="42"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="10" t="s">
         <v>53</v>
       </c>
@@ -3997,7 +4003,7 @@
         <v>http://192.168.0.197:8080</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H58" s="18" t="s">
         <v>166</v>
@@ -4008,7 +4014,7 @@
       </c>
       <c r="K58" s="41"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
         <v>73</v>
       </c>
@@ -4027,7 +4033,7 @@
         <v>http://192.168.0.193</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H59" s="18" t="s">
         <v>167</v>
@@ -4040,7 +4046,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
         <v>116</v>
       </c>
@@ -4070,7 +4076,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
         <v>112</v>
       </c>
@@ -4093,7 +4099,7 @@
         <v>166</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J61" s="6" t="s">
         <v>111</v>
@@ -4102,19 +4108,19 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" ht="17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="19"/>
@@ -4123,7 +4129,7 @@
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K62" s="41">
         <v>12</v>
@@ -4137,17 +4143,17 @@
         <v>170</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F63" s="7"/>
       <c r="G63" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H63" s="18" t="s">
         <v>166</v>
@@ -4156,13 +4162,13 @@
       <c r="J63" s="6"/>
       <c r="K63" s="41"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="17" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>100</v>
@@ -4181,19 +4187,19 @@
       </c>
       <c r="K64" s="41"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
         <v>151</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="6"/>
@@ -4202,13 +4208,13 @@
       </c>
       <c r="I65" s="9"/>
       <c r="J65" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K65" s="41">
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
         <v>145</v>
       </c>
@@ -4236,7 +4242,7 @@
       </c>
       <c r="K66" s="41"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
         <v>1</v>
       </c>
@@ -4254,7 +4260,7 @@
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H67" s="18" t="s">
         <v>166</v>
@@ -4265,7 +4271,7 @@
       </c>
       <c r="K67" s="41"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
         <v>1</v>
       </c>
@@ -4283,7 +4289,7 @@
       </c>
       <c r="F68" s="6"/>
       <c r="G68" s="6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H68" s="18" t="s">
         <v>166</v>
@@ -4294,65 +4300,65 @@
       </c>
       <c r="K68" s="41"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="53" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F69" s="6"/>
       <c r="G69" s="19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H69" s="18" t="s">
         <v>166</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="K69" s="44" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="53" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D70" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F70" s="6"/>
       <c r="G70" s="19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H70" s="18" t="s">
         <v>166</v>
       </c>
       <c r="I70" s="9"/>
       <c r="J70" s="38" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="K70" s="43" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
         <v>97</v>
       </c>
@@ -4372,7 +4378,7 @@
         <v>166</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J71" s="6" t="s">
         <v>96</v>
@@ -4381,7 +4387,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
         <v>60</v>
       </c>
@@ -4400,13 +4406,13 @@
         <v>http://192.168.0.183</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H72" s="18" t="s">
         <v>166</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J72" s="6" t="s">
         <v>59</v>
@@ -4415,23 +4421,23 @@
         <v>56</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F73" s="6"/>
       <c r="G73" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H73" s="18" t="s">
         <v>166</v>
@@ -4442,23 +4448,23 @@
       </c>
       <c r="K73" s="41"/>
     </row>
-    <row r="74" spans="1:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A74" s="22" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F74" s="6"/>
       <c r="G74" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H74" s="18" t="s">
         <v>166</v>
@@ -4469,7 +4475,7 @@
       </c>
       <c r="K74" s="41"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
         <v>81</v>
       </c>
@@ -4492,7 +4498,7 @@
         <v>166</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J75" s="6" t="s">
         <v>77</v>
@@ -4501,7 +4507,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="6" t="s">
         <v>78</v>
       </c>
@@ -4524,7 +4530,7 @@
         <v>166</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J76" s="6" t="s">
         <v>77</v>
@@ -4533,13 +4539,13 @@
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
         <v>158</v>
       </c>
       <c r="B77" s="25"/>
       <c r="C77" s="33" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D77" s="54" t="s">
         <v>100</v>
@@ -4554,13 +4560,13 @@
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="K77" s="41">
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="6" t="s">
         <v>91</v>
       </c>
@@ -4587,13 +4593,13 @@
         <v>87</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
         <v>159</v>
       </c>
       <c r="B79" s="25"/>
       <c r="C79" s="26" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D79" s="54" t="s">
         <v>100</v>
@@ -4602,21 +4608,21 @@
         <v>156</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="8"/>
       <c r="I79" s="9"/>
       <c r="J79" s="29" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="K79" s="43">
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>331</v>
+        <v>436</v>
       </c>
       <c r="B80" s="25" t="s">
         <v>174</v>
@@ -4632,34 +4638,34 @@
       </c>
       <c r="F80" s="33"/>
       <c r="G80" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H80" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I80" s="9"/>
       <c r="J80" s="6" t="s">
-        <v>177</v>
+        <v>437</v>
       </c>
       <c r="K80" s="41"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B81" s="27"/>
       <c r="C81" s="28" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E81" s="35" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F81" s="35"/>
       <c r="G81" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H81" s="18" t="s">
         <v>166</v>
@@ -4670,19 +4676,19 @@
       </c>
       <c r="K81" s="41"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B82" s="25"/>
       <c r="C82" s="26" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D82" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E82" s="33" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F82" s="33"/>
       <c r="G82" s="19"/>
@@ -4691,11 +4697,11 @@
       </c>
       <c r="I82" s="9"/>
       <c r="J82" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="K82" s="41"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
         <v>168</v>
       </c>
@@ -4703,13 +4709,13 @@
         <v>170</v>
       </c>
       <c r="C83" s="26" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D83" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E83" s="33" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F83" s="36"/>
       <c r="G83" s="7"/>
@@ -4718,31 +4724,31 @@
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="K83" s="41">
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
         <v>168</v>
       </c>
       <c r="B84" s="25" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C84" s="26" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E84" s="33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F84" s="36"/>
       <c r="G84" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H84" s="8" t="s">
         <v>167</v>
@@ -4753,36 +4759,36 @@
       </c>
       <c r="K84" s="41"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B85" s="25"/>
       <c r="C85" s="23" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D85" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F85" s="33"/>
       <c r="G85" s="19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H85" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I85" s="9"/>
       <c r="J85" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K85" s="44">
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="30" t="s">
         <v>65</v>
       </c>
@@ -4801,7 +4807,7 @@
         <v>http://192.168.0.195</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H86" s="8" t="s">
         <v>167</v>
@@ -4814,7 +4820,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="52" t="s">
         <v>69</v>
       </c>
@@ -4833,7 +4839,7 @@
         <v>http://192.168.0.194</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H87" s="18" t="s">
         <v>167</v>
@@ -4846,7 +4852,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="32" t="s">
         <v>18</v>
       </c>
@@ -4871,7 +4877,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6" t="s">
         <v>120</v>
       </c>
@@ -4901,63 +4907,63 @@
         <v>70</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B90" s="25"/>
       <c r="C90" s="26" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E90" s="33" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F90" s="33"/>
       <c r="G90" s="19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H90" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I90" s="9"/>
       <c r="J90" s="33" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="K90" s="47"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="25" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B91" s="5"/>
       <c r="C91" s="26" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E91" s="33" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F91" s="33"/>
       <c r="G91" s="19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H91" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I91" s="9"/>
       <c r="J91" s="33" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="K91" s="47">
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
         <v>14</v>
       </c>
@@ -4982,7 +4988,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="25" t="s">
         <v>152</v>
       </c>
@@ -5012,16 +5018,16 @@
         <v>3</v>
       </c>
       <c r="B94" s="25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C94" s="26" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D94" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E94" s="33" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F94" s="36"/>
       <c r="G94" s="7"/>
@@ -5034,7 +5040,7 @@
       </c>
       <c r="K94" s="47"/>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6" t="s">
         <v>20</v>
       </c>
@@ -5044,7 +5050,7 @@
         <v>100</v>
       </c>
       <c r="E95" s="34" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F95" s="33"/>
       <c r="G95" s="6"/>
@@ -5057,9 +5063,9 @@
       </c>
       <c r="K95" s="47"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="25" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B96" s="5"/>
       <c r="C96" s="26"/>
@@ -5067,24 +5073,24 @@
         <v>100</v>
       </c>
       <c r="E96" s="34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F96" s="33"/>
       <c r="G96" s="19" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H96" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I96" s="9"/>
       <c r="J96" s="33" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K96" s="47"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="25" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B97" s="5"/>
       <c r="C97" s="26"/>
@@ -5092,7 +5098,7 @@
         <v>100</v>
       </c>
       <c r="E97" s="33" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F97" s="33"/>
       <c r="G97" s="19"/>
@@ -5101,9 +5107,9 @@
       <c r="J97" s="33"/>
       <c r="K97" s="47"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="25" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="26"/>
@@ -5111,7 +5117,7 @@
         <v>100</v>
       </c>
       <c r="E98" s="33" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F98" s="33"/>
       <c r="G98" s="19"/>
@@ -5122,7 +5128,7 @@
       <c r="J98" s="33"/>
       <c r="K98" s="47"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="27" t="s">
         <v>9</v>
       </c>
@@ -5143,9 +5149,9 @@
       </c>
       <c r="K99" s="45"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="25" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B100" s="5"/>
       <c r="C100" s="26"/>
@@ -5167,16 +5173,16 @@
         <v>3</v>
       </c>
       <c r="B101" s="25" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C101" s="26" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D101" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E101" s="33" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="F101" s="36"/>
       <c r="G101" s="7"/>
@@ -5185,25 +5191,25 @@
       </c>
       <c r="I101" s="9"/>
       <c r="J101" s="33" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="K101" s="47"/>
     </row>
-    <row r="102" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" ht="17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B102" s="25" t="s">
         <v>174</v>
       </c>
       <c r="C102" s="26" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D102" s="54" t="s">
         <v>100</v>
       </c>
       <c r="E102" s="33" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F102" s="36"/>
       <c r="G102" s="7"/>
@@ -5211,14 +5217,14 @@
         <v>166</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J102" s="33" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="K102" s="47"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="30" t="s">
         <v>33</v>
       </c>
@@ -5239,7 +5245,7 @@
       </c>
       <c r="K103" s="47"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="30" t="s">
         <v>32</v>
       </c>
@@ -5260,7 +5266,7 @@
       </c>
       <c r="K104" s="47"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="30" t="s">
         <v>29</v>
       </c>
@@ -5281,7 +5287,7 @@
       </c>
       <c r="K105" s="47"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="30" t="s">
         <v>28</v>
       </c>
@@ -5302,7 +5308,7 @@
       </c>
       <c r="K106" s="47"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="30" t="s">
         <v>23</v>
       </c>
@@ -5325,7 +5331,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="30" t="s">
         <v>31</v>
       </c>
@@ -5346,7 +5352,7 @@
       </c>
       <c r="K108" s="47"/>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="30" t="s">
         <v>25</v>
       </c>
@@ -5367,7 +5373,7 @@
       </c>
       <c r="K109" s="47"/>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="30" t="s">
         <v>30</v>
       </c>
@@ -5388,7 +5394,7 @@
       </c>
       <c r="K110" s="47"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="30" t="s">
         <v>26</v>
       </c>
@@ -5409,12 +5415,12 @@
       </c>
       <c r="K111" s="47"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C112" s="5"/>
       <c r="D112" s="54" t="s">
@@ -5428,16 +5434,16 @@
       </c>
       <c r="I112" s="9"/>
       <c r="J112" s="35" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K112" s="45"/>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="6" t="s">
         <v>38</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C113" s="5"/>
       <c r="D113" s="54" t="s">
@@ -5451,25 +5457,25 @@
       </c>
       <c r="I113" s="9"/>
       <c r="J113" s="39" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K113" s="47"/>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="55" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>161</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F114" s="6"/>
       <c r="G114" s="7"/>
@@ -5480,50 +5486,50 @@
       <c r="J114" s="26"/>
       <c r="K114" s="46"/>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="55" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F115" s="6"/>
       <c r="G115" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H115" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I115" s="9"/>
       <c r="J115" s="23" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="K115" s="48"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="55" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F116" s="6"/>
       <c r="G116" s="7"/>
@@ -5532,27 +5538,27 @@
       </c>
       <c r="I116" s="9"/>
       <c r="J116" s="26" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="K116" s="46" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="55" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F117" s="6"/>
       <c r="G117" s="7"/>
@@ -5561,25 +5567,25 @@
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="23" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="K117" s="48"/>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="55" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F118" s="6"/>
       <c r="G118" s="7"/>
@@ -5588,50 +5594,50 @@
       </c>
       <c r="I118" s="9"/>
       <c r="J118" s="26" t="s">
+        <v>403</v>
+      </c>
+      <c r="K118" s="46"/>
+    </row>
+    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="55" t="s">
+        <v>400</v>
+      </c>
+      <c r="B119" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="K118" s="46"/>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A119" s="55" t="s">
-        <v>402</v>
-      </c>
-      <c r="B119" s="5" t="s">
-        <v>407</v>
-      </c>
       <c r="C119" s="5" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F119" s="6"/>
       <c r="G119" s="7"/>
       <c r="H119" s="8"/>
       <c r="I119" s="9"/>
       <c r="J119" s="23" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="K119" s="48"/>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="55" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F120" s="6"/>
       <c r="G120" s="7"/>
@@ -5640,25 +5646,25 @@
       </c>
       <c r="I120" s="9"/>
       <c r="J120" s="26" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="K120" s="46"/>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="55" t="s">
+        <v>425</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C121" s="5" t="s">
         <v>427</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>429</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F121" s="6"/>
       <c r="G121" s="19"/>
@@ -5667,16 +5673,16 @@
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="24" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="K121" s="49"/>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="55" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C122" s="5"/>
       <c r="D122" s="54" t="s">
@@ -5688,25 +5694,25 @@
       <c r="H122" s="8"/>
       <c r="I122" s="9"/>
       <c r="J122" s="26" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="K122" s="46"/>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="55" t="s">
+        <v>426</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C123" s="5" t="s">
         <v>428</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>430</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F123" s="6"/>
       <c r="G123" s="7"/>
@@ -5715,16 +5721,16 @@
       </c>
       <c r="I123" s="9"/>
       <c r="J123" s="23" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="K123" s="48"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="55" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C124" s="5"/>
       <c r="D124" s="54" t="s">
@@ -5736,11 +5742,11 @@
       <c r="H124" s="8"/>
       <c r="I124" s="9"/>
       <c r="J124" s="26" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="K124" s="46"/>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="55"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -5753,7 +5759,7 @@
       <c r="J125" s="23"/>
       <c r="K125" s="48"/>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="55"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -5766,7 +5772,7 @@
       <c r="J126" s="26"/>
       <c r="K126" s="46"/>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="55"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -5779,7 +5785,7 @@
       <c r="J127" s="23"/>
       <c r="K127" s="48"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="5"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -5792,7 +5798,7 @@
       <c r="J128" s="26"/>
       <c r="K128" s="46"/>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="5"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -5805,7 +5811,7 @@
       <c r="J129" s="24"/>
       <c r="K129" s="49"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -5818,7 +5824,7 @@
       <c r="J130" s="26"/>
       <c r="K130" s="46"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="5"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -5831,7 +5837,7 @@
       <c r="J131" s="23"/>
       <c r="K131" s="48"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="5"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -5844,7 +5850,7 @@
       <c r="J132" s="28"/>
       <c r="K132" s="50"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="5"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -5857,7 +5863,7 @@
       <c r="J133" s="6"/>
       <c r="K133" s="41"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="5"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -5870,7 +5876,7 @@
       <c r="J134" s="6"/>
       <c r="K134" s="41"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="5"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC8F5C25-01B6-0046-ACA1-F6957BDAFC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F866D403-0D90-8F4D-9A70-C986CF2C5127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33320" yWindow="-29420" windowWidth="43300" windowHeight="26180" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
   <sheets>
     <sheet name="network" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="478">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -1410,6 +1410,126 @@
   </si>
   <si>
     <t>USB Nic for cumu-g001</t>
+  </si>
+  <si>
+    <t>outer_lobby</t>
+  </si>
+  <si>
+    <t>E0:A7:00:1C:FB:4C</t>
+  </si>
+  <si>
+    <t>192.168.0.115</t>
+  </si>
+  <si>
+    <t>Security Camera</t>
+  </si>
+  <si>
+    <t>office_exterior</t>
+  </si>
+  <si>
+    <t>E0:A7:00:72:27:D8</t>
+  </si>
+  <si>
+    <t>192.168.0.131</t>
+  </si>
+  <si>
+    <t>Exterior Camera</t>
+  </si>
+  <si>
+    <t>off_camera</t>
+  </si>
+  <si>
+    <t>192.168.0.230</t>
+  </si>
+  <si>
+    <t>E0:A7:00:06:63:A4</t>
+  </si>
+  <si>
+    <t>Office door camera</t>
+  </si>
+  <si>
+    <t>south_lot</t>
+  </si>
+  <si>
+    <t>E0:A7:00:1D:B6:C2</t>
+  </si>
+  <si>
+    <t>192.168.0.117</t>
+  </si>
+  <si>
+    <t>south lot camera</t>
+  </si>
+  <si>
+    <t>car_port_cam</t>
+  </si>
+  <si>
+    <t>E0:A7:00:49:3B:D0</t>
+  </si>
+  <si>
+    <t>192.168.0.126</t>
+  </si>
+  <si>
+    <t>Car port camera</t>
+  </si>
+  <si>
+    <t>lower_door</t>
+  </si>
+  <si>
+    <t>E0:A7:00:06:63:A2</t>
+  </si>
+  <si>
+    <t>192.168.0.231</t>
+  </si>
+  <si>
+    <t>16th Ave Lower door</t>
+  </si>
+  <si>
+    <t>inner_lobby</t>
+  </si>
+  <si>
+    <t>E0:A7:00:06:48:56</t>
+  </si>
+  <si>
+    <t>192.168.0.233</t>
+  </si>
+  <si>
+    <t>Inner lobby cam</t>
+  </si>
+  <si>
+    <t>west_cam_1</t>
+  </si>
+  <si>
+    <t>E0:A7:00:07:6A:33</t>
+  </si>
+  <si>
+    <t>192.168.0.234</t>
+  </si>
+  <si>
+    <t>West Wall Southward</t>
+  </si>
+  <si>
+    <t>west_cam_2</t>
+  </si>
+  <si>
+    <t>E0:A7:00:07:6A:35</t>
+  </si>
+  <si>
+    <t>192.168.0.235</t>
+  </si>
+  <si>
+    <t>West Wall Northward</t>
+  </si>
+  <si>
+    <t>youth_cam</t>
+  </si>
+  <si>
+    <t>E0:A7:00:06:48:57</t>
+  </si>
+  <si>
+    <t>192.168.0.232</t>
+  </si>
+  <si>
+    <t>Youth Cam</t>
   </si>
 </sst>
 </file>
@@ -1699,7 +1819,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1784,6 +1904,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2069,13 +2190,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K135" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K135" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="CUMU-E001"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K135" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{EF2C341F-E5C1-604C-942C-FB7E9F76F1CD}" name="AssetTag" dataDxfId="10"/>
     <tableColumn id="13" xr3:uid="{41250547-1480-7146-952C-14798A4748DA}" name="NIC" dataDxfId="9"/>
@@ -2443,7 +2558,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>235</v>
       </c>
@@ -2470,7 +2585,7 @@
       </c>
       <c r="K2" s="41"/>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>188</v>
       </c>
@@ -2497,7 +2612,7 @@
       </c>
       <c r="K3" s="41"/>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>188</v>
       </c>
@@ -2522,7 +2637,7 @@
       </c>
       <c r="K4" s="41"/>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>206</v>
       </c>
@@ -2549,7 +2664,7 @@
       </c>
       <c r="K5" s="41"/>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>206</v>
       </c>
@@ -2574,7 +2689,7 @@
       </c>
       <c r="K6" s="41"/>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>213</v>
       </c>
@@ -2603,7 +2718,7 @@
       </c>
       <c r="K7" s="41"/>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>213</v>
       </c>
@@ -2628,7 +2743,7 @@
       </c>
       <c r="K8" s="41"/>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>212</v>
       </c>
@@ -2655,7 +2770,7 @@
       </c>
       <c r="K9" s="41"/>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>212</v>
       </c>
@@ -2680,7 +2795,7 @@
       </c>
       <c r="K10" s="41"/>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="29" t="s">
         <v>346</v>
       </c>
@@ -2711,7 +2826,7 @@
       </c>
       <c r="K11" s="44"/>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>347</v>
       </c>
@@ -2742,7 +2857,7 @@
       </c>
       <c r="K12" s="43"/>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>343</v>
       </c>
@@ -2771,7 +2886,7 @@
       </c>
       <c r="K13" s="43"/>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>344</v>
       </c>
@@ -2802,7 +2917,7 @@
       </c>
       <c r="K14" s="43"/>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>342</v>
       </c>
@@ -2833,7 +2948,7 @@
       </c>
       <c r="K15" s="43"/>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>345</v>
       </c>
@@ -2864,7 +2979,7 @@
       </c>
       <c r="K16" s="43"/>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="29" t="s">
         <v>339</v>
       </c>
@@ -2895,7 +3010,7 @@
       </c>
       <c r="K17" s="44"/>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="29" t="s">
         <v>341</v>
       </c>
@@ -2926,7 +3041,7 @@
       </c>
       <c r="K18" s="44"/>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>340</v>
       </c>
@@ -2957,7 +3072,7 @@
       </c>
       <c r="K19" s="43"/>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="29" t="s">
         <v>348</v>
       </c>
@@ -2988,7 +3103,7 @@
       </c>
       <c r="K20" s="44"/>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>361</v>
       </c>
@@ -3011,7 +3126,7 @@
       <c r="J21" s="6"/>
       <c r="K21" s="41"/>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
         <v>55</v>
       </c>
@@ -3042,7 +3157,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
         <v>45</v>
       </c>
@@ -3073,7 +3188,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
         <v>47</v>
       </c>
@@ -3104,7 +3219,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>49</v>
       </c>
@@ -3135,7 +3250,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>137</v>
       </c>
@@ -3162,7 +3277,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>362</v>
       </c>
@@ -3183,7 +3298,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>93</v>
       </c>
@@ -3215,7 +3330,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>41</v>
       </c>
@@ -3244,7 +3359,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>38</v>
       </c>
@@ -3273,7 +3388,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>6</v>
       </c>
@@ -3298,7 +3413,7 @@
       </c>
       <c r="K31" s="41"/>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>197</v>
       </c>
@@ -3325,7 +3440,7 @@
       </c>
       <c r="K32" s="41"/>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>219</v>
       </c>
@@ -3350,7 +3465,7 @@
       </c>
       <c r="K33" s="41"/>
     </row>
-    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>363</v>
       </c>
@@ -3373,7 +3488,7 @@
       <c r="J34" s="6"/>
       <c r="K34" s="41"/>
     </row>
-    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>364</v>
       </c>
@@ -3396,7 +3511,7 @@
       <c r="J35" s="6"/>
       <c r="K35" s="41"/>
     </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>365</v>
       </c>
@@ -3419,7 +3534,7 @@
       <c r="J36" s="6"/>
       <c r="K36" s="41"/>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>366</v>
       </c>
@@ -3442,7 +3557,7 @@
       <c r="J37" s="6"/>
       <c r="K37" s="41"/>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>367</v>
       </c>
@@ -3467,7 +3582,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>368</v>
       </c>
@@ -3492,7 +3607,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
         <v>369</v>
       </c>
@@ -3517,7 +3632,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>370</v>
       </c>
@@ -3542,7 +3657,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>371</v>
       </c>
@@ -3567,7 +3682,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>372</v>
       </c>
@@ -3592,7 +3707,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>373</v>
       </c>
@@ -3617,7 +3732,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>374</v>
       </c>
@@ -3642,7 +3757,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
         <v>375</v>
       </c>
@@ -3667,7 +3782,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>108</v>
       </c>
@@ -3697,7 +3812,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>103</v>
       </c>
@@ -3727,7 +3842,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>86</v>
       </c>
@@ -3757,7 +3872,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>231</v>
       </c>
@@ -3786,7 +3901,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="31" t="s">
         <v>380</v>
       </c>
@@ -3811,7 +3926,7 @@
       <c r="J51" s="6"/>
       <c r="K51" s="41"/>
     </row>
-    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
         <v>27</v>
       </c>
@@ -3841,7 +3956,7 @@
       </c>
       <c r="K52" s="42"/>
     </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
         <v>2</v>
       </c>
@@ -3871,7 +3986,7 @@
       </c>
       <c r="K53" s="42"/>
     </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
         <v>130</v>
       </c>
@@ -3894,7 +4009,7 @@
       </c>
       <c r="K54" s="42"/>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
         <v>7</v>
       </c>
@@ -3924,7 +4039,7 @@
       </c>
       <c r="K55" s="42"/>
     </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
         <v>0</v>
       </c>
@@ -3954,7 +4069,7 @@
       </c>
       <c r="K56" s="41"/>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
         <v>24</v>
       </c>
@@ -3984,7 +4099,7 @@
       </c>
       <c r="K57" s="42"/>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="10" t="s">
         <v>53</v>
       </c>
@@ -4014,7 +4129,7 @@
       </c>
       <c r="K58" s="41"/>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
         <v>73</v>
       </c>
@@ -4046,7 +4161,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
         <v>116</v>
       </c>
@@ -4076,7 +4191,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
         <v>112</v>
       </c>
@@ -4108,7 +4223,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
         <v>268</v>
       </c>
@@ -4162,7 +4277,7 @@
       <c r="J63" s="6"/>
       <c r="K63" s="41"/>
     </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" s="17" t="s">
         <v>223</v>
       </c>
@@ -4187,7 +4302,7 @@
       </c>
       <c r="K64" s="41"/>
     </row>
-    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
         <v>151</v>
       </c>
@@ -4214,7 +4329,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
         <v>145</v>
       </c>
@@ -4242,7 +4357,7 @@
       </c>
       <c r="K66" s="41"/>
     </row>
-    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
         <v>1</v>
       </c>
@@ -4271,7 +4386,7 @@
       </c>
       <c r="K67" s="41"/>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
         <v>1</v>
       </c>
@@ -4300,7 +4415,7 @@
       </c>
       <c r="K68" s="41"/>
     </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
         <v>327</v>
       </c>
@@ -4329,7 +4444,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
         <v>328</v>
       </c>
@@ -4358,7 +4473,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
         <v>97</v>
       </c>
@@ -4387,7 +4502,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
         <v>60</v>
       </c>
@@ -4421,7 +4536,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
         <v>248</v>
       </c>
@@ -4448,7 +4563,7 @@
       </c>
       <c r="K73" s="41"/>
     </row>
-    <row r="74" spans="1:11" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A74" s="22" t="s">
         <v>249</v>
       </c>
@@ -4475,7 +4590,7 @@
       </c>
       <c r="K74" s="41"/>
     </row>
-    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
         <v>81</v>
       </c>
@@ -4507,7 +4622,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" s="6" t="s">
         <v>78</v>
       </c>
@@ -4539,7 +4654,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
         <v>158</v>
       </c>
@@ -4566,7 +4681,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" s="6" t="s">
         <v>91</v>
       </c>
@@ -4593,7 +4708,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
         <v>159</v>
       </c>
@@ -4620,7 +4735,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
         <v>436</v>
       </c>
@@ -4649,7 +4764,7 @@
       </c>
       <c r="K80" s="41"/>
     </row>
-    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
         <v>247</v>
       </c>
@@ -4676,7 +4791,7 @@
       </c>
       <c r="K81" s="41"/>
     </row>
-    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
         <v>258</v>
       </c>
@@ -4701,7 +4816,7 @@
       </c>
       <c r="K82" s="41"/>
     </row>
-    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
         <v>168</v>
       </c>
@@ -4730,7 +4845,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
         <v>168</v>
       </c>
@@ -4759,7 +4874,7 @@
       </c>
       <c r="K84" s="41"/>
     </row>
-    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
         <v>254</v>
       </c>
@@ -4788,7 +4903,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" s="30" t="s">
         <v>65</v>
       </c>
@@ -4820,7 +4935,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" s="52" t="s">
         <v>69</v>
       </c>
@@ -4852,7 +4967,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" s="32" t="s">
         <v>18</v>
       </c>
@@ -4877,7 +4992,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" s="6" t="s">
         <v>120</v>
       </c>
@@ -4907,7 +5022,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
         <v>397</v>
       </c>
@@ -4934,7 +5049,7 @@
       </c>
       <c r="K90" s="47"/>
     </row>
-    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" s="25" t="s">
         <v>264</v>
       </c>
@@ -4963,7 +5078,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
         <v>14</v>
       </c>
@@ -4988,7 +5103,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" s="25" t="s">
         <v>152</v>
       </c>
@@ -5040,7 +5155,7 @@
       </c>
       <c r="K94" s="47"/>
     </row>
-    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" s="6" t="s">
         <v>20</v>
       </c>
@@ -5063,7 +5178,7 @@
       </c>
       <c r="K95" s="47"/>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" s="25" t="s">
         <v>244</v>
       </c>
@@ -5088,7 +5203,7 @@
       </c>
       <c r="K96" s="47"/>
     </row>
-    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" s="25" t="s">
         <v>234</v>
       </c>
@@ -5107,7 +5222,7 @@
       <c r="J97" s="33"/>
       <c r="K97" s="47"/>
     </row>
-    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="25" t="s">
         <v>270</v>
       </c>
@@ -5128,7 +5243,7 @@
       <c r="J98" s="33"/>
       <c r="K98" s="47"/>
     </row>
-    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" s="27" t="s">
         <v>9</v>
       </c>
@@ -5149,7 +5264,7 @@
       </c>
       <c r="K99" s="45"/>
     </row>
-    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" s="25" t="s">
         <v>233</v>
       </c>
@@ -5195,7 +5310,7 @@
       </c>
       <c r="K101" s="47"/>
     </row>
-    <row r="102" spans="1:11" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
         <v>415</v>
       </c>
@@ -5224,7 +5339,7 @@
       </c>
       <c r="K102" s="47"/>
     </row>
-    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" s="30" t="s">
         <v>33</v>
       </c>
@@ -5245,7 +5360,7 @@
       </c>
       <c r="K103" s="47"/>
     </row>
-    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" s="30" t="s">
         <v>32</v>
       </c>
@@ -5266,7 +5381,7 @@
       </c>
       <c r="K104" s="47"/>
     </row>
-    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" s="30" t="s">
         <v>29</v>
       </c>
@@ -5287,7 +5402,7 @@
       </c>
       <c r="K105" s="47"/>
     </row>
-    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" s="30" t="s">
         <v>28</v>
       </c>
@@ -5308,7 +5423,7 @@
       </c>
       <c r="K106" s="47"/>
     </row>
-    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" s="30" t="s">
         <v>23</v>
       </c>
@@ -5331,7 +5446,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" s="30" t="s">
         <v>31</v>
       </c>
@@ -5352,7 +5467,7 @@
       </c>
       <c r="K108" s="47"/>
     </row>
-    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" s="30" t="s">
         <v>25</v>
       </c>
@@ -5373,7 +5488,7 @@
       </c>
       <c r="K109" s="47"/>
     </row>
-    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" s="30" t="s">
         <v>30</v>
       </c>
@@ -5394,7 +5509,7 @@
       </c>
       <c r="K110" s="47"/>
     </row>
-    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" s="30" t="s">
         <v>26</v>
       </c>
@@ -5415,7 +5530,7 @@
       </c>
       <c r="K111" s="47"/>
     </row>
-    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="6" t="s">
         <v>41</v>
       </c>
@@ -5438,7 +5553,7 @@
       </c>
       <c r="K112" s="45"/>
     </row>
-    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" s="6" t="s">
         <v>38</v>
       </c>
@@ -5461,7 +5576,7 @@
       </c>
       <c r="K113" s="47"/>
     </row>
-    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="55" t="s">
         <v>381</v>
       </c>
@@ -5486,7 +5601,7 @@
       <c r="J114" s="26"/>
       <c r="K114" s="46"/>
     </row>
-    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="55" t="s">
         <v>381</v>
       </c>
@@ -5515,7 +5630,7 @@
       </c>
       <c r="K115" s="48"/>
     </row>
-    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" s="55" t="s">
         <v>390</v>
       </c>
@@ -5544,7 +5659,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" s="55" t="s">
         <v>392</v>
       </c>
@@ -5571,7 +5686,7 @@
       </c>
       <c r="K117" s="48"/>
     </row>
-    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" s="55" t="s">
         <v>400</v>
       </c>
@@ -5598,7 +5713,7 @@
       </c>
       <c r="K118" s="46"/>
     </row>
-    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" s="55" t="s">
         <v>400</v>
       </c>
@@ -5616,14 +5731,16 @@
       </c>
       <c r="F119" s="6"/>
       <c r="G119" s="7"/>
-      <c r="H119" s="8"/>
+      <c r="H119" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I119" s="9"/>
       <c r="J119" s="23" t="s">
         <v>408</v>
       </c>
       <c r="K119" s="48"/>
     </row>
-    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120" s="55" t="s">
         <v>411</v>
       </c>
@@ -5650,7 +5767,7 @@
       </c>
       <c r="K120" s="46"/>
     </row>
-    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121" s="55" t="s">
         <v>425</v>
       </c>
@@ -5677,7 +5794,7 @@
       </c>
       <c r="K121" s="49"/>
     </row>
-    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122" s="55" t="s">
         <v>425</v>
       </c>
@@ -5691,14 +5808,16 @@
       <c r="E122" s="6"/>
       <c r="F122" s="6"/>
       <c r="G122" s="7"/>
-      <c r="H122" s="8"/>
+      <c r="H122" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I122" s="9"/>
       <c r="J122" s="26" t="s">
         <v>432</v>
       </c>
       <c r="K122" s="46"/>
     </row>
-    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123" s="55" t="s">
         <v>426</v>
       </c>
@@ -5725,7 +5844,7 @@
       </c>
       <c r="K123" s="48"/>
     </row>
-    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" s="55" t="s">
         <v>426</v>
       </c>
@@ -5739,144 +5858,286 @@
       <c r="E124" s="6"/>
       <c r="F124" s="6"/>
       <c r="G124" s="7"/>
-      <c r="H124" s="8"/>
+      <c r="H124" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I124" s="9"/>
       <c r="J124" s="26" t="s">
         <v>432</v>
       </c>
       <c r="K124" s="46"/>
     </row>
-    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="55"/>
-      <c r="B125" s="5"/>
-      <c r="C125" s="5"/>
-      <c r="D125" s="6"/>
-      <c r="E125" s="6"/>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A125" s="55" t="s">
+        <v>438</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="D125" s="54" t="s">
+        <v>100</v>
+      </c>
+      <c r="E125" s="54" t="s">
+        <v>440</v>
+      </c>
       <c r="F125" s="6"/>
       <c r="G125" s="7"/>
-      <c r="H125" s="8"/>
+      <c r="H125" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I125" s="9"/>
-      <c r="J125" s="23"/>
+      <c r="J125" s="23" t="s">
+        <v>441</v>
+      </c>
       <c r="K125" s="48"/>
     </row>
-    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="55"/>
-      <c r="B126" s="5"/>
-      <c r="C126" s="5"/>
-      <c r="D126" s="6"/>
-      <c r="E126" s="6"/>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A126" s="55" t="s">
+        <v>442</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>444</v>
+      </c>
       <c r="F126" s="6"/>
       <c r="G126" s="7"/>
-      <c r="H126" s="8"/>
+      <c r="H126" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I126" s="9"/>
-      <c r="J126" s="26"/>
+      <c r="J126" s="26" t="s">
+        <v>445</v>
+      </c>
       <c r="K126" s="46"/>
     </row>
-    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="55"/>
-      <c r="B127" s="5"/>
-      <c r="C127" s="5"/>
-      <c r="D127" s="6"/>
-      <c r="E127" s="6"/>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A127" s="55" t="s">
+        <v>446</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>447</v>
+      </c>
       <c r="F127" s="6"/>
       <c r="G127" s="7"/>
-      <c r="H127" s="8"/>
+      <c r="H127" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I127" s="9"/>
-      <c r="J127" s="23"/>
+      <c r="J127" s="23" t="s">
+        <v>449</v>
+      </c>
       <c r="K127" s="48"/>
     </row>
-    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="5"/>
-      <c r="B128" s="5"/>
-      <c r="C128" s="5"/>
-      <c r="D128" s="6"/>
-      <c r="E128" s="6"/>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A128" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>452</v>
+      </c>
       <c r="F128" s="6"/>
       <c r="G128" s="7"/>
-      <c r="H128" s="8"/>
+      <c r="H128" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I128" s="9"/>
-      <c r="J128" s="26"/>
+      <c r="J128" s="26" t="s">
+        <v>453</v>
+      </c>
       <c r="K128" s="46"/>
     </row>
-    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="5"/>
-      <c r="B129" s="5"/>
-      <c r="C129" s="5"/>
-      <c r="D129" s="6"/>
-      <c r="E129" s="6"/>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A129" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E129" s="6" t="s">
+        <v>456</v>
+      </c>
       <c r="F129" s="6"/>
       <c r="G129" s="19"/>
-      <c r="H129" s="18"/>
+      <c r="H129" s="18" t="s">
+        <v>167</v>
+      </c>
       <c r="I129" s="9"/>
-      <c r="J129" s="24"/>
+      <c r="J129" s="24" t="s">
+        <v>457</v>
+      </c>
       <c r="K129" s="49"/>
     </row>
-    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="5"/>
-      <c r="B130" s="5"/>
-      <c r="C130" s="5"/>
-      <c r="D130" s="6"/>
-      <c r="E130" s="6"/>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A130" s="56" t="s">
+        <v>458</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E130" t="s">
+        <v>460</v>
+      </c>
       <c r="F130" s="6"/>
       <c r="G130" s="7"/>
-      <c r="H130" s="8"/>
+      <c r="H130" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I130" s="9"/>
-      <c r="J130" s="26"/>
+      <c r="J130" s="26" t="s">
+        <v>461</v>
+      </c>
       <c r="K130" s="46"/>
     </row>
-    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="5"/>
-      <c r="B131" s="5"/>
-      <c r="C131" s="5"/>
-      <c r="D131" s="6"/>
-      <c r="E131" s="6"/>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A131" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E131" s="6" t="s">
+        <v>464</v>
+      </c>
       <c r="F131" s="6"/>
       <c r="G131" s="7"/>
-      <c r="H131" s="8"/>
+      <c r="H131" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I131" s="9"/>
-      <c r="J131" s="23"/>
+      <c r="J131" s="23" t="s">
+        <v>465</v>
+      </c>
       <c r="K131" s="48"/>
     </row>
-    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="5"/>
-      <c r="B132" s="5"/>
-      <c r="C132" s="5"/>
-      <c r="D132" s="6"/>
-      <c r="E132" s="6"/>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A132" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>468</v>
+      </c>
       <c r="F132" s="6"/>
       <c r="G132" s="19"/>
-      <c r="H132" s="18"/>
+      <c r="H132" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I132" s="9"/>
-      <c r="J132" s="28"/>
+      <c r="J132" s="28" t="s">
+        <v>469</v>
+      </c>
       <c r="K132" s="50"/>
     </row>
-    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="5"/>
-      <c r="B133" s="5"/>
-      <c r="C133" s="5"/>
-      <c r="D133" s="6"/>
-      <c r="E133" s="6"/>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A133" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E133" s="6" t="s">
+        <v>472</v>
+      </c>
       <c r="F133" s="6"/>
       <c r="G133" s="19"/>
-      <c r="H133" s="18"/>
+      <c r="H133" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I133" s="9"/>
-      <c r="J133" s="6"/>
+      <c r="J133" s="6" t="s">
+        <v>473</v>
+      </c>
       <c r="K133" s="41"/>
     </row>
-    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="5"/>
-      <c r="B134" s="5"/>
-      <c r="C134" s="5"/>
-      <c r="D134" s="6"/>
-      <c r="E134" s="6"/>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A134" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>476</v>
+      </c>
       <c r="F134" s="6"/>
       <c r="G134" s="19"/>
-      <c r="H134" s="18"/>
+      <c r="H134" s="18" t="s">
+        <v>167</v>
+      </c>
       <c r="I134" s="9"/>
-      <c r="J134" s="6"/>
+      <c r="J134" s="6" t="s">
+        <v>477</v>
+      </c>
       <c r="K134" s="41"/>
     </row>
-    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" s="5"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F866D403-0D90-8F4D-9A70-C986CF2C5127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF61CBBA-5DE7-4040-951E-4B202A99F04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="483">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -1530,6 +1530,21 @@
   </si>
   <si>
     <t>Youth Cam</t>
+  </si>
+  <si>
+    <t>NAHI-B007</t>
+  </si>
+  <si>
+    <t>192.168.0.44</t>
+  </si>
+  <si>
+    <t>192.168.0.45</t>
+  </si>
+  <si>
+    <t>192.168.0.48</t>
+  </si>
+  <si>
+    <t>ITNET WAP</t>
   </si>
 </sst>
 </file>
@@ -1819,7 +1834,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1905,6 +1920,12 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2189,8 +2210,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K135" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K135" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K137" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K137" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{EF2C341F-E5C1-604C-942C-FB7E9F76F1CD}" name="AssetTag" dataDxfId="10"/>
     <tableColumn id="13" xr3:uid="{41250547-1480-7146-952C-14798A4748DA}" name="NIC" dataDxfId="9"/>
@@ -6138,25 +6159,79 @@
       <c r="K134" s="41"/>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A135" s="5"/>
-      <c r="B135" s="5"/>
+      <c r="A135" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>382</v>
+      </c>
       <c r="C135" s="5"/>
-      <c r="D135" s="6"/>
-      <c r="E135" s="6"/>
+      <c r="D135" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E135" s="6" t="s">
+        <v>479</v>
+      </c>
       <c r="F135" s="6"/>
       <c r="G135" s="19"/>
-      <c r="H135" s="18"/>
+      <c r="H135" s="18" t="s">
+        <v>167</v>
+      </c>
       <c r="I135" s="9"/>
-      <c r="J135" s="6"/>
+      <c r="J135" s="6" t="s">
+        <v>482</v>
+      </c>
       <c r="K135" s="41"/>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H136"/>
-      <c r="I136"/>
+      <c r="A136" s="57" t="s">
+        <v>478</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C136" s="57"/>
+      <c r="D136" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E136" s="58" t="s">
+        <v>480</v>
+      </c>
+      <c r="F136" s="58"/>
+      <c r="G136" s="19"/>
+      <c r="H136" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="I136" s="59"/>
+      <c r="J136" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="K136" s="60"/>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H137"/>
-      <c r="I137"/>
+      <c r="A137" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C137" s="57"/>
+      <c r="D137" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E137" s="58" t="s">
+        <v>481</v>
+      </c>
+      <c r="F137" s="58"/>
+      <c r="G137" s="19"/>
+      <c r="H137" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="I137" s="59"/>
+      <c r="J137" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="K137" s="60"/>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H138"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF61CBBA-5DE7-4040-951E-4B202A99F04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA44528-389F-8B4C-8014-14DDEEE92F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
+    <workbookView xWindow="0" yWindow="3500" windowWidth="30240" windowHeight="16140" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
   <sheets>
     <sheet name="network" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="486">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -1545,13 +1545,22 @@
   </si>
   <si>
     <t>ITNET WAP</t>
+  </si>
+  <si>
+    <t>MHPR-J001</t>
+  </si>
+  <si>
+    <t>B0:F5:30:CA:16:B0</t>
+  </si>
+  <si>
+    <t>ITNET Modem</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1656,6 +1665,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1834,7 +1849,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1926,6 +1941,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2210,8 +2229,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K137" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K137" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K138" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K138" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{EF2C341F-E5C1-604C-942C-FB7E9F76F1CD}" name="AssetTag" dataDxfId="10"/>
     <tableColumn id="13" xr3:uid="{41250547-1480-7146-952C-14798A4748DA}" name="NIC" dataDxfId="9"/>
@@ -6234,8 +6253,29 @@
       <c r="K137" s="60"/>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H138"/>
-      <c r="I138"/>
+      <c r="A138" s="61" t="s">
+        <v>483</v>
+      </c>
+      <c r="B138" s="57" t="s">
+        <v>382</v>
+      </c>
+      <c r="C138" s="62" t="s">
+        <v>484</v>
+      </c>
+      <c r="D138" s="58" t="s">
+        <v>100</v>
+      </c>
+      <c r="E138" s="58"/>
+      <c r="F138" s="58"/>
+      <c r="G138" s="19"/>
+      <c r="H138" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="I138" s="59"/>
+      <c r="J138" s="58" t="s">
+        <v>485</v>
+      </c>
+      <c r="K138" s="60"/>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H139"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA44528-389F-8B4C-8014-14DDEEE92F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F3D9B7E-ACE9-B443-90B5-295B495888B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3500" windowWidth="30240" windowHeight="16140" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="485">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -164,9 +164,6 @@
     <t>Lobby (port14 on switch 50-80m in length)</t>
   </si>
   <si>
-    <t>Wireless Access Point</t>
-  </si>
-  <si>
     <t>NAHU-B005</t>
   </si>
   <si>
@@ -1358,9 +1355,6 @@
     <t>80:6d:97:20:a7:89</t>
   </si>
   <si>
-    <t>builtin AVNET</t>
-  </si>
-  <si>
     <t>80:6d: 97:20:a7:8e</t>
   </si>
   <si>
@@ -1544,16 +1538,19 @@
     <t>192.168.0.48</t>
   </si>
   <si>
-    <t>ITNET WAP</t>
-  </si>
-  <si>
     <t>MHPR-J001</t>
   </si>
   <si>
     <t>B0:F5:30:CA:16:B0</t>
   </si>
   <si>
-    <t>ITNET Modem</t>
+    <t>ITNet WAP</t>
+  </si>
+  <si>
+    <t>ITNet Modem</t>
+  </si>
+  <si>
+    <t>builtin AVNet</t>
   </si>
 </sst>
 </file>
@@ -2565,600 +2562,600 @@
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="K1" s="40" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K2" s="41"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="C3" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K3" s="41"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>194</v>
-      </c>
       <c r="D4" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K4" s="41"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K5" s="41"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K6" s="41"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K7" s="41"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K8" s="41"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K9" s="41"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K10" s="41"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="29" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K11" s="44"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K12" s="43"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>376</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>377</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K13" s="43"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K14" s="43"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K15" s="43"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K16" s="43"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="29" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K17" s="44"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="29" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F18" s="29" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K18" s="44"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K19" s="43"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="29" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K20" s="44"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B21" s="29"/>
       <c r="C21" s="29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E21" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="F21" s="29" t="s">
         <v>283</v>
-      </c>
-      <c r="F21" s="29" t="s">
-        <v>284</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="8"/>
@@ -3168,165 +3165,165 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K22" s="41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K23" s="41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K24" s="41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K25" s="41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I26" s="9"/>
       <c r="J26" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K26" s="42" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
@@ -3335,36 +3332,36 @@
       <c r="I27" s="9"/>
       <c r="J27" s="6"/>
       <c r="K27" s="41" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F28" s="19" t="str">
         <f>CONCATENATE("http://", E28)</f>
         <v>http://192.168.201.110</v>
       </c>
       <c r="G28" s="21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I28" s="9"/>
       <c r="J28" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K28" s="42">
         <v>4</v>
@@ -3372,60 +3369,60 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I29" s="9"/>
       <c r="J29" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K29" s="41" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K30" s="41" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
@@ -3437,67 +3434,67 @@
         <v>5</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="K31" s="41"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K32" s="41"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I33" s="9"/>
       <c r="J33" s="6">
@@ -3507,20 +3504,20 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="8"/>
@@ -3530,20 +3527,20 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B35" s="29"/>
       <c r="C35" s="29" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G35" s="19"/>
       <c r="H35" s="8"/>
@@ -3553,20 +3550,20 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B36" s="29"/>
       <c r="C36" s="29" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="8"/>
@@ -3576,20 +3573,20 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="8"/>
@@ -3599,242 +3596,242 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B38" s="29"/>
       <c r="C38" s="29" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="8"/>
       <c r="I38" s="9"/>
       <c r="J38" s="6"/>
       <c r="K38" s="41" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B39" s="29"/>
       <c r="C39" s="29" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F39" s="29" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="8"/>
       <c r="I39" s="9"/>
       <c r="J39" s="6"/>
       <c r="K39" s="41" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="29" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F40" s="29" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="8"/>
       <c r="I40" s="9"/>
       <c r="J40" s="6"/>
       <c r="K40" s="41" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="8"/>
       <c r="I41" s="9"/>
       <c r="J41" s="6"/>
       <c r="K41" s="41" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="8"/>
       <c r="I42" s="9"/>
       <c r="J42" s="6"/>
       <c r="K42" s="41" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="8"/>
       <c r="I43" s="9"/>
       <c r="J43" s="6"/>
       <c r="K43" s="41" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="8"/>
       <c r="I44" s="9"/>
       <c r="J44" s="6"/>
       <c r="K44" s="41" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B45" s="29"/>
       <c r="C45" s="29" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E45" s="29" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F45" s="29" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="8"/>
       <c r="I45" s="9"/>
       <c r="J45" s="6"/>
       <c r="K45" s="41" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B46" s="29"/>
       <c r="C46" s="29" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E46" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="F46" s="29" t="s">
         <v>272</v>
-      </c>
-      <c r="F46" s="29" t="s">
-        <v>273</v>
       </c>
       <c r="G46" s="19"/>
       <c r="H46" s="8"/>
       <c r="I46" s="9"/>
       <c r="J46" s="6"/>
       <c r="K46" s="41" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F47" s="7" t="str">
         <f>CONCATENATE("http://", E47)</f>
@@ -3842,29 +3839,29 @@
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I47" s="9"/>
       <c r="J47" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K47" s="41" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F48" s="7" t="str">
         <f>CONCATENATE("http://", E48)</f>
@@ -3872,29 +3869,29 @@
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I48" s="9"/>
       <c r="J48" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K48" s="41" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F49" s="7" t="str">
         <f>CONCATENATE("http://", E49)</f>
@@ -3902,40 +3899,40 @@
       </c>
       <c r="G49" s="7"/>
       <c r="H49" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K49" s="42" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="19" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K50" s="41">
         <v>22</v>
@@ -3943,24 +3940,24 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="31" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B51" s="13"/>
       <c r="C51" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="6"/>
@@ -3968,31 +3965,31 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F52" s="7" t="str">
         <f>CONCATENATE("http://", E52)</f>
         <v>http://192.168.0.23</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I52" s="9"/>
       <c r="J52" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K52" s="42"/>
     </row>
@@ -4002,50 +3999,50 @@
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F53" s="7" t="str">
         <f>CONCATENATE("http://", E53)</f>
         <v>http://192.168.0.22</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K53" s="42"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E54" s="6"/>
       <c r="F54" s="19"/>
       <c r="G54" s="7"/>
       <c r="H54" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I54" s="9"/>
       <c r="J54" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K54" s="42"/>
     </row>
@@ -4055,27 +4052,27 @@
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F55" s="7" t="str">
         <f>CONCATENATE("http://", E55)</f>
         <v>http://192.168.0.24</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H55" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K55" s="42"/>
     </row>
@@ -4085,135 +4082,135 @@
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F56" s="7" t="str">
         <f>CONCATENATE("http://", E56)</f>
         <v>http://192.168.0.25</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H56" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I56" s="9"/>
       <c r="J56" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K56" s="41"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F57" s="7" t="str">
         <f>CONCATENATE("http://", E57)</f>
         <v>http://192.168.0.26</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H57" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K57" s="42"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B58" s="10"/>
       <c r="C58" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F58" s="6" t="str">
         <f>CONCATENATE("http://", E58, ":8080")</f>
         <v>http://192.168.0.197:8080</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H58" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I58" s="9"/>
       <c r="J58" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K58" s="41"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F59" s="7" t="str">
         <f>CONCATENATE("http://", E59)</f>
         <v>http://192.168.0.193</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H59" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K59" s="41" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F60" s="7" t="str">
         <f>CONCATENATE("http://", E60)</f>
@@ -4221,29 +4218,29 @@
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I60" s="9"/>
       <c r="J60" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K60" s="41" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F61" s="7" t="str">
         <f>CONCATENATE("http://", E61)</f>
@@ -4251,40 +4248,40 @@
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K61" s="41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="19"/>
       <c r="H62" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K62" s="41">
         <v>12</v>
@@ -4295,23 +4292,23 @@
         <v>3</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C63" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E63" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="F63" s="7"/>
       <c r="G63" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H63" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="6"/>
@@ -4319,22 +4316,22 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" s="17" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F64" s="6"/>
       <c r="G64" s="6"/>
       <c r="H64" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I64" s="9"/>
       <c r="J64" s="6" t="s">
@@ -4344,26 +4341,26 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="6"/>
       <c r="H65" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I65" s="9"/>
       <c r="J65" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K65" s="41">
         <v>6</v>
@@ -4371,17 +4368,17 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B66" s="5"/>
       <c r="C66" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F66" s="7" t="str">
         <f>CONCATENATE("http://", E66)</f>
@@ -4389,11 +4386,11 @@
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I66" s="9"/>
       <c r="J66" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K66" s="41"/>
     </row>
@@ -4402,27 +4399,27 @@
         <v>1</v>
       </c>
       <c r="B67" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E67" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="C67" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H67" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K67" s="41"/>
     </row>
@@ -4431,218 +4428,218 @@
         <v>1</v>
       </c>
       <c r="B68" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E68" s="14" t="s">
         <v>170</v>
-      </c>
-      <c r="C68" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E68" s="14" t="s">
-        <v>171</v>
       </c>
       <c r="F68" s="6"/>
       <c r="G68" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H68" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I68" s="9"/>
       <c r="J68" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K68" s="41"/>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="53" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F69" s="6"/>
       <c r="G69" s="19" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H69" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K69" s="44" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="53" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D70" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F70" s="6"/>
       <c r="G70" s="19" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H70" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I70" s="9"/>
       <c r="J70" s="38" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K70" s="43" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
       <c r="H71" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K71" s="42" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B72" s="6"/>
       <c r="C72" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F72" s="7" t="str">
         <f>CONCATENATE("http://", E72)</f>
         <v>http://192.168.0.183</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H72" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K72" s="41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F73" s="6"/>
       <c r="G73" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H73" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I73" s="9"/>
       <c r="J73" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K73" s="41"/>
     </row>
     <row r="74" spans="1:11" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A74" s="22" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F74" s="6"/>
       <c r="G74" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H74" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I74" s="9"/>
       <c r="J74" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K74" s="41"/>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B75" s="30"/>
       <c r="C75" s="33" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E75" s="33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F75" s="36" t="str">
         <f>CONCATENATE("ftp://", E75)</f>
@@ -4650,31 +4647,31 @@
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K75" s="42" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B76" s="30"/>
       <c r="C76" s="33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E76" s="33" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F76" s="36" t="str">
         <f>CONCATENATE("ftp://", E76)</f>
@@ -4682,40 +4679,40 @@
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K76" s="42" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B77" s="25"/>
       <c r="C77" s="33" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D77" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E77" s="33" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F77" s="33"/>
       <c r="G77" s="6"/>
       <c r="H77" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="K77" s="41">
         <v>18</v>
@@ -4723,53 +4720,53 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B78" s="30"/>
       <c r="C78" s="33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E78" s="33" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F78" s="33"/>
       <c r="G78" s="6"/>
       <c r="H78" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I78" s="9"/>
       <c r="J78" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K78" s="41" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B79" s="25"/>
       <c r="C79" s="26" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D79" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E79" s="26" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="8"/>
       <c r="I79" s="9"/>
       <c r="J79" s="29" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K79" s="43">
         <v>14</v>
@@ -4777,109 +4774,109 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B80" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C80" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="D80" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="E80" s="34" t="s">
         <v>172</v>
-      </c>
-      <c r="D80" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="E80" s="34" t="s">
-        <v>173</v>
       </c>
       <c r="F80" s="33"/>
       <c r="G80" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I80" s="9"/>
       <c r="J80" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K80" s="41"/>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B81" s="27"/>
       <c r="C81" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E81" s="35" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F81" s="35"/>
       <c r="G81" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H81" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K81" s="41"/>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B82" s="25"/>
       <c r="C82" s="26" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D82" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E82" s="33" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F82" s="33"/>
       <c r="G82" s="19"/>
       <c r="H82" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I82" s="9"/>
       <c r="J82" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K82" s="41"/>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B83" s="25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C83" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="D83" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="E83" s="33" t="s">
         <v>184</v>
-      </c>
-      <c r="D83" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="E83" s="33" t="s">
-        <v>185</v>
       </c>
       <c r="F83" s="36"/>
       <c r="G83" s="7"/>
       <c r="H83" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="6" t="s">
-        <v>420</v>
+        <v>484</v>
       </c>
       <c r="K83" s="41">
         <v>10</v>
@@ -4887,57 +4884,57 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B84" s="25" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C84" s="26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E84" s="33" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F84" s="36"/>
       <c r="G84" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I84" s="9"/>
       <c r="J84" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K84" s="41"/>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B85" s="25"/>
       <c r="C85" s="23" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D85" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F85" s="33"/>
       <c r="G85" s="19" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I85" s="9"/>
       <c r="J85" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K85" s="44">
         <v>4</v>
@@ -4945,66 +4942,66 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" s="30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E86" s="33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F86" s="36" t="str">
         <f>CONCATENATE("http://", E86)</f>
         <v>http://192.168.0.195</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I86" s="9"/>
       <c r="J86" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K86" s="41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" s="52" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E87" s="35" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F87" s="37" t="str">
         <f>CONCATENATE("http://", E87)</f>
         <v>http://192.168.0.194</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H87" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I87" s="9"/>
       <c r="J87" s="35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K87" s="45" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.2">
@@ -5016,13 +5013,13 @@
         <v>16</v>
       </c>
       <c r="D88" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E88" s="33"/>
       <c r="F88" s="33"/>
       <c r="G88" s="6"/>
       <c r="H88" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I88" s="9"/>
       <c r="J88" s="33" t="s">
@@ -5034,17 +5031,17 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B89" s="30"/>
       <c r="C89" s="33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E89" s="33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F89" s="36" t="str">
         <f>CONCATENATE("http://", E89)</f>
@@ -5052,67 +5049,67 @@
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="33" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K89" s="47" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B90" s="25"/>
       <c r="C90" s="26" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E90" s="33" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F90" s="33"/>
       <c r="G90" s="19" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I90" s="9"/>
       <c r="J90" s="33" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K90" s="47"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" s="25" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B91" s="5"/>
       <c r="C91" s="26" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E91" s="33" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F91" s="33"/>
       <c r="G91" s="19" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I91" s="9"/>
       <c r="J91" s="33" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K91" s="47">
         <v>13</v>
@@ -5127,13 +5124,13 @@
         <v>12</v>
       </c>
       <c r="D92" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E92" s="33"/>
       <c r="F92" s="33"/>
       <c r="G92" s="6"/>
       <c r="H92" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I92" s="9"/>
       <c r="J92" s="33" t="s">
@@ -5145,26 +5142,26 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B93" s="5"/>
       <c r="C93" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="D93" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="E93" s="33" t="s">
         <v>154</v>
-      </c>
-      <c r="D93" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="E93" s="33" t="s">
-        <v>155</v>
       </c>
       <c r="F93" s="33"/>
       <c r="G93" s="6"/>
       <c r="H93" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I93" s="9"/>
       <c r="J93" s="33" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K93" s="47"/>
     </row>
@@ -5173,25 +5170,25 @@
         <v>3</v>
       </c>
       <c r="B94" s="25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C94" s="26" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D94" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E94" s="33" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F94" s="36"/>
       <c r="G94" s="7"/>
       <c r="H94" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I94" s="9"/>
       <c r="J94" s="26" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K94" s="47"/>
     </row>
@@ -5202,15 +5199,15 @@
       <c r="B95" s="30"/>
       <c r="C95" s="33"/>
       <c r="D95" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E95" s="34" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F95" s="33"/>
       <c r="G95" s="6"/>
       <c r="H95" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="33" t="s">
@@ -5220,40 +5217,40 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" s="25" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B96" s="5"/>
       <c r="C96" s="26"/>
       <c r="D96" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E96" s="34" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F96" s="33"/>
       <c r="G96" s="19" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I96" s="9"/>
       <c r="J96" s="33" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K96" s="47"/>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" s="25" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B97" s="5"/>
       <c r="C97" s="26"/>
       <c r="D97" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E97" s="33" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F97" s="33"/>
       <c r="G97" s="19"/>
@@ -5264,20 +5261,20 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="25" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="26"/>
       <c r="D98" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E98" s="33" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F98" s="33"/>
       <c r="G98" s="19"/>
       <c r="H98" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I98" s="9"/>
       <c r="J98" s="33"/>
@@ -5290,7 +5287,7 @@
       <c r="B99" s="5"/>
       <c r="C99" s="35"/>
       <c r="D99" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E99" s="35" t="s">
         <v>4</v>
@@ -5306,18 +5303,18 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" s="25" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B100" s="5"/>
       <c r="C100" s="26"/>
       <c r="D100" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E100" s="33"/>
       <c r="F100" s="33"/>
       <c r="G100" s="19"/>
       <c r="H100" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I100" s="9"/>
       <c r="J100" s="33"/>
@@ -5328,159 +5325,159 @@
         <v>3</v>
       </c>
       <c r="B101" s="25" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C101" s="26" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D101" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E101" s="33" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F101" s="36"/>
       <c r="G101" s="7"/>
       <c r="H101" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I101" s="9"/>
       <c r="J101" s="33" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="K101" s="47"/>
     </row>
     <row r="102" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B102" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C102" s="26" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D102" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E102" s="33" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F102" s="36"/>
       <c r="G102" s="7"/>
       <c r="H102" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J102" s="33" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K102" s="47"/>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B103" s="6"/>
       <c r="C103" s="33"/>
       <c r="D103" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E103" s="33"/>
       <c r="F103" s="33"/>
       <c r="G103" s="6"/>
       <c r="H103" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I103" s="9"/>
       <c r="J103" s="33" t="s">
-        <v>22</v>
+        <v>482</v>
       </c>
       <c r="K103" s="47"/>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B104" s="6"/>
       <c r="C104" s="33"/>
       <c r="D104" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E104" s="33"/>
       <c r="F104" s="33"/>
       <c r="G104" s="6"/>
       <c r="H104" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I104" s="9"/>
       <c r="J104" s="33" t="s">
-        <v>22</v>
+        <v>482</v>
       </c>
       <c r="K104" s="47"/>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B105" s="6"/>
       <c r="C105" s="33"/>
       <c r="D105" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E105" s="33"/>
       <c r="F105" s="33"/>
       <c r="G105" s="6"/>
       <c r="H105" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I105" s="9"/>
       <c r="J105" s="33" t="s">
-        <v>22</v>
+        <v>482</v>
       </c>
       <c r="K105" s="47"/>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B106" s="6"/>
       <c r="C106" s="33"/>
       <c r="D106" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E106" s="33"/>
       <c r="F106" s="33"/>
       <c r="G106" s="6"/>
       <c r="H106" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I106" s="9"/>
       <c r="J106" s="33" t="s">
-        <v>22</v>
+        <v>482</v>
       </c>
       <c r="K106" s="47"/>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B107" s="6"/>
       <c r="C107" s="33"/>
       <c r="D107" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E107" s="33"/>
       <c r="F107" s="33"/>
       <c r="G107" s="6"/>
       <c r="H107" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I107" s="9"/>
       <c r="J107" s="33" t="s">
-        <v>22</v>
+        <v>482</v>
       </c>
       <c r="K107" s="47" t="s">
         <v>21</v>
@@ -5488,154 +5485,154 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B108" s="6"/>
       <c r="C108" s="33"/>
       <c r="D108" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E108" s="33"/>
       <c r="F108" s="33"/>
       <c r="G108" s="6"/>
       <c r="H108" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I108" s="9"/>
       <c r="J108" s="33" t="s">
-        <v>22</v>
+        <v>482</v>
       </c>
       <c r="K108" s="47"/>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" s="30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B109" s="6"/>
       <c r="C109" s="33"/>
       <c r="D109" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E109" s="33"/>
       <c r="F109" s="33"/>
       <c r="G109" s="6"/>
       <c r="H109" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I109" s="9"/>
       <c r="J109" s="33" t="s">
-        <v>22</v>
+        <v>482</v>
       </c>
       <c r="K109" s="47"/>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B110" s="6"/>
       <c r="C110" s="33"/>
       <c r="D110" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E110" s="33"/>
       <c r="F110" s="33"/>
       <c r="G110" s="6"/>
       <c r="H110" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I110" s="9"/>
       <c r="J110" s="33" t="s">
-        <v>22</v>
+        <v>482</v>
       </c>
       <c r="K110" s="47"/>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B111" s="6"/>
       <c r="C111" s="33"/>
       <c r="D111" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E111" s="33"/>
       <c r="F111" s="33"/>
       <c r="G111" s="6"/>
       <c r="H111" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I111" s="9"/>
       <c r="J111" s="33" t="s">
-        <v>22</v>
+        <v>482</v>
       </c>
       <c r="K111" s="47"/>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C112" s="5"/>
       <c r="D112" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
       <c r="G112" s="7"/>
       <c r="H112" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I112" s="9"/>
       <c r="J112" s="35" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K112" s="45"/>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C113" s="5"/>
       <c r="D113" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
       <c r="G113" s="7"/>
       <c r="H113" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I113" s="9"/>
       <c r="J113" s="39" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K113" s="47"/>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="55" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C114" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="E114" s="6" t="s">
         <v>383</v>
-      </c>
-      <c r="D114" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="E114" s="6" t="s">
-        <v>384</v>
       </c>
       <c r="F114" s="6"/>
       <c r="G114" s="7"/>
       <c r="H114" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I114" s="9"/>
       <c r="J114" s="26"/>
@@ -5643,558 +5640,558 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="B115" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="B115" s="5" t="s">
-        <v>382</v>
-      </c>
       <c r="C115" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E115" s="6" t="s">
         <v>387</v>
-      </c>
-      <c r="D115" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E115" s="6" t="s">
-        <v>388</v>
       </c>
       <c r="F115" s="6"/>
       <c r="G115" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H115" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I115" s="9"/>
       <c r="J115" s="23" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="K115" s="48"/>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" s="55" t="s">
+        <v>389</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C116" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="B116" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>391</v>
-      </c>
       <c r="D116" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F116" s="6"/>
       <c r="G116" s="7"/>
       <c r="H116" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I116" s="9"/>
       <c r="J116" s="26" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K116" s="46" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" s="55" t="s">
+        <v>391</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C117" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="B117" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>393</v>
-      </c>
       <c r="D117" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F117" s="6"/>
       <c r="G117" s="7"/>
       <c r="H117" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="23" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K117" s="48"/>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" s="55" t="s">
+        <v>399</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="C118" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="B118" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="C118" s="5" t="s">
+      <c r="D118" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E118" s="6" t="s">
         <v>401</v>
-      </c>
-      <c r="D118" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E118" s="6" t="s">
-        <v>402</v>
       </c>
       <c r="F118" s="6"/>
       <c r="G118" s="7"/>
       <c r="H118" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I118" s="9"/>
       <c r="J118" s="26" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K118" s="46"/>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" s="55" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B119" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C119" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="C119" s="5" t="s">
+      <c r="D119" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E119" s="6" t="s">
         <v>406</v>
-      </c>
-      <c r="D119" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E119" s="6" t="s">
-        <v>407</v>
       </c>
       <c r="F119" s="6"/>
       <c r="G119" s="7"/>
       <c r="H119" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I119" s="9"/>
       <c r="J119" s="23" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K119" s="48"/>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120" s="55" t="s">
+        <v>410</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E120" s="6" t="s">
         <v>411</v>
-      </c>
-      <c r="B120" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="D120" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E120" s="6" t="s">
-        <v>412</v>
       </c>
       <c r="F120" s="6"/>
       <c r="G120" s="7"/>
       <c r="H120" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I120" s="9"/>
       <c r="J120" s="26" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K120" s="46"/>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121" s="55" t="s">
+        <v>423</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C121" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="B121" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C121" s="5" t="s">
+      <c r="D121" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E121" s="6" t="s">
         <v>427</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E121" s="6" t="s">
-        <v>429</v>
       </c>
       <c r="F121" s="6"/>
       <c r="G121" s="19"/>
       <c r="H121" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="24" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="K121" s="49"/>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122" s="55" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C122" s="5"/>
       <c r="D122" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E122" s="6"/>
       <c r="F122" s="6"/>
       <c r="G122" s="7"/>
       <c r="H122" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I122" s="9"/>
       <c r="J122" s="26" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="K122" s="46"/>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123" s="55" t="s">
+        <v>424</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C123" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="B123" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C123" s="5" t="s">
+      <c r="D123" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E123" s="6" t="s">
         <v>428</v>
-      </c>
-      <c r="D123" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E123" s="6" t="s">
-        <v>430</v>
       </c>
       <c r="F123" s="6"/>
       <c r="G123" s="7"/>
       <c r="H123" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I123" s="9"/>
       <c r="J123" s="23" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="K123" s="48"/>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" s="55" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C124" s="5"/>
       <c r="D124" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E124" s="6"/>
       <c r="F124" s="6"/>
       <c r="G124" s="7"/>
       <c r="H124" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I124" s="9"/>
       <c r="J124" s="26" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="K124" s="46"/>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125" s="55" t="s">
+        <v>436</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="D125" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="E125" s="54" t="s">
         <v>438</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="D125" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="E125" s="54" t="s">
-        <v>440</v>
       </c>
       <c r="F125" s="6"/>
       <c r="G125" s="7"/>
       <c r="H125" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I125" s="9"/>
       <c r="J125" s="23" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="K125" s="48"/>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126" s="55" t="s">
+        <v>440</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E126" s="6" t="s">
         <v>442</v>
-      </c>
-      <c r="B126" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="D126" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E126" s="6" t="s">
-        <v>444</v>
       </c>
       <c r="F126" s="6"/>
       <c r="G126" s="7"/>
       <c r="H126" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I126" s="9"/>
       <c r="J126" s="26" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="K126" s="46"/>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127" s="55" t="s">
+        <v>444</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C127" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="B127" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>448</v>
-      </c>
       <c r="D127" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F127" s="6"/>
       <c r="G127" s="7"/>
       <c r="H127" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I127" s="9"/>
       <c r="J127" s="23" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="K127" s="48"/>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E128" s="6" t="s">
         <v>450</v>
-      </c>
-      <c r="B128" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="D128" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E128" s="6" t="s">
-        <v>452</v>
       </c>
       <c r="F128" s="6"/>
       <c r="G128" s="7"/>
       <c r="H128" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I128" s="9"/>
       <c r="J128" s="26" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K128" s="46"/>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E129" s="6" t="s">
         <v>454</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="D129" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E129" s="6" t="s">
-        <v>456</v>
       </c>
       <c r="F129" s="6"/>
       <c r="G129" s="19"/>
       <c r="H129" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I129" s="9"/>
       <c r="J129" s="24" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K129" s="49"/>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" s="56" t="s">
+        <v>456</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E130" t="s">
         <v>458</v>
-      </c>
-      <c r="B130" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="D130" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E130" t="s">
-        <v>460</v>
       </c>
       <c r="F130" s="6"/>
       <c r="G130" s="7"/>
       <c r="H130" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I130" s="9"/>
       <c r="J130" s="26" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K130" s="46"/>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E131" s="6" t="s">
         <v>462</v>
-      </c>
-      <c r="B131" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="D131" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E131" s="6" t="s">
-        <v>464</v>
       </c>
       <c r="F131" s="6"/>
       <c r="G131" s="7"/>
       <c r="H131" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="23" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="K131" s="48"/>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E132" s="6" t="s">
         <v>466</v>
-      </c>
-      <c r="B132" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>467</v>
-      </c>
-      <c r="D132" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E132" s="6" t="s">
-        <v>468</v>
       </c>
       <c r="F132" s="6"/>
       <c r="G132" s="19"/>
       <c r="H132" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I132" s="9"/>
       <c r="J132" s="28" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K132" s="50"/>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E133" s="6" t="s">
         <v>470</v>
-      </c>
-      <c r="B133" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="D133" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E133" s="6" t="s">
-        <v>472</v>
       </c>
       <c r="F133" s="6"/>
       <c r="G133" s="19"/>
       <c r="H133" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="6" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K133" s="41"/>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E134" s="6" t="s">
         <v>474</v>
-      </c>
-      <c r="B134" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="D134" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E134" s="6" t="s">
-        <v>476</v>
       </c>
       <c r="F134" s="6"/>
       <c r="G134" s="19"/>
       <c r="H134" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I134" s="9"/>
       <c r="J134" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="K134" s="41"/>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C135" s="5"/>
       <c r="D135" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F135" s="6"/>
       <c r="G135" s="19"/>
       <c r="H135" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="6" t="s">
@@ -6204,22 +6201,22 @@
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" s="57" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C136" s="57"/>
       <c r="D136" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E136" s="58" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F136" s="58"/>
       <c r="G136" s="19"/>
       <c r="H136" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I136" s="59"/>
       <c r="J136" s="6" t="s">
@@ -6229,22 +6226,22 @@
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" s="57" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C137" s="57"/>
       <c r="D137" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E137" s="58" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F137" s="58"/>
       <c r="G137" s="19"/>
       <c r="H137" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I137" s="59"/>
       <c r="J137" s="6" t="s">
@@ -6254,26 +6251,26 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" s="61" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B138" s="57" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C138" s="62" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D138" s="58" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E138" s="58"/>
       <c r="F138" s="58"/>
       <c r="G138" s="19"/>
       <c r="H138" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I138" s="59"/>
       <c r="J138" s="58" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="K138" s="60"/>
     </row>

--- a/network.xlsx
+++ b/network.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F3D9B7E-ACE9-B443-90B5-295B495888B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C791074-892C-794A-B907-C8CD34E7CC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3500" windowWidth="30240" windowHeight="16140" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="491">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -1551,6 +1551,24 @@
   </si>
   <si>
     <t>builtin AVNet</t>
+  </si>
+  <si>
+    <t>demoma3</t>
+  </si>
+  <si>
+    <t>NIC1</t>
+  </si>
+  <si>
+    <t>Dynamic</t>
+  </si>
+  <si>
+    <t>192.168.0.123</t>
+  </si>
+  <si>
+    <t>Loaner MA2 console</t>
+  </si>
+  <si>
+    <t>osc:8000</t>
   </si>
 </sst>
 </file>
@@ -1932,16 +1950,16 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2226,8 +2244,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K138" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K138" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K139" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K139" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{EF2C341F-E5C1-604C-942C-FB7E9F76F1CD}" name="AssetTag" dataDxfId="10"/>
     <tableColumn id="13" xr3:uid="{41250547-1480-7146-952C-14798A4748DA}" name="NIC" dataDxfId="9"/>
@@ -6200,83 +6218,106 @@
       <c r="K135" s="41"/>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A136" s="57" t="s">
+      <c r="A136" s="5" t="s">
         <v>476</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="C136" s="57"/>
+      <c r="C136" s="5"/>
       <c r="D136" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E136" s="58" t="s">
+      <c r="E136" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="F136" s="58"/>
+      <c r="F136" s="6"/>
       <c r="G136" s="19"/>
       <c r="H136" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I136" s="59"/>
+      <c r="I136" s="9"/>
       <c r="J136" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="K136" s="60"/>
+      <c r="K136" s="41"/>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A137" s="57" t="s">
+      <c r="A137" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="C137" s="57"/>
+      <c r="C137" s="5"/>
       <c r="D137" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E137" s="58" t="s">
+      <c r="E137" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="F137" s="58"/>
+      <c r="F137" s="6"/>
       <c r="G137" s="19"/>
       <c r="H137" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I137" s="59"/>
+      <c r="I137" s="9"/>
       <c r="J137" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="K137" s="60"/>
+      <c r="K137" s="41"/>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A138" s="61" t="s">
+      <c r="A138" s="57" t="s">
         <v>480</v>
       </c>
-      <c r="B138" s="57" t="s">
+      <c r="B138" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="C138" s="62" t="s">
+      <c r="C138" s="58" t="s">
         <v>481</v>
       </c>
-      <c r="D138" s="58" t="s">
+      <c r="D138" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E138" s="58"/>
-      <c r="F138" s="58"/>
+      <c r="E138" s="6"/>
+      <c r="F138" s="6"/>
       <c r="G138" s="19"/>
       <c r="H138" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I138" s="59"/>
-      <c r="J138" s="58" t="s">
+      <c r="I138" s="9"/>
+      <c r="J138" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="K138" s="60"/>
+      <c r="K138" s="41"/>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H139"/>
-      <c r="I139"/>
+      <c r="A139" s="59" t="s">
+        <v>485</v>
+      </c>
+      <c r="B139" s="59" t="s">
+        <v>486</v>
+      </c>
+      <c r="C139" s="59"/>
+      <c r="D139" s="60" t="s">
+        <v>487</v>
+      </c>
+      <c r="E139" s="60" t="s">
+        <v>488</v>
+      </c>
+      <c r="F139" s="60"/>
+      <c r="G139" s="19" t="s">
+        <v>490</v>
+      </c>
+      <c r="H139" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="I139" s="61"/>
+      <c r="J139" s="60" t="s">
+        <v>489</v>
+      </c>
+      <c r="K139" s="62"/>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H140"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C791074-892C-794A-B907-C8CD34E7CC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EB87DA7-BE8E-C94C-A188-A741DCE37BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3500" windowWidth="30240" windowHeight="16140" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -1568,7 +1568,7 @@
     <t>Loaner MA2 console</t>
   </si>
   <si>
-    <t>osc:8000</t>
+    <t>osc:8000, web:80</t>
   </si>
 </sst>
 </file>

--- a/network.xlsx
+++ b/network.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EB87DA7-BE8E-C94C-A188-A741DCE37BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1C71C2-AD97-784C-9105-B0339715393C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3500" windowWidth="30240" windowHeight="16140" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="496">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -1569,6 +1569,21 @@
   </si>
   <si>
     <t>osc:8000, web:80</t>
+  </si>
+  <si>
+    <t>2607-1000</t>
+  </si>
+  <si>
+    <t>2607-1001</t>
+  </si>
+  <si>
+    <t>E8CF83FF38C8</t>
+  </si>
+  <si>
+    <t>E8CF83FF3955</t>
+  </si>
+  <si>
+    <t>2607-2100</t>
   </si>
 </sst>
 </file>
@@ -2244,8 +2259,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K139" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K139" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K142" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K142" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{EF2C341F-E5C1-604C-942C-FB7E9F76F1CD}" name="AssetTag" dataDxfId="10"/>
     <tableColumn id="13" xr3:uid="{41250547-1480-7146-952C-14798A4748DA}" name="NIC" dataDxfId="9"/>
@@ -6293,43 +6308,102 @@
       <c r="K138" s="41"/>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A139" s="59" t="s">
+      <c r="A139" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="B139" s="59" t="s">
+      <c r="B139" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="C139" s="59"/>
-      <c r="D139" s="60" t="s">
+      <c r="C139" s="5"/>
+      <c r="D139" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="E139" s="60" t="s">
+      <c r="E139" s="6" t="s">
         <v>488</v>
       </c>
-      <c r="F139" s="60"/>
+      <c r="F139" s="6"/>
       <c r="G139" s="19" t="s">
         <v>490</v>
       </c>
       <c r="H139" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="I139" s="61"/>
-      <c r="J139" s="60" t="s">
+      <c r="I139" s="9"/>
+      <c r="J139" s="6" t="s">
         <v>489</v>
       </c>
-      <c r="K139" s="62"/>
+      <c r="K139" s="41"/>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H140"/>
-      <c r="I140"/>
+      <c r="A140" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C140" s="58" t="s">
+        <v>494</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="E140" s="6"/>
+      <c r="F140" s="6"/>
+      <c r="G140" s="7"/>
+      <c r="H140" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="I140" s="9"/>
+      <c r="J140" s="6"/>
+      <c r="K140" s="41"/>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H141"/>
-      <c r="I141"/>
+      <c r="A141" s="59" t="s">
+        <v>492</v>
+      </c>
+      <c r="B141" s="59" t="s">
+        <v>381</v>
+      </c>
+      <c r="C141" s="58" t="s">
+        <v>493</v>
+      </c>
+      <c r="D141" s="60" t="s">
+        <v>388</v>
+      </c>
+      <c r="E141" s="60"/>
+      <c r="F141" s="60"/>
+      <c r="G141" s="19"/>
+      <c r="H141" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="I141" s="61"/>
+      <c r="J141" s="60"/>
+      <c r="K141" s="62"/>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H142"/>
-      <c r="I142"/>
+      <c r="A142" s="55" t="s">
+        <v>495</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C142" s="5"/>
+      <c r="D142" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E142" s="6"/>
+      <c r="F142" s="6"/>
+      <c r="G142" s="19" t="s">
+        <v>490</v>
+      </c>
+      <c r="H142" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="I142" s="9"/>
+      <c r="J142" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K142" s="41"/>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H143"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1C71C2-AD97-784C-9105-B0339715393C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2C339A-5777-1F49-9CEC-07B5B95411BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3500" windowWidth="30240" windowHeight="16140" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="499">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -1584,6 +1584,15 @@
   </si>
   <si>
     <t>2607-2100</t>
+  </si>
+  <si>
+    <t>192.168.0.81</t>
+  </si>
+  <si>
+    <t>LAN1</t>
+  </si>
+  <si>
+    <t>LAN2</t>
   </si>
 </sst>
 </file>
@@ -2259,8 +2268,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K142" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K142" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K143" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K143" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{EF2C341F-E5C1-604C-942C-FB7E9F76F1CD}" name="AssetTag" dataDxfId="10"/>
     <tableColumn id="13" xr3:uid="{41250547-1480-7146-952C-14798A4748DA}" name="NIC" dataDxfId="9"/>
@@ -6358,40 +6367,42 @@
       <c r="K140" s="41"/>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A141" s="59" t="s">
+      <c r="A141" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="B141" s="59" t="s">
+      <c r="B141" s="5" t="s">
         <v>381</v>
       </c>
       <c r="C141" s="58" t="s">
         <v>493</v>
       </c>
-      <c r="D141" s="60" t="s">
+      <c r="D141" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="E141" s="60"/>
-      <c r="F141" s="60"/>
+      <c r="E141" s="6"/>
+      <c r="F141" s="6"/>
       <c r="G141" s="19"/>
       <c r="H141" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I141" s="61"/>
-      <c r="J141" s="60"/>
-      <c r="K141" s="62"/>
+      <c r="I141" s="9"/>
+      <c r="J141" s="6"/>
+      <c r="K141" s="41"/>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" s="55" t="s">
         <v>495</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>381</v>
+        <v>497</v>
       </c>
       <c r="C142" s="5"/>
       <c r="D142" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E142" s="6"/>
+        <v>487</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>496</v>
+      </c>
       <c r="F142" s="6"/>
       <c r="G142" s="19" t="s">
         <v>490</v>
@@ -6406,8 +6417,25 @@
       <c r="K142" s="41"/>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H143"/>
-      <c r="I143"/>
+      <c r="A143" s="55" t="s">
+        <v>495</v>
+      </c>
+      <c r="B143" s="59" t="s">
+        <v>498</v>
+      </c>
+      <c r="C143" s="59"/>
+      <c r="D143" s="60"/>
+      <c r="E143" s="60"/>
+      <c r="F143" s="60"/>
+      <c r="G143" s="19"/>
+      <c r="H143" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="I143" s="61"/>
+      <c r="J143" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K143" s="62"/>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H144"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2C339A-5777-1F49-9CEC-07B5B95411BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C08F53-22A1-9F4C-BA6A-DE5BB5F776AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3500" windowWidth="30240" windowHeight="16140" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="502">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -1583,9 +1583,6 @@
     <t>E8CF83FF3955</t>
   </si>
   <si>
-    <t>2607-2100</t>
-  </si>
-  <si>
     <t>192.168.0.81</t>
   </si>
   <si>
@@ -1593,6 +1590,18 @@
   </si>
   <si>
     <t>LAN2</t>
+  </si>
+  <si>
+    <t>2607-2500</t>
+  </si>
+  <si>
+    <t>e4-4f-29-00-0d-74</t>
+  </si>
+  <si>
+    <t>e4-4f-29-00-0d-73</t>
+  </si>
+  <si>
+    <t>Lighting Console - unused</t>
   </si>
 </sst>
 </file>
@@ -1888,7 +1897,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1978,12 +1987,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -6391,17 +6394,19 @@
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" s="55" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>497</v>
-      </c>
-      <c r="C142" s="5"/>
+        <v>496</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>499</v>
+      </c>
       <c r="D142" s="6" t="s">
         <v>487</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F142" s="6"/>
       <c r="G142" s="19" t="s">
@@ -6418,24 +6423,28 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" s="55" t="s">
-        <v>495</v>
-      </c>
-      <c r="B143" s="59" t="s">
         <v>498</v>
       </c>
-      <c r="C143" s="59"/>
-      <c r="D143" s="60"/>
-      <c r="E143" s="60"/>
-      <c r="F143" s="60"/>
+      <c r="B143" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="E143" s="6"/>
+      <c r="F143" s="6"/>
       <c r="G143" s="19"/>
       <c r="H143" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="I143" s="61"/>
+      <c r="I143" s="9"/>
       <c r="J143" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="K143" s="62"/>
+        <v>501</v>
+      </c>
+      <c r="K143" s="41"/>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H144"/>

--- a/network.xlsx
+++ b/network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C08F53-22A1-9F4C-BA6A-DE5BB5F776AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A454927D-F2F6-4B46-9C2F-2AF626A7B872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3500" windowWidth="30240" windowHeight="16140" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -6338,7 +6338,7 @@
         <v>490</v>
       </c>
       <c r="H139" s="18" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I139" s="9"/>
       <c r="J139" s="6" t="s">

--- a/network.xlsx
+++ b/network.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A454927D-F2F6-4B46-9C2F-2AF626A7B872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAE24AC-56D1-C640-82E5-E38C679B39E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3500" windowWidth="30240" windowHeight="16140" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="503">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -896,9 +896,6 @@
     <t>192.168.204.31</t>
   </si>
   <si>
-    <t>192.168.207.100</t>
-  </si>
-  <si>
     <t>2310-1700</t>
   </si>
   <si>
@@ -1602,6 +1599,12 @@
   </si>
   <si>
     <t>Lighting Console - unused</t>
+  </si>
+  <si>
+    <t>WiFi</t>
+  </si>
+  <si>
+    <t>192.168.207.103</t>
   </si>
 </sst>
 </file>
@@ -2646,7 +2649,7 @@
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>99</v>
@@ -2705,7 +2708,7 @@
         <v>193</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -2757,7 +2760,7 @@
         <v>201</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -2811,7 +2814,7 @@
         <v>217</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -2863,7 +2866,7 @@
         <v>204</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -2879,22 +2882,22 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="29" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>34</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>227</v>
@@ -2904,28 +2907,28 @@
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K11" s="44"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>227</v>
@@ -2935,25 +2938,25 @@
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K12" s="43"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="7" t="s">
@@ -2964,28 +2967,28 @@
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K13" s="43"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>227</v>
@@ -2995,28 +2998,28 @@
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K14" s="43"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>227</v>
@@ -3026,28 +3029,28 @@
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K15" s="43"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>34</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>227</v>
@@ -3057,28 +3060,28 @@
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K16" s="43"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="29" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>34</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>227</v>
@@ -3088,28 +3091,28 @@
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K17" s="44"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="29" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F18" s="29" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>227</v>
@@ -3119,28 +3122,28 @@
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K18" s="44"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>227</v>
@@ -3150,28 +3153,28 @@
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K19" s="43"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>227</v>
@@ -3181,26 +3184,26 @@
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K20" s="44"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B21" s="29"/>
       <c r="C21" s="29" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E21" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="F21" s="29" t="s">
         <v>282</v>
-      </c>
-      <c r="F21" s="29" t="s">
-        <v>283</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="8"/>
@@ -3222,7 +3225,7 @@
         <v>34</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
@@ -3253,7 +3256,7 @@
         <v>34</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
@@ -3284,7 +3287,7 @@
         <v>34</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
@@ -3315,7 +3318,7 @@
         <v>34</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
@@ -3361,7 +3364,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5" t="s">
@@ -3386,7 +3389,7 @@
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>34</v>
@@ -3491,7 +3494,7 @@
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K31" s="41"/>
     </row>
@@ -3518,7 +3521,7 @@
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="K32" s="41"/>
     </row>
@@ -3549,20 +3552,20 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="8"/>
@@ -3572,20 +3575,20 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B35" s="29"/>
       <c r="C35" s="29" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G35" s="19"/>
       <c r="H35" s="8"/>
@@ -3595,20 +3598,20 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B36" s="29"/>
       <c r="C36" s="29" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="8"/>
@@ -3618,20 +3621,20 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="8"/>
@@ -3641,227 +3644,227 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B38" s="29"/>
       <c r="C38" s="29" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="8"/>
       <c r="I38" s="9"/>
       <c r="J38" s="6"/>
       <c r="K38" s="41" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B39" s="29"/>
       <c r="C39" s="29" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F39" s="29" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="8"/>
       <c r="I39" s="9"/>
       <c r="J39" s="6"/>
       <c r="K39" s="41" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="29" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F40" s="29" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="8"/>
       <c r="I40" s="9"/>
       <c r="J40" s="6"/>
       <c r="K40" s="41" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="8"/>
       <c r="I41" s="9"/>
       <c r="J41" s="6"/>
       <c r="K41" s="41" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="8"/>
       <c r="I42" s="9"/>
       <c r="J42" s="6"/>
       <c r="K42" s="41" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="8"/>
       <c r="I43" s="9"/>
       <c r="J43" s="6"/>
       <c r="K43" s="41" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="8"/>
       <c r="I44" s="9"/>
       <c r="J44" s="6"/>
       <c r="K44" s="41" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B45" s="29"/>
       <c r="C45" s="29" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E45" s="29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F45" s="29" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="8"/>
       <c r="I45" s="9"/>
       <c r="J45" s="6"/>
       <c r="K45" s="41" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B46" s="29"/>
       <c r="C46" s="29" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E46" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="F46" s="29" t="s">
         <v>271</v>
-      </c>
-      <c r="F46" s="29" t="s">
-        <v>272</v>
       </c>
       <c r="G46" s="19"/>
       <c r="H46" s="8"/>
       <c r="I46" s="9"/>
       <c r="J46" s="6"/>
       <c r="K46" s="41" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
@@ -3985,7 +3988,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="31" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B51" s="13"/>
       <c r="C51" s="5" t="s">
@@ -4307,17 +4310,19 @@
     </row>
     <row r="62" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="B62" s="5"/>
+        <v>266</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>380</v>
+      </c>
       <c r="C62" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>266</v>
+        <v>502</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="19"/>
@@ -4326,7 +4331,7 @@
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K62" s="41">
         <v>12</v>
@@ -4365,7 +4370,7 @@
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>99</v>
@@ -4390,7 +4395,7 @@
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>99</v>
@@ -4457,7 +4462,7 @@
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H67" s="18" t="s">
         <v>165</v>
@@ -4486,7 +4491,7 @@
       </c>
       <c r="F68" s="6"/>
       <c r="G68" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H68" s="18" t="s">
         <v>165</v>
@@ -4499,17 +4504,17 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="53" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F69" s="6"/>
       <c r="G69" s="19" t="s">
@@ -4520,25 +4525,25 @@
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K69" s="44" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="53" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D70" s="54" t="s">
         <v>99</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F70" s="6"/>
       <c r="G70" s="19" t="s">
@@ -4549,10 +4554,10 @@
       </c>
       <c r="I70" s="9"/>
       <c r="J70" s="38" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K70" s="43" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
@@ -4624,7 +4629,7 @@
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>34</v>
@@ -4651,7 +4656,7 @@
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>34</v>
@@ -4742,7 +4747,7 @@
       </c>
       <c r="B77" s="25"/>
       <c r="C77" s="33" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D77" s="54" t="s">
         <v>99</v>
@@ -4757,7 +4762,7 @@
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K77" s="41">
         <v>18</v>
@@ -4796,7 +4801,7 @@
       </c>
       <c r="B79" s="25"/>
       <c r="C79" s="26" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D79" s="54" t="s">
         <v>99</v>
@@ -4805,13 +4810,13 @@
         <v>155</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="8"/>
       <c r="I79" s="9"/>
       <c r="J79" s="29" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K79" s="43">
         <v>14</v>
@@ -4819,7 +4824,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B80" s="25" t="s">
         <v>173</v>
@@ -4842,7 +4847,7 @@
       </c>
       <c r="I80" s="9"/>
       <c r="J80" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="K80" s="41"/>
     </row>
@@ -4852,7 +4857,7 @@
       </c>
       <c r="B81" s="27"/>
       <c r="C81" s="28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>34</v>
@@ -4879,7 +4884,7 @@
       </c>
       <c r="B82" s="25"/>
       <c r="C82" s="26" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D82" s="54" t="s">
         <v>99</v>
@@ -4921,7 +4926,7 @@
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="K83" s="41">
         <v>10</v>
@@ -4932,7 +4937,7 @@
         <v>167</v>
       </c>
       <c r="B84" s="25" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C84" s="26" t="s">
         <v>182</v>
@@ -4962,7 +4967,7 @@
       </c>
       <c r="B85" s="25"/>
       <c r="C85" s="23" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D85" s="54" t="s">
         <v>99</v>
@@ -5106,11 +5111,11 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B90" s="25"/>
       <c r="C90" s="26" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>34</v>
@@ -5127,7 +5132,7 @@
       </c>
       <c r="I90" s="9"/>
       <c r="J90" s="33" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K90" s="47"/>
     </row>
@@ -5137,7 +5142,7 @@
       </c>
       <c r="B91" s="5"/>
       <c r="C91" s="26" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>34</v>
@@ -5154,7 +5159,7 @@
       </c>
       <c r="I91" s="9"/>
       <c r="J91" s="33" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K91" s="47">
         <v>13</v>
@@ -5218,7 +5223,7 @@
         <v>181</v>
       </c>
       <c r="C94" s="26" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D94" s="54" t="s">
         <v>99</v>
@@ -5274,7 +5279,7 @@
       </c>
       <c r="F96" s="33"/>
       <c r="G96" s="19" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H96" s="8" t="s">
         <v>165</v>
@@ -5306,7 +5311,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="25" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="26"/>
@@ -5314,7 +5319,7 @@
         <v>99</v>
       </c>
       <c r="E98" s="33" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F98" s="33"/>
       <c r="G98" s="19"/>
@@ -5350,7 +5355,9 @@
       <c r="A100" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="B100" s="5"/>
+      <c r="B100" s="5" t="s">
+        <v>501</v>
+      </c>
       <c r="C100" s="26"/>
       <c r="D100" s="54" t="s">
         <v>99</v>
@@ -5370,16 +5377,16 @@
         <v>3</v>
       </c>
       <c r="B101" s="25" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C101" s="26" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D101" s="54" t="s">
         <v>99</v>
       </c>
       <c r="E101" s="33" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F101" s="36"/>
       <c r="G101" s="7"/>
@@ -5388,25 +5395,25 @@
       </c>
       <c r="I101" s="9"/>
       <c r="J101" s="33" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="K101" s="47"/>
     </row>
     <row r="102" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B102" s="25" t="s">
         <v>173</v>
       </c>
       <c r="C102" s="26" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D102" s="54" t="s">
         <v>99</v>
       </c>
       <c r="E102" s="33" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F102" s="36"/>
       <c r="G102" s="7"/>
@@ -5417,7 +5424,7 @@
         <v>245</v>
       </c>
       <c r="J102" s="33" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="K102" s="47"/>
     </row>
@@ -5438,7 +5445,7 @@
       </c>
       <c r="I103" s="9"/>
       <c r="J103" s="33" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K103" s="47"/>
     </row>
@@ -5459,7 +5466,7 @@
       </c>
       <c r="I104" s="9"/>
       <c r="J104" s="33" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K104" s="47"/>
     </row>
@@ -5480,7 +5487,7 @@
       </c>
       <c r="I105" s="9"/>
       <c r="J105" s="33" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K105" s="47"/>
     </row>
@@ -5501,7 +5508,7 @@
       </c>
       <c r="I106" s="9"/>
       <c r="J106" s="33" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K106" s="47"/>
     </row>
@@ -5522,7 +5529,7 @@
       </c>
       <c r="I107" s="9"/>
       <c r="J107" s="33" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K107" s="47" t="s">
         <v>21</v>
@@ -5545,7 +5552,7 @@
       </c>
       <c r="I108" s="9"/>
       <c r="J108" s="33" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K108" s="47"/>
     </row>
@@ -5566,7 +5573,7 @@
       </c>
       <c r="I109" s="9"/>
       <c r="J109" s="33" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K109" s="47"/>
     </row>
@@ -5587,7 +5594,7 @@
       </c>
       <c r="I110" s="9"/>
       <c r="J110" s="33" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K110" s="47"/>
     </row>
@@ -5608,7 +5615,7 @@
       </c>
       <c r="I111" s="9"/>
       <c r="J111" s="33" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K111" s="47"/>
     </row>
@@ -5660,19 +5667,19 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="55" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C114" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="E114" s="6" t="s">
         <v>382</v>
-      </c>
-      <c r="D114" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="E114" s="6" t="s">
-        <v>383</v>
       </c>
       <c r="F114" s="6"/>
       <c r="G114" s="7"/>
@@ -5685,48 +5692,48 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="55" t="s">
+        <v>379</v>
+      </c>
+      <c r="B115" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="B115" s="5" t="s">
-        <v>381</v>
-      </c>
       <c r="C115" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>34</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F115" s="6"/>
       <c r="G115" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H115" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I115" s="9"/>
       <c r="J115" s="23" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="K115" s="48"/>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" s="55" t="s">
+        <v>388</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C116" s="5" t="s">
         <v>389</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>390</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>34</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F116" s="6"/>
       <c r="G116" s="7"/>
@@ -5735,27 +5742,27 @@
       </c>
       <c r="I116" s="9"/>
       <c r="J116" s="26" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K116" s="46" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" s="55" t="s">
+        <v>390</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C117" s="5" t="s">
         <v>391</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>392</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>34</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F117" s="6"/>
       <c r="G117" s="7"/>
@@ -5764,25 +5771,25 @@
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="23" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K117" s="48"/>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" s="55" t="s">
+        <v>398</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="C118" s="5" t="s">
         <v>399</v>
-      </c>
-      <c r="B118" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>400</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F118" s="6"/>
       <c r="G118" s="7"/>
@@ -5791,25 +5798,25 @@
       </c>
       <c r="I118" s="9"/>
       <c r="J118" s="26" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="K118" s="46"/>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" s="55" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B119" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="C119" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="C119" s="5" t="s">
+      <c r="D119" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E119" s="6" t="s">
         <v>405</v>
-      </c>
-      <c r="D119" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E119" s="6" t="s">
-        <v>406</v>
       </c>
       <c r="F119" s="6"/>
       <c r="G119" s="7"/>
@@ -5818,25 +5825,25 @@
       </c>
       <c r="I119" s="9"/>
       <c r="J119" s="23" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="K119" s="48"/>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120" s="55" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>34</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F120" s="6"/>
       <c r="G120" s="7"/>
@@ -5845,25 +5852,25 @@
       </c>
       <c r="I120" s="9"/>
       <c r="J120" s="26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="K120" s="46"/>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121" s="55" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>188</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>34</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F121" s="6"/>
       <c r="G121" s="19"/>
@@ -5872,13 +5879,13 @@
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="24" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="K121" s="49"/>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122" s="55" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>192</v>
@@ -5895,25 +5902,25 @@
       </c>
       <c r="I122" s="9"/>
       <c r="J122" s="26" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K122" s="46"/>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123" s="55" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>188</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>34</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F123" s="6"/>
       <c r="G123" s="7"/>
@@ -5922,13 +5929,13 @@
       </c>
       <c r="I123" s="9"/>
       <c r="J123" s="23" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="K123" s="48"/>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" s="55" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>192</v>
@@ -5945,25 +5952,25 @@
       </c>
       <c r="I124" s="9"/>
       <c r="J124" s="26" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K124" s="46"/>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125" s="55" t="s">
+        <v>435</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C125" s="5" t="s">
         <v>436</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>437</v>
       </c>
       <c r="D125" s="54" t="s">
         <v>99</v>
       </c>
       <c r="E125" s="54" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F125" s="6"/>
       <c r="G125" s="7"/>
@@ -5972,25 +5979,25 @@
       </c>
       <c r="I125" s="9"/>
       <c r="J125" s="23" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K125" s="48"/>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126" s="55" t="s">
+        <v>439</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C126" s="5" t="s">
         <v>440</v>
-      </c>
-      <c r="B126" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>441</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F126" s="6"/>
       <c r="G126" s="7"/>
@@ -5999,25 +6006,25 @@
       </c>
       <c r="I126" s="9"/>
       <c r="J126" s="26" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="K126" s="46"/>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127" s="55" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F127" s="6"/>
       <c r="G127" s="7"/>
@@ -6026,25 +6033,25 @@
       </c>
       <c r="I127" s="9"/>
       <c r="J127" s="23" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="K127" s="48"/>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C128" s="5" t="s">
         <v>448</v>
-      </c>
-      <c r="B128" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>449</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F128" s="6"/>
       <c r="G128" s="7"/>
@@ -6053,25 +6060,25 @@
       </c>
       <c r="I128" s="9"/>
       <c r="J128" s="26" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K128" s="46"/>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C129" s="5" t="s">
         <v>452</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>453</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F129" s="6"/>
       <c r="G129" s="19"/>
@@ -6080,25 +6087,25 @@
       </c>
       <c r="I129" s="9"/>
       <c r="J129" s="24" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K129" s="49"/>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" s="56" t="s">
+        <v>455</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C130" s="5" t="s">
         <v>456</v>
-      </c>
-      <c r="B130" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>457</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E130" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F130" s="6"/>
       <c r="G130" s="7"/>
@@ -6107,25 +6114,25 @@
       </c>
       <c r="I130" s="9"/>
       <c r="J130" s="26" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K130" s="46"/>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C131" s="5" t="s">
         <v>460</v>
-      </c>
-      <c r="B131" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>461</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F131" s="6"/>
       <c r="G131" s="7"/>
@@ -6134,25 +6141,25 @@
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="23" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K131" s="48"/>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C132" s="5" t="s">
         <v>464</v>
-      </c>
-      <c r="B132" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>465</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F132" s="6"/>
       <c r="G132" s="19"/>
@@ -6161,25 +6168,25 @@
       </c>
       <c r="I132" s="9"/>
       <c r="J132" s="28" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K132" s="50"/>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C133" s="5" t="s">
         <v>468</v>
-      </c>
-      <c r="B133" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>469</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F133" s="6"/>
       <c r="G133" s="19"/>
@@ -6188,25 +6195,25 @@
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K133" s="41"/>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C134" s="5" t="s">
         <v>472</v>
-      </c>
-      <c r="B134" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>473</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F134" s="6"/>
       <c r="G134" s="19"/>
@@ -6215,7 +6222,7 @@
       </c>
       <c r="I134" s="9"/>
       <c r="J134" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K134" s="41"/>
     </row>
@@ -6224,14 +6231,14 @@
         <v>22</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C135" s="5"/>
       <c r="D135" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F135" s="6"/>
       <c r="G135" s="19"/>
@@ -6240,23 +6247,23 @@
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K135" s="41"/>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" s="5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C136" s="5"/>
       <c r="D136" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F136" s="6"/>
       <c r="G136" s="19"/>
@@ -6265,7 +6272,7 @@
       </c>
       <c r="I136" s="9"/>
       <c r="J136" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K136" s="41"/>
     </row>
@@ -6274,14 +6281,14 @@
         <v>25</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C137" s="5"/>
       <c r="D137" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F137" s="6"/>
       <c r="G137" s="19"/>
@@ -6290,19 +6297,19 @@
       </c>
       <c r="I137" s="9"/>
       <c r="J137" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K137" s="41"/>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" s="57" t="s">
+        <v>479</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C138" s="58" t="s">
         <v>480</v>
-      </c>
-      <c r="B138" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="C138" s="58" t="s">
-        <v>481</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>99</v>
@@ -6315,49 +6322,49 @@
       </c>
       <c r="I138" s="9"/>
       <c r="J138" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K138" s="41"/>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="B139" s="5" t="s">
         <v>485</v>
-      </c>
-      <c r="B139" s="5" t="s">
-        <v>486</v>
       </c>
       <c r="C139" s="5"/>
       <c r="D139" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="E139" s="6" t="s">
         <v>487</v>
-      </c>
-      <c r="E139" s="6" t="s">
-        <v>488</v>
       </c>
       <c r="F139" s="6"/>
       <c r="G139" s="19" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H139" s="18" t="s">
         <v>166</v>
       </c>
       <c r="I139" s="9"/>
       <c r="J139" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="K139" s="41"/>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" s="5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C140" s="58" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E140" s="6"/>
       <c r="F140" s="6"/>
@@ -6371,16 +6378,16 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C141" s="58" t="s">
         <v>492</v>
       </c>
-      <c r="B141" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="C141" s="58" t="s">
-        <v>493</v>
-      </c>
       <c r="D141" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E141" s="6"/>
       <c r="F141" s="6"/>
@@ -6394,23 +6401,23 @@
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" s="55" t="s">
+        <v>497</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="C142" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="B142" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>499</v>
-      </c>
       <c r="D142" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F142" s="6"/>
       <c r="G142" s="19" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H142" s="8" t="s">
         <v>165</v>
@@ -6423,16 +6430,16 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" s="55" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E143" s="6"/>
       <c r="F143" s="6"/>
@@ -6442,7 +6449,7 @@
       </c>
       <c r="I143" s="9"/>
       <c r="J143" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="K143" s="41"/>
     </row>

--- a/network.xlsx
+++ b/network.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAE24AC-56D1-C640-82E5-E38C679B39E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6F2A03-1762-7B48-B166-3B9F9BEEF6C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3500" windowWidth="30240" windowHeight="16140" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="508">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -1605,6 +1605,21 @@
   </si>
   <si>
     <t>192.168.207.103</t>
+  </si>
+  <si>
+    <t>ZVVU-0002</t>
+  </si>
+  <si>
+    <t>Nursery TV</t>
+  </si>
+  <si>
+    <t>14-bb-6e-e6-4c-b3</t>
+  </si>
+  <si>
+    <t>192.168.207.4</t>
+  </si>
+  <si>
+    <t>May be come unused if power control is implemented via IP Relay</t>
   </si>
 </sst>
 </file>
@@ -1900,7 +1915,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1990,6 +2005,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2274,8 +2295,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K143" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K143" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}" name="Table1" displayName="Table1" ref="A1:K145" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K145" xr:uid="{157AC5DF-1534-C144-A7F4-07F88FA8E6FA}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{EF2C341F-E5C1-604C-942C-FB7E9F76F1CD}" name="AssetTag" dataDxfId="10"/>
     <tableColumn id="13" xr3:uid="{41250547-1480-7146-952C-14798A4748DA}" name="NIC" dataDxfId="9"/>
@@ -6454,70 +6475,104 @@
       <c r="K143" s="41"/>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H144"/>
-      <c r="I144"/>
-    </row>
-    <row r="145" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H145"/>
-      <c r="I145"/>
-    </row>
-    <row r="146" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="A144" s="59" t="s">
+        <v>503</v>
+      </c>
+      <c r="B144" s="59" t="s">
+        <v>380</v>
+      </c>
+      <c r="C144" s="59" t="s">
+        <v>505</v>
+      </c>
+      <c r="D144" s="60" t="s">
+        <v>34</v>
+      </c>
+      <c r="E144" s="60" t="s">
+        <v>506</v>
+      </c>
+      <c r="F144" s="60"/>
+      <c r="G144" s="19"/>
+      <c r="H144" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="I144" s="61"/>
+      <c r="J144" s="60" t="s">
+        <v>504</v>
+      </c>
+      <c r="K144" s="62" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A145" s="59"/>
+      <c r="B145" s="59"/>
+      <c r="C145" s="59"/>
+      <c r="D145" s="60"/>
+      <c r="E145" s="60"/>
+      <c r="F145" s="60"/>
+      <c r="G145" s="19"/>
+      <c r="H145" s="18"/>
+      <c r="I145" s="61"/>
+      <c r="J145" s="60"/>
+      <c r="K145" s="62"/>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H146"/>
       <c r="I146"/>
     </row>
-    <row r="147" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H147"/>
       <c r="I147"/>
     </row>
-    <row r="148" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H148"/>
       <c r="I148"/>
     </row>
-    <row r="149" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H149"/>
       <c r="I149"/>
     </row>
-    <row r="150" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H150"/>
       <c r="I150"/>
     </row>
-    <row r="151" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H151"/>
       <c r="I151"/>
     </row>
-    <row r="152" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H152"/>
       <c r="I152"/>
     </row>
-    <row r="153" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H153"/>
       <c r="I153"/>
     </row>
-    <row r="154" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H154"/>
       <c r="I154"/>
     </row>
-    <row r="155" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H155"/>
       <c r="I155"/>
     </row>
-    <row r="156" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H156"/>
       <c r="I156"/>
     </row>
-    <row r="157" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H157"/>
       <c r="I157"/>
     </row>
-    <row r="158" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H158"/>
       <c r="I158"/>
     </row>
-    <row r="159" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H159"/>
       <c r="I159"/>
     </row>
-    <row r="160" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="H160"/>
       <c r="I160"/>
     </row>
